--- a/Backtest_Modelo.xlsx
+++ b/Backtest_Modelo.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB121"/>
+  <dimension ref="A1:AB122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,13 +738,13 @@
         </is>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.3864712194844517</v>
+        <v>0.3864978570526009</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.3029442947314572</v>
+        <v>0.3028910195951589</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0.310584485784091</v>
+        <v>0.3106111233522402</v>
       </c>
       <c r="O2" s="5" t="n">
         <v>0.3827775037433976</v>
@@ -758,9 +758,10 @@
       <c r="R2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="3">
-        <f>IF(OR(Q2="",R2=""),"[APOSTAR] LOCAL",IF(Q2&gt;R2,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Info Oculta</t>
+        </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
@@ -768,7 +769,7 @@
         </is>
       </c>
       <c r="U2" s="6" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="V2" s="6" t="n">
         <v>0</v>
@@ -841,13 +842,13 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.4475866949290641</v>
+        <v>0.4476100757343092</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.2604082983113981</v>
+        <v>0.2603615367009079</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.2920050067595378</v>
+        <v>0.2920283875647829</v>
       </c>
       <c r="O3" s="5" t="n">
         <v>0.5339922462117932</v>
@@ -976,7 +977,7 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U4" s="6" t="n">
@@ -1082,15 +1083,16 @@
           <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
         </is>
       </c>
-      <c r="T5" s="3">
-        <f>IF(OR(Q5="",R5=""),"[APOSTAR] OVER 2.5",IF((Q5+R5)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
       </c>
       <c r="U5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="W5" s="3">
         <f>IF(L5="","",IF((MAX(L5,M5,N5)-MEDIAN(L5,M5,N5))&gt;0.05,IF(OR(Q5="",R5=""),"[PREDICCION] "&amp;IF(L5=MAX(L5,M5,N5),"LOCAL",IF(M5=MAX(L5,M5,N5),"EMPATE","VISITA")),IF(L5=MAX(L5,M5,N5),IF(Q5&gt;R5,"[ACIERTO]","[FALLO]"),IF(M5=MAX(L5,M5,N5),IF(Q5=R5,"[ACIERTO]","[FALLO]"),IF(Q5&lt;R5,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -1164,13 +1166,13 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.3773418111731573</v>
+        <v>0.3773682980448494</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.2979746723846374</v>
+        <v>0.2979216986412532</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.3246835164422053</v>
+        <v>0.3247100033138974</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>0.4019708307918864</v>
@@ -1272,13 +1274,13 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.4563664869848881</v>
+        <v>0.4563919014097364</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.2838899717075707</v>
+        <v>0.2838391428578743</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.2597435413075411</v>
+        <v>0.2597689557323894</v>
       </c>
       <c r="O7" s="5" t="n">
         <v>0.4272824863232347</v>
@@ -1299,7 +1301,7 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U7" s="6" t="n">
@@ -1380,13 +1382,13 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.3798615710572955</v>
+        <v>0.3798872826491178</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.2847329793347727</v>
+        <v>0.2846815561511281</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.3354054496079319</v>
+        <v>0.3354311611997542</v>
       </c>
       <c r="O8" s="5" t="n">
         <v>0.4513030188855334</v>
@@ -1407,7 +1409,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U8" s="6" t="n">
@@ -1488,19 +1490,19 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.4069740211310929</v>
+        <v>0.4183345171957876</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.3120677683623739</v>
+        <v>0.2858548258481274</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.2809582105065332</v>
+        <v>0.295810656956085</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>0.3464517962857688</v>
+        <v>0.4371983044114202</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>0.6535482037142312</v>
+        <v>0.5628016955885798</v>
       </c>
       <c r="Q9" s="2" t="n">
         <v>1</v>
@@ -1518,7 +1520,7 @@
         </is>
       </c>
       <c r="U9" s="6" t="n">
-        <v>1767.77</v>
+        <v>2500</v>
       </c>
       <c r="V9" s="6" t="n">
         <v>0</v>
@@ -1540,7 +1542,7 @@
         <v/>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>0.4799</v>
+        <v>0.5397</v>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
@@ -1595,19 +1597,19 @@
         </is>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.3251529677910009</v>
+        <v>0.359173987377978</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.2954016341458891</v>
+        <v>0.2762794012496651</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.3794453980631101</v>
+        <v>0.3645466113723568</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.4109755725200973</v>
+        <v>0.4859535014450479</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.5890244274799028</v>
+        <v>0.514046498554952</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>1</v>
@@ -1615,17 +1617,18 @@
       <c r="R10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="S10" s="3">
-        <f>IF(OR(Q10="",R10=""),"[APOSTAR] LOCAL",IF(Q10&gt;R10,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Valor</t>
+          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
         </is>
       </c>
       <c r="U10" s="6" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="V10" s="6" t="n">
         <v>0</v>
@@ -1647,7 +1650,7 @@
         <v/>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>0.5361</v>
+        <v>0.6189</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1702,13 +1705,13 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.5389595970726782</v>
+        <v>0.5389815488646714</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.2438527042840704</v>
+        <v>0.2438088007000837</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.2171876986432515</v>
+        <v>0.2172096504352448</v>
       </c>
       <c r="O11" s="5" t="n">
         <v>0.5422530919991749</v>
@@ -1729,7 +1732,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U11" s="6" t="n">
@@ -3098,13 +3101,13 @@
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4602844528724606</v>
+        <v>0.4603099883848589</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0.2873802282534934</v>
+        <v>0.2873291572286968</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.2523353188740459</v>
+        <v>0.2523608543864443</v>
       </c>
       <c r="O25" s="5" t="n">
         <v>0.4109749443702656</v>
@@ -3206,13 +3209,13 @@
         </is>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.3771663709959308</v>
+        <v>0.3771927193531374</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.2949877925073544</v>
+        <v>0.2949350957929414</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.3278458364967148</v>
+        <v>0.3278721848539213</v>
       </c>
       <c r="O26" s="5" t="n">
         <v>0.4128242964781709</v>
@@ -3421,13 +3424,13 @@
         </is>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.4006995787297076</v>
+        <v>0.4007247689924239</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2783874950113365</v>
+        <v>0.2783371144859038</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.320912926258956</v>
+        <v>0.3209381165216723</v>
       </c>
       <c r="O28" s="5" t="n">
         <v>0.4728740634574408</v>
@@ -3447,7 +3450,7 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U28" s="6" t="n">
@@ -3555,7 +3558,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U29" s="6" t="n">
@@ -3661,15 +3664,16 @@
           <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
-      <c r="T30" s="3">
-        <f>IF(OR(Q30="",R30=""),"[APOSTAR] OVER 2.5",IF((Q30+R30)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
       </c>
       <c r="U30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="W30" s="3">
         <f>IF(L30="","",IF((MAX(L30,M30,N30)-MEDIAN(L30,M30,N30))&gt;0.05,IF(OR(Q30="",R30=""),"[PREDICCION] "&amp;IF(L30=MAX(L30,M30,N30),"LOCAL",IF(M30=MAX(L30,M30,N30),"EMPATE","VISITA")),IF(L30=MAX(L30,M30,N30),IF(Q30&gt;R30,"[ACIERTO]","[FALLO]"),IF(M30=MAX(L30,M30,N30),IF(Q30=R30,"[ACIERTO]","[FALLO]"),IF(Q30&lt;R30,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -3959,13 +3963,13 @@
         </is>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.4225597218522608</v>
+        <v>0.4225851901483987</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.2822520609602481</v>
+        <v>0.2822011243679723</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.2951882171874911</v>
+        <v>0.295213685483629</v>
       </c>
       <c r="O33" s="5" t="n">
         <v>0.4502724152114714</v>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U33" s="6" t="n">
@@ -4093,7 +4097,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U34" s="6" t="n">
@@ -4174,13 +4178,13 @@
         </is>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.3778424308189837</v>
+        <v>0.3778678928128769</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.2815175646638742</v>
+        <v>0.2814666406760878</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.3406400045171421</v>
+        <v>0.3406654665110352</v>
       </c>
       <c r="O35" s="5" t="n">
         <v>0.4642402790842933</v>
@@ -4201,7 +4205,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U35" s="6" t="n">
@@ -4302,20 +4306,20 @@
       <c r="R36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T36" s="3">
-        <f>IF(OR(Q36="",R36=""),"[APOSTAR] OVER 2.5",IF((Q36+R36)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S36" s="3">
+        <f>IF(OR(Q36="",R36=""),"[APOSTAR] VISITA",IF(Q36&lt;R36,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
       </c>
       <c r="U36" s="6" t="n">
-        <v>0</v>
+        <v>1632.49</v>
       </c>
       <c r="V36" s="6" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="W36" s="3">
         <f>IF(L36="","",IF((MAX(L36,M36,N36)-MEDIAN(L36,M36,N36))&gt;0.05,IF(OR(Q36="",R36=""),"[PREDICCION] "&amp;IF(L36=MAX(L36,M36,N36),"LOCAL",IF(M36=MAX(L36,M36,N36),"EMPATE","VISITA")),IF(L36=MAX(L36,M36,N36),IF(Q36&gt;R36,"[ACIERTO]","[FALLO]"),IF(M36=MAX(L36,M36,N36),IF(Q36=R36,"[ACIERTO]","[FALLO]"),IF(Q36&lt;R36,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -4389,13 +4393,13 @@
         </is>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.3846226823626572</v>
+        <v>0.3846486994578493</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.2893087007798147</v>
+        <v>0.2892566665894307</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.326068616857528</v>
+        <v>0.32609463395272</v>
       </c>
       <c r="O37" s="5" t="n">
         <v>0.4329010012935023</v>
@@ -4415,7 +4419,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U37" s="6" t="n">
@@ -4629,11 +4633,11 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U39" s="6" t="n">
-        <v>662.6799999999999</v>
+        <v>541.08</v>
       </c>
       <c r="V39" s="6" t="n">
         <v>0</v>
@@ -4817,13 +4821,13 @@
         </is>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.3278105992180673</v>
+        <v>0.3278372158498828</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.3008241159499364</v>
+        <v>0.3007708826863054</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.3713652848319963</v>
+        <v>0.3713919014638117</v>
       </c>
       <c r="O41" s="5" t="n">
         <v>0.3926604043241473</v>
@@ -4925,19 +4929,19 @@
         </is>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.4722930484720415</v>
+        <v>0.4723184954330658</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.2891280590874311</v>
+        <v>0.2890771651653824</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.2385788924405274</v>
+        <v>0.2386043394015517</v>
       </c>
       <c r="O42" s="5" t="n">
-        <v>0.3963885637853248</v>
+        <v>0.3963885637853247</v>
       </c>
       <c r="P42" s="5" t="n">
-        <v>0.6036114362146752</v>
+        <v>0.6036114362146753</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>2</v>
@@ -5060,7 +5064,7 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U43" s="6" t="n">
@@ -5161,20 +5165,20 @@
       <c r="R44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T44" s="3">
-        <f>IF(OR(Q44="",R44=""),"[APOSTAR] OVER 2.5",IF((Q44+R44)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S44" s="3">
+        <f>IF(OR(Q44="",R44=""),"[APOSTAR] VISITA",IF(Q44&lt;R44,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
       </c>
       <c r="U44" s="6" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V44" s="6" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W44" s="3">
         <f>IF(L44="","",IF((MAX(L44,M44,N44)-MEDIAN(L44,M44,N44))&gt;0.05,IF(OR(Q44="",R44=""),"[PREDICCION] "&amp;IF(L44=MAX(L44,M44,N44),"LOCAL",IF(M44=MAX(L44,M44,N44),"EMPATE","VISITA")),IF(L44=MAX(L44,M44,N44),IF(Q44&gt;R44,"[ACIERTO]","[FALLO]"),IF(M44=MAX(L44,M44,N44),IF(Q44=R44,"[ACIERTO]","[FALLO]"),IF(Q44&lt;R44,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -5248,16 +5252,16 @@
         </is>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.3300752709987969</v>
+        <v>0.3301017111367058</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.2967300732151796</v>
+        <v>0.2966771929393615</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.3731946557860236</v>
+        <v>0.3732210959239327</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.4070079729829672</v>
+        <v>0.4070079729829673</v>
       </c>
       <c r="P45" s="5" t="n">
         <v>0.5929920270170328</v>
@@ -5383,7 +5387,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U46" s="6" t="n">
@@ -5491,7 +5495,7 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U47" s="6" t="n">
@@ -5597,16 +5601,15 @@
           <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
-      <c r="T48" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
-        </is>
+      <c r="T48" s="3">
+        <f>IF(OR(Q48="",R48=""),"[APOSTAR] OVER 2.5",IF((Q48+R48)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
+        <v/>
       </c>
       <c r="U48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V48" s="6" t="n">
-        <v>0</v>
+        <v>1443.38</v>
       </c>
       <c r="W48" s="3">
         <f>IF(L48="","",IF((MAX(L48,M48,N48)-MEDIAN(L48,M48,N48))&gt;0.05,IF(OR(Q48="",R48=""),"[PREDICCION] "&amp;IF(L48=MAX(L48,M48,N48),"LOCAL",IF(M48=MAX(L48,M48,N48),"EMPATE","VISITA")),IF(L48=MAX(L48,M48,N48),IF(Q48&gt;R48,"[ACIERTO]","[FALLO]"),IF(M48=MAX(L48,M48,N48),IF(Q48=R48,"[ACIERTO]","[FALLO]"),IF(Q48&lt;R48,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -5707,7 +5710,7 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U49" s="6" t="n">
@@ -5814,7 +5817,7 @@
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U50" s="6" t="n">
@@ -6110,13 +6113,13 @@
         </is>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.457454332660802</v>
+        <v>0.4574797180586591</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>0.2834740986487994</v>
+        <v>0.283423327853085</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.2590715686903986</v>
+        <v>0.2590969540882558</v>
       </c>
       <c r="O53" s="5" t="n">
         <v>0.4283291668066846</v>
@@ -6136,11 +6139,11 @@
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U53" s="6" t="n">
-        <v>1343.13</v>
+        <v>1345.4</v>
       </c>
       <c r="V53" s="6" t="n">
         <v>0</v>
@@ -6243,7 +6246,7 @@
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U54" s="6" t="n">
@@ -6350,11 +6353,11 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Overlap Riesgo (1X2 Priorizado)</t>
         </is>
       </c>
       <c r="U55" s="6" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
       <c r="V55" s="6" t="n">
         <v>0</v>
@@ -6451,20 +6454,20 @@
       <c r="R56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="S56" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T56" s="3">
-        <f>IF(OR(Q56="",R56=""),"[APOSTAR] OVER 2.5",IF((Q56+R56)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S56" s="3">
+        <f>IF(OR(Q56="",R56=""),"[APOSTAR] VISITA",IF(Q56&lt;R56,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T56" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
       </c>
       <c r="U56" s="6" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V56" s="6" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W56" s="3">
         <f>IF(L56="","",IF((MAX(L56,M56,N56)-MEDIAN(L56,M56,N56))&gt;0.05,IF(OR(Q56="",R56=""),"[PREDICCION] "&amp;IF(L56=MAX(L56,M56,N56),"LOCAL",IF(M56=MAX(L56,M56,N56),"EMPATE","VISITA")),IF(L56=MAX(L56,M56,N56),IF(Q56&gt;R56,"[ACIERTO]","[FALLO]"),IF(M56=MAX(L56,M56,N56),IF(Q56=R56,"[ACIERTO]","[FALLO]"),IF(Q56&lt;R56,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -6564,7 +6567,7 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U57" s="6" t="n">
@@ -6645,13 +6648,13 @@
         </is>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.4861455834470699</v>
+        <v>0.4861706420931886</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>0.2825156066180544</v>
+        <v>0.2824654893258172</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0.2313388099348757</v>
+        <v>0.2313638685809943</v>
       </c>
       <c r="O58" s="5" t="n">
         <v>0.4128232474368506</v>
@@ -6753,13 +6756,13 @@
         </is>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.5733983104227208</v>
+        <v>0.573420969401321</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.2544284890419143</v>
+        <v>0.2543831710847136</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.1721732005353649</v>
+        <v>0.1721958595139652</v>
       </c>
       <c r="O59" s="5" t="n">
         <v>0.4463974102627131</v>
@@ -6780,7 +6783,7 @@
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U59" s="6" t="n">
@@ -6861,13 +6864,13 @@
         </is>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.3574002129603266</v>
+        <v>0.3574258951997223</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0.2842453289890072</v>
+        <v>0.2841939645102157</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.3583544580506661</v>
+        <v>0.3583801402900619</v>
       </c>
       <c r="O60" s="5" t="n">
         <v>0.4546459849409152</v>
@@ -6888,7 +6891,7 @@
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U60" s="6" t="n">
@@ -6969,13 +6972,13 @@
         </is>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.4392961184668734</v>
+        <v>0.4393221343286683</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>0.295245274746423</v>
+        <v>0.2951932430228332</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.2654586067867036</v>
+        <v>0.2654846226484984</v>
       </c>
       <c r="O61" s="5" t="n">
         <v>0.3922601733778666</v>
@@ -7077,19 +7080,19 @@
         </is>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.4094691656420323</v>
+        <v>0.4023657947060328</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.3142022266959207</v>
+        <v>0.3284209102267546</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0.2763286076620469</v>
+        <v>0.2692132950672127</v>
       </c>
       <c r="O62" s="5" t="n">
-        <v>0.2976156163420789</v>
+        <v>0.297629510143734</v>
       </c>
       <c r="P62" s="5" t="n">
-        <v>0.7023843836579211</v>
+        <v>0.7023704898562659</v>
       </c>
       <c r="Q62" s="2" t="n">
         <v>1</v>
@@ -7099,7 +7102,7 @@
       </c>
       <c r="S62" s="3" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
@@ -7108,7 +7111,7 @@
         </is>
       </c>
       <c r="U62" s="6" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="V62" s="6" t="n">
         <v>0</v>
@@ -7129,7 +7132,9 @@
         <f>IF(OR(Q62="",R62=""),"",(L62-IF(Q62&gt;R62,1,0))^2+(M62-IF(Q62=R62,1,0))^2+(N62-IF(Q62&lt;R62,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA62" s="9" t="n"/>
+      <c r="AA62" s="8" t="n">
+        <v>0.4857</v>
+      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7173,19 +7178,19 @@
         </is>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.4958938011102199</v>
+        <v>0.4892612349928771</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.2679207593102701</v>
+        <v>0.2812730261494115</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0.23618543957951</v>
+        <v>0.2294657388577114</v>
       </c>
       <c r="O63" s="5" t="n">
-        <v>0.4152526267373821</v>
+        <v>0.4153291784124106</v>
       </c>
       <c r="P63" s="5" t="n">
-        <v>0.5847473732626179</v>
+        <v>0.5846708215875894</v>
       </c>
       <c r="Q63" s="2" t="n">
         <v>2</v>
@@ -7225,7 +7230,9 @@
         <f>IF(OR(Q63="",R63=""),"",(L63-IF(Q63&gt;R63,1,0))^2+(M63-IF(Q63=R63,1,0))^2+(N63-IF(Q63&lt;R63,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA63" s="9" t="n"/>
+      <c r="AA63" s="8" t="n">
+        <v>0.5878</v>
+      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7275,19 +7282,19 @@
         </is>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.4792198934747284</v>
+        <v>0.4744318944785971</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>0.2503404114630621</v>
+        <v>0.2600732912732497</v>
       </c>
       <c r="N64" s="5" t="n">
-        <v>0.2704396950622094</v>
+        <v>0.2654948142481531</v>
       </c>
       <c r="O64" s="5" t="n">
-        <v>0.5068581021814974</v>
+        <v>0.5069844030763599</v>
       </c>
       <c r="P64" s="5" t="n">
-        <v>0.4931418978185027</v>
+        <v>0.49301559692364</v>
       </c>
       <c r="Q64" s="2" t="n">
         <v>4</v>
@@ -7306,7 +7313,7 @@
         </is>
       </c>
       <c r="U64" s="6" t="n">
-        <v>2500</v>
+        <v>1427.88</v>
       </c>
       <c r="V64" s="6" t="n">
         <v>0</v>
@@ -7327,7 +7334,9 @@
         <f>IF(OR(Q64="",R64=""),"",(L64-IF(Q64&gt;R64,1,0))^2+(M64-IF(Q64=R64,1,0))^2+(N64-IF(Q64&lt;R64,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA64" s="9" t="n"/>
+      <c r="AA64" s="8" t="n">
+        <v>0.7355</v>
+      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7381,19 +7390,19 @@
         </is>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.3592167536462595</v>
+        <v>0.3521013716439972</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0.2850352364071356</v>
+        <v>0.2992669195013188</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.3557480099466048</v>
+        <v>0.348631708854684</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.3991510715073303</v>
+        <v>0.3991818995325883</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.6008489284926697</v>
+        <v>0.6008181004674118</v>
       </c>
       <c r="Q65" s="2" t="n">
         <v>0</v>
@@ -7433,7 +7442,9 @@
         <f>IF(OR(Q65="",R65=""),"",(L65-IF(Q65&gt;R65,1,0))^2+(M65-IF(Q65=R65,1,0))^2+(N65-IF(Q65&lt;R65,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA65" s="9" t="n"/>
+      <c r="AA65" s="8" t="n">
+        <v>0.594</v>
+      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7487,19 +7498,19 @@
         </is>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0.5150502601834692</v>
+        <v>0.4935777371590139</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.2466242235936462</v>
+        <v>0.221988472962442</v>
       </c>
       <c r="N66" s="5" t="n">
-        <v>0.2383255162228845</v>
+        <v>0.2844337898785441</v>
       </c>
       <c r="O66" s="5" t="n">
-        <v>0.5401679498832862</v>
+        <v>0.6853780312818094</v>
       </c>
       <c r="P66" s="5" t="n">
-        <v>0.4598320501167139</v>
+        <v>0.3146219687181906</v>
       </c>
       <c r="Q66" s="2" t="n">
         <v>3</v>
@@ -7509,16 +7520,16 @@
       </c>
       <c r="S66" s="3" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] Info Oculta</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U66" s="6" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="V66" s="6" t="n">
         <v>0</v>
@@ -7539,7 +7550,9 @@
         <f>IF(OR(Q66="",R66=""),"",(L66-IF(Q66&gt;R66,1,0))^2+(M66-IF(Q66=R66,1,0))^2+(N66-IF(Q66&lt;R66,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA66" s="9" t="n"/>
+      <c r="AA66" s="8" t="n">
+        <v>0.6017</v>
+      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7593,19 +7606,19 @@
         </is>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.4827886646873569</v>
+        <v>0.4608628661134519</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.2512966792986987</v>
+        <v>0.2235072597858858</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>0.2659146560139444</v>
+        <v>0.3156298741006623</v>
       </c>
       <c r="O67" s="5" t="n">
-        <v>0.5434962545008356</v>
+        <v>0.6959966261239385</v>
       </c>
       <c r="P67" s="5" t="n">
-        <v>0.4565037454991643</v>
+        <v>0.3040033738760615</v>
       </c>
       <c r="Q67" s="2" t="n">
         <v>3</v>
@@ -7620,11 +7633,11 @@
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U67" s="6" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="V67" s="6" t="n">
         <v>0</v>
@@ -7645,7 +7658,9 @@
         <f>IF(OR(Q67="",R67=""),"",(L67-IF(Q67&gt;R67,1,0))^2+(M67-IF(Q67=R67,1,0))^2+(N67-IF(Q67&lt;R67,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA67" s="9" t="n"/>
+      <c r="AA67" s="8" t="n">
+        <v>0.6833</v>
+      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7699,19 +7714,19 @@
         </is>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.4358142186065552</v>
+        <v>0.428315508133313</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.2565066179178108</v>
+        <v>0.2317739926170445</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>0.307679163475634</v>
+        <v>0.3399104992496425</v>
       </c>
       <c r="O68" s="5" t="n">
-        <v>0.5449423545554228</v>
+        <v>0.6665727670302382</v>
       </c>
       <c r="P68" s="5" t="n">
-        <v>0.4550576454445772</v>
+        <v>0.333427232969762</v>
       </c>
       <c r="Q68" s="2" t="n">
         <v>1</v>
@@ -7726,11 +7741,11 @@
       </c>
       <c r="T68" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U68" s="6" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="V68" s="6" t="n">
         <v>0</v>
@@ -7751,7 +7766,9 @@
         <f>IF(OR(Q68="",R68=""),"",(L68-IF(Q68&gt;R68,1,0))^2+(M68-IF(Q68=R68,1,0))^2+(N68-IF(Q68&lt;R68,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA68" s="9" t="n"/>
+      <c r="AA68" s="8" t="n">
+        <v>0.8587</v>
+      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7805,19 +7822,19 @@
         </is>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.5632474055848253</v>
+        <v>0.5375160149659614</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0.2384298779432382</v>
+        <v>0.2174025775247129</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>0.1983227164719363</v>
+        <v>0.2450814075093257</v>
       </c>
       <c r="O69" s="5" t="n">
-        <v>0.5291932149801006</v>
+        <v>0.673639038286969</v>
       </c>
       <c r="P69" s="5" t="n">
-        <v>0.4708067850198994</v>
+        <v>0.326360961713031</v>
       </c>
       <c r="Q69" s="2" t="n">
         <v>3</v>
@@ -7827,12 +7844,12 @@
       </c>
       <c r="S69" s="3" t="inlineStr">
         <is>
+          <t>[PASAR] Riesgo/Beneficio</t>
+        </is>
+      </c>
+      <c r="T69" s="3" t="inlineStr">
+        <is>
           <t>[PASAR] Sin Valor</t>
-        </is>
-      </c>
-      <c r="T69" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
         </is>
       </c>
       <c r="U69" s="6" t="n">
@@ -7857,7 +7874,9 @@
         <f>IF(OR(Q69="",R69=""),"",(L69-IF(Q69&gt;R69,1,0))^2+(M69-IF(Q69=R69,1,0))^2+(N69-IF(Q69&lt;R69,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA69" s="9" t="n"/>
+      <c r="AA69" s="8" t="n">
+        <v>0.8431999999999999</v>
+      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -7911,19 +7930,19 @@
         </is>
       </c>
       <c r="L70" s="5" t="n">
-        <v>0.5235415322364162</v>
+        <v>0.5162411598485025</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.2701965479983924</v>
+        <v>0.2235830183298888</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>0.2062619197651913</v>
+        <v>0.2601758218216086</v>
       </c>
       <c r="O70" s="5" t="n">
-        <v>0.4207519190896275</v>
+        <v>0.6595672583678465</v>
       </c>
       <c r="P70" s="5" t="n">
-        <v>0.5792480809103725</v>
+        <v>0.3404327416321535</v>
       </c>
       <c r="Q70" s="2" t="n">
         <v>3</v>
@@ -7933,7 +7952,7 @@
       </c>
       <c r="S70" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Valor</t>
+          <t>[PASAR] Techo Cuota</t>
         </is>
       </c>
       <c r="T70" s="3" t="inlineStr">
@@ -7963,7 +7982,9 @@
         <f>IF(OR(Q70="",R70=""),"",(L70-IF(Q70&gt;R70,1,0))^2+(M70-IF(Q70=R70,1,0))^2+(N70-IF(Q70&lt;R70,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA70" s="9" t="n"/>
+      <c r="AA70" s="8" t="n">
+        <v>0.8226</v>
+      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8017,19 +8038,19 @@
         </is>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.4964885772833537</v>
+        <v>0.4556490644531648</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.2695985320345707</v>
+        <v>0.2381679457189354</v>
       </c>
       <c r="N71" s="5" t="n">
-        <v>0.2339128906820757</v>
+        <v>0.3061829898278999</v>
       </c>
       <c r="O71" s="5" t="n">
-        <v>0.4477207898072098</v>
+        <v>0.624350320299942</v>
       </c>
       <c r="P71" s="5" t="n">
-        <v>0.5522792101927904</v>
+        <v>0.3756496797000581</v>
       </c>
       <c r="Q71" s="2" t="n">
         <v>1</v>
@@ -8044,11 +8065,11 @@
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U71" s="6" t="n">
-        <v>1250</v>
+        <v>1157.99</v>
       </c>
       <c r="V71" s="6" t="n">
         <v>0</v>
@@ -8069,7 +8090,9 @@
         <f>IF(OR(Q71="",R71=""),"",(L71-IF(Q71&gt;R71,1,0))^2+(M71-IF(Q71=R71,1,0))^2+(N71-IF(Q71&lt;R71,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA71" s="9" t="n"/>
+      <c r="AA71" s="8" t="n">
+        <v>0.7464</v>
+      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8119,19 +8142,19 @@
         </is>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.4341466229276166</v>
+        <v>0.4123535362184771</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>0.2916865937645456</v>
+        <v>0.2769519643593042</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>0.2741667833078378</v>
+        <v>0.3106944994222188</v>
       </c>
       <c r="O72" s="5" t="n">
-        <v>0.408283532473147</v>
+        <v>0.4754011830978497</v>
       </c>
       <c r="P72" s="5" t="n">
-        <v>0.591716467526853</v>
+        <v>0.5245988169021503</v>
       </c>
       <c r="Q72" s="2" t="n">
         <v>0</v>
@@ -8171,7 +8194,9 @@
         <f>IF(OR(Q72="",R72=""),"",(L72-IF(Q72&gt;R72,1,0))^2+(M72-IF(Q72=R72,1,0))^2+(N72-IF(Q72&lt;R72,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA72" s="9" t="n"/>
+      <c r="AA72" s="8" t="n">
+        <v>0.7466</v>
+      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8221,19 +8246,19 @@
         </is>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.4631610971338595</v>
+        <v>0.4180058214094384</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0.2749680430095705</v>
+        <v>0.2584517932169718</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>0.26187085985657</v>
+        <v>0.3235423853735896</v>
       </c>
       <c r="O73" s="5" t="n">
-        <v>0.4607938128029536</v>
+        <v>0.5544961797151675</v>
       </c>
       <c r="P73" s="5" t="n">
-        <v>0.5392061871970464</v>
+        <v>0.4455038202848325</v>
       </c>
       <c r="Q73" s="2" t="n">
         <v>1</v>
@@ -8252,7 +8277,7 @@
         </is>
       </c>
       <c r="U73" s="6" t="n">
-        <v>1767.77</v>
+        <v>2500</v>
       </c>
       <c r="V73" s="6" t="n">
         <v>0</v>
@@ -8274,7 +8299,7 @@
         <v/>
       </c>
       <c r="AA73" s="8" t="n">
-        <v>0.6324</v>
+        <v>0.6138</v>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
@@ -8325,19 +8350,19 @@
         </is>
       </c>
       <c r="L74" s="5" t="n">
-        <v>0.4508135647270181</v>
+        <v>0.3759681097405576</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>0.2725414129728858</v>
+        <v>0.2315921253740646</v>
       </c>
       <c r="N74" s="5" t="n">
-        <v>0.276645022300096</v>
+        <v>0.3924397648853779</v>
       </c>
       <c r="O74" s="5" t="n">
-        <v>0.4658949957692715</v>
+        <v>0.6733716590854798</v>
       </c>
       <c r="P74" s="5" t="n">
-        <v>0.5341050042307285</v>
+        <v>0.3266283409145201</v>
       </c>
       <c r="Q74" s="2" t="n">
         <v>0</v>
@@ -8347,7 +8372,7 @@
       </c>
       <c r="S74" s="3" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
         </is>
       </c>
       <c r="T74" s="3" t="inlineStr">
@@ -8356,7 +8381,7 @@
         </is>
       </c>
       <c r="U74" s="6" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="V74" s="6" t="n">
         <v>0</v>
@@ -8378,7 +8403,7 @@
         <v/>
       </c>
       <c r="AA74" s="8" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.9306</v>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
@@ -8429,19 +8454,19 @@
         </is>
       </c>
       <c r="L75" s="5" t="n">
-        <v>0.5157194503278281</v>
+        <v>0.5162411598485025</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>0.2239410019469031</v>
+        <v>0.2235830183298888</v>
       </c>
       <c r="N75" s="5" t="n">
-        <v>0.2603395477252687</v>
+        <v>0.2601758218216086</v>
       </c>
       <c r="O75" s="5" t="n">
-        <v>0.659164336345094</v>
+        <v>0.6595672583678465</v>
       </c>
       <c r="P75" s="5" t="n">
-        <v>0.340835663654906</v>
+        <v>0.3404327416321535</v>
       </c>
       <c r="Q75" s="2" t="n">
         <v>3</v>
@@ -8451,7 +8476,7 @@
       </c>
       <c r="S75" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Valor</t>
+          <t>[PASAR] Techo Cuota</t>
         </is>
       </c>
       <c r="T75" s="3" t="inlineStr">
@@ -8481,7 +8506,9 @@
         <f>IF(OR(Q75="",R75=""),"",(L75-IF(Q75&gt;R75,1,0))^2+(M75-IF(Q75=R75,1,0))^2+(N75-IF(Q75&lt;R75,1,0))^2)</f>
         <v/>
       </c>
-      <c r="AA75" s="9" t="n"/>
+      <c r="AA75" s="8" t="n">
+        <v>0.8226</v>
+      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>NO</t>
@@ -8535,19 +8562,19 @@
         </is>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0.5716490365650259</v>
+        <v>0.498029966303805</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.2316040802089988</v>
+        <v>0.2204259477322383</v>
       </c>
       <c r="N76" s="5" t="n">
-        <v>0.1967468832259754</v>
+        <v>0.2815440859639567</v>
       </c>
       <c r="O76" s="5" t="n">
-        <v>0.5550645096264784</v>
+        <v>0.690539118596024</v>
       </c>
       <c r="P76" s="5" t="n">
-        <v>0.4449354903735216</v>
+        <v>0.3094608814039759</v>
       </c>
       <c r="Q76" s="2" t="n">
         <v>2</v>
@@ -8562,7 +8589,7 @@
       </c>
       <c r="T76" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U76" s="6" t="n">
@@ -8588,7 +8615,7 @@
         <v/>
       </c>
       <c r="AA76" s="8" t="n">
-        <v>0.9016</v>
+        <v>0.8442</v>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
@@ -8639,19 +8666,19 @@
         </is>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.3421345096991719</v>
+        <v>0.4193324642728689</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>0.2719523418080652</v>
+        <v>0.2344147851592908</v>
       </c>
       <c r="N77" s="5" t="n">
-        <v>0.3859131484927629</v>
+        <v>0.3462527505678402</v>
       </c>
       <c r="O77" s="5" t="n">
-        <v>0.4900706660630247</v>
+        <v>0.6558913692263365</v>
       </c>
       <c r="P77" s="5" t="n">
-        <v>0.5099293339369753</v>
+        <v>0.3441086307736635</v>
       </c>
       <c r="Q77" s="2" t="n">
         <v>3</v>
@@ -8661,7 +8688,7 @@
       </c>
       <c r="S77" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+          <t>[PASAR] Info Oculta</t>
         </is>
       </c>
       <c r="T77" s="3" t="inlineStr">
@@ -8692,7 +8719,7 @@
         <v/>
       </c>
       <c r="AA77" s="8" t="n">
-        <v>0.7808</v>
+        <v>0.849</v>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
@@ -8747,19 +8774,19 @@
         </is>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.4449780550473174</v>
+        <v>0.4365826829717591</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0.2689601578658951</v>
+        <v>0.2358621504957905</v>
       </c>
       <c r="N78" s="5" t="n">
-        <v>0.2860617870867873</v>
+        <v>0.3275551665324503</v>
       </c>
       <c r="O78" s="5" t="n">
-        <v>0.4844515690304679</v>
+        <v>0.6437684226844578</v>
       </c>
       <c r="P78" s="5" t="n">
-        <v>0.5155484309695321</v>
+        <v>0.3562315773155422</v>
       </c>
       <c r="Q78" s="2" t="n">
         <v>2</v>
@@ -8774,7 +8801,7 @@
       </c>
       <c r="T78" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U78" s="6" t="n">
@@ -8800,7 +8827,7 @@
         <v/>
       </c>
       <c r="AA78" s="8" t="n">
-        <v>0.67</v>
+        <v>0.6263</v>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
@@ -8845,19 +8872,19 @@
         </is>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.3725785639949842</v>
+        <v>0.3664801997762926</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>0.2857380232940304</v>
+        <v>0.2674955889524718</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>0.3416834127109853</v>
+        <v>0.3660242112712357</v>
       </c>
       <c r="O79" s="5" t="n">
-        <v>0.4485968193081611</v>
+        <v>0.5224005312757404</v>
       </c>
       <c r="P79" s="5" t="n">
-        <v>0.5514031806918389</v>
+        <v>0.4775994687242596</v>
       </c>
       <c r="Q79" s="2" t="n">
         <v>0</v>
@@ -8898,7 +8925,7 @@
         <v/>
       </c>
       <c r="AA79" s="8" t="n">
-        <v>0.5552</v>
+        <v>0.5788</v>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
@@ -8949,19 +8976,19 @@
         </is>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.3939039303760287</v>
+        <v>0.3822767492292049</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.2971577630976777</v>
+        <v>0.2638886591923574</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0.3089383065262937</v>
+        <v>0.3538345915784377</v>
       </c>
       <c r="O80" s="5" t="n">
-        <v>0.4021034890769937</v>
+        <v>0.537191674357519</v>
       </c>
       <c r="P80" s="5" t="n">
-        <v>0.5978965109230062</v>
+        <v>0.4628083256424809</v>
       </c>
       <c r="Q80" s="2" t="n">
         <v>0</v>
@@ -8971,7 +8998,7 @@
       </c>
       <c r="S80" s="3" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr">
@@ -8980,7 +9007,7 @@
         </is>
       </c>
       <c r="U80" s="6" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="V80" s="6" t="n">
         <v>0</v>
@@ -9002,7 +9029,7 @@
         <v/>
       </c>
       <c r="AA80" s="8" t="n">
-        <v>0.5564</v>
+        <v>0.5338000000000001</v>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
@@ -9053,25 +9080,29 @@
         </is>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.3420430874133247</v>
+        <v>0.4072131864905001</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.289773294583381</v>
+        <v>0.2521724438648174</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.3681836180032942</v>
+        <v>0.3406143696446824</v>
       </c>
       <c r="O81" s="5" t="n">
-        <v>0.4331618529754852</v>
+        <v>0.5860389248216261</v>
       </c>
       <c r="P81" s="5" t="n">
-        <v>0.5668381470245148</v>
-      </c>
-      <c r="Q81" s="9" t="n"/>
-      <c r="R81" s="9" t="n"/>
+        <v>0.4139610751783738</v>
+      </c>
+      <c r="Q81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R81" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="S81" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+          <t>[PASAR] Info Oculta</t>
         </is>
       </c>
       <c r="T81" s="3" t="inlineStr">
@@ -9102,7 +9133,7 @@
         <v/>
       </c>
       <c r="AA81" s="8" t="n">
-        <v>0.5354</v>
+        <v>0.6916</v>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
@@ -9184,14 +9215,14 @@
       </c>
       <c r="T82" s="3" t="inlineStr">
         <is>
-          <t>[GANADA] OVER 2.5</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U82" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V82" s="6" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="W82" s="3">
         <f>IF(L82="","",IF((MAX(L82,M82,N82)-MEDIAN(L82,M82,N82))&gt;0.05,IF(OR(Q82="",R82=""),"[PREDICCION] "&amp;IF(L82=MAX(L82,M82,N82),"LOCAL",IF(M82=MAX(L82,M82,N82),"EMPATE","VISITA")),IF(L82=MAX(L82,M82,N82),IF(Q82&gt;R82,"[ACIERTO]","[FALLO]"),IF(M82=MAX(L82,M82,N82),IF(Q82=R82,"[ACIERTO]","[FALLO]"),IF(Q82&lt;R82,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -9343,13 +9374,13 @@
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
@@ -9359,13 +9390,13 @@
         </is>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.3315769799378339</v>
+        <v>0.3316036296256834</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.3014570557115247</v>
+        <v>0.3014037563358256</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.3669659643506414</v>
+        <v>0.3669926140384909</v>
       </c>
       <c r="O84" s="5" t="n">
         <v>0.3909271006079778</v>
@@ -9459,22 +9490,26 @@
         </is>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0.4662754299183444</v>
+        <v>0.4733161801380862</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.291775460976421</v>
+        <v>0.2527997846520488</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.2419491091052345</v>
+        <v>0.2738840352098651</v>
       </c>
       <c r="O85" s="5" t="n">
-        <v>0.3901260615981589</v>
+        <v>0.554841106162472</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.609873938401841</v>
-      </c>
-      <c r="Q85" s="9" t="n"/>
-      <c r="R85" s="9" t="n"/>
+        <v>0.445158893837528</v>
+      </c>
+      <c r="Q85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R85" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="S85" s="3" t="inlineStr">
         <is>
           <t>[PASAR] Riesgo/Beneficio</t>
@@ -9508,7 +9543,7 @@
         <v/>
       </c>
       <c r="AA85" s="8" t="n">
-        <v>0.5639</v>
+        <v>0.6399</v>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
@@ -9543,13 +9578,13 @@
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>4.07</v>
+        <v>4.12</v>
       </c>
       <c r="I86" s="4" t="n"/>
       <c r="J86" s="4" t="n"/>
@@ -9559,13 +9594,13 @@
         </is>
       </c>
       <c r="L86" s="5" t="n">
-        <v>0.4408053864252985</v>
+        <v>0.4408309583973712</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.2849985641209511</v>
+        <v>0.2849474201768056</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.2741960494537503</v>
+        <v>0.274221621425823</v>
       </c>
       <c r="O86" s="5" t="n">
         <v>0.4312042519825969</v>
@@ -9585,7 +9620,7 @@
         </is>
       </c>
       <c r="U86" s="6" t="n">
-        <v>1888.89</v>
+        <v>2080.02</v>
       </c>
       <c r="V86" s="6" t="n">
         <v>0</v>
@@ -9836,13 +9871,13 @@
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>3.33</v>
+        <v>3.51</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="I89" s="4" t="n"/>
       <c r="J89" s="4" t="n"/>
@@ -9939,10 +9974,10 @@
         <v>2.61</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="I90" s="4" t="n"/>
       <c r="J90" s="4" t="n"/>
@@ -9952,13 +9987,13 @@
         </is>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0.3824203608641429</v>
+        <v>0.3824461426497117</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0.2857308689901677</v>
+        <v>0.2856793054190302</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0.3318487701456893</v>
+        <v>0.3318745519312581</v>
       </c>
       <c r="O90" s="5" t="n">
         <v>0.4470479370050782</v>
@@ -10036,19 +10071,19 @@
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="I91" s="4" t="n">
         <v>1.93</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
@@ -10079,7 +10114,7 @@
       </c>
       <c r="T91" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U91" s="6" t="n">
@@ -10140,13 +10175,13 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="G92" s="4" t="n">
         <v>3.24</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="I92" s="4" t="n"/>
       <c r="J92" s="4" t="n"/>
@@ -10182,7 +10217,7 @@
         </is>
       </c>
       <c r="U92" s="6" t="n">
-        <v>2406.58</v>
+        <v>1767.77</v>
       </c>
       <c r="V92" s="6" t="n">
         <v>0</v>
@@ -10242,7 +10277,7 @@
         <v>3.42</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="H93" s="4" t="n">
         <v>2.16</v>
@@ -10339,13 +10374,13 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>4.04</v>
+        <v>4.07</v>
       </c>
       <c r="I94" s="4" t="n"/>
       <c r="J94" s="4" t="n"/>
@@ -10439,13 +10474,13 @@
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>3.43</v>
+        <v>3.32</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>4.16</v>
+        <v>4.41</v>
       </c>
       <c r="I95" s="4" t="n"/>
       <c r="J95" s="4" t="n"/>
@@ -10574,20 +10609,20 @@
       </c>
       <c r="Q96" s="9" t="n"/>
       <c r="R96" s="9" t="n"/>
-      <c r="S96" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T96" s="3">
-        <f>IF(OR(Q96="",R96=""),"[APOSTAR] OVER 2.5",IF((Q96+R96)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S96" s="3">
+        <f>IF(OR(Q96="",R96=""),"[APOSTAR] LOCAL",IF(Q96&gt;R96,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T96" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
       </c>
       <c r="U96" s="6" t="n">
-        <v>0</v>
+        <v>1118.03</v>
       </c>
       <c r="V96" s="6" t="n">
-        <v>1118.03</v>
+        <v>0</v>
       </c>
       <c r="W96" s="3">
         <f>IF(L96="","",IF((MAX(L96,M96,N96)-MEDIAN(L96,M96,N96))&gt;0.05,IF(OR(Q96="",R96=""),"[PREDICCION] "&amp;IF(L96=MAX(L96,M96,N96),"LOCAL",IF(M96=MAX(L96,M96,N96),"EMPATE","VISITA")),IF(L96=MAX(L96,M96,N96),IF(Q96&gt;R96,"[ACIERTO]","[FALLO]"),IF(M96=MAX(L96,M96,N96),IF(Q96=R96,"[ACIERTO]","[FALLO]"),IF(Q96&lt;R96,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -10657,16 +10692,16 @@
         </is>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.5153724423169271</v>
+        <v>0.5153965634929999</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>0.2688407164392261</v>
+        <v>0.2687924740870805</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0.2157868412438468</v>
+        <v>0.2158109624199196</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>0.4462706911952379</v>
+        <v>0.446270691195238</v>
       </c>
       <c r="P97" s="5" t="n">
         <v>0.553729308804762</v>
@@ -11144,10 +11179,10 @@
         <v>1.33</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>10.02</v>
+        <v>10.06</v>
       </c>
       <c r="I102" s="4" t="n"/>
       <c r="J102" s="4" t="n"/>
@@ -11251,13 +11286,13 @@
         </is>
       </c>
       <c r="L103" s="5" t="n">
-        <v>0.3689260629480804</v>
+        <v>0.3689524796970511</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>0.2960894177881392</v>
+        <v>0.2960365842901977</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>0.3349845192637804</v>
+        <v>0.3350109360127511</v>
       </c>
       <c r="O103" s="5" t="n">
         <v>0.4097861749290452</v>
@@ -11435,13 +11470,13 @@
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="I105" s="4" t="n"/>
       <c r="J105" s="4" t="n"/>
@@ -11550,13 +11585,13 @@
         </is>
       </c>
       <c r="L106" s="5" t="n">
-        <v>0.5183396286630546</v>
+        <v>0.518363136619953</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>0.2599119746221581</v>
+        <v>0.2598649587083614</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0.2217483967147873</v>
+        <v>0.2217719046716857</v>
       </c>
       <c r="O106" s="5" t="n">
         <v>0.4844492602992937</v>
@@ -11634,13 +11669,13 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>3.65</v>
+        <v>3.51</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>5.82</v>
+        <v>5.38</v>
       </c>
       <c r="I107" s="4" t="n"/>
       <c r="J107" s="4" t="n"/>
@@ -11650,19 +11685,19 @@
         </is>
       </c>
       <c r="L107" s="5" t="n">
-        <v>0.5139470780983998</v>
+        <v>0.5139712492517915</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0.2695208223876904</v>
+        <v>0.2694724800809071</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>0.2165320995139097</v>
+        <v>0.2165562706673014</v>
       </c>
       <c r="O107" s="5" t="n">
         <v>0.4445899234793541</v>
       </c>
       <c r="P107" s="5" t="n">
-        <v>0.555410076520646</v>
+        <v>0.5554100765206459</v>
       </c>
       <c r="Q107" s="9" t="n"/>
       <c r="R107" s="9" t="n"/>
@@ -11869,16 +11904,15 @@
           <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
-      <c r="T109" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
-        </is>
+      <c r="T109" s="3">
+        <f>IF(OR(Q109="",R109=""),"[APOSTAR] OVER 2.5",IF((Q109+R109)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
+        <v/>
       </c>
       <c r="U109" s="6" t="n">
         <v>0</v>
       </c>
       <c r="V109" s="6" t="n">
-        <v>0</v>
+        <v>1767.77</v>
       </c>
       <c r="W109" s="3">
         <f>IF(L109="","",IF((MAX(L109,M109,N109)-MEDIAN(L109,M109,N109))&gt;0.05,IF(OR(Q109="",R109=""),"[PREDICCION] "&amp;IF(L109=MAX(L109,M109,N109),"LOCAL",IF(M109=MAX(L109,M109,N109),"EMPATE","VISITA")),IF(L109=MAX(L109,M109,N109),IF(Q109&gt;R109,"[ACIERTO]","[FALLO]"),IF(M109=MAX(L109,M109,N109),IF(Q109=R109,"[ACIERTO]","[FALLO]"),IF(Q109&lt;R109,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -11948,13 +11982,13 @@
         </is>
       </c>
       <c r="L110" s="5" t="n">
-        <v>0.5563711974356382</v>
+        <v>0.5563943021271643</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>0.2583536067740375</v>
+        <v>0.2583073973909855</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>0.1852751957903242</v>
+        <v>0.1852983004818502</v>
       </c>
       <c r="O110" s="5" t="n">
         <v>0.4497533845612681</v>
@@ -12064,9 +12098,10 @@
       </c>
       <c r="Q111" s="9" t="n"/>
       <c r="R111" s="9" t="n"/>
-      <c r="S111" s="3">
-        <f>IF(OR(Q111="",R111=""),"[APOSTAR] LOCAL",IF(Q111&gt;R111,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+      <c r="S111" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Info Oculta</t>
+        </is>
       </c>
       <c r="T111" s="3" t="inlineStr">
         <is>
@@ -12074,7 +12109,7 @@
         </is>
       </c>
       <c r="U111" s="6" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="V111" s="6" t="n">
         <v>0</v>
@@ -12457,9 +12492,10 @@
       </c>
       <c r="Q115" s="9" t="n"/>
       <c r="R115" s="9" t="n"/>
-      <c r="S115" s="3">
-        <f>IF(OR(Q115="",R115=""),"[APOSTAR] VISITA",IF(Q115&lt;R115,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S115" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Info Oculta</t>
+        </is>
       </c>
       <c r="T115" s="3" t="inlineStr">
         <is>
@@ -12467,7 +12503,7 @@
         </is>
       </c>
       <c r="U115" s="6" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="V115" s="6" t="n">
         <v>0</v>
@@ -12624,13 +12660,13 @@
         </is>
       </c>
       <c r="F117" s="4" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="I117" s="4" t="n"/>
       <c r="J117" s="4" t="n"/>
@@ -12766,7 +12802,7 @@
       </c>
       <c r="T118" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U118" s="6" t="n">
@@ -12830,10 +12866,10 @@
         <v>2</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="I119" s="4" t="n"/>
       <c r="J119" s="4" t="n"/>
@@ -12843,13 +12879,13 @@
         </is>
       </c>
       <c r="L119" s="5" t="n">
-        <v>0.3887953824534637</v>
+        <v>0.3888211956565762</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>0.2862846580127962</v>
+        <v>0.2862330316065712</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>0.32491995953374</v>
+        <v>0.3249457727368525</v>
       </c>
       <c r="O119" s="5" t="n">
         <v>0.4438155267438119</v>
@@ -12996,64 +13032,74 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08goztepegalatasaray</t>
+          <t>2026-04-07kfumsandefjord</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Goztepe vs Galatasaray</t>
+          <t>Kfum vs Sandefjord</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Kfum</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="n"/>
-      <c r="G121" s="4" t="n"/>
-      <c r="H121" s="4" t="n"/>
-      <c r="I121" s="4" t="n"/>
-      <c r="J121" s="4" t="n"/>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I121" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J121" s="4" t="n">
+        <v>2</v>
+      </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="L121" s="5" t="n">
-        <v>0.3503567059368736</v>
+        <v>0.3539561359318152</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>0.283028484029018</v>
+        <v>0.2440401065418481</v>
       </c>
       <c r="N121" s="5" t="n">
-        <v>0.3666148100341084</v>
+        <v>0.4020037575263367</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>0.4513030547014477</v>
+        <v>0.5999136059153706</v>
       </c>
       <c r="P121" s="5" t="n">
-        <v>0.5486969452985523</v>
+        <v>0.4000863940846294</v>
       </c>
       <c r="Q121" s="9" t="n"/>
       <c r="R121" s="9" t="n"/>
       <c r="S121" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
         </is>
       </c>
       <c r="T121" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U121" s="6" t="n">
@@ -13079,9 +13125,103 @@
         <v/>
       </c>
       <c r="AA121" s="8" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="AB121" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-08goztepegalatasaray</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Goztepe vs Galatasaray</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="n"/>
+      <c r="H122" s="4" t="n"/>
+      <c r="I122" s="4" t="n"/>
+      <c r="J122" s="4" t="n"/>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>0.3503567059368736</v>
+      </c>
+      <c r="M122" s="5" t="n">
+        <v>0.283028484029018</v>
+      </c>
+      <c r="N122" s="5" t="n">
+        <v>0.3666148100341084</v>
+      </c>
+      <c r="O122" s="5" t="n">
+        <v>0.4513030547014477</v>
+      </c>
+      <c r="P122" s="5" t="n">
+        <v>0.5486969452985523</v>
+      </c>
+      <c r="Q122" s="9" t="n"/>
+      <c r="R122" s="9" t="n"/>
+      <c r="S122" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T122" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="3">
+        <f>IF(L122="","",IF((MAX(L122,M122,N122)-MEDIAN(L122,M122,N122))&gt;0.05,IF(OR(Q122="",R122=""),"[PREDICCION] "&amp;IF(L122=MAX(L122,M122,N122),"LOCAL",IF(M122=MAX(L122,M122,N122),"EMPATE","VISITA")),IF(L122=MAX(L122,M122,N122),IF(Q122&gt;R122,"[ACIERTO]","[FALLO]"),IF(M122=MAX(L122,M122,N122),IF(Q122=R122,"[ACIERTO]","[FALLO]"),IF(Q122&lt;R122,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X122" s="6">
+        <f>IFERROR(IF(U122=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S122)),U122*(IF(ISNUMBER(SEARCH("LOCAL",S122)),F122,IF(ISNUMBER(SEARCH("EMPATE",S122)),G122,H122))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S122)),-U122,0))),0)+IFERROR(IF(V122=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T122)),V122*(IF(ISNUMBER(SEARCH("OVER",T122)),I122,J122)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T122)),-V122,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y122" s="6">
+        <f>Y121+X122</f>
+        <v/>
+      </c>
+      <c r="Z122" s="7">
+        <f>IF(OR(Q122="",R122=""),"",(L122-IF(Q122&gt;R122,1,0))^2+(M122-IF(Q122=R122,1,0))^2+(N122-IF(Q122&lt;R122,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA122" s="8" t="n">
         <v>0.6991000000000001</v>
       </c>
-      <c r="AB121" s="2" t="inlineStr">
+      <c r="AB122" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13089,7 +13229,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
-  <conditionalFormatting sqref="S2:T121">
+  <conditionalFormatting sqref="S2:T122">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("[GANADA]",S2))</formula>
     </cfRule>
@@ -13172,25 +13312,25 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>-1818.01</v>
+        <v>-5000</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>-0.2129934368534388</v>
+        <v>-1</v>
       </c>
       <c r="H2" s="13" t="n">
-        <v>8535.540000000001</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="3">
@@ -13200,25 +13340,25 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="11" t="n">
-        <v>4</v>
-      </c>
       <c r="E3" s="12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.25</v>
       </c>
       <c r="F3" s="13" t="n">
-        <v>987.5</v>
+        <v>-1849.75</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.07899999999999996</v>
+        <v>-0.3379994993266491</v>
       </c>
       <c r="H3" s="13" t="n">
-        <v>12500</v>
+        <v>5472.63</v>
       </c>
     </row>
     <row r="4">
@@ -13312,31 +13452,31 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>-830.51</v>
+        <v>-6849.75</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.03948146802982008</v>
+        <v>-0.654061701788376</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>21035.54</v>
+        <v>10472.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Generado: 03/04/2026 14:10</t>
+          <t>Generado: 03/04/2026 19:29</t>
         </is>
       </c>
     </row>

--- a/Backtest_Modelo.xlsx
+++ b/Backtest_Modelo.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB122"/>
+  <dimension ref="A1:AB123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,19 +738,19 @@
         </is>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.3864978570526009</v>
+        <v>0.3882109364178973</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.3028910195951589</v>
+        <v>0.2903127352171255</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>0.3106111233522402</v>
+        <v>0.3214763283649771</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>0.3827775037433976</v>
+        <v>0.4283298117362779</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>0.6172224962566024</v>
+        <v>0.5716701882637221</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0</v>
@@ -791,7 +791,7 @@
         <v/>
       </c>
       <c r="AA2" s="8" t="n">
-        <v>0.6575</v>
+        <v>0.6524</v>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.4476100757343092</v>
+        <v>0.4475983853316866</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.2603615367009079</v>
+        <v>0.260384917506153</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>0.2920283875647829</v>
+        <v>0.2920166971621604</v>
       </c>
       <c r="O3" s="5" t="n">
-        <v>0.5339922462117932</v>
+        <v>0.5339922462117933</v>
       </c>
       <c r="P3" s="5" t="n">
-        <v>0.4660077537882068</v>
+        <v>0.4660077537882067</v>
       </c>
       <c r="Q3" s="2" t="n">
         <v>2</v>
@@ -1166,13 +1166,13 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.3773682980448494</v>
+        <v>0.3773550546090034</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.2979216986412532</v>
+        <v>0.2979481855129453</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.3247100033138974</v>
+        <v>0.3246967598780514</v>
       </c>
       <c r="O6" s="5" t="n">
         <v>0.4019708307918864</v>
@@ -1274,19 +1274,19 @@
         </is>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.4563919014097364</v>
+        <v>0.4328109162577859</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.2838391428578743</v>
+        <v>0.2779739500112063</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.2597689557323894</v>
+        <v>0.2892151337310078</v>
       </c>
       <c r="O7" s="5" t="n">
-        <v>0.4272824863232347</v>
+        <v>0.4636024826220113</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>0.5727175136767653</v>
+        <v>0.5363975173779887</v>
       </c>
       <c r="Q7" s="2" t="n">
         <v>2</v>
@@ -1327,7 +1327,7 @@
         <v/>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.6019</v>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
@@ -1382,19 +1382,19 @@
         </is>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.3798872826491178</v>
+        <v>0.3892422783098451</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.2846815561511281</v>
+        <v>0.2699924816756117</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.3354311611997542</v>
+        <v>0.3407652400145432</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>0.4513030188855334</v>
+        <v>0.5101630222875012</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>0.5486969811144666</v>
+        <v>0.4898369777124988</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>2</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Valor</t>
+          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
         </is>
       </c>
       <c r="U8" s="6" t="n">
@@ -1435,7 +1435,7 @@
         <v/>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>0.7539</v>
+        <v>0.7287</v>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
@@ -1490,13 +1490,13 @@
         </is>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.4183345171957876</v>
+        <v>0.418321655985102</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.2858548258481274</v>
+        <v>0.2858805482694986</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.295810656956085</v>
+        <v>0.2957977957453993</v>
       </c>
       <c r="O9" s="5" t="n">
         <v>0.4371983044114202</v>
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.359173987377978</v>
+        <v>0.3807644871796496</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.2762794012496651</v>
+        <v>0.2598887409557634</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.3645466113723568</v>
+        <v>0.359346771864587</v>
       </c>
       <c r="O10" s="5" t="n">
-        <v>0.4859535014450479</v>
+        <v>0.5549589419807658</v>
       </c>
       <c r="P10" s="5" t="n">
-        <v>0.514046498554952</v>
+        <v>0.4450410580192341</v>
       </c>
       <c r="Q10" s="2" t="n">
         <v>1</v>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo O/U Insuficiente (&lt;15%)</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U10" s="6" t="n">
@@ -1650,7 +1650,7 @@
         <v/>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>0.6189</v>
+        <v>0.601</v>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.5389815488646714</v>
+        <v>0.5389705729686748</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.2438088007000837</v>
+        <v>0.243830752492077</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.2172096504352448</v>
+        <v>0.2171986745392482</v>
       </c>
       <c r="O11" s="5" t="n">
         <v>0.5422530919991749</v>
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.4714950682292441</v>
+        <v>0.4715077324405782</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.2827861433763474</v>
+        <v>0.2827608149536792</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.2457187883944085</v>
+        <v>0.2457314526057426</v>
       </c>
       <c r="O12" s="5" t="n">
         <v>0.4148022099731867</v>
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.4143338364837813</v>
+        <v>0.4143462864297805</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.2731865517515846</v>
+        <v>0.2731616518595862</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.3124796117646341</v>
+        <v>0.3124920617106333</v>
       </c>
       <c r="O16" s="5" t="n">
         <v>0.4828233891977304</v>
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.2861270283395916</v>
+        <v>0.2861388612055159</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.2607651812525669</v>
+        <v>0.2607415155207183</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.4531077904078414</v>
+        <v>0.4531196232737658</v>
       </c>
       <c r="O17" s="5" t="n">
         <v>0.5214361653599625</v>
@@ -2382,9 +2382,15 @@
           <t>Galatasaray</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="F18" s="4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.67</v>
+      </c>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="2" t="inlineStr">
@@ -2393,25 +2399,25 @@
         </is>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.3503567059368736</v>
+        <v>0.3981045687317345</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.283028484029018</v>
+        <v>0.2585785927225737</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.3666148100341084</v>
+        <v>0.3433168385456918</v>
       </c>
       <c r="O18" s="5" t="n">
-        <v>0.4513030547014477</v>
+        <v>0.5506715830807075</v>
       </c>
       <c r="P18" s="5" t="n">
-        <v>0.5486969452985523</v>
+        <v>0.4493284169192925</v>
       </c>
       <c r="Q18" s="9" t="n"/>
       <c r="R18" s="9" t="n"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Info Oculta</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -2442,7 +2448,7 @@
         <v/>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.694</v>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
@@ -2487,13 +2493,13 @@
         </is>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.4450762606164246</v>
+        <v>0.445088480371811</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.2681926644878433</v>
+        <v>0.2681682249770704</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.2867310748957321</v>
+        <v>0.2867432946511186</v>
       </c>
       <c r="O19" s="5" t="n">
         <v>0.4920602783752462</v>
@@ -3101,13 +3107,13 @@
         </is>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.4603099883848589</v>
+        <v>0.4602972206286598</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0.2873291572286968</v>
+        <v>0.287354692741095</v>
       </c>
       <c r="N25" s="5" t="n">
-        <v>0.2523608543864443</v>
+        <v>0.2523480866302451</v>
       </c>
       <c r="O25" s="5" t="n">
         <v>0.4109749443702656</v>
@@ -3209,13 +3215,13 @@
         </is>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.3771927193531374</v>
+        <v>0.3771795451745341</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.2949350957929414</v>
+        <v>0.2949614441501479</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>0.3278721848539213</v>
+        <v>0.327859010675318</v>
       </c>
       <c r="O26" s="5" t="n">
         <v>0.4128242964781709</v>
@@ -3424,13 +3430,13 @@
         </is>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.4007247689924239</v>
+        <v>0.4007121738610658</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.2783371144859038</v>
+        <v>0.2783623047486202</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>0.3209381165216723</v>
+        <v>0.3209255213903141</v>
       </c>
       <c r="O28" s="5" t="n">
         <v>0.4728740634574408</v>
@@ -3963,13 +3969,13 @@
         </is>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.4225851901483987</v>
+        <v>0.4225724560003298</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.2822011243679723</v>
+        <v>0.2822265926641102</v>
       </c>
       <c r="N33" s="5" t="n">
-        <v>0.295213685483629</v>
+        <v>0.2952009513355601</v>
       </c>
       <c r="O33" s="5" t="n">
         <v>0.4502724152114714</v>
@@ -4178,13 +4184,13 @@
         </is>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.3778678928128769</v>
+        <v>0.3778551618159303</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.2814666406760878</v>
+        <v>0.281492102669981</v>
       </c>
       <c r="N35" s="5" t="n">
-        <v>0.3406654665110352</v>
+        <v>0.3406527355140887</v>
       </c>
       <c r="O35" s="5" t="n">
         <v>0.4642402790842933</v>
@@ -4393,13 +4399,13 @@
         </is>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.3846486994578493</v>
+        <v>0.3846356909102533</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.2892566665894307</v>
+        <v>0.2892826836846227</v>
       </c>
       <c r="N37" s="5" t="n">
-        <v>0.32609463395272</v>
+        <v>0.326081625405124</v>
       </c>
       <c r="O37" s="5" t="n">
         <v>0.4329010012935023</v>
@@ -4821,13 +4827,13 @@
         </is>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.3278372158498828</v>
+        <v>0.327823907533975</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.3007708826863054</v>
+        <v>0.3007974993181209</v>
       </c>
       <c r="N41" s="5" t="n">
-        <v>0.3713919014638117</v>
+        <v>0.371378593147904</v>
       </c>
       <c r="O41" s="5" t="n">
         <v>0.3926604043241473</v>
@@ -4929,13 +4935,13 @@
         </is>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.4723184954330658</v>
+        <v>0.4723057719525537</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.2890771651653824</v>
+        <v>0.2891026121264068</v>
       </c>
       <c r="N42" s="5" t="n">
-        <v>0.2386043394015517</v>
+        <v>0.2385916159210396</v>
       </c>
       <c r="O42" s="5" t="n">
         <v>0.3963885637853247</v>
@@ -5252,16 +5258,16 @@
         </is>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.3301017111367058</v>
+        <v>0.3300884910677514</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.2966771929393615</v>
+        <v>0.2967036330772706</v>
       </c>
       <c r="N45" s="5" t="n">
-        <v>0.3732210959239327</v>
+        <v>0.3732078758549781</v>
       </c>
       <c r="O45" s="5" t="n">
-        <v>0.4070079729829673</v>
+        <v>0.4070079729829672</v>
       </c>
       <c r="P45" s="5" t="n">
         <v>0.5929920270170328</v>
@@ -6113,13 +6119,13 @@
         </is>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.4574797180586591</v>
+        <v>0.4574670253597306</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>0.283423327853085</v>
+        <v>0.2834487132509422</v>
       </c>
       <c r="N53" s="5" t="n">
-        <v>0.2590969540882558</v>
+        <v>0.2590842613893272</v>
       </c>
       <c r="O53" s="5" t="n">
         <v>0.4283291668066846</v>
@@ -6143,7 +6149,7 @@
         </is>
       </c>
       <c r="U53" s="6" t="n">
-        <v>1345.4</v>
+        <v>1344.26</v>
       </c>
       <c r="V53" s="6" t="n">
         <v>0</v>
@@ -6648,13 +6654,13 @@
         </is>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.4861706420931886</v>
+        <v>0.4861581127701293</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>0.2824654893258172</v>
+        <v>0.2824905479719358</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0.2313638685809943</v>
+        <v>0.231351339257935</v>
       </c>
       <c r="O58" s="5" t="n">
         <v>0.4128232474368506</v>
@@ -6756,13 +6762,13 @@
         </is>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.573420969401321</v>
+        <v>0.573409639912021</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.2543831710847136</v>
+        <v>0.254405830063314</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>0.1721958595139652</v>
+        <v>0.1721845300246651</v>
       </c>
       <c r="O59" s="5" t="n">
         <v>0.4463974102627131</v>
@@ -6864,13 +6870,13 @@
         </is>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.3574258951997223</v>
+        <v>0.3574130540800245</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0.2841939645102157</v>
+        <v>0.2842196467496114</v>
       </c>
       <c r="N60" s="5" t="n">
-        <v>0.3583801402900619</v>
+        <v>0.358367299170364</v>
       </c>
       <c r="O60" s="5" t="n">
         <v>0.4546459849409152</v>
@@ -6972,13 +6978,13 @@
         </is>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.4393221343286683</v>
+        <v>0.4393091263977709</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>0.2951932430228332</v>
+        <v>0.2952192588846281</v>
       </c>
       <c r="N61" s="5" t="n">
-        <v>0.2654846226484984</v>
+        <v>0.265471614717601</v>
       </c>
       <c r="O61" s="5" t="n">
         <v>0.3922601733778666</v>
@@ -7080,13 +7086,13 @@
         </is>
       </c>
       <c r="L62" s="5" t="n">
-        <v>0.4023657947060328</v>
+        <v>0.4023525252109772</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.3284209102267546</v>
+        <v>0.3284474492168657</v>
       </c>
       <c r="N62" s="5" t="n">
-        <v>0.2692132950672127</v>
+        <v>0.2692000255721571</v>
       </c>
       <c r="O62" s="5" t="n">
         <v>0.297629510143734</v>
@@ -7178,13 +7184,13 @@
         </is>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.4892612349928771</v>
+        <v>0.4892487468016895</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.2812730261494115</v>
+        <v>0.2812980025317868</v>
       </c>
       <c r="N63" s="5" t="n">
-        <v>0.2294657388577114</v>
+        <v>0.2294532506665238</v>
       </c>
       <c r="O63" s="5" t="n">
         <v>0.4153291784124106</v>
@@ -7390,19 +7396,19 @@
         </is>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.3521013716439972</v>
+        <v>0.3548638595674269</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0.2992669195013188</v>
+        <v>0.2869089881362343</v>
       </c>
       <c r="N65" s="5" t="n">
-        <v>0.348631708854684</v>
+        <v>0.3582271522963387</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>0.3991818995325883</v>
+        <v>0.4443332923376039</v>
       </c>
       <c r="P65" s="5" t="n">
-        <v>0.6008181004674118</v>
+        <v>0.5556667076623961</v>
       </c>
       <c r="Q65" s="2" t="n">
         <v>0</v>
@@ -7443,7 +7449,7 @@
         <v/>
       </c>
       <c r="AA65" s="8" t="n">
-        <v>0.594</v>
+        <v>0.5883</v>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
@@ -8142,13 +8148,13 @@
         </is>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.4123535362184771</v>
+        <v>0.4123410031015248</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>0.2769519643593042</v>
+        <v>0.2769770305932087</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>0.3106944994222188</v>
+        <v>0.3106819663052665</v>
       </c>
       <c r="O72" s="5" t="n">
         <v>0.4754011830978497</v>
@@ -8246,13 +8252,13 @@
         </is>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.4180058214094384</v>
+        <v>0.4179943215785809</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0.2584517932169718</v>
+        <v>0.2584747928786869</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>0.3235423853735896</v>
+        <v>0.3235308855427321</v>
       </c>
       <c r="O73" s="5" t="n">
         <v>0.5544961797151675</v>
@@ -8872,13 +8878,13 @@
         </is>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.3664801997762926</v>
+        <v>0.3664681663993374</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>0.2674955889524718</v>
+        <v>0.2675196557063821</v>
       </c>
       <c r="N79" s="5" t="n">
-        <v>0.3660242112712357</v>
+        <v>0.3660121778942805</v>
       </c>
       <c r="O79" s="5" t="n">
         <v>0.5224005312757404</v>
@@ -8976,13 +8982,13 @@
         </is>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.3822767492292049</v>
+        <v>0.3822649324095744</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.2638886591923574</v>
+        <v>0.2639122928316185</v>
       </c>
       <c r="N80" s="5" t="n">
-        <v>0.3538345915784377</v>
+        <v>0.3538227747588071</v>
       </c>
       <c r="O80" s="5" t="n">
         <v>0.537191674357519</v>
@@ -9080,13 +9086,13 @@
         </is>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.4072131864905001</v>
+        <v>0.407202168049996</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.2521724438648174</v>
+        <v>0.2521944807458257</v>
       </c>
       <c r="N81" s="5" t="n">
-        <v>0.3406143696446824</v>
+        <v>0.3406033512041783</v>
       </c>
       <c r="O81" s="5" t="n">
         <v>0.5860389248216261</v>
@@ -9390,22 +9396,26 @@
         </is>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.3316036296256834</v>
+        <v>0.3666379659641704</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.3014037563358256</v>
+        <v>0.2671796201116068</v>
       </c>
       <c r="N84" s="5" t="n">
-        <v>0.3669926140384909</v>
+        <v>0.3661824139242228</v>
       </c>
       <c r="O84" s="5" t="n">
-        <v>0.3909271006079778</v>
+        <v>0.5238432985648792</v>
       </c>
       <c r="P84" s="5" t="n">
-        <v>0.6090728993920221</v>
-      </c>
-      <c r="Q84" s="9" t="n"/>
-      <c r="R84" s="9" t="n"/>
+        <v>0.4761567014351207</v>
+      </c>
+      <c r="Q84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R84" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="S84" s="3" t="inlineStr">
         <is>
           <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
@@ -9439,7 +9449,7 @@
         <v/>
       </c>
       <c r="AA84" s="8" t="n">
-        <v>0.6847</v>
+        <v>0.64</v>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
@@ -9490,19 +9500,19 @@
         </is>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0.4733161801380862</v>
+        <v>0.4733049021528176</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.2527997846520488</v>
+        <v>0.2528223406225858</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>0.2738840352098651</v>
+        <v>0.2738727572245965</v>
       </c>
       <c r="O85" s="5" t="n">
         <v>0.554841106162472</v>
       </c>
       <c r="P85" s="5" t="n">
-        <v>0.445158893837528</v>
+        <v>0.4451588938375281</v>
       </c>
       <c r="Q85" s="2" t="n">
         <v>2</v>
@@ -9594,25 +9604,30 @@
         </is>
       </c>
       <c r="L86" s="5" t="n">
-        <v>0.4408309583973712</v>
+        <v>0.4181030605818887</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.2849474201768056</v>
+        <v>0.2683736187672844</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.274221621425823</v>
+        <v>0.313523320650827</v>
       </c>
       <c r="O86" s="5" t="n">
-        <v>0.4312042519825969</v>
+        <v>0.5102846778231006</v>
       </c>
       <c r="P86" s="5" t="n">
-        <v>0.5687957480174031</v>
-      </c>
-      <c r="Q86" s="9" t="n"/>
-      <c r="R86" s="9" t="n"/>
-      <c r="S86" s="3">
-        <f>IF(OR(Q86="",R86=""),"[APOSTAR] VISITA",IF(Q86&lt;R86,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+        <v>0.4897153221768994</v>
+      </c>
+      <c r="Q86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3" t="inlineStr">
+        <is>
+          <t>[PERDIDA] VISITA</t>
+        </is>
       </c>
       <c r="T86" s="3" t="inlineStr">
         <is>
@@ -9620,7 +9635,7 @@
         </is>
       </c>
       <c r="U86" s="6" t="n">
-        <v>2080.02</v>
+        <v>1767.77</v>
       </c>
       <c r="V86" s="6" t="n">
         <v>0</v>
@@ -9642,7 +9657,7 @@
         <v/>
       </c>
       <c r="AA86" s="8" t="n">
-        <v>0.6484</v>
+        <v>0.6549</v>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
@@ -9677,13 +9692,13 @@
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="I87" s="4" t="n"/>
       <c r="J87" s="4" t="n"/>
@@ -9787,22 +9802,26 @@
         </is>
       </c>
       <c r="L88" s="5" t="n">
-        <v>0.3888866300077002</v>
+        <v>0.4048115656689204</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>0.2606801417071365</v>
+        <v>0.2290705683138505</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>0.3504332282851633</v>
+        <v>0.366117866017229</v>
       </c>
       <c r="O88" s="5" t="n">
-        <v>0.5427289352337143</v>
+        <v>0.6884717147660365</v>
       </c>
       <c r="P88" s="5" t="n">
-        <v>0.4572710647662857</v>
-      </c>
-      <c r="Q88" s="9" t="n"/>
-      <c r="R88" s="9" t="n"/>
+        <v>0.3115282852339635</v>
+      </c>
+      <c r="Q88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R88" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S88" s="3" t="inlineStr">
         <is>
           <t>[PASAR] Sin Cuotas</t>
@@ -9836,7 +9855,7 @@
         <v/>
       </c>
       <c r="AA88" s="8" t="n">
-        <v>0.6449</v>
+        <v>0.61</v>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
@@ -9887,22 +9906,26 @@
         </is>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.3881265244504047</v>
+        <v>0.3646246508210028</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0.2639256587340179</v>
+        <v>0.2342798847627089</v>
       </c>
       <c r="N89" s="5" t="n">
-        <v>0.3479478168155773</v>
+        <v>0.4010954644162882</v>
       </c>
       <c r="O89" s="5" t="n">
-        <v>0.5285155352917529</v>
+        <v>0.6639022170684276</v>
       </c>
       <c r="P89" s="5" t="n">
-        <v>0.4714844647082471</v>
-      </c>
-      <c r="Q89" s="9" t="n"/>
-      <c r="R89" s="9" t="n"/>
+        <v>0.3360977829315725</v>
+      </c>
+      <c r="Q89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="S89" s="3" t="inlineStr">
         <is>
           <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
@@ -9936,7 +9959,7 @@
         <v/>
       </c>
       <c r="AA89" s="8" t="n">
-        <v>0.7967</v>
+        <v>0.8338</v>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
@@ -9971,13 +9994,13 @@
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2.61</v>
+        <v>2.47</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="I90" s="4" t="n"/>
       <c r="J90" s="4" t="n"/>
@@ -9987,13 +10010,13 @@
         </is>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0.3824461426497117</v>
+        <v>0.3824332517569273</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0.2856793054190302</v>
+        <v>0.285705087204599</v>
       </c>
       <c r="N90" s="5" t="n">
-        <v>0.3318745519312581</v>
+        <v>0.3318616610384737</v>
       </c>
       <c r="O90" s="5" t="n">
         <v>0.4470479370050782</v>
@@ -10003,10 +10026,9 @@
       </c>
       <c r="Q90" s="9" t="n"/>
       <c r="R90" s="9" t="n"/>
-      <c r="S90" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Riesgo/Beneficio</t>
-        </is>
+      <c r="S90" s="3">
+        <f>IF(OR(Q90="",R90=""),"[APOSTAR] VISITA",IF(Q90&lt;R90,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
       </c>
       <c r="T90" s="3" t="inlineStr">
         <is>
@@ -10014,7 +10036,7 @@
         </is>
       </c>
       <c r="U90" s="6" t="n">
-        <v>0</v>
+        <v>1767.77</v>
       </c>
       <c r="V90" s="6" t="n">
         <v>0</v>
@@ -10091,25 +10113,29 @@
         </is>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.4339762137504555</v>
+        <v>0.4444767526297125</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.2734478289586073</v>
+        <v>0.2364653693587922</v>
       </c>
       <c r="N91" s="5" t="n">
-        <v>0.2925759572909372</v>
+        <v>0.3190578780114953</v>
       </c>
       <c r="O91" s="5" t="n">
-        <v>0.4743906965749504</v>
+        <v>0.642169075997571</v>
       </c>
       <c r="P91" s="5" t="n">
-        <v>0.5256093034250495</v>
-      </c>
-      <c r="Q91" s="9" t="n"/>
-      <c r="R91" s="9" t="n"/>
+        <v>0.357830924002429</v>
+      </c>
+      <c r="Q91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R91" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="S91" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Riesgo/Beneficio</t>
+          <t>[PERDIDA] VISITA</t>
         </is>
       </c>
       <c r="T91" s="3" t="inlineStr">
@@ -10118,7 +10144,7 @@
         </is>
       </c>
       <c r="U91" s="6" t="n">
-        <v>0</v>
+        <v>1340.4</v>
       </c>
       <c r="V91" s="6" t="n">
         <v>0</v>
@@ -10140,7 +10166,7 @@
         <v/>
       </c>
       <c r="AA91" s="8" t="n">
-        <v>0.7998</v>
+        <v>0.7872</v>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
@@ -10175,13 +10201,13 @@
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>3.24</v>
+        <v>3.13</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I92" s="4" t="n"/>
       <c r="J92" s="4" t="n"/>
@@ -10290,22 +10316,26 @@
         </is>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.3820489641973929</v>
+        <v>0.4059501345793776</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>0.2625765741645809</v>
+        <v>0.2292674690390933</v>
       </c>
       <c r="N93" s="5" t="n">
-        <v>0.3553744616380262</v>
+        <v>0.3647823963815291</v>
       </c>
       <c r="O93" s="5" t="n">
-        <v>0.5350608595088769</v>
+        <v>0.6873848456576175</v>
       </c>
       <c r="P93" s="5" t="n">
-        <v>0.4649391404911231</v>
-      </c>
-      <c r="Q93" s="9" t="n"/>
-      <c r="R93" s="9" t="n"/>
+        <v>0.3126151543423826</v>
+      </c>
+      <c r="Q93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R93" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="S93" s="3" t="inlineStr">
         <is>
           <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
@@ -10339,7 +10369,7 @@
         <v/>
       </c>
       <c r="AA93" s="8" t="n">
-        <v>0.7436</v>
+        <v>0.7115</v>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
@@ -10374,13 +10404,13 @@
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>2.89</v>
+        <v>2.96</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>4.07</v>
+        <v>4.14</v>
       </c>
       <c r="I94" s="4" t="n"/>
       <c r="J94" s="4" t="n"/>
@@ -10390,19 +10420,19 @@
         </is>
       </c>
       <c r="L94" s="5" t="n">
-        <v>0.3774842620479749</v>
+        <v>0.3774962623290449</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0.2650645959520047</v>
+        <v>0.2650405953898647</v>
       </c>
       <c r="N94" s="5" t="n">
-        <v>0.3574511420000204</v>
+        <v>0.3574631422810903</v>
       </c>
       <c r="O94" s="5" t="n">
         <v>0.5245637627586317</v>
       </c>
       <c r="P94" s="5" t="n">
-        <v>0.4754362372413684</v>
+        <v>0.4754362372413683</v>
       </c>
       <c r="Q94" s="9" t="n"/>
       <c r="R94" s="9" t="n"/>
@@ -10516,7 +10546,7 @@
         </is>
       </c>
       <c r="U95" s="6" t="n">
-        <v>1118.03</v>
+        <v>1250</v>
       </c>
       <c r="V95" s="6" t="n">
         <v>0</v>
@@ -10573,19 +10603,19 @@
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="I96" s="4" t="n">
         <v>1.97</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
@@ -10619,7 +10649,7 @@
         </is>
       </c>
       <c r="U96" s="6" t="n">
-        <v>1118.03</v>
+        <v>1250</v>
       </c>
       <c r="V96" s="6" t="n">
         <v>0</v>
@@ -10676,13 +10706,13 @@
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="I97" s="4" t="n"/>
       <c r="J97" s="4" t="n"/>
@@ -10692,16 +10722,16 @@
         </is>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.5153965634929999</v>
+        <v>0.5153845029049635</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>0.2687924740870805</v>
+        <v>0.2688165952631533</v>
       </c>
       <c r="N97" s="5" t="n">
-        <v>0.2158109624199196</v>
+        <v>0.2157989018318832</v>
       </c>
       <c r="O97" s="5" t="n">
-        <v>0.446270691195238</v>
+        <v>0.4462706911952379</v>
       </c>
       <c r="P97" s="5" t="n">
         <v>0.553729308804762</v>
@@ -10775,13 +10805,13 @@
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="I98" s="4" t="n"/>
       <c r="J98" s="4" t="n"/>
@@ -10817,7 +10847,7 @@
         </is>
       </c>
       <c r="U98" s="6" t="n">
-        <v>1118.03</v>
+        <v>1250</v>
       </c>
       <c r="V98" s="6" t="n">
         <v>0</v>
@@ -10874,13 +10904,13 @@
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I99" s="4" t="n"/>
       <c r="J99" s="4" t="n"/>
@@ -10906,9 +10936,10 @@
       </c>
       <c r="Q99" s="9" t="n"/>
       <c r="R99" s="9" t="n"/>
-      <c r="S99" s="3">
-        <f>IF(OR(Q99="",R99=""),"[APOSTAR] VISITA",IF(Q99&lt;R99,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S99" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Riesgo/Beneficio</t>
+        </is>
       </c>
       <c r="T99" s="3" t="inlineStr">
         <is>
@@ -10916,7 +10947,7 @@
         </is>
       </c>
       <c r="U99" s="6" t="n">
-        <v>562.95</v>
+        <v>0</v>
       </c>
       <c r="V99" s="6" t="n">
         <v>0</v>
@@ -10973,13 +11004,13 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="I100" s="4" t="n">
         <v>1.87</v>
@@ -10993,13 +11024,13 @@
         </is>
       </c>
       <c r="L100" s="5" t="n">
-        <v>0.3514426200719207</v>
+        <v>0.3514549848930091</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>0.2716075812871424</v>
+        <v>0.2715828516449654</v>
       </c>
       <c r="N100" s="5" t="n">
-        <v>0.376949798640937</v>
+        <v>0.3769621634620255</v>
       </c>
       <c r="O100" s="5" t="n">
         <v>0.4967726530136669</v>
@@ -11077,13 +11108,13 @@
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="G101" s="4" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H101" s="4" t="n">
         <v>3.62</v>
-      </c>
-      <c r="H101" s="4" t="n">
-        <v>3.54</v>
       </c>
       <c r="I101" s="4" t="n"/>
       <c r="J101" s="4" t="n"/>
@@ -11093,13 +11124,13 @@
         </is>
       </c>
       <c r="L101" s="5" t="n">
-        <v>0.4306682642088859</v>
+        <v>0.4306791103881857</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>0.2475750063177246</v>
+        <v>0.2475533139591249</v>
       </c>
       <c r="N101" s="5" t="n">
-        <v>0.3217567294733895</v>
+        <v>0.3217675756526893</v>
       </c>
       <c r="O101" s="5" t="n">
         <v>0.5933963385823751</v>
@@ -11176,16 +11207,20 @@
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>4.97</v>
+        <v>4.75</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>10.06</v>
-      </c>
-      <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
+        <v>9.25</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>2.04</v>
+      </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
           <t>Brasil</t>
@@ -11215,7 +11250,7 @@
       </c>
       <c r="T102" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U102" s="6" t="n">
@@ -11286,13 +11321,13 @@
         </is>
       </c>
       <c r="L103" s="5" t="n">
-        <v>0.3689524796970511</v>
+        <v>0.3689392713225658</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>0.2960365842901977</v>
+        <v>0.2960630010391685</v>
       </c>
       <c r="N103" s="5" t="n">
-        <v>0.3350109360127511</v>
+        <v>0.3349977276382657</v>
       </c>
       <c r="O103" s="5" t="n">
         <v>0.4097861749290452</v>
@@ -11473,13 +11508,17 @@
         <v>2.23</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="I105" s="4" t="n"/>
-      <c r="J105" s="4" t="n"/>
+        <v>3.3</v>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="J105" s="4" t="n">
+        <v>1.85</v>
+      </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
           <t>Brasil</t>
@@ -11508,11 +11547,11 @@
       </c>
       <c r="T105" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U105" s="6" t="n">
-        <v>1118.03</v>
+        <v>1250</v>
       </c>
       <c r="V105" s="6" t="n">
         <v>0</v>
@@ -11572,10 +11611,10 @@
         <v>1.58</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>6.23</v>
+        <v>6.29</v>
       </c>
       <c r="I106" s="4" t="n"/>
       <c r="J106" s="4" t="n"/>
@@ -11585,13 +11624,13 @@
         </is>
       </c>
       <c r="L106" s="5" t="n">
-        <v>0.518363136619953</v>
+        <v>0.5183513826415038</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>0.2598649587083614</v>
+        <v>0.2598884666652597</v>
       </c>
       <c r="N106" s="5" t="n">
-        <v>0.2217719046716857</v>
+        <v>0.2217601506932365</v>
       </c>
       <c r="O106" s="5" t="n">
         <v>0.4844492602992937</v>
@@ -11669,13 +11708,13 @@
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>5.38</v>
+        <v>5.88</v>
       </c>
       <c r="I107" s="4" t="n"/>
       <c r="J107" s="4" t="n"/>
@@ -11685,13 +11724,13 @@
         </is>
       </c>
       <c r="L107" s="5" t="n">
-        <v>0.5139712492517915</v>
+        <v>0.5139591636750956</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0.2694724800809071</v>
+        <v>0.2694966512342987</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>0.2165562706673014</v>
+        <v>0.2165441850906056</v>
       </c>
       <c r="O107" s="5" t="n">
         <v>0.4445899234793541</v>
@@ -11779,13 +11818,13 @@
         </is>
       </c>
       <c r="L108" s="5" t="n">
-        <v>0.4326940218702164</v>
+        <v>0.4327065118354139</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.2741415535192428</v>
+        <v>0.2741165735888479</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>0.2931644246105408</v>
+        <v>0.2931769145757382</v>
       </c>
       <c r="O108" s="5" t="n">
         <v>0.4719878585254011</v>
@@ -11863,13 +11902,13 @@
         </is>
       </c>
       <c r="F109" s="4" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>3.64</v>
+        <v>3.9</v>
       </c>
       <c r="I109" s="4" t="n">
         <v>2</v>
@@ -11969,10 +12008,10 @@
         <v>1.51</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>3.92</v>
+        <v>3.93</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="I110" s="4" t="n"/>
       <c r="J110" s="4" t="n"/>
@@ -11982,13 +12021,13 @@
         </is>
       </c>
       <c r="L110" s="5" t="n">
-        <v>0.5563943021271643</v>
+        <v>0.5563827497814012</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>0.2583073973909855</v>
+        <v>0.2583305020825115</v>
       </c>
       <c r="N110" s="5" t="n">
-        <v>0.1852983004818502</v>
+        <v>0.1852867481360872</v>
       </c>
       <c r="O110" s="5" t="n">
         <v>0.4497533845612681</v>
@@ -12066,13 +12105,13 @@
         </is>
       </c>
       <c r="F111" s="4" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I111" s="4" t="n"/>
       <c r="J111" s="4" t="n"/>
@@ -12098,10 +12137,9 @@
       </c>
       <c r="Q111" s="9" t="n"/>
       <c r="R111" s="9" t="n"/>
-      <c r="S111" s="3" t="inlineStr">
-        <is>
-          <t>[PASAR] Info Oculta</t>
-        </is>
+      <c r="S111" s="3">
+        <f>IF(OR(Q111="",R111=""),"[APOSTAR] LOCAL",IF(Q111&gt;R111,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T111" s="3" t="inlineStr">
         <is>
@@ -12109,7 +12147,7 @@
         </is>
       </c>
       <c r="U111" s="6" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="V111" s="6" t="n">
         <v>0</v>
@@ -12176,13 +12214,13 @@
         </is>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0.3333326837740704</v>
+        <v>0.3333452995346447</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.2768377365086844</v>
+        <v>0.2768125049875358</v>
       </c>
       <c r="N112" s="5" t="n">
-        <v>0.3898295797172452</v>
+        <v>0.3898421954778195</v>
       </c>
       <c r="O112" s="5" t="n">
         <v>0.4735064796585714</v>
@@ -12460,13 +12498,13 @@
         </is>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>4.58</v>
+        <v>4.66</v>
       </c>
       <c r="I115" s="4" t="n"/>
       <c r="J115" s="4" t="n"/>
@@ -12879,13 +12917,13 @@
         </is>
       </c>
       <c r="L119" s="5" t="n">
-        <v>0.3888211956565762</v>
+        <v>0.38880828905502</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>0.2862330316065712</v>
+        <v>0.2862588448096837</v>
       </c>
       <c r="N119" s="5" t="n">
-        <v>0.3249457727368525</v>
+        <v>0.3249328661352963</v>
       </c>
       <c r="O119" s="5" t="n">
         <v>0.4438155267438119</v>
@@ -13159,9 +13197,15 @@
           <t>Galatasaray</t>
         </is>
       </c>
-      <c r="F122" s="4" t="n"/>
-      <c r="G122" s="4" t="n"/>
-      <c r="H122" s="4" t="n"/>
+      <c r="F122" s="4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>1.67</v>
+      </c>
       <c r="I122" s="4" t="n"/>
       <c r="J122" s="4" t="n"/>
       <c r="K122" s="2" t="inlineStr">
@@ -13170,25 +13214,25 @@
         </is>
       </c>
       <c r="L122" s="5" t="n">
-        <v>0.3503567059368736</v>
+        <v>0.3981045687317345</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.283028484029018</v>
+        <v>0.2585785927225737</v>
       </c>
       <c r="N122" s="5" t="n">
-        <v>0.3666148100341084</v>
+        <v>0.3433168385456918</v>
       </c>
       <c r="O122" s="5" t="n">
-        <v>0.4513030547014477</v>
+        <v>0.5506715830807075</v>
       </c>
       <c r="P122" s="5" t="n">
-        <v>0.5486969452985523</v>
+        <v>0.4493284169192925</v>
       </c>
       <c r="Q122" s="9" t="n"/>
       <c r="R122" s="9" t="n"/>
       <c r="S122" s="3" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Info Oculta</t>
         </is>
       </c>
       <c r="T122" s="3" t="inlineStr">
@@ -13219,9 +13263,103 @@
         <v/>
       </c>
       <c r="AA122" s="8" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.694</v>
       </c>
       <c r="AB122" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-09caykurrizesporsamsunspor</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor vs Samsunspor</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="n"/>
+      <c r="H123" s="4" t="n"/>
+      <c r="I123" s="4" t="n"/>
+      <c r="J123" s="4" t="n"/>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>0.4143462864297805</v>
+      </c>
+      <c r="M123" s="5" t="n">
+        <v>0.2731616518595862</v>
+      </c>
+      <c r="N123" s="5" t="n">
+        <v>0.3124920617106333</v>
+      </c>
+      <c r="O123" s="5" t="n">
+        <v>0.4828233891977304</v>
+      </c>
+      <c r="P123" s="5" t="n">
+        <v>0.5171766108022696</v>
+      </c>
+      <c r="Q123" s="9" t="n"/>
+      <c r="R123" s="9" t="n"/>
+      <c r="S123" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T123" s="3" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="3">
+        <f>IF(L123="","",IF((MAX(L123,M123,N123)-MEDIAN(L123,M123,N123))&gt;0.05,IF(OR(Q123="",R123=""),"[PREDICCION] "&amp;IF(L123=MAX(L123,M123,N123),"LOCAL",IF(M123=MAX(L123,M123,N123),"EMPATE","VISITA")),IF(L123=MAX(L123,M123,N123),IF(Q123&gt;R123,"[ACIERTO]","[FALLO]"),IF(M123=MAX(L123,M123,N123),IF(Q123=R123,"[ACIERTO]","[FALLO]"),IF(Q123&lt;R123,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X123" s="6">
+        <f>IFERROR(IF(U123=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S123)),U123*(IF(ISNUMBER(SEARCH("LOCAL",S123)),F123,IF(ISNUMBER(SEARCH("EMPATE",S123)),G123,H123))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S123)),-U123,0))),0)+IFERROR(IF(V123=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T123)),V123*(IF(ISNUMBER(SEARCH("OVER",T123)),I123,J123)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T123)),-V123,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y123" s="6">
+        <f>Y122+X123</f>
+        <v/>
+      </c>
+      <c r="Z123" s="7">
+        <f>IF(OR(Q123="",R123=""),"",(L123-IF(Q123&gt;R123,1,0))^2+(M123-IF(Q123=R123,1,0))^2+(N123-IF(Q123&lt;R123,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA123" s="8" t="n">
+        <v>0.859</v>
+      </c>
+      <c r="AB123" s="2" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -13229,7 +13367,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AB1"/>
-  <conditionalFormatting sqref="S2:T122">
+  <conditionalFormatting sqref="S2:T123">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>ISNUMBER(SEARCH("[GANADA]",S2))</formula>
     </cfRule>
@@ -13312,25 +13450,25 @@
         </is>
       </c>
       <c r="B2" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>-5000</v>
+        <v>-6767.77</v>
       </c>
       <c r="G2" s="12" t="n">
         <v>-1</v>
       </c>
       <c r="H2" s="13" t="n">
-        <v>5000</v>
+        <v>6767.77</v>
       </c>
     </row>
     <row r="3">
@@ -13424,25 +13562,25 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0</v>
+        <v>-1340.4</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>0</v>
+        <v>1340.4</v>
       </c>
     </row>
     <row r="7">
@@ -13452,31 +13590,31 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.125</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>-6849.75</v>
+        <v>-9957.92</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>-0.654061701788376</v>
+        <v>-0.7332348757068802</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>10472.63</v>
+        <v>13580.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>Generado: 03/04/2026 19:29</t>
+          <t>Generado: 04/04/2026 17:18</t>
         </is>
       </c>
     </row>

--- a/Backtest_Modelo.xlsx
+++ b/Backtest_Modelo.xlsx
@@ -896,7 +896,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/04/2026 13:18   |   Bankroll: $100,000.00</t>
+          <t>Generado: 05/04/2026 15:35   |   Bankroll: $100,000.00</t>
         </is>
       </c>
     </row>
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>110586.1725</v>
+        <v>95233.98699999999</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>108889.1133</v>
+        <v>93848.3422</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1697.0592</v>
+        <v>1385.6448</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1.905773933163079</v>
+        <v>1.576675435173506</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1.935491962728189</v>
+        <v>1.591772472077341</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0.96</v>
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>58026.91</v>
+        <v>60401.77</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>56259.14</v>
+        <v>58958.39</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>1</v>
@@ -1003,14 +1003,14 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>% Acierto P  (col. Acierto, 48/70 partidos)</t>
+          <t>% Acierto P  (col. Acierto, 50/73 partidos)</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.684931506849315</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.75</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>1</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.7216450216450216</v>
+        <v>0.6996086105675147</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.7178571428571429</v>
+        <v>0.6954069298952458</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>1</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>5.5055</v>
+        <v>4.8227</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>5.4437</v>
+        <v>4.7538</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>0</v>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>0.5722736849719164</v>
+        <v>0.5636221108909509</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>0.5722736849719164</v>
+        <v>0.5636221108909509</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B20" s="14" t="n">
-        <v>-0.07352064242882927</v>
+        <v>-0.08217221650979478</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>-0.07352064242882927</v>
+        <v>-0.08217221650979478</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="L3" s="31" t="n">
-        <v>0.4327630176588643</v>
+        <v>0.455627</v>
       </c>
       <c r="M3" s="31" t="n">
-        <v>0.2503501502239416</v>
+        <v>0.240259</v>
       </c>
       <c r="N3" s="31" t="n">
-        <v>0.3168868321171942</v>
+        <v>0.304114</v>
       </c>
       <c r="O3" s="31" t="n">
         <v>0.5870316109295243</v>
@@ -1781,13 +1781,13 @@
         </is>
       </c>
       <c r="L4" s="31" t="n">
-        <v>0.434312261576528</v>
+        <v>0.457113</v>
       </c>
       <c r="M4" s="31" t="n">
-        <v>0.2744559912783204</v>
+        <v>0.263393</v>
       </c>
       <c r="N4" s="31" t="n">
-        <v>0.2912317471451517</v>
+        <v>0.279493</v>
       </c>
       <c r="O4" s="31" t="n">
         <v>0.4665313709826981</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="L7" s="31" t="n">
-        <v>0.4328360476795187</v>
+        <v>0.455697</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>0.2779236871677406</v>
+        <v>0.266721</v>
       </c>
       <c r="N7" s="31" t="n">
-        <v>0.2892402651527407</v>
+        <v>0.277582</v>
       </c>
       <c r="O7" s="31" t="n">
         <v>0.4636024826220113</v>
@@ -2330,13 +2330,13 @@
         </is>
       </c>
       <c r="L9" s="31" t="n">
-        <v>0.4183473784064732</v>
+        <v>0.441792</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>0.2858291034267562</v>
+        <v>0.274308</v>
       </c>
       <c r="N9" s="31" t="n">
-        <v>0.2958235181667705</v>
+        <v>0.2839</v>
       </c>
       <c r="O9" s="31" t="n">
         <v>0.4371983044114202</v>
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="L12" s="31" t="n">
-        <v>0.4714950682292441</v>
+        <v>0.492798</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>0.2827861433763474</v>
+        <v>0.271388</v>
       </c>
       <c r="N12" s="31" t="n">
-        <v>0.2457187883944085</v>
+        <v>0.235815</v>
       </c>
       <c r="O12" s="31" t="n">
         <v>0.4148022099731867</v>
@@ -2751,13 +2751,13 @@
         </is>
       </c>
       <c r="L13" s="31" t="n">
-        <v>0.4728842474200235</v>
+        <v>0.494131</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>0.2408487917260128</v>
+        <v>0.231141</v>
       </c>
       <c r="N13" s="31" t="n">
-        <v>0.2862669608539637</v>
+        <v>0.274728</v>
       </c>
       <c r="O13" s="31" t="n">
         <v>0.6015291871790185</v>
@@ -2853,13 +2853,13 @@
         </is>
       </c>
       <c r="L14" s="31" t="n">
-        <v>0.4709801108113196</v>
+        <v>0.492303</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>0.2388541216074238</v>
+        <v>0.229227</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>0.2901657675812566</v>
+        <v>0.27847</v>
       </c>
       <c r="O14" s="31" t="n">
         <v>0.6127357803698895</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="L16" s="31" t="n">
-        <v>0.4143338364837813</v>
+        <v>0.43794</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>0.2731865517515846</v>
+        <v>0.262175</v>
       </c>
       <c r="N16" s="31" t="n">
-        <v>0.3124796117646341</v>
+        <v>0.299884</v>
       </c>
       <c r="O16" s="31" t="n">
         <v>0.4828233891977304</v>
@@ -3161,13 +3161,13 @@
         </is>
       </c>
       <c r="L17" s="31" t="n">
-        <v>0.2861270283395916</v>
+        <v>0.274594</v>
       </c>
       <c r="M17" s="31" t="n">
-        <v>0.2607651812525669</v>
+        <v>0.250254</v>
       </c>
       <c r="N17" s="31" t="n">
-        <v>0.4531077904078414</v>
+        <v>0.475151</v>
       </c>
       <c r="O17" s="31" t="n">
         <v>0.5214361653599625</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="L19" s="31" t="n">
-        <v>0.4450762606164246</v>
+        <v>0.467444</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>0.2681926644878433</v>
+        <v>0.257383</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>0.2867310748957321</v>
+        <v>0.275174</v>
       </c>
       <c r="O19" s="31" t="n">
         <v>0.4920602783752462</v>
@@ -3464,13 +3464,13 @@
         </is>
       </c>
       <c r="L20" s="31" t="n">
-        <v>0.482975468966526</v>
+        <v>0.503815</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>0.2489943090805346</v>
+        <v>0.238958</v>
       </c>
       <c r="N20" s="31" t="n">
-        <v>0.2680302219529394</v>
+        <v>0.257227</v>
       </c>
       <c r="O20" s="31" t="n">
         <v>0.5542627005521311</v>
@@ -3564,13 +3564,13 @@
         </is>
       </c>
       <c r="L21" s="31" t="n">
-        <v>0.4788512867037201</v>
+        <v>0.499857</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>0.2219314635183941</v>
+        <v>0.212986</v>
       </c>
       <c r="N21" s="31" t="n">
-        <v>0.2992172497778857</v>
+        <v>0.287157</v>
       </c>
       <c r="O21" s="31" t="n">
         <v>0.6949277206627653</v>
@@ -3666,13 +3666,13 @@
         </is>
       </c>
       <c r="L22" s="31" t="n">
-        <v>0.4564242566712488</v>
+        <v>0.478334</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>0.2445861736316765</v>
+        <v>0.234728</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>0.2989895696970746</v>
+        <v>0.286938</v>
       </c>
       <c r="O22" s="31" t="n">
         <v>0.5921931616962641</v>
@@ -3768,13 +3768,13 @@
         </is>
       </c>
       <c r="L23" s="31" t="n">
-        <v>0.4179454983170294</v>
+        <v>0.441406</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>0.2262501769591969</v>
+        <v>0.217131</v>
       </c>
       <c r="N23" s="31" t="n">
-        <v>0.3558043247237737</v>
+        <v>0.341463</v>
       </c>
       <c r="O23" s="31" t="n">
         <v>0.6962658764730534</v>
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="L25" s="31" t="n">
-        <v>0.4603227561410582</v>
+        <v>0.482076</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>0.2873036217162985</v>
+        <v>0.275723</v>
       </c>
       <c r="N25" s="31" t="n">
-        <v>0.2523736221426435</v>
+        <v>0.242201</v>
       </c>
       <c r="O25" s="31" t="n">
         <v>0.4109749443702656</v>
@@ -4009,7 +4009,7 @@
       </c>
       <c r="S25" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Riesgo/Beneficio</t>
+          <t>[PASAR] EV Insuf (0.041&lt;0.080)</t>
         </is>
       </c>
       <c r="T25" s="28" t="inlineStr">
@@ -4206,13 +4206,13 @@
         </is>
       </c>
       <c r="L27" s="31" t="n">
-        <v>0.4108978929417581</v>
+        <v>0.434643</v>
       </c>
       <c r="M27" s="31" t="n">
-        <v>0.2678994893669501</v>
+        <v>0.257101</v>
       </c>
       <c r="N27" s="31" t="n">
-        <v>0.3212026176912918</v>
+        <v>0.308256</v>
       </c>
       <c r="O27" s="31" t="n">
         <v>0.5030608941671695</v>
@@ -4315,13 +4315,13 @@
         </is>
       </c>
       <c r="L28" s="31" t="n">
-        <v>0.4007373641237821</v>
+        <v>0.424892</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>0.2783119242231875</v>
+        <v>0.267094</v>
       </c>
       <c r="N28" s="31" t="n">
-        <v>0.3209507116530305</v>
+        <v>0.308014</v>
       </c>
       <c r="O28" s="31" t="n">
         <v>0.4728740634574408</v>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="L30" s="31" t="n">
-        <v>0.4890383775254059</v>
+        <v>0.509634</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>0.226928211007076</v>
+        <v>0.217781</v>
       </c>
       <c r="N30" s="31" t="n">
-        <v>0.2840334114675181</v>
+        <v>0.272585</v>
       </c>
       <c r="O30" s="31" t="n">
         <v>0.6626510174407112</v>
@@ -4644,13 +4644,13 @@
         </is>
       </c>
       <c r="L31" s="31" t="n">
-        <v>0.4747849593452914</v>
+        <v>0.495955</v>
       </c>
       <c r="M31" s="31" t="n">
-        <v>0.2608106257157422</v>
+        <v>0.250298</v>
       </c>
       <c r="N31" s="31" t="n">
-        <v>0.2644044149389664</v>
+        <v>0.253747</v>
       </c>
       <c r="O31" s="31" t="n">
         <v>0.5046559413263287</v>
@@ -4864,13 +4864,13 @@
         </is>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.413123913794344</v>
+        <v>0.436779</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>0.2751580186117192</v>
+        <v>0.264067</v>
       </c>
       <c r="N33" s="31" t="n">
-        <v>0.3117180675939367</v>
+        <v>0.299154</v>
       </c>
       <c r="O33" s="31" t="n">
         <v>0.4825726127876495</v>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="S33" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (31%&lt;33%)</t>
+          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
         </is>
       </c>
       <c r="T33" s="28" t="inlineStr">
@@ -5193,13 +5193,13 @@
         </is>
       </c>
       <c r="L36" s="31" t="n">
-        <v>0.4371080543458052</v>
+        <v>0.459797</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>0.2296551705392528</v>
+        <v>0.220398</v>
       </c>
       <c r="N36" s="31" t="n">
-        <v>0.333236775114942</v>
+        <v>0.319805</v>
       </c>
       <c r="O36" s="31" t="n">
         <v>0.6744931291712692</v>
@@ -5213,9 +5213,10 @@
       <c r="R36" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="S36" s="28">
-        <f>IF(OR(Q36="",R36=""),"[APOSTAR] VISITA",IF(Q36&lt;R36,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S36" s="28" t="inlineStr">
+        <is>
+          <t>[PASAR] Floor Prob (32%&lt;33%)</t>
+        </is>
       </c>
       <c r="T36" s="28" t="inlineStr">
         <is>
@@ -5223,7 +5224,7 @@
         </is>
       </c>
       <c r="U36" s="32" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="V36" s="32" t="n">
         <v>0</v>
@@ -5521,13 +5522,13 @@
         </is>
       </c>
       <c r="L39" s="31" t="n">
-        <v>0.4928664544249471</v>
+        <v>0.513308</v>
       </c>
       <c r="M39" s="31" t="n">
-        <v>0.2525110804175839</v>
+        <v>0.242333</v>
       </c>
       <c r="N39" s="31" t="n">
-        <v>0.2546224651574689</v>
+        <v>0.244359</v>
       </c>
       <c r="O39" s="31" t="n">
         <v>0.5308988957465525</v>
@@ -5541,10 +5542,9 @@
       <c r="R39" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="28" t="inlineStr">
-        <is>
-          <t>[PASAR] Floor Prob (25%&lt;33%)</t>
-        </is>
+      <c r="S39" s="28">
+        <f>IF(OR(Q39="",R39=""),"[APOSTAR] LOCAL",IF(Q39&gt;R39,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T39" s="28" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         </is>
       </c>
       <c r="U39" s="32" t="n">
-        <v>0</v>
+        <v>1308.71</v>
       </c>
       <c r="V39" s="32" t="n">
         <v>0</v>
@@ -5631,13 +5631,13 @@
         </is>
       </c>
       <c r="L40" s="31" t="n">
-        <v>0.4325257967730947</v>
+        <v>0.455399</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>0.2666484292202701</v>
+        <v>0.255901</v>
       </c>
       <c r="N40" s="31" t="n">
-        <v>0.3008257740066352</v>
+        <v>0.2887</v>
       </c>
       <c r="O40" s="31" t="n">
         <v>0.4998597255701074</v>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="S40" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
+          <t>[PASAR] Floor Prob (29%&lt;33%)</t>
         </is>
       </c>
       <c r="T40" s="28" t="inlineStr">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="L42" s="31" t="n">
-        <v>0.472331218913578</v>
+        <v>0.4936</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>0.2890517182043581</v>
+        <v>0.277401</v>
       </c>
       <c r="N42" s="31" t="n">
-        <v>0.2386170628820639</v>
+        <v>0.228999</v>
       </c>
       <c r="O42" s="31" t="n">
         <v>0.3963885637853248</v>
@@ -5991,7 +5991,7 @@
         </is>
       </c>
       <c r="U43" s="32" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="V43" s="32" t="n">
         <v>0</v>
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="L44" s="31" t="n">
-        <v>0.4949402584051957</v>
+        <v>0.515298</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>0.2384619846153782</v>
+        <v>0.22885</v>
       </c>
       <c r="N44" s="31" t="n">
-        <v>0.2665977569794261</v>
+        <v>0.255852</v>
       </c>
       <c r="O44" s="31" t="n">
         <v>0.5985032908303799</v>
@@ -6092,7 +6092,7 @@
       </c>
       <c r="S44" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (27%&lt;33%)</t>
+          <t>[PASAR] Floor Prob (26%&lt;33%)</t>
         </is>
       </c>
       <c r="T44" s="28" t="inlineStr">
@@ -6400,13 +6400,13 @@
         </is>
       </c>
       <c r="L47" s="31" t="n">
-        <v>0.4766029423588835</v>
+        <v>0.4977</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>0.2464959847328186</v>
+        <v>0.23656</v>
       </c>
       <c r="N47" s="31" t="n">
-        <v>0.276901072908298</v>
+        <v>0.26574</v>
       </c>
       <c r="O47" s="31" t="n">
         <v>0.5709537516820591</v>
@@ -6510,13 +6510,13 @@
         </is>
       </c>
       <c r="L48" s="31" t="n">
-        <v>0.4508549739721156</v>
+        <v>0.472989</v>
       </c>
       <c r="M48" s="31" t="n">
-        <v>0.2538639291312507</v>
+        <v>0.243631</v>
       </c>
       <c r="N48" s="31" t="n">
-        <v>0.2952810968966337</v>
+        <v>0.283379</v>
       </c>
       <c r="O48" s="31" t="n">
         <v>0.5513673051023443</v>
@@ -6543,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="32" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
       <c r="W48" s="28">
         <f>IF(L48="","",IF((MAX(L48,M48,N48)-MEDIAN(L48,M48,N48))&gt;0.05,IF(OR(Q48="",R48=""),"[PREDICCION] "&amp;IF(L48=MAX(L48,M48,N48),"LOCAL",IF(M48=MAX(L48,M48,N48),"EMPATE","VISITA")),IF(L48=MAX(L48,M48,N48),IF(Q48&gt;R48,"[ACIERTO]","[FALLO]"),IF(M48=MAX(L48,M48,N48),IF(Q48=R48,"[ACIERTO]","[FALLO]"),IF(Q48&lt;R48,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -6619,13 +6619,13 @@
         </is>
       </c>
       <c r="L49" s="31" t="n">
-        <v>0.4732293327193446</v>
+        <v>0.494462</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>0.2488329350843732</v>
+        <v>0.238803</v>
       </c>
       <c r="N49" s="31" t="n">
-        <v>0.2779377321962822</v>
+        <v>0.266735</v>
       </c>
       <c r="O49" s="31" t="n">
         <v>0.5616275155884431</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="U49" s="32" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="V49" s="32" t="n">
         <v>0</v>
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L50" s="31" t="n">
-        <v>0.4866934908317617</v>
+        <v>0.507383</v>
       </c>
       <c r="M50" s="31" t="n">
-        <v>0.2477732271558427</v>
+        <v>0.237786</v>
       </c>
       <c r="N50" s="31" t="n">
-        <v>0.2655332820123957</v>
+        <v>0.25483</v>
       </c>
       <c r="O50" s="31" t="n">
         <v>0.5442511332454576</v>
@@ -6758,7 +6758,7 @@
         </is>
       </c>
       <c r="U50" s="32" t="n">
-        <v>1767.77</v>
+        <v>2500</v>
       </c>
       <c r="V50" s="32" t="n">
         <v>0</v>
@@ -6837,13 +6837,13 @@
         </is>
       </c>
       <c r="L51" s="31" t="n">
-        <v>0.4042249201863001</v>
+        <v>0.428239</v>
       </c>
       <c r="M51" s="31" t="n">
-        <v>0.2470649039021326</v>
+        <v>0.237106</v>
       </c>
       <c r="N51" s="31" t="n">
-        <v>0.3487101759115673</v>
+        <v>0.334655</v>
       </c>
       <c r="O51" s="31" t="n">
         <v>0.585044147222101</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="S51" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.098&lt;0.120)</t>
+          <t>[PASAR] EV Insuf (0.054&lt;0.120)</t>
         </is>
       </c>
       <c r="T51" s="28" t="inlineStr">
@@ -7057,13 +7057,13 @@
         </is>
       </c>
       <c r="L53" s="31" t="n">
-        <v>0.4574924107575877</v>
+        <v>0.479359</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>0.2833979424552279</v>
+        <v>0.271975</v>
       </c>
       <c r="N53" s="31" t="n">
-        <v>0.2591096467871843</v>
+        <v>0.248666</v>
       </c>
       <c r="O53" s="31" t="n">
         <v>0.4283291668066846</v>
@@ -7077,10 +7077,9 @@
       <c r="R53" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="28" t="inlineStr">
-        <is>
-          <t>[PASAR] EV Insuf (0.034&lt;0.080)</t>
-        </is>
+      <c r="S53" s="28">
+        <f>IF(OR(Q53="",R53=""),"[APOSTAR] LOCAL",IF(Q53&gt;R53,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T53" s="28" t="inlineStr">
         <is>
@@ -7088,7 +7087,7 @@
         </is>
       </c>
       <c r="U53" s="32" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="V53" s="32" t="n">
         <v>0</v>
@@ -7167,13 +7166,13 @@
         </is>
       </c>
       <c r="L54" s="31" t="n">
-        <v>0.4012742120202197</v>
+        <v>0.425407</v>
       </c>
       <c r="M54" s="31" t="n">
-        <v>0.2569191123823455</v>
+        <v>0.246563</v>
       </c>
       <c r="N54" s="31" t="n">
-        <v>0.3418066755974347</v>
+        <v>0.328029</v>
       </c>
       <c r="O54" s="31" t="n">
         <v>0.5395525426368118</v>
@@ -7187,9 +7186,10 @@
       <c r="R54" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="S54" s="28">
-        <f>IF(OR(Q54="",R54=""),"[APOSTAR] VISITA",IF(Q54&lt;R54,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S54" s="28" t="inlineStr">
+        <is>
+          <t>[PASAR] Floor Prob (33%&lt;33%)</t>
+        </is>
       </c>
       <c r="T54" s="28" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="U54" s="32" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="V54" s="32" t="n">
         <v>0</v>
@@ -7276,13 +7276,13 @@
         </is>
       </c>
       <c r="L55" s="31" t="n">
-        <v>0.3189858742001957</v>
+        <v>0.306128</v>
       </c>
       <c r="M55" s="31" t="n">
-        <v>0.2610953806422436</v>
+        <v>0.250571</v>
       </c>
       <c r="N55" s="31" t="n">
-        <v>0.4199187451575607</v>
+        <v>0.4433</v>
       </c>
       <c r="O55" s="31" t="n">
         <v>0.5305437527495472</v>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="U55" s="32" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
       <c r="V55" s="32" t="n">
         <v>0</v>
@@ -7385,13 +7385,13 @@
         </is>
       </c>
       <c r="L56" s="31" t="n">
-        <v>0.4376025748268576</v>
+        <v>0.460271</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>0.2237084213430154</v>
+        <v>0.214691</v>
       </c>
       <c r="N56" s="31" t="n">
-        <v>0.3386890038301269</v>
+        <v>0.325037</v>
       </c>
       <c r="O56" s="31" t="n">
         <v>0.7039103277145289</v>
@@ -7405,9 +7405,10 @@
       <c r="R56" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="S56" s="28">
-        <f>IF(OR(Q56="",R56=""),"[APOSTAR] VISITA",IF(Q56&lt;R56,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S56" s="28" t="inlineStr">
+        <is>
+          <t>[PASAR] Floor Prob (33%&lt;33%)</t>
+        </is>
       </c>
       <c r="T56" s="28" t="inlineStr">
         <is>
@@ -7415,7 +7416,7 @@
         </is>
       </c>
       <c r="U56" s="32" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="V56" s="32" t="n">
         <v>0</v>
@@ -7494,13 +7495,13 @@
         </is>
       </c>
       <c r="L57" s="31" t="n">
-        <v>0.4430807149531331</v>
+        <v>0.465529</v>
       </c>
       <c r="M57" s="31" t="n">
-        <v>0.2556007184478316</v>
+        <v>0.245298</v>
       </c>
       <c r="N57" s="31" t="n">
-        <v>0.3013185665990354</v>
+        <v>0.289173</v>
       </c>
       <c r="O57" s="31" t="n">
         <v>0.545657589335549</v>
@@ -7524,7 +7525,7 @@
         </is>
       </c>
       <c r="U57" s="32" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="V57" s="32" t="n">
         <v>0</v>
@@ -7603,13 +7604,13 @@
         </is>
       </c>
       <c r="L58" s="31" t="n">
-        <v>0.4861831714162479</v>
+        <v>0.506894</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>0.2824404306796986</v>
+        <v>0.271056</v>
       </c>
       <c r="N58" s="31" t="n">
-        <v>0.2313763979040536</v>
+        <v>0.22205</v>
       </c>
       <c r="O58" s="31" t="n">
         <v>0.4128232474368506</v>
@@ -7933,13 +7934,13 @@
         </is>
       </c>
       <c r="L61" s="31" t="n">
-        <v>0.4393351422595658</v>
+        <v>0.461934</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>0.2951672271610383</v>
+        <v>0.28327</v>
       </c>
       <c r="N61" s="31" t="n">
-        <v>0.2654976305793959</v>
+        <v>0.254796</v>
       </c>
       <c r="O61" s="31" t="n">
         <v>0.3922601733778666</v>
@@ -8043,13 +8044,13 @@
         </is>
       </c>
       <c r="L62" s="31" t="n">
-        <v>0.4023790642010883</v>
+        <v>0.426467</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>0.3283943712366434</v>
+        <v>0.315158</v>
       </c>
       <c r="N62" s="31" t="n">
-        <v>0.2692265645622682</v>
+        <v>0.258375</v>
       </c>
       <c r="O62" s="31" t="n">
         <v>0.297629510143734</v>
@@ -8063,10 +8064,9 @@
       <c r="R62" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="S62" s="28" t="inlineStr">
-        <is>
-          <t>[PASAR] Riesgo/Beneficio</t>
-        </is>
+      <c r="S62" s="28">
+        <f>IF(OR(Q62="",R62=""),"[APOSTAR] LOCAL",IF(Q62&gt;R62,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T62" s="28" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="U62" s="32" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="V62" s="32" t="n">
         <v>0</v>
@@ -8143,13 +8143,13 @@
         </is>
       </c>
       <c r="L63" s="31" t="n">
-        <v>0.4892737231840647</v>
+        <v>0.50986</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>0.2812480497670363</v>
+        <v>0.269912</v>
       </c>
       <c r="N63" s="31" t="n">
-        <v>0.229478227048899</v>
+        <v>0.220229</v>
       </c>
       <c r="O63" s="31" t="n">
         <v>0.4153291784124106</v>
@@ -8249,13 +8249,13 @@
         </is>
       </c>
       <c r="L64" s="31" t="n">
-        <v>0.4421842316329352</v>
+        <v>0.464668</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>0.2430641665154168</v>
+        <v>0.233267</v>
       </c>
       <c r="N64" s="31" t="n">
-        <v>0.3147516018516479</v>
+        <v>0.302065</v>
       </c>
       <c r="O64" s="31" t="n">
         <v>0.606252855964858</v>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="S64" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (31%&lt;33%)</t>
+          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
         </is>
       </c>
       <c r="T64" s="28" t="inlineStr">
@@ -8469,13 +8469,13 @@
         </is>
       </c>
       <c r="L66" s="31" t="n">
-        <v>0.4935688183854592</v>
+        <v>0.513982</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>0.2220063105095515</v>
+        <v>0.213058</v>
       </c>
       <c r="N66" s="31" t="n">
-        <v>0.2844248711049894</v>
+        <v>0.272961</v>
       </c>
       <c r="O66" s="31" t="n">
         <v>0.6853780312818094</v>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="U66" s="32" t="n">
-        <v>1118.03</v>
+        <v>1020.62</v>
       </c>
       <c r="V66" s="32" t="n">
         <v>0</v>
@@ -8579,13 +8579,13 @@
         </is>
       </c>
       <c r="L67" s="31" t="n">
-        <v>0.4608540743870485</v>
+        <v>0.482585</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>0.2235248432386927</v>
+        <v>0.214515</v>
       </c>
       <c r="N67" s="31" t="n">
-        <v>0.3156210823742588</v>
+        <v>0.302899</v>
       </c>
       <c r="O67" s="31" t="n">
         <v>0.6959966261239385</v>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="U67" s="32" t="n">
-        <v>1118.03</v>
+        <v>1020.62</v>
       </c>
       <c r="V67" s="32" t="n">
         <v>0</v>
@@ -8689,13 +8689,13 @@
         </is>
       </c>
       <c r="L68" s="31" t="n">
-        <v>0.4333422552635994</v>
+        <v>0.456183</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>0.2231545889831509</v>
+        <v>0.21416</v>
       </c>
       <c r="N68" s="31" t="n">
-        <v>0.3435031557532497</v>
+        <v>0.329658</v>
       </c>
       <c r="O68" s="31" t="n">
         <v>0.7078930653966972</v>
@@ -8720,7 +8720,7 @@
         </is>
       </c>
       <c r="U68" s="32" t="n">
-        <v>1118.03</v>
+        <v>1020.62</v>
       </c>
       <c r="V68" s="32" t="n">
         <v>0</v>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="U70" s="32" t="n">
-        <v>1118.03</v>
+        <v>1020.62</v>
       </c>
       <c r="V70" s="32" t="n">
         <v>0</v>
@@ -9019,13 +9019,13 @@
         </is>
       </c>
       <c r="L71" s="31" t="n">
-        <v>0.4556388335045961</v>
+        <v>0.47758</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>0.2381884076160726</v>
+        <v>0.228588</v>
       </c>
       <c r="N71" s="31" t="n">
-        <v>0.3061727588793313</v>
+        <v>0.293832</v>
       </c>
       <c r="O71" s="31" t="n">
         <v>0.6243503202999419</v>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="S71" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.053&lt;0.080)</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="T71" s="28" t="inlineStr">
@@ -9050,7 +9050,7 @@
         </is>
       </c>
       <c r="U71" s="32" t="n">
-        <v>0</v>
+        <v>1020.62</v>
       </c>
       <c r="V71" s="32" t="n">
         <v>0</v>
@@ -9125,13 +9125,13 @@
         </is>
       </c>
       <c r="L72" s="31" t="n">
-        <v>0.4123660693354294</v>
+        <v>0.436052</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>0.2769268981253996</v>
+        <v>0.265765</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>0.310707032539171</v>
+        <v>0.298183</v>
       </c>
       <c r="O72" s="31" t="n">
         <v>0.4754011830978497</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="S72" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (31%&lt;33%)</t>
+          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
         </is>
       </c>
       <c r="T72" s="28" t="inlineStr">
@@ -9231,13 +9231,13 @@
         </is>
       </c>
       <c r="L73" s="31" t="n">
-        <v>0.4180173212402959</v>
+        <v>0.441475</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>0.2584287935552567</v>
+        <v>0.248012</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>0.3235538852044472</v>
+        <v>0.310512</v>
       </c>
       <c r="O73" s="31" t="n">
         <v>0.5544961797151675</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="U75" s="32" t="n">
-        <v>1118.03</v>
+        <v>1020.62</v>
       </c>
       <c r="V75" s="32" t="n">
         <v>0</v>
@@ -9554,13 +9554,13 @@
         </is>
       </c>
       <c r="L76" s="31" t="n">
-        <v>0.4980211699682912</v>
+        <v>0.518254</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>0.2204435404032659</v>
+        <v>0.211558</v>
       </c>
       <c r="N76" s="31" t="n">
-        <v>0.2815352896284428</v>
+        <v>0.270187</v>
       </c>
       <c r="O76" s="31" t="n">
         <v>0.690539118596024</v>
@@ -9660,13 +9660,13 @@
         </is>
       </c>
       <c r="L77" s="31" t="n">
-        <v>0.4193227560980125</v>
+        <v>0.442728</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>0.2344342015090037</v>
+        <v>0.224985</v>
       </c>
       <c r="N77" s="31" t="n">
-        <v>0.3462430423929839</v>
+        <v>0.332287</v>
       </c>
       <c r="O77" s="31" t="n">
         <v>0.6558913692263365</v>
@@ -9770,13 +9770,13 @@
         </is>
       </c>
       <c r="L78" s="31" t="n">
-        <v>0.436572765969433</v>
+        <v>0.459283</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>0.2358819845004429</v>
+        <v>0.226374</v>
       </c>
       <c r="N78" s="31" t="n">
-        <v>0.3275452495301243</v>
+        <v>0.314343</v>
       </c>
       <c r="O78" s="31" t="n">
         <v>0.6437684226844578</v>
@@ -10082,13 +10082,13 @@
         </is>
       </c>
       <c r="L81" s="31" t="n">
-        <v>0.4072242049310042</v>
+        <v>0.431117</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>0.2521504069838092</v>
+        <v>0.241987</v>
       </c>
       <c r="N81" s="31" t="n">
-        <v>0.3406253880851866</v>
+        <v>0.326896</v>
       </c>
       <c r="O81" s="31" t="n">
         <v>0.5860389248216261</v>
@@ -10192,13 +10192,13 @@
         </is>
       </c>
       <c r="L82" s="31" t="n">
-        <v>0.4980211699682912</v>
+        <v>0.518254</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>0.2204435404032659</v>
+        <v>0.211558</v>
       </c>
       <c r="N82" s="31" t="n">
-        <v>0.2815352896284428</v>
+        <v>0.270187</v>
       </c>
       <c r="O82" s="31" t="n">
         <v>0.690539118596024</v>
@@ -10293,13 +10293,13 @@
         </is>
       </c>
       <c r="L83" s="31" t="n">
-        <v>0.4193227560980125</v>
+        <v>0.442728</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>0.2344342015090037</v>
+        <v>0.224985</v>
       </c>
       <c r="N83" s="31" t="n">
-        <v>0.3462430423929839</v>
+        <v>0.332287</v>
       </c>
       <c r="O83" s="31" t="n">
         <v>0.6558913692263365</v>
@@ -10505,13 +10505,13 @@
         </is>
       </c>
       <c r="L85" s="31" t="n">
-        <v>0.4733274581233547</v>
+        <v>0.494556</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>0.2527772286815116</v>
+        <v>0.242589</v>
       </c>
       <c r="N85" s="31" t="n">
-        <v>0.2738953131951335</v>
+        <v>0.262855</v>
       </c>
       <c r="O85" s="31" t="n">
         <v>0.554841106162472</v>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="L86" s="31" t="n">
-        <v>0.4181272829293341</v>
+        <v>0.441581</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>0.2683251740723935</v>
+        <v>0.25751</v>
       </c>
       <c r="N86" s="31" t="n">
-        <v>0.3135475429982724</v>
+        <v>0.300909</v>
       </c>
       <c r="O86" s="31" t="n">
         <v>0.5102846778231006</v>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="S86" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (31%&lt;33%)</t>
+          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
         </is>
       </c>
       <c r="T86" s="28" t="inlineStr">
@@ -10823,13 +10823,13 @@
         </is>
       </c>
       <c r="L88" s="31" t="n">
-        <v>0.4048025257187246</v>
+        <v>0.428793</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>0.2290886482142422</v>
+        <v>0.219855</v>
       </c>
       <c r="N88" s="31" t="n">
-        <v>0.3661088260670332</v>
+        <v>0.351352</v>
       </c>
       <c r="O88" s="31" t="n">
         <v>0.6884717147660365</v>
@@ -10931,13 +10931,13 @@
         </is>
       </c>
       <c r="L89" s="31" t="n">
-        <v>0.3646150875007567</v>
+        <v>0.349919</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>0.2342990114032013</v>
+        <v>0.224855</v>
       </c>
       <c r="N89" s="31" t="n">
-        <v>0.4010859010960421</v>
+        <v>0.425226</v>
       </c>
       <c r="O89" s="31" t="n">
         <v>0.6639022170684276</v>
@@ -11151,13 +11151,13 @@
         </is>
       </c>
       <c r="L91" s="31" t="n">
-        <v>0.4444668243826172</v>
+        <v>0.466859</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>0.2364852258529828</v>
+        <v>0.226953</v>
       </c>
       <c r="N91" s="31" t="n">
-        <v>0.3190479497644</v>
+        <v>0.306188</v>
       </c>
       <c r="O91" s="31" t="n">
         <v>0.642169075997571</v>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="S91" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (32%&lt;33%)</t>
+          <t>[PASAR] EV Insuf (0.055&lt;0.080)</t>
         </is>
       </c>
       <c r="T91" s="28" t="inlineStr">
@@ -11259,13 +11259,13 @@
         </is>
       </c>
       <c r="L92" s="31" t="n">
-        <v>0.4663822486345678</v>
+        <v>0.487891</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>0.2268392065648523</v>
+        <v>0.217696</v>
       </c>
       <c r="N92" s="31" t="n">
-        <v>0.3067785448005799</v>
+        <v>0.294413</v>
       </c>
       <c r="O92" s="31" t="n">
         <v>0.6764492201281175</v>
@@ -11367,13 +11367,13 @@
         </is>
       </c>
       <c r="L93" s="31" t="n">
-        <v>0.4059410718076608</v>
+        <v>0.429886</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>0.229285594582527</v>
+        <v>0.220044</v>
       </c>
       <c r="N93" s="31" t="n">
-        <v>0.3647733336098123</v>
+        <v>0.35007</v>
       </c>
       <c r="O93" s="31" t="n">
         <v>0.6873848456576175</v>
@@ -11475,13 +11475,13 @@
         </is>
       </c>
       <c r="L94" s="31" t="n">
-        <v>0.4656785869538326</v>
+        <v>0.487216</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>0.236059455651217</v>
+        <v>0.226545</v>
       </c>
       <c r="N94" s="31" t="n">
-        <v>0.2982619573949504</v>
+        <v>0.28624</v>
       </c>
       <c r="O94" s="31" t="n">
         <v>0.634300558214799</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="S94" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
+          <t>[PASAR] EV Insuf (0.077&lt;0.080)</t>
         </is>
       </c>
       <c r="T94" s="28" t="inlineStr">
@@ -11567,13 +11567,13 @@
         </is>
       </c>
       <c r="F95" s="29" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G95" s="29" t="n">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="H95" s="29" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="I95" s="29" t="n"/>
       <c r="J95" s="29" t="n"/>
@@ -11583,13 +11583,13 @@
         </is>
       </c>
       <c r="L95" s="31" t="n">
-        <v>0.4615532498272125</v>
+        <v>0.483256</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>0.2364280155192461</v>
+        <v>0.226898</v>
       </c>
       <c r="N95" s="31" t="n">
-        <v>0.3020187346535414</v>
+        <v>0.289845</v>
       </c>
       <c r="O95" s="31" t="n">
         <v>0.6302198486764455</v>
@@ -11601,7 +11601,7 @@
       <c r="R95" s="35" t="n"/>
       <c r="S95" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
+          <t>[PASAR] Floor Prob (29%&lt;33%)</t>
         </is>
       </c>
       <c r="T95" s="28" t="inlineStr">
@@ -11671,10 +11671,10 @@
         </is>
       </c>
       <c r="F96" s="29" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="H96" s="29" t="n">
         <v>2.94</v>
@@ -11691,13 +11691,13 @@
         </is>
       </c>
       <c r="L96" s="31" t="n">
-        <v>0.4215709574982022</v>
+        <v>0.444886</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>0.2397291007375396</v>
+        <v>0.230066</v>
       </c>
       <c r="N96" s="31" t="n">
-        <v>0.3386999417642583</v>
+        <v>0.325048</v>
       </c>
       <c r="O96" s="31" t="n">
         <v>0.6295043800536333</v>
@@ -11778,13 +11778,13 @@
         </is>
       </c>
       <c r="F97" s="29" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="G97" s="29" t="n">
         <v>2.9</v>
       </c>
       <c r="H97" s="29" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="I97" s="29" t="n"/>
       <c r="J97" s="29" t="n"/>
@@ -11881,13 +11881,13 @@
         </is>
       </c>
       <c r="F98" s="29" t="n">
-        <v>2.57</v>
+        <v>2.65</v>
       </c>
       <c r="G98" s="29" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="H98" s="29" t="n">
-        <v>2.99</v>
+        <v>2.87</v>
       </c>
       <c r="I98" s="29" t="n"/>
       <c r="J98" s="29" t="n"/>
@@ -11897,13 +11897,13 @@
         </is>
       </c>
       <c r="L98" s="31" t="n">
-        <v>0.4560615788606749</v>
+        <v>0.477986</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>0.2238717736037344</v>
+        <v>0.214848</v>
       </c>
       <c r="N98" s="31" t="n">
-        <v>0.3200666475355907</v>
+        <v>0.307166</v>
       </c>
       <c r="O98" s="31" t="n">
         <v>0.6963520928617232</v>
@@ -11984,13 +11984,13 @@
         </is>
       </c>
       <c r="F99" s="29" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="H99" s="29" t="n">
-        <v>3.81</v>
+        <v>3.87</v>
       </c>
       <c r="I99" s="29" t="n"/>
       <c r="J99" s="29" t="n"/>
@@ -12000,13 +12000,13 @@
         </is>
       </c>
       <c r="L99" s="31" t="n">
-        <v>0.4519225289005756</v>
+        <v>0.474014</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>0.2697127200793154</v>
+        <v>0.258841</v>
       </c>
       <c r="N99" s="31" t="n">
-        <v>0.2783647510201091</v>
+        <v>0.267145</v>
       </c>
       <c r="O99" s="31" t="n">
         <v>0.4771663073686631</v>
@@ -12018,7 +12018,7 @@
       <c r="R99" s="35" t="n"/>
       <c r="S99" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (28%&lt;33%)</t>
+          <t>[PASAR] EV Insuf (0.033&lt;0.080)</t>
         </is>
       </c>
       <c r="T99" s="28" t="inlineStr">
@@ -12139,7 +12139,7 @@
         </is>
       </c>
       <c r="U100" s="32" t="n">
-        <v>2500</v>
+        <v>1443.38</v>
       </c>
       <c r="V100" s="32" t="n">
         <v>0</v>
@@ -12200,13 +12200,13 @@
         </is>
       </c>
       <c r="F101" s="29" t="n">
-        <v>1.99</v>
+        <v>2.69</v>
       </c>
       <c r="G101" s="29" t="n">
-        <v>3.51</v>
+        <v>2.18</v>
       </c>
       <c r="H101" s="29" t="n">
-        <v>4.03</v>
+        <v>4.38</v>
       </c>
       <c r="I101" s="29" t="n"/>
       <c r="J101" s="29" t="n"/>
@@ -12216,13 +12216,13 @@
         </is>
       </c>
       <c r="L101" s="31" t="n">
-        <v>0.4306682642088859</v>
+        <v>0.453616</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>0.2475750063177246</v>
+        <v>0.237596</v>
       </c>
       <c r="N101" s="31" t="n">
-        <v>0.3217567294733895</v>
+        <v>0.308788</v>
       </c>
       <c r="O101" s="31" t="n">
         <v>0.5933963385823751</v>
@@ -12232,10 +12232,9 @@
       </c>
       <c r="Q101" s="35" t="n"/>
       <c r="R101" s="35" t="n"/>
-      <c r="S101" s="28" t="inlineStr">
-        <is>
-          <t>[PASAR] Floor Prob (32%&lt;33%)</t>
-        </is>
+      <c r="S101" s="28">
+        <f>IF(OR(Q101="",R101=""),"[APOSTAR] LOCAL",IF(Q101&gt;R101,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T101" s="28" t="inlineStr">
         <is>
@@ -12243,7 +12242,7 @@
         </is>
       </c>
       <c r="U101" s="32" t="n">
-        <v>0</v>
+        <v>1443.38</v>
       </c>
       <c r="V101" s="32" t="n">
         <v>0</v>
@@ -12310,7 +12309,7 @@
         <v>4.77</v>
       </c>
       <c r="H102" s="29" t="n">
-        <v>9.81</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="I102" s="29" t="n">
         <v>1.93</v>
@@ -12513,10 +12512,10 @@
         <v>1.62</v>
       </c>
       <c r="G104" s="29" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="H104" s="29" t="n">
-        <v>5.93</v>
+        <v>5.91</v>
       </c>
       <c r="I104" s="29" t="n">
         <v>1.83</v>
@@ -12530,13 +12529,13 @@
         </is>
       </c>
       <c r="L104" s="31" t="n">
-        <v>0.4977670434040495</v>
+        <v>0.518011</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>0.2350263346206427</v>
+        <v>0.225553</v>
       </c>
       <c r="N104" s="31" t="n">
-        <v>0.2672066219753078</v>
+        <v>0.256436</v>
       </c>
       <c r="O104" s="31" t="n">
         <v>0.6141062694228666</v>
@@ -12621,16 +12620,16 @@
         <v>2.12</v>
       </c>
       <c r="G105" s="29" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="H105" s="29" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="I105" s="29" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="K105" s="30" t="inlineStr">
         <is>
@@ -12845,13 +12844,13 @@
         </is>
       </c>
       <c r="L107" s="31" t="n">
-        <v>0.4883799249630442</v>
+        <v>0.509002</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>0.246101930558475</v>
+        <v>0.236182</v>
       </c>
       <c r="N107" s="31" t="n">
-        <v>0.2655181444784808</v>
+        <v>0.254816</v>
       </c>
       <c r="O107" s="31" t="n">
         <v>0.5770269103124676</v>
@@ -12953,13 +12952,13 @@
         </is>
       </c>
       <c r="L108" s="31" t="n">
-        <v>0.4438473121786483</v>
+        <v>0.466264</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>0.2304413243321968</v>
+        <v>0.221153</v>
       </c>
       <c r="N108" s="31" t="n">
-        <v>0.325711363489155</v>
+        <v>0.312583</v>
       </c>
       <c r="O108" s="31" t="n">
         <v>0.6723378196207546</v>
@@ -12975,7 +12974,7 @@
       </c>
       <c r="S108" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.061&lt;0.080)</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="T108" s="28" t="inlineStr">
@@ -12984,7 +12983,7 @@
         </is>
       </c>
       <c r="U108" s="32" t="n">
-        <v>0</v>
+        <v>1443.38</v>
       </c>
       <c r="V108" s="32" t="n">
         <v>0</v>
@@ -13065,13 +13064,13 @@
         </is>
       </c>
       <c r="L109" s="31" t="n">
-        <v>0.4191168527431521</v>
+        <v>0.442531</v>
       </c>
       <c r="M109" s="31" t="n">
-        <v>0.2237751767220289</v>
+        <v>0.214755</v>
       </c>
       <c r="N109" s="31" t="n">
-        <v>0.3571079705348189</v>
+        <v>0.342714</v>
       </c>
       <c r="O109" s="31" t="n">
         <v>0.7081521294456694</v>
@@ -13277,13 +13276,13 @@
         </is>
       </c>
       <c r="L111" s="31" t="n">
-        <v>0.4486757801788941</v>
+        <v>0.470898</v>
       </c>
       <c r="M111" s="31" t="n">
-        <v>0.2371454964032732</v>
+        <v>0.227587</v>
       </c>
       <c r="N111" s="31" t="n">
-        <v>0.3141787234178327</v>
+        <v>0.301515</v>
       </c>
       <c r="O111" s="31" t="n">
         <v>0.6200891137750755</v>
@@ -13364,13 +13363,13 @@
         </is>
       </c>
       <c r="F112" s="29" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="G112" s="29" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="H112" s="29" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="I112" s="29" t="n"/>
       <c r="J112" s="29" t="n"/>
@@ -13398,7 +13397,7 @@
       <c r="R112" s="35" t="n"/>
       <c r="S112" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Riesgo/Beneficio</t>
+          <t>[PASAR] EV Insuf (0.053&lt;0.120)</t>
         </is>
       </c>
       <c r="T112" s="28" t="inlineStr">
@@ -13468,7 +13467,7 @@
         </is>
       </c>
       <c r="F113" s="29" t="n">
-        <v>8.050000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="G113" s="29" t="n">
         <v>6.57</v>
@@ -13484,13 +13483,13 @@
         </is>
       </c>
       <c r="L113" s="31" t="n">
-        <v>0.2685554359060944</v>
+        <v>0.257731</v>
       </c>
       <c r="M113" s="31" t="n">
-        <v>0.2382308588689295</v>
+        <v>0.228628</v>
       </c>
       <c r="N113" s="31" t="n">
-        <v>0.4932137052249761</v>
+        <v>0.513641</v>
       </c>
       <c r="O113" s="31" t="n">
         <v>0.5879103320327207</v>
@@ -13588,13 +13587,13 @@
         </is>
       </c>
       <c r="L114" s="31" t="n">
-        <v>0.4566563276940353</v>
+        <v>0.478557</v>
       </c>
       <c r="M114" s="31" t="n">
-        <v>0.2465314821330628</v>
+        <v>0.236595</v>
       </c>
       <c r="N114" s="31" t="n">
-        <v>0.2968121901729019</v>
+        <v>0.284849</v>
       </c>
       <c r="O114" s="31" t="n">
         <v>0.5692579408856451</v>
@@ -13606,7 +13605,7 @@
       <c r="R114" s="35" t="n"/>
       <c r="S114" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Riesgo/Beneficio</t>
+          <t>[PASAR] EV Insuf (0.038&lt;0.080)</t>
         </is>
       </c>
       <c r="T114" s="28" t="inlineStr">
@@ -13676,13 +13675,13 @@
         </is>
       </c>
       <c r="F115" s="29" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G115" s="29" t="n">
-        <v>4.2</v>
+        <v>4.14</v>
       </c>
       <c r="H115" s="29" t="n">
-        <v>4.68</v>
+        <v>4.49</v>
       </c>
       <c r="I115" s="29" t="n"/>
       <c r="J115" s="29" t="n"/>
@@ -13692,13 +13691,13 @@
         </is>
       </c>
       <c r="L115" s="31" t="n">
-        <v>0.3429638610175831</v>
+        <v>0.32914</v>
       </c>
       <c r="M115" s="31" t="n">
-        <v>0.2489684277026439</v>
+        <v>0.238933</v>
       </c>
       <c r="N115" s="31" t="n">
-        <v>0.408067711279773</v>
+        <v>0.431927</v>
       </c>
       <c r="O115" s="31" t="n">
         <v>0.5752361140664245</v>
@@ -13779,13 +13778,13 @@
         </is>
       </c>
       <c r="F116" s="29" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="G116" s="29" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="H116" s="29" t="n">
-        <v>6.25</v>
+        <v>6.14</v>
       </c>
       <c r="I116" s="29" t="n"/>
       <c r="J116" s="29" t="n"/>
@@ -14007,13 +14006,13 @@
         </is>
       </c>
       <c r="L118" s="31" t="n">
-        <v>0.4192423319145392</v>
+        <v>0.442651</v>
       </c>
       <c r="M118" s="31" t="n">
-        <v>0.2544728671319984</v>
+        <v>0.244216</v>
       </c>
       <c r="N118" s="31" t="n">
-        <v>0.3262848009534624</v>
+        <v>0.313133</v>
       </c>
       <c r="O118" s="31" t="n">
         <v>0.5464765093450419</v>
@@ -14428,13 +14427,13 @@
         </is>
       </c>
       <c r="L122" s="31" t="n">
-        <v>0.4143338364837813</v>
+        <v>0.43794</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>0.2731865517515846</v>
+        <v>0.262175</v>
       </c>
       <c r="N122" s="31" t="n">
-        <v>0.3124796117646341</v>
+        <v>0.299884</v>
       </c>
       <c r="O122" s="31" t="n">
         <v>0.4828233891977304</v>
@@ -14515,9 +14514,15 @@
           <t>Antalyaspor</t>
         </is>
       </c>
-      <c r="F123" s="29" t="n"/>
-      <c r="G123" s="29" t="n"/>
-      <c r="H123" s="29" t="n"/>
+      <c r="F123" s="29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G123" s="29" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="H123" s="29" t="n">
+        <v>9.449999999999999</v>
+      </c>
       <c r="I123" s="29" t="n"/>
       <c r="J123" s="29" t="n"/>
       <c r="K123" s="30" t="inlineStr">
@@ -14544,7 +14549,7 @@
       <c r="R123" s="35" t="n"/>
       <c r="S123" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T123" s="28" t="inlineStr">
@@ -14732,13 +14737,13 @@
         </is>
       </c>
       <c r="L125" s="31" t="n">
-        <v>0.4492776167937391</v>
+        <v>0.471476</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>0.2978974816425914</v>
+        <v>0.28589</v>
       </c>
       <c r="N125" s="31" t="n">
-        <v>0.2528249015636696</v>
+        <v>0.242634</v>
       </c>
       <c r="O125" s="31" t="n">
         <v>0.377017356090305</v>
@@ -14872,7 +14877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15249,7 +15254,7 @@
       </c>
       <c r="B9" s="42" t="inlineStr">
         <is>
-          <t>Banfield vs Tigre</t>
+          <t>Atlético Tucumán vs Gimnasia la Plata</t>
         </is>
       </c>
       <c r="C9" s="41" t="inlineStr">
@@ -15259,42 +15264,40 @@
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
+          <t>[PASAR] EV Insuf (0.041&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="42" t="inlineStr">
+        <is>
           <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
-      <c r="E9" s="43" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F9" s="44" t="inlineStr">
+      <c r="I9" s="43" t="n">
+        <v>1779.49</v>
+      </c>
+      <c r="J9" s="44" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G9" s="45" t="n">
-        <v>2886.76</v>
-      </c>
-      <c r="H9" s="42" t="inlineStr">
-        <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I9" s="43" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J9" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
       <c r="K9" s="45" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L9" s="52" t="n">
-        <v>-2113.24</v>
-      </c>
-      <c r="M9" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+        <v>2064.21</v>
+      </c>
+      <c r="L9" s="49" t="n"/>
+      <c r="M9" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="44" t="inlineStr">
@@ -15311,12 +15314,12 @@
       </c>
       <c r="B10" s="48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion vs Liverpool</t>
+          <t>Banfield vs Tigre</t>
         </is>
       </c>
       <c r="C10" s="47" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D10" s="48" t="inlineStr">
@@ -15325,7 +15328,7 @@
         </is>
       </c>
       <c r="E10" s="49" t="n">
-        <v>2500</v>
+        <v>1443.38</v>
       </c>
       <c r="F10" s="44" t="inlineStr">
         <is>
@@ -15333,7 +15336,7 @@
         </is>
       </c>
       <c r="G10" s="45" t="n">
-        <v>5625</v>
+        <v>2886.76</v>
       </c>
       <c r="H10" s="48" t="inlineStr">
         <is>
@@ -15349,10 +15352,10 @@
         </is>
       </c>
       <c r="K10" s="45" t="n">
-        <v>5625</v>
-      </c>
-      <c r="L10" s="46" t="n">
-        <v>0</v>
+        <v>5000</v>
+      </c>
+      <c r="L10" s="52" t="n">
+        <v>-2113.24</v>
       </c>
       <c r="M10" s="44" t="inlineStr">
         <is>
@@ -15373,12 +15376,12 @@
       </c>
       <c r="B11" s="42" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs Unión (santa Fe)</t>
+          <t>Brighton &amp; Hove Albion vs Liverpool</t>
         </is>
       </c>
       <c r="C11" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
@@ -15387,7 +15390,7 @@
         </is>
       </c>
       <c r="E11" s="43" t="n">
-        <v>1443.38</v>
+        <v>2500</v>
       </c>
       <c r="F11" s="44" t="inlineStr">
         <is>
@@ -15395,7 +15398,7 @@
         </is>
       </c>
       <c r="G11" s="45" t="n">
-        <v>2742.42</v>
+        <v>5625</v>
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
@@ -15411,10 +15414,10 @@
         </is>
       </c>
       <c r="K11" s="45" t="n">
-        <v>4750</v>
-      </c>
-      <c r="L11" s="52" t="n">
-        <v>-2007.58</v>
+        <v>5625</v>
+      </c>
+      <c r="L11" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="44" t="inlineStr">
         <is>
@@ -15435,7 +15438,7 @@
       </c>
       <c r="B12" s="48" t="inlineStr">
         <is>
-          <t>Newell's Old Boys vs Gimnasia (mendoza)</t>
+          <t>Defensa y Justicia vs Unión (santa Fe)</t>
         </is>
       </c>
       <c r="C12" s="47" t="inlineStr">
@@ -15445,47 +15448,47 @@
       </c>
       <c r="D12" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E12" s="49" t="n">
         <v>1443.38</v>
       </c>
-      <c r="F12" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G12" s="52" t="n">
-        <v>-1443.38</v>
+      <c r="F12" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G12" s="45" t="n">
+        <v>2742.42</v>
       </c>
       <c r="H12" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I12" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J12" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K12" s="52" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L12" s="45" t="n">
-        <v>1056.62</v>
-      </c>
-      <c r="M12" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N12" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J12" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K12" s="45" t="n">
+        <v>4750</v>
+      </c>
+      <c r="L12" s="52" t="n">
+        <v>-2007.58</v>
+      </c>
+      <c r="M12" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N12" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -15497,12 +15500,12 @@
       </c>
       <c r="B13" s="42" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino vs Botafogo</t>
+          <t>Newell's Old Boys vs Gimnasia (mendoza)</t>
         </is>
       </c>
       <c r="C13" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D13" s="42" t="inlineStr">
@@ -15511,15 +15514,15 @@
         </is>
       </c>
       <c r="E13" s="43" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F13" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G13" s="45" t="n">
-        <v>6975</v>
+        <v>1443.38</v>
+      </c>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G13" s="52" t="n">
+        <v>-1443.38</v>
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
@@ -15529,25 +15532,25 @@
       <c r="I13" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J13" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K13" s="45" t="n">
-        <v>6975</v>
-      </c>
-      <c r="L13" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N13" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="J13" s="51" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K13" s="52" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L13" s="45" t="n">
+        <v>1056.62</v>
+      </c>
+      <c r="M13" s="51" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N13" s="51" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -15631,27 +15634,27 @@
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (25%&lt;33%)</t>
-        </is>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="n">
+        <v>1308.71</v>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G15" s="45" t="n">
+        <v>1361.06</v>
+      </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I15" s="43" t="n">
-        <v>261.9</v>
+        <v>2266.75</v>
       </c>
       <c r="J15" s="44" t="inlineStr">
         <is>
@@ -15659,12 +15662,14 @@
         </is>
       </c>
       <c r="K15" s="45" t="n">
-        <v>272.38</v>
-      </c>
-      <c r="L15" s="49" t="n"/>
-      <c r="M15" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2357.42</v>
+      </c>
+      <c r="L15" s="52" t="n">
+        <v>-996.36</v>
+      </c>
+      <c r="M15" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="N15" s="44" t="inlineStr">
@@ -15695,7 +15700,7 @@
         </is>
       </c>
       <c r="E16" s="49" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="F16" s="51" t="inlineStr">
         <is>
@@ -15703,7 +15708,7 @@
         </is>
       </c>
       <c r="G16" s="52" t="n">
-        <v>-1250</v>
+        <v>-1443.38</v>
       </c>
       <c r="H16" s="48" t="inlineStr">
         <is>
@@ -15722,7 +15727,7 @@
         <v>-2500</v>
       </c>
       <c r="L16" s="45" t="n">
-        <v>1250</v>
+        <v>1056.62</v>
       </c>
       <c r="M16" s="51" t="inlineStr">
         <is>
@@ -15757,7 +15762,7 @@
         </is>
       </c>
       <c r="E17" s="43" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="F17" s="44" t="inlineStr">
         <is>
@@ -15765,7 +15770,7 @@
         </is>
       </c>
       <c r="G17" s="45" t="n">
-        <v>3362.5</v>
+        <v>3882.69</v>
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
@@ -15784,7 +15789,7 @@
         <v>6725</v>
       </c>
       <c r="L17" s="52" t="n">
-        <v>-3362.5</v>
+        <v>-2842.31</v>
       </c>
       <c r="M17" s="44" t="inlineStr">
         <is>
@@ -15819,7 +15824,7 @@
         </is>
       </c>
       <c r="E18" s="49" t="n">
-        <v>1767.77</v>
+        <v>2500</v>
       </c>
       <c r="F18" s="51" t="inlineStr">
         <is>
@@ -15827,7 +15832,7 @@
         </is>
       </c>
       <c r="G18" s="52" t="n">
-        <v>-1767.77</v>
+        <v>-2500</v>
       </c>
       <c r="H18" s="48" t="inlineStr">
         <is>
@@ -15845,8 +15850,8 @@
       <c r="K18" s="52" t="n">
         <v>-2500</v>
       </c>
-      <c r="L18" s="45" t="n">
-        <v>732.23</v>
+      <c r="L18" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="51" t="inlineStr">
         <is>
@@ -15877,7 +15882,7 @@
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.098&lt;0.120)</t>
+          <t>[PASAR] EV Insuf (0.054&lt;0.120)</t>
         </is>
       </c>
       <c r="E19" s="43" t="inlineStr">
@@ -15897,7 +15902,7 @@
         </is>
       </c>
       <c r="I19" s="43" t="n">
-        <v>2289.23</v>
+        <v>1259.61</v>
       </c>
       <c r="J19" s="44" t="inlineStr">
         <is>
@@ -15905,7 +15910,7 @@
         </is>
       </c>
       <c r="K19" s="45" t="n">
-        <v>4921.84</v>
+        <v>2708.16</v>
       </c>
       <c r="L19" s="49" t="n"/>
       <c r="M19" s="41" t="inlineStr">
@@ -15937,27 +15942,27 @@
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.034&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="E20" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F20" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G20" s="45" t="n">
+        <v>3150</v>
+      </c>
       <c r="H20" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I20" s="49" t="n">
-        <v>1346.54</v>
+        <v>2500</v>
       </c>
       <c r="J20" s="44" t="inlineStr">
         <is>
@@ -15965,12 +15970,14 @@
         </is>
       </c>
       <c r="K20" s="45" t="n">
-        <v>1696.64</v>
-      </c>
-      <c r="L20" s="49" t="n"/>
-      <c r="M20" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3150</v>
+      </c>
+      <c r="L20" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="N20" s="44" t="inlineStr">
@@ -15987,12 +15994,12 @@
       </c>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>Sk Brann vs Tromso</t>
+          <t>Tottenham Hotspur vs Nottingham Forest</t>
         </is>
       </c>
       <c r="C21" s="41" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D21" s="42" t="inlineStr">
@@ -16001,7 +16008,7 @@
         </is>
       </c>
       <c r="E21" s="43" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
       <c r="F21" s="44" t="inlineStr">
         <is>
@@ -16009,7 +16016,7 @@
         </is>
       </c>
       <c r="G21" s="45" t="n">
-        <v>4242.65</v>
+        <v>3464.11</v>
       </c>
       <c r="H21" s="42" t="inlineStr">
         <is>
@@ -16028,7 +16035,7 @@
         <v>6000</v>
       </c>
       <c r="L21" s="52" t="n">
-        <v>-1757.35</v>
+        <v>-2535.89</v>
       </c>
       <c r="M21" s="44" t="inlineStr">
         <is>
@@ -16049,21 +16056,21 @@
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur vs Nottingham Forest</t>
+          <t>Vitória vs Mirassol</t>
         </is>
       </c>
       <c r="C22" s="47" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E22" s="49" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
       <c r="F22" s="44" t="inlineStr">
         <is>
@@ -16071,11 +16078,11 @@
         </is>
       </c>
       <c r="G22" s="45" t="n">
-        <v>4242.65</v>
+        <v>2237.24</v>
       </c>
       <c r="H22" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I22" s="49" t="n">
@@ -16087,10 +16094,10 @@
         </is>
       </c>
       <c r="K22" s="45" t="n">
-        <v>6000</v>
+        <v>3875</v>
       </c>
       <c r="L22" s="52" t="n">
-        <v>-1757.35</v>
+        <v>-1637.76</v>
       </c>
       <c r="M22" s="44" t="inlineStr">
         <is>
@@ -16106,26 +16113,26 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="41" t="inlineStr">
         <is>
-          <t>22/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>Vasco da Gama vs Grêmio</t>
+          <t>Deportivo Riestra vs San Lorenzo</t>
         </is>
       </c>
       <c r="C23" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D23" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E23" s="43" t="n">
-        <v>1250</v>
+        <v>2500</v>
       </c>
       <c r="F23" s="51" t="inlineStr">
         <is>
@@ -16133,11 +16140,11 @@
         </is>
       </c>
       <c r="G23" s="52" t="n">
-        <v>-1250</v>
+        <v>-2500</v>
       </c>
       <c r="H23" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I23" s="43" t="n">
@@ -16151,8 +16158,8 @@
       <c r="K23" s="52" t="n">
         <v>-2500</v>
       </c>
-      <c r="L23" s="45" t="n">
-        <v>1250</v>
+      <c r="L23" s="46" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="51" t="inlineStr">
         <is>
@@ -16168,12 +16175,12 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="47" t="inlineStr">
         <is>
-          <t>22/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Vitória vs Mirassol</t>
+          <t>Bahia vs Athletico Paranaense</t>
         </is>
       </c>
       <c r="C24" s="47" t="inlineStr">
@@ -16183,20 +16190,20 @@
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F24" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G24" s="45" t="n">
-        <v>1937.5</v>
-      </c>
+          <t>[GANADA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="49" t="n"/>
       <c r="H24" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16211,14 +16218,12 @@
         </is>
       </c>
       <c r="K24" s="45" t="n">
-        <v>3875</v>
-      </c>
-      <c r="L24" s="52" t="n">
-        <v>-1937.5</v>
-      </c>
-      <c r="M24" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+        <v>8900</v>
+      </c>
+      <c r="L24" s="49" t="n"/>
+      <c r="M24" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="44" t="inlineStr">
@@ -16235,7 +16240,7 @@
       </c>
       <c r="B25" s="42" t="inlineStr">
         <is>
-          <t>Bahia vs Athletico Paranaense</t>
+          <t>Botafogo vs Mirassol</t>
         </is>
       </c>
       <c r="C25" s="41" t="inlineStr">
@@ -16273,7 +16278,7 @@
         </is>
       </c>
       <c r="K25" s="45" t="n">
-        <v>8900</v>
+        <v>3775</v>
       </c>
       <c r="L25" s="49" t="n"/>
       <c r="M25" s="41" t="inlineStr">
@@ -16295,7 +16300,7 @@
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Botafogo vs Mirassol</t>
+          <t>Coritiba vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C26" s="47" t="inlineStr">
@@ -16305,7 +16310,7 @@
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E26" s="49" t="inlineStr">
@@ -16327,13 +16332,13 @@
       <c r="I26" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J26" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K26" s="45" t="n">
-        <v>3775</v>
+      <c r="J26" s="51" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K26" s="52" t="n">
+        <v>-2500</v>
       </c>
       <c r="L26" s="49" t="n"/>
       <c r="M26" s="47" t="inlineStr">
@@ -16341,9 +16346,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N26" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16360,7 @@
       </c>
       <c r="B27" s="42" t="inlineStr">
         <is>
-          <t>Coritiba vs Vasco da Gama</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
@@ -16365,7 +16370,7 @@
       </c>
       <c r="D27" s="42" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E27" s="43" t="inlineStr">
@@ -16387,13 +16392,13 @@
       <c r="I27" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J27" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K27" s="52" t="n">
-        <v>-2500</v>
+      <c r="J27" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K27" s="45" t="n">
+        <v>12075</v>
       </c>
       <c r="L27" s="49" t="n"/>
       <c r="M27" s="41" t="inlineStr">
@@ -16401,9 +16406,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N27" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N27" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -16415,7 +16420,7 @@
       </c>
       <c r="B28" s="48" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Internacional vs São Paulo</t>
         </is>
       </c>
       <c r="C28" s="47" t="inlineStr">
@@ -16425,7 +16430,7 @@
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E28" s="49" t="inlineStr">
@@ -16447,13 +16452,13 @@
       <c r="I28" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J28" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K28" s="45" t="n">
-        <v>12075</v>
+      <c r="J28" s="51" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K28" s="52" t="n">
+        <v>-2500</v>
       </c>
       <c r="L28" s="49" t="n"/>
       <c r="M28" s="47" t="inlineStr">
@@ -16461,31 +16466,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N28" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N28" s="51" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B29" s="42" t="inlineStr">
         <is>
-          <t>Internacional vs São Paulo</t>
+          <t>Barracas Central vs Sarmiento (junin)</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D29" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.053&lt;0.080)</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E29" s="43" t="inlineStr">
@@ -16505,7 +16510,7 @@
         </is>
       </c>
       <c r="I29" s="43" t="n">
-        <v>2004.8</v>
+        <v>2500</v>
       </c>
       <c r="J29" s="51" t="inlineStr">
         <is>
@@ -16513,7 +16518,7 @@
         </is>
       </c>
       <c r="K29" s="52" t="n">
-        <v>-2004.8</v>
+        <v>-2500</v>
       </c>
       <c r="L29" s="49" t="n"/>
       <c r="M29" s="41" t="inlineStr">
@@ -16530,35 +16535,35 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="47" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B30" s="48" t="inlineStr">
         <is>
-          <t>Barracas Central vs Sarmiento (junin)</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C30" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="n">
+        <v>1020.62</v>
+      </c>
+      <c r="F30" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G30" s="45" t="n">
+        <v>4929.59</v>
+      </c>
       <c r="H30" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16567,35 +16572,37 @@
       <c r="I30" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J30" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K30" s="52" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L30" s="49" t="n"/>
-      <c r="M30" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N30" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J30" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K30" s="45" t="n">
+        <v>12075</v>
+      </c>
+      <c r="L30" s="52" t="n">
+        <v>-7145.41</v>
+      </c>
+      <c r="M30" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N30" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B31" s="42" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Palmeiras vs Grêmio</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
@@ -16605,20 +16612,20 @@
       </c>
       <c r="D31" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="n">
-        <v>1118.03</v>
-      </c>
-      <c r="F31" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G31" s="45" t="n">
-        <v>5400.08</v>
-      </c>
+          <t>[GANADA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E31" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" s="49" t="n"/>
       <c r="H31" s="42" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16633,14 +16640,12 @@
         </is>
       </c>
       <c r="K31" s="45" t="n">
-        <v>12075</v>
-      </c>
-      <c r="L31" s="52" t="n">
-        <v>-6674.92</v>
-      </c>
-      <c r="M31" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+        <v>12575</v>
+      </c>
+      <c r="L31" s="49" t="n"/>
+      <c r="M31" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="44" t="inlineStr">
@@ -16657,7 +16662,7 @@
       </c>
       <c r="B32" s="48" t="inlineStr">
         <is>
-          <t>Palmeiras vs Grêmio</t>
+          <t>Red Bull Bragantino vs Flamengo</t>
         </is>
       </c>
       <c r="C32" s="47" t="inlineStr">
@@ -16695,7 +16700,7 @@
         </is>
       </c>
       <c r="K32" s="45" t="n">
-        <v>12575</v>
+        <v>8550</v>
       </c>
       <c r="L32" s="49" t="n"/>
       <c r="M32" s="47" t="inlineStr">
@@ -16717,7 +16722,7 @@
       </c>
       <c r="B33" s="42" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino vs Flamengo</t>
+          <t>Santos vs Remo</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
@@ -16755,7 +16760,7 @@
         </is>
       </c>
       <c r="K33" s="45" t="n">
-        <v>8550</v>
+        <v>12625</v>
       </c>
       <c r="L33" s="49" t="n"/>
       <c r="M33" s="41" t="inlineStr">
@@ -16772,17 +16777,17 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="47" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B34" s="48" t="inlineStr">
         <is>
-          <t>Santos vs Remo</t>
+          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
         </is>
       </c>
       <c r="C34" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D34" s="48" t="inlineStr">
@@ -16815,7 +16820,7 @@
         </is>
       </c>
       <c r="K34" s="45" t="n">
-        <v>12625</v>
+        <v>7750</v>
       </c>
       <c r="L34" s="49" t="n"/>
       <c r="M34" s="47" t="inlineStr">
@@ -16832,35 +16837,35 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="41" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B35" s="42" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
+          <t>Palmeiras vs Gremio</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D35" s="42" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E35" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F35" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G35" s="45" t="n">
+        <v>6900</v>
+      </c>
       <c r="H35" s="42" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16875,12 +16880,14 @@
         </is>
       </c>
       <c r="K35" s="45" t="n">
-        <v>7750</v>
-      </c>
-      <c r="L35" s="49" t="n"/>
-      <c r="M35" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13800</v>
+      </c>
+      <c r="L35" s="52" t="n">
+        <v>-6900</v>
+      </c>
+      <c r="M35" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="N35" s="44" t="inlineStr">
@@ -16892,35 +16899,35 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="47" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B36" s="48" t="inlineStr">
         <is>
-          <t>Palmeiras vs Gremio</t>
+          <t>Genclerbirligi vs Goztepe</t>
         </is>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E36" s="49" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F36" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G36" s="45" t="n">
-        <v>6900</v>
-      </c>
+          <t>[PERDIDA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="49" t="n"/>
       <c r="H36" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16929,25 +16936,23 @@
       <c r="I36" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J36" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K36" s="45" t="n">
-        <v>13800</v>
-      </c>
-      <c r="L36" s="52" t="n">
-        <v>-6900</v>
-      </c>
-      <c r="M36" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N36" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="J36" s="51" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K36" s="52" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L36" s="49" t="n"/>
+      <c r="M36" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="51" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -16959,17 +16964,17 @@
       </c>
       <c r="B37" s="42" t="inlineStr">
         <is>
-          <t>Genclerbirligi vs Goztepe</t>
+          <t>Independiente vs Racing Club</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D37" s="42" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E37" s="43" t="inlineStr">
@@ -16991,13 +16996,13 @@
       <c r="I37" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J37" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K37" s="52" t="n">
-        <v>-2500</v>
+      <c r="J37" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K37" s="45" t="n">
+        <v>11575</v>
       </c>
       <c r="L37" s="49" t="n"/>
       <c r="M37" s="41" t="inlineStr">
@@ -17005,9 +17010,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N37" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N37" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -17019,17 +17024,17 @@
       </c>
       <c r="B38" s="48" t="inlineStr">
         <is>
-          <t>Independiente vs Racing Club</t>
+          <t>Kasimpasa vs Kayserispor</t>
         </is>
       </c>
       <c r="C38" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.055&lt;0.080)</t>
         </is>
       </c>
       <c r="E38" s="49" t="inlineStr">
@@ -17049,7 +17054,7 @@
         </is>
       </c>
       <c r="I38" s="49" t="n">
-        <v>2500</v>
+        <v>2186.56</v>
       </c>
       <c r="J38" s="44" t="inlineStr">
         <is>
@@ -17057,7 +17062,7 @@
         </is>
       </c>
       <c r="K38" s="45" t="n">
-        <v>11575</v>
+        <v>2755.07</v>
       </c>
       <c r="L38" s="49" t="n"/>
       <c r="M38" s="47" t="inlineStr">
@@ -17079,7 +17084,7 @@
       </c>
       <c r="B39" s="42" t="inlineStr">
         <is>
-          <t>Kasimpasa vs Kayserispor</t>
+          <t>Trabzonspor vs Galatasaray</t>
         </is>
       </c>
       <c r="C39" s="41" t="inlineStr">
@@ -17089,7 +17094,7 @@
       </c>
       <c r="D39" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (32%&lt;33%)</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E39" s="43" t="inlineStr">
@@ -17109,7 +17114,7 @@
         </is>
       </c>
       <c r="I39" s="43" t="n">
-        <v>178.37</v>
+        <v>2500</v>
       </c>
       <c r="J39" s="44" t="inlineStr">
         <is>
@@ -17117,7 +17122,7 @@
         </is>
       </c>
       <c r="K39" s="45" t="n">
-        <v>224.75</v>
+        <v>6050</v>
       </c>
       <c r="L39" s="49" t="n"/>
       <c r="M39" s="41" t="inlineStr">
@@ -17134,12 +17139,12 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="47" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B40" s="48" t="inlineStr">
         <is>
-          <t>Trabzonspor vs Galatasaray</t>
+          <t>Antalyaspor vs Eyupspor</t>
         </is>
       </c>
       <c r="C40" s="47" t="inlineStr">
@@ -17149,7 +17154,7 @@
       </c>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.077&lt;0.080)</t>
         </is>
       </c>
       <c r="E40" s="49" t="inlineStr">
@@ -17177,7 +17182,7 @@
         </is>
       </c>
       <c r="K40" s="45" t="n">
-        <v>6050</v>
+        <v>3025</v>
       </c>
       <c r="L40" s="49" t="n"/>
       <c r="M40" s="47" t="inlineStr">
@@ -17199,27 +17204,25 @@
       </c>
       <c r="B41" s="42" t="inlineStr">
         <is>
-          <t>Antalyaspor vs Eyupspor</t>
+          <t>Bahia vs Palmeiras</t>
         </is>
       </c>
       <c r="C41" s="41" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D41" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (30%&lt;33%)</t>
-        </is>
-      </c>
-      <c r="E41" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F41" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F41" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="G41" s="49" t="n"/>
@@ -17229,25 +17232,23 @@
         </is>
       </c>
       <c r="I41" s="43" t="n">
-        <v>1204.53</v>
-      </c>
-      <c r="J41" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K41" s="45" t="n">
-        <v>1457.48</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="J41" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K41" s="49" t="n"/>
       <c r="L41" s="49" t="n"/>
       <c r="M41" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N41" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N41" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17259,12 +17260,12 @@
       </c>
       <c r="B42" s="48" t="inlineStr">
         <is>
-          <t>Bahia vs Palmeiras</t>
+          <t>Central Córdoba (santiago del Estero) vs Newell's Old Boys</t>
         </is>
       </c>
       <c r="C42" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D42" s="48" t="inlineStr">
@@ -17273,7 +17274,7 @@
         </is>
       </c>
       <c r="E42" s="49" t="n">
-        <v>1443.38</v>
+        <v>2500</v>
       </c>
       <c r="F42" s="50" t="inlineStr">
         <is>
@@ -17315,12 +17316,12 @@
       </c>
       <c r="B43" s="42" t="inlineStr">
         <is>
-          <t>Central Córdoba (santiago del Estero) vs Newell's Old Boys</t>
+          <t>Chapecoense vs Vitoria</t>
         </is>
       </c>
       <c r="C43" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D43" s="42" t="inlineStr">
@@ -17329,7 +17330,7 @@
         </is>
       </c>
       <c r="E43" s="43" t="n">
-        <v>2500</v>
+        <v>1443.38</v>
       </c>
       <c r="F43" s="50" t="inlineStr">
         <is>
@@ -17371,7 +17372,7 @@
       </c>
       <c r="B44" s="48" t="inlineStr">
         <is>
-          <t>Chapecoense vs Vitoria</t>
+          <t>Corinthians vs Internacional</t>
         </is>
       </c>
       <c r="C44" s="47" t="inlineStr">
@@ -17381,11 +17382,13 @@
       </c>
       <c r="D44" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E44" s="49" t="n">
-        <v>1443.38</v>
+          <t>[PASAR] EV Insuf (0.033&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E44" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" s="50" t="inlineStr">
         <is>
@@ -17399,7 +17402,7 @@
         </is>
       </c>
       <c r="I44" s="49" t="n">
-        <v>2500</v>
+        <v>1413.16</v>
       </c>
       <c r="J44" s="50" t="inlineStr">
         <is>
@@ -17487,12 +17490,12 @@
       </c>
       <c r="B46" s="48" t="inlineStr">
         <is>
-          <t>Mirassol vs Red Bull Bragantino</t>
+          <t>Fenerbahce vs Besiktas</t>
         </is>
       </c>
       <c r="C46" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D46" s="48" t="inlineStr">
@@ -17543,27 +17546,25 @@
       </c>
       <c r="B47" s="42" t="inlineStr">
         <is>
-          <t>Samsunspor vs Konyaspor</t>
+          <t>Mirassol vs Red Bull Bragantino</t>
         </is>
       </c>
       <c r="C47" s="41" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D47" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.061&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="E47" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F47" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F47" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="G47" s="49" t="n"/>
@@ -17573,47 +17574,45 @@
         </is>
       </c>
       <c r="I47" s="43" t="n">
-        <v>2186.87</v>
-      </c>
-      <c r="J47" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K47" s="52" t="n">
-        <v>-2186.87</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="J47" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K47" s="49" t="n"/>
       <c r="L47" s="49" t="n"/>
       <c r="M47" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N47" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N47" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="47" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B48" s="48" t="inlineStr">
         <is>
-          <t>Vasco da Gama vs Botafogo</t>
+          <t>Samsunspor vs Konyaspor</t>
         </is>
       </c>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E48" s="49" t="inlineStr">
@@ -17629,19 +17628,19 @@
       <c r="G48" s="49" t="n"/>
       <c r="H48" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I48" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J48" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K48" s="45" t="n">
-        <v>7200</v>
+      <c r="J48" s="51" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K48" s="52" t="n">
+        <v>-2500</v>
       </c>
       <c r="L48" s="49" t="n"/>
       <c r="M48" s="47" t="inlineStr">
@@ -17649,65 +17648,69 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N48" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N48" s="51" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="41" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B49" s="42" t="inlineStr">
         <is>
-          <t>Hamkam vs Sk Brann</t>
+          <t>Vasco da Gama vs Botafogo</t>
         </is>
       </c>
       <c r="C49" s="41" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D49" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E49" s="43" t="n">
-        <v>1767.77</v>
-      </c>
-      <c r="F49" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] VISITA</t>
+        </is>
+      </c>
+      <c r="E49" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G49" s="49" t="n"/>
       <c r="H49" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I49" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J49" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K49" s="49" t="n"/>
+      <c r="J49" s="44" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K49" s="45" t="n">
+        <v>7200</v>
+      </c>
       <c r="L49" s="49" t="n"/>
       <c r="M49" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N49" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N49" s="44" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -17719,7 +17722,7 @@
       </c>
       <c r="B50" s="48" t="inlineStr">
         <is>
-          <t>Sarpsborg fk vs Ik Start</t>
+          <t>Hamkam vs Sk Brann</t>
         </is>
       </c>
       <c r="C50" s="47" t="inlineStr">
@@ -17729,7 +17732,7 @@
       </c>
       <c r="D50" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E50" s="49" t="n">
@@ -17743,7 +17746,7 @@
       <c r="G50" s="49" t="n"/>
       <c r="H50" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I50" s="49" t="n">
@@ -17770,26 +17773,28 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="41" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B51" s="42" t="inlineStr">
         <is>
-          <t>Aalesund vs Fredrikstad</t>
+          <t>Kocaelispor vs Istanbul Basaksehir</t>
         </is>
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D51" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E51" s="43" t="n">
-        <v>1767.77</v>
+          <t>[PASAR] EV Insuf (0.053&lt;0.120)</t>
+        </is>
+      </c>
+      <c r="E51" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F51" s="50" t="inlineStr">
         <is>
@@ -17803,7 +17808,7 @@
         </is>
       </c>
       <c r="I51" s="43" t="n">
-        <v>2500</v>
+        <v>1234.52</v>
       </c>
       <c r="J51" s="50" t="inlineStr">
         <is>
@@ -17826,26 +17831,28 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="47" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B52" s="48" t="inlineStr">
         <is>
-          <t>Goztepe vs Galatasaray</t>
+          <t>Molde vs Lillestrom</t>
         </is>
       </c>
       <c r="C52" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D52" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E52" s="49" t="n">
-        <v>2500</v>
+          <t>[PASAR] EV Insuf (0.038&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E52" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F52" s="50" t="inlineStr">
         <is>
@@ -17859,7 +17866,7 @@
         </is>
       </c>
       <c r="I52" s="49" t="n">
-        <v>2500</v>
+        <v>1643.96</v>
       </c>
       <c r="J52" s="50" t="inlineStr">
         <is>
@@ -17879,124 +17886,220 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="53" t="inlineStr">
+    <row r="53" ht="16" customHeight="1">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="42" t="inlineStr">
+        <is>
+          <t>Sarpsborg fk vs Ik Start</t>
+        </is>
+      </c>
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="D53" s="42" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E53" s="43" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F53" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G53" s="49" t="n"/>
+      <c r="H53" s="42" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I53" s="43" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J53" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K53" s="49" t="n"/>
+      <c r="L53" s="49" t="n"/>
+      <c r="M53" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="47" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="48" t="inlineStr">
+        <is>
+          <t>Aalesund vs Fredrikstad</t>
+        </is>
+      </c>
+      <c r="C54" s="47" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="D54" s="48" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E54" s="49" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F54" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G54" s="49" t="n"/>
+      <c r="H54" s="48" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I54" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J54" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K54" s="49" t="n"/>
+      <c r="L54" s="49" t="n"/>
+      <c r="M54" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="42" t="inlineStr">
+        <is>
+          <t>Goztepe vs Galatasaray</t>
+        </is>
+      </c>
+      <c r="C55" s="41" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="D55" s="42" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E55" s="43" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F55" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G55" s="49" t="n"/>
+      <c r="H55" s="42" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I55" s="43" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J55" s="50" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K55" s="49" t="n"/>
+      <c r="L55" s="49" t="n"/>
+      <c r="M55" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="53" t="inlineStr">
         <is>
           <t>RESUMEN COMPARATIVO DE RENDIMIENTO</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="37" t="inlineStr">
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B55" s="38" t="inlineStr">
+      <c r="B58" s="38" t="inlineStr">
         <is>
           <t>Opcion 1 (Activa)</t>
         </is>
       </c>
-      <c r="D55" s="39" t="inlineStr">
+      <c r="D58" s="39" t="inlineStr">
         <is>
           <t>Opcion 4 (Shadow)</t>
         </is>
       </c>
-      <c r="F55" s="40" t="inlineStr">
+      <c r="F58" s="40" t="inlineStr">
         <is>
           <t>Mejor</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="17" customHeight="1">
-      <c r="A56" s="54" t="inlineStr">
-        <is>
-          <t>N apuestas liquidadas</t>
-        </is>
-      </c>
-      <c r="B56" s="55" t="n">
-        <v>18</v>
-      </c>
-      <c r="C56" s="55" t="n">
-        <v>18</v>
-      </c>
-      <c r="D56" s="55" t="n">
-        <v>39</v>
-      </c>
-      <c r="E56" s="55" t="n">
-        <v>39</v>
-      </c>
-      <c r="F56" s="56" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="17" customHeight="1">
-      <c r="A57" s="54" t="inlineStr">
-        <is>
-          <t>Ganadas</t>
-        </is>
-      </c>
-      <c r="B57" s="57" t="n">
-        <v>13</v>
-      </c>
-      <c r="C57" s="57" t="n">
-        <v>13</v>
-      </c>
-      <c r="D57" s="58" t="n">
-        <v>29</v>
-      </c>
-      <c r="E57" s="58" t="n">
-        <v>29</v>
-      </c>
-      <c r="F57" s="59" t="inlineStr">
-        <is>
-          <t>Op4</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="54" t="inlineStr">
-        <is>
-          <t>Hit rate</t>
-        </is>
-      </c>
-      <c r="B58" s="60" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="C58" s="60" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="D58" s="61" t="n">
-        <v>0.7435897435897436</v>
-      </c>
-      <c r="E58" s="61" t="n">
-        <v>0.7435897435897436</v>
-      </c>
-      <c r="F58" s="59" t="inlineStr">
-        <is>
-          <t>Op4</t>
         </is>
       </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="54" t="inlineStr">
         <is>
-          <t>Volumen apostado</t>
-        </is>
-      </c>
-      <c r="B59" s="46" t="n">
-        <v>32001.48</v>
-      </c>
-      <c r="C59" s="46" t="n">
-        <v>32001.48</v>
-      </c>
-      <c r="D59" s="46" t="n">
-        <v>89472.23999999999</v>
-      </c>
-      <c r="E59" s="46" t="n">
-        <v>89472.23999999999</v>
+          <t>N apuestas liquidadas</t>
+        </is>
+      </c>
+      <c r="B59" s="55" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" s="55" t="n">
+        <v>18</v>
+      </c>
+      <c r="D59" s="55" t="n">
+        <v>38</v>
+      </c>
+      <c r="E59" s="55" t="n">
+        <v>38</v>
       </c>
       <c r="F59" s="56" t="inlineStr">
         <is>
@@ -18007,20 +18110,20 @@
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="54" t="inlineStr">
         <is>
-          <t>P/L neto</t>
-        </is>
-      </c>
-      <c r="B60" s="52" t="n">
-        <v>49853.41</v>
-      </c>
-      <c r="C60" s="52" t="n">
-        <v>49853.41</v>
-      </c>
-      <c r="D60" s="45" t="n">
-        <v>165706.42</v>
-      </c>
-      <c r="E60" s="45" t="n">
-        <v>165706.42</v>
+          <t>Ganadas</t>
+        </is>
+      </c>
+      <c r="B60" s="57" t="n">
+        <v>13</v>
+      </c>
+      <c r="C60" s="57" t="n">
+        <v>13</v>
+      </c>
+      <c r="D60" s="58" t="n">
+        <v>28</v>
+      </c>
+      <c r="E60" s="58" t="n">
+        <v>28</v>
       </c>
       <c r="F60" s="59" t="inlineStr">
         <is>
@@ -18031,29 +18134,101 @@
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="54" t="inlineStr">
         <is>
+          <t>Hit rate</t>
+        </is>
+      </c>
+      <c r="B61" s="60" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="C61" s="60" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="D61" s="61" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="E61" s="61" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="F61" s="59" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="54" t="inlineStr">
+        <is>
+          <t>Volumen apostado</t>
+        </is>
+      </c>
+      <c r="B62" s="46" t="n">
+        <v>33682.99000000001</v>
+      </c>
+      <c r="C62" s="46" t="n">
+        <v>33682.99000000001</v>
+      </c>
+      <c r="D62" s="46" t="n">
+        <v>92492.41</v>
+      </c>
+      <c r="E62" s="46" t="n">
+        <v>92492.41</v>
+      </c>
+      <c r="F62" s="56" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="54" t="inlineStr">
+        <is>
+          <t>P/L neto</t>
+        </is>
+      </c>
+      <c r="B63" s="52" t="n">
+        <v>40542.11</v>
+      </c>
+      <c r="C63" s="52" t="n">
+        <v>40542.11</v>
+      </c>
+      <c r="D63" s="45" t="n">
+        <v>159409.86</v>
+      </c>
+      <c r="E63" s="45" t="n">
+        <v>159409.86</v>
+      </c>
+      <c r="F63" s="59" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="17" customHeight="1">
+      <c r="A64" s="54" t="inlineStr">
+        <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="B61" s="60" t="n">
-        <v>1.557847012075692</v>
-      </c>
-      <c r="C61" s="60" t="n">
-        <v>1.557847012075692</v>
-      </c>
-      <c r="D61" s="61" t="n">
-        <v>1.852042823561811</v>
-      </c>
-      <c r="E61" s="61" t="n">
-        <v>1.852042823561811</v>
-      </c>
-      <c r="F61" s="59" t="inlineStr">
+      <c r="B64" s="60" t="n">
+        <v>1.203637503677672</v>
+      </c>
+      <c r="C64" s="60" t="n">
+        <v>1.203637503677672</v>
+      </c>
+      <c r="D64" s="61" t="n">
+        <v>1.723491257282624</v>
+      </c>
+      <c r="E64" s="61" t="n">
+        <v>1.723491257282624</v>
+      </c>
+      <c r="F64" s="59" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="62" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="62" t="inlineStr">
         <is>
           <t>Verde = celda ganadora en ese KPI / partido   |   Rojo = celda perdedora   |   Amarillo en Resultado = pendiente de liquidar   |   Op1 activa desde V4.3: empates bloqueados + xG Margen O/U + Camino 2B (desacuerdo) + Camino 3 (alta conv.)</t>
         </is>
@@ -18064,10 +18239,10 @@
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A54:N54"/>
+    <mergeCell ref="A57:N57"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A63:N63"/>
     <mergeCell ref="L3:N3"/>
+    <mergeCell ref="A66:N66"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18142,25 +18317,25 @@
         </is>
       </c>
       <c r="B2" s="63" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="64" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="F2" s="65" t="n">
-        <v>32510.8</v>
+        <v>33160.8</v>
       </c>
       <c r="G2" s="64" t="n">
-        <v>1.931701221736718</v>
+        <v>1.519037532512389</v>
       </c>
       <c r="H2" s="65" t="n">
-        <v>16830.14</v>
+        <v>21830.14</v>
       </c>
     </row>
     <row r="3">
@@ -18170,25 +18345,25 @@
         </is>
       </c>
       <c r="B3" s="63" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="63" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="63" t="n">
         <v>3</v>
       </c>
       <c r="E3" s="64" t="n">
-        <v>0.8</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="F3" s="65" t="n">
-        <v>56100.55</v>
+        <v>48644.04</v>
       </c>
       <c r="G3" s="64" t="n">
-        <v>2.724630558786604</v>
+        <v>2.709391952482641</v>
       </c>
       <c r="H3" s="65" t="n">
-        <v>20590.15</v>
+        <v>17953.86</v>
       </c>
     </row>
     <row r="4">
@@ -18198,25 +18373,25 @@
         </is>
       </c>
       <c r="B4" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="63" t="n">
         <v>4</v>
-      </c>
-      <c r="C4" s="63" t="n">
-        <v>3</v>
       </c>
       <c r="D4" s="63" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="64" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F4" s="65" t="n">
-        <v>9064.709999999999</v>
+        <v>9335.82</v>
       </c>
       <c r="G4" s="64" t="n">
-        <v>1.061995749536643</v>
+        <v>1.015262428130373</v>
       </c>
       <c r="H4" s="65" t="n">
-        <v>8535.540000000001</v>
+        <v>9195.469999999999</v>
       </c>
     </row>
     <row r="5">
@@ -18226,25 +18401,25 @@
         </is>
       </c>
       <c r="B5" s="63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="63" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="64" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="F5" s="65" t="n">
-        <v>4724.88</v>
+        <v>-250</v>
       </c>
       <c r="G5" s="64" t="n">
-        <v>0.782842628828572</v>
+        <v>-0.05</v>
       </c>
       <c r="H5" s="65" t="n">
-        <v>6035.54</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6">
@@ -18254,25 +18429,25 @@
         </is>
       </c>
       <c r="B6" s="63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="63" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="64" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>8185.23</v>
+        <v>4343.33</v>
       </c>
       <c r="G6" s="64" t="n">
-        <v>1.356172504862862</v>
+        <v>0.6762882456440839</v>
       </c>
       <c r="H6" s="65" t="n">
-        <v>6035.54</v>
+        <v>6422.3</v>
       </c>
     </row>
     <row r="7">
@@ -18282,31 +18457,31 @@
         </is>
       </c>
       <c r="B7" s="66" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C7" s="66" t="n">
         <v>25</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="F7" s="68" t="n">
-        <v>110586.17</v>
+        <v>95233.99000000001</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>1.905773933163079</v>
+        <v>1.576675435173506</v>
       </c>
       <c r="H7" s="68" t="n">
-        <v>58026.91</v>
+        <v>60401.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="69" t="inlineStr">
         <is>
-          <t>Generado: 05/04/2026 13:18</t>
+          <t>Generado: 05/04/2026 15:35</t>
         </is>
       </c>
     </row>

--- a/Backtest_Modelo.xlsx
+++ b/Backtest_Modelo.xlsx
@@ -366,10 +366,10 @@
     <xf numFmtId="4" fontId="2" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -384,13 +384,13 @@
     <xf numFmtId="4" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -896,7 +896,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/04/2026 15:35   |   Bankroll: $100,000.00</t>
+          <t>Generado: 05/04/2026 18:55   |   Bankroll: $100,000.00</t>
         </is>
       </c>
     </row>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>95233.98699999999</v>
+        <v>93729.9192</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>93848.3422</v>
+        <v>92344.27439999999</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>1385.6448</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1.576675435173506</v>
+        <v>1.424715207954943</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1.591772472077341</v>
+        <v>1.435139624353972</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>0.96</v>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>60401.77</v>
+        <v>65788.53</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>58958.39</v>
+        <v>64345.15</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>1443.38</v>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>1</v>
@@ -1003,14 +1003,14 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>% Acierto P  (col. Acierto, 50/73 partidos)</t>
+          <t>% Acierto P  (col. Acierto, 51/75 partidos)</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.684931506849315</v>
+        <v>0.68</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.684931506849315</v>
+        <v>0.68</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>1</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.6996086105675147</v>
+        <v>0.6821052631578948</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.6954069298952458</v>
+        <v>0.6778378378378378</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>1</v>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>4.8227</v>
+        <v>4.5966</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>4.7538</v>
+        <v>4.5272</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>0</v>
@@ -1121,10 +1121,10 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>0.5636221108909509</v>
+        <v>0.5674942865554274</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>0.5636221108909509</v>
+        <v>0.5674942865554274</v>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="B19" s="17" t="n">
-        <v>0.6457943274007457</v>
+        <v>0.647029216376605</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>0.6457943274007457</v>
+        <v>0.647029216376605</v>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B20" s="14" t="n">
-        <v>-0.08217221650979478</v>
+        <v>-0.0795349298211776</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>-0.08217221650979478</v>
+        <v>-0.0795349298211776</v>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
@@ -1565,19 +1565,19 @@
         </is>
       </c>
       <c r="L2" s="31" t="n">
-        <v>0.3882370092415332</v>
+        <v>0.3719183589563244</v>
       </c>
       <c r="M2" s="31" t="n">
-        <v>0.2902605895698538</v>
+        <v>0.2738021407523997</v>
       </c>
       <c r="N2" s="31" t="n">
-        <v>0.321502401188613</v>
+        <v>0.354279500291276</v>
       </c>
       <c r="O2" s="31" t="n">
-        <v>0.4283298117362779</v>
+        <v>0.4955349103122064</v>
       </c>
       <c r="P2" s="31" t="n">
-        <v>0.5716701882637221</v>
+        <v>0.5044650896877936</v>
       </c>
       <c r="Q2" s="30" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="S2" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Info Oculta</t>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
         </is>
       </c>
       <c r="T2" s="28" t="inlineStr">
@@ -1622,7 +1622,7 @@
         <v/>
       </c>
       <c r="AB2" s="34" t="n">
-        <v>0.6524</v>
+        <v>0.673</v>
       </c>
       <c r="AC2" s="30" t="inlineStr">
         <is>
@@ -1671,16 +1671,16 @@
         </is>
       </c>
       <c r="L3" s="31" t="n">
-        <v>0.455627</v>
+        <v>0.455648</v>
       </c>
       <c r="M3" s="31" t="n">
-        <v>0.240259</v>
+        <v>0.240217</v>
       </c>
       <c r="N3" s="31" t="n">
-        <v>0.304114</v>
+        <v>0.304135</v>
       </c>
       <c r="O3" s="31" t="n">
-        <v>0.5870316109295243</v>
+        <v>0.5870316109295244</v>
       </c>
       <c r="P3" s="31" t="n">
         <v>0.4129683890704757</v>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="T4" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.54, delta=0.04&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.54, delta=0.04&lt;0.30)</t>
         </is>
       </c>
       <c r="U4" s="32" t="n">
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="L5" s="31" t="n">
-        <v>0.3937602485601033</v>
+        <v>0.431526</v>
       </c>
       <c r="M5" s="31" t="n">
-        <v>0.2279331420748819</v>
+        <v>0.205911</v>
       </c>
       <c r="N5" s="31" t="n">
-        <v>0.3783066093650147</v>
+        <v>0.362563</v>
       </c>
       <c r="O5" s="31" t="n">
-        <v>0.6909968073204885</v>
+        <v>0.7544576675717418</v>
       </c>
       <c r="P5" s="31" t="n">
-        <v>0.3090031926795115</v>
+        <v>0.2455423324282581</v>
       </c>
       <c r="Q5" s="30" t="n">
         <v>1</v>
@@ -1911,10 +1911,9 @@
       <c r="R5" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="28" t="inlineStr">
-        <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
+      <c r="S5" s="28">
+        <f>IF(OR(Q5="",R5=""),"[APOSTAR] LOCAL",IF(Q5&gt;R5,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T5" s="28" t="inlineStr">
         <is>
@@ -1922,7 +1921,7 @@
         </is>
       </c>
       <c r="U5" s="32" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="V5" s="32" t="n">
         <v>0</v>
@@ -1948,7 +1947,7 @@
         <v/>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>0.7547</v>
+        <v>0.7239</v>
       </c>
       <c r="AC5" s="30" t="inlineStr">
         <is>
@@ -2001,13 +2000,13 @@
         </is>
       </c>
       <c r="L6" s="31" t="n">
-        <v>0.3773815414806954</v>
+        <v>0.3774080283523876</v>
       </c>
       <c r="M6" s="31" t="n">
-        <v>0.2978952117695611</v>
+        <v>0.2978422380261768</v>
       </c>
       <c r="N6" s="31" t="n">
-        <v>0.3247232467497435</v>
+        <v>0.3247497336214356</v>
       </c>
       <c r="O6" s="31" t="n">
         <v>0.4019708307918866</v>
@@ -2111,13 +2110,13 @@
         </is>
       </c>
       <c r="L7" s="31" t="n">
-        <v>0.455697</v>
+        <v>0.455721</v>
       </c>
       <c r="M7" s="31" t="n">
-        <v>0.266721</v>
+        <v>0.266673</v>
       </c>
       <c r="N7" s="31" t="n">
-        <v>0.277582</v>
+        <v>0.277606</v>
       </c>
       <c r="O7" s="31" t="n">
         <v>0.4636024826220113</v>
@@ -2138,7 +2137,7 @@
       </c>
       <c r="T7" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.53, delta=0.03&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.53, delta=0.03&lt;0.30)</t>
         </is>
       </c>
       <c r="U7" s="32" t="n">
@@ -2221,13 +2220,13 @@
         </is>
       </c>
       <c r="L8" s="31" t="n">
-        <v>0.389266638939047</v>
+        <v>0.389290999568249</v>
       </c>
       <c r="M8" s="31" t="n">
-        <v>0.2699437604172079</v>
+        <v>0.2698950391588039</v>
       </c>
       <c r="N8" s="31" t="n">
-        <v>0.3407896006437452</v>
+        <v>0.3408139612729471</v>
       </c>
       <c r="O8" s="31" t="n">
         <v>0.5101630222875012</v>
@@ -2247,7 +2246,7 @@
       </c>
       <c r="T8" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.72, delta=0.22&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.72, delta=0.22&lt;0.30)</t>
         </is>
       </c>
       <c r="U8" s="32" t="n">
@@ -2330,13 +2329,13 @@
         </is>
       </c>
       <c r="L9" s="31" t="n">
-        <v>0.441792</v>
+        <v>0.441817</v>
       </c>
       <c r="M9" s="31" t="n">
-        <v>0.274308</v>
+        <v>0.274259</v>
       </c>
       <c r="N9" s="31" t="n">
-        <v>0.2839</v>
+        <v>0.283924</v>
       </c>
       <c r="O9" s="31" t="n">
         <v>0.4371983044114202</v>
@@ -2439,13 +2438,13 @@
         </is>
       </c>
       <c r="L10" s="31" t="n">
-        <v>0.3807875895261522</v>
+        <v>0.3808106918726547</v>
       </c>
       <c r="M10" s="31" t="n">
-        <v>0.2598425362627583</v>
+        <v>0.2597963315697532</v>
       </c>
       <c r="N10" s="31" t="n">
-        <v>0.3593698742110895</v>
+        <v>0.3593929765575921</v>
       </c>
       <c r="O10" s="31" t="n">
         <v>0.5549589419807658</v>
@@ -2549,13 +2548,13 @@
         </is>
       </c>
       <c r="L11" s="31" t="n">
-        <v>0.5389925247606683</v>
+        <v>0.5390144765526615</v>
       </c>
       <c r="M11" s="31" t="n">
-        <v>0.2437868489080903</v>
+        <v>0.2437429453241036</v>
       </c>
       <c r="N11" s="31" t="n">
-        <v>0.2172206263312415</v>
+        <v>0.2172425781232348</v>
       </c>
       <c r="O11" s="31" t="n">
         <v>0.5422530919991749</v>
@@ -2649,13 +2648,13 @@
         </is>
       </c>
       <c r="L12" s="31" t="n">
-        <v>0.492798</v>
+        <v>0.49281</v>
       </c>
       <c r="M12" s="31" t="n">
-        <v>0.271388</v>
+        <v>0.271364</v>
       </c>
       <c r="N12" s="31" t="n">
-        <v>0.235815</v>
+        <v>0.235827</v>
       </c>
       <c r="O12" s="31" t="n">
         <v>0.4148022099731867</v>
@@ -2751,13 +2750,13 @@
         </is>
       </c>
       <c r="L13" s="31" t="n">
-        <v>0.494131</v>
+        <v>0.4941</v>
       </c>
       <c r="M13" s="31" t="n">
-        <v>0.231141</v>
+        <v>0.231202</v>
       </c>
       <c r="N13" s="31" t="n">
-        <v>0.274728</v>
+        <v>0.274698</v>
       </c>
       <c r="O13" s="31" t="n">
         <v>0.6015291871790185</v>
@@ -2853,13 +2852,13 @@
         </is>
       </c>
       <c r="L14" s="31" t="n">
-        <v>0.492303</v>
+        <v>0.492273</v>
       </c>
       <c r="M14" s="31" t="n">
-        <v>0.229227</v>
+        <v>0.229286</v>
       </c>
       <c r="N14" s="31" t="n">
-        <v>0.27847</v>
+        <v>0.27844</v>
       </c>
       <c r="O14" s="31" t="n">
         <v>0.6127357803698895</v>
@@ -2955,13 +2954,13 @@
         </is>
       </c>
       <c r="L15" s="31" t="n">
-        <v>0.5375917150253967</v>
+        <v>0.5375619846858887</v>
       </c>
       <c r="M15" s="31" t="n">
-        <v>0.2271909306028471</v>
+        <v>0.2272503912818629</v>
       </c>
       <c r="N15" s="31" t="n">
-        <v>0.2352173543717563</v>
+        <v>0.2351876240322484</v>
       </c>
       <c r="O15" s="31" t="n">
         <v>0.6197678553969835</v>
@@ -3065,13 +3064,13 @@
         </is>
       </c>
       <c r="L16" s="31" t="n">
-        <v>0.43794</v>
+        <v>0.437952</v>
       </c>
       <c r="M16" s="31" t="n">
-        <v>0.262175</v>
+        <v>0.262151</v>
       </c>
       <c r="N16" s="31" t="n">
-        <v>0.299884</v>
+        <v>0.299896</v>
       </c>
       <c r="O16" s="31" t="n">
         <v>0.4828233891977304</v>
@@ -3088,7 +3087,7 @@
       </c>
       <c r="T16" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.61, delta=0.11&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.61, delta=0.11&lt;0.30)</t>
         </is>
       </c>
       <c r="U16" s="32" t="n">
@@ -3161,13 +3160,13 @@
         </is>
       </c>
       <c r="L17" s="31" t="n">
-        <v>0.274594</v>
+        <v>0.274605</v>
       </c>
       <c r="M17" s="31" t="n">
-        <v>0.250254</v>
+        <v>0.250232</v>
       </c>
       <c r="N17" s="31" t="n">
-        <v>0.475151</v>
+        <v>0.475163</v>
       </c>
       <c r="O17" s="31" t="n">
         <v>0.5214361653599625</v>
@@ -3267,13 +3266,13 @@
         </is>
       </c>
       <c r="L18" s="31" t="n">
-        <v>0.3980929690869996</v>
+        <v>0.3981045687317345</v>
       </c>
       <c r="M18" s="31" t="n">
-        <v>0.2586017920120435</v>
+        <v>0.2585785927225737</v>
       </c>
       <c r="N18" s="31" t="n">
-        <v>0.3433052389009569</v>
+        <v>0.3433168385456918</v>
       </c>
       <c r="O18" s="31" t="n">
         <v>0.5506715830807075</v>
@@ -3362,13 +3361,13 @@
         </is>
       </c>
       <c r="L19" s="31" t="n">
-        <v>0.467444</v>
+        <v>0.467455</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>0.257383</v>
+        <v>0.257359</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>0.275174</v>
+        <v>0.275186</v>
       </c>
       <c r="O19" s="31" t="n">
         <v>0.4920602783752462</v>
@@ -3464,13 +3463,13 @@
         </is>
       </c>
       <c r="L20" s="31" t="n">
-        <v>0.503815</v>
+        <v>0.503783</v>
       </c>
       <c r="M20" s="31" t="n">
-        <v>0.238958</v>
+        <v>0.239023</v>
       </c>
       <c r="N20" s="31" t="n">
-        <v>0.257227</v>
+        <v>0.257194</v>
       </c>
       <c r="O20" s="31" t="n">
         <v>0.5542627005521311</v>
@@ -3564,19 +3563,19 @@
         </is>
       </c>
       <c r="L21" s="31" t="n">
-        <v>0.499857</v>
+        <v>0.499832</v>
       </c>
       <c r="M21" s="31" t="n">
-        <v>0.212986</v>
+        <v>0.213037</v>
       </c>
       <c r="N21" s="31" t="n">
-        <v>0.287157</v>
+        <v>0.287131</v>
       </c>
       <c r="O21" s="31" t="n">
         <v>0.6949277206627653</v>
       </c>
       <c r="P21" s="31" t="n">
-        <v>0.3050722793372347</v>
+        <v>0.3050722793372346</v>
       </c>
       <c r="Q21" s="30" t="n">
         <v>2</v>
@@ -3666,19 +3665,19 @@
         </is>
       </c>
       <c r="L22" s="31" t="n">
-        <v>0.478334</v>
+        <v>0.478303</v>
       </c>
       <c r="M22" s="31" t="n">
-        <v>0.234728</v>
+        <v>0.23479</v>
       </c>
       <c r="N22" s="31" t="n">
-        <v>0.286938</v>
+        <v>0.286907</v>
       </c>
       <c r="O22" s="31" t="n">
         <v>0.5921931616962641</v>
       </c>
       <c r="P22" s="31" t="n">
-        <v>0.4078068383037359</v>
+        <v>0.4078068383037358</v>
       </c>
       <c r="Q22" s="30" t="n">
         <v>1</v>
@@ -3768,16 +3767,16 @@
         </is>
       </c>
       <c r="L23" s="31" t="n">
-        <v>0.441406</v>
+        <v>0.441381</v>
       </c>
       <c r="M23" s="31" t="n">
-        <v>0.217131</v>
+        <v>0.217182</v>
       </c>
       <c r="N23" s="31" t="n">
-        <v>0.341463</v>
+        <v>0.341437</v>
       </c>
       <c r="O23" s="31" t="n">
-        <v>0.6962658764730534</v>
+        <v>0.6962658764730535</v>
       </c>
       <c r="P23" s="31" t="n">
         <v>0.3037341235269466</v>
@@ -3904,7 +3903,7 @@
       </c>
       <c r="T24" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.66, delta=0.16&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.66, delta=0.16&lt;0.30)</t>
         </is>
       </c>
       <c r="U24" s="32" t="n">
@@ -3987,13 +3986,13 @@
         </is>
       </c>
       <c r="L25" s="31" t="n">
-        <v>0.482076</v>
+        <v>0.4821</v>
       </c>
       <c r="M25" s="31" t="n">
-        <v>0.275723</v>
+        <v>0.275674</v>
       </c>
       <c r="N25" s="31" t="n">
-        <v>0.242201</v>
+        <v>0.242226</v>
       </c>
       <c r="O25" s="31" t="n">
         <v>0.4109749443702656</v>
@@ -4097,13 +4096,13 @@
         </is>
       </c>
       <c r="L26" s="31" t="n">
-        <v>0.3772058935317406</v>
+        <v>0.3772322418889471</v>
       </c>
       <c r="M26" s="31" t="n">
-        <v>0.2949087474357349</v>
+        <v>0.2948560507213218</v>
       </c>
       <c r="N26" s="31" t="n">
-        <v>0.3278853590325246</v>
+        <v>0.3279117073897311</v>
       </c>
       <c r="O26" s="31" t="n">
         <v>0.4128242964781709</v>
@@ -4232,7 +4231,7 @@
       </c>
       <c r="T27" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.69, delta=0.19&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.69, delta=0.19&lt;0.30)</t>
         </is>
       </c>
       <c r="U27" s="32" t="n">
@@ -4315,13 +4314,13 @@
         </is>
       </c>
       <c r="L28" s="31" t="n">
-        <v>0.424892</v>
+        <v>0.424916</v>
       </c>
       <c r="M28" s="31" t="n">
-        <v>0.267094</v>
+        <v>0.267046</v>
       </c>
       <c r="N28" s="31" t="n">
-        <v>0.308014</v>
+        <v>0.308038</v>
       </c>
       <c r="O28" s="31" t="n">
         <v>0.4728740634574408</v>
@@ -4341,7 +4340,7 @@
       </c>
       <c r="T28" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.57, delta=0.07&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.57, delta=0.07&lt;0.30)</t>
         </is>
       </c>
       <c r="U28" s="32" t="n">
@@ -4534,13 +4533,13 @@
         </is>
       </c>
       <c r="L30" s="31" t="n">
-        <v>0.509634</v>
+        <v>0.509607</v>
       </c>
       <c r="M30" s="31" t="n">
-        <v>0.217781</v>
+        <v>0.217835</v>
       </c>
       <c r="N30" s="31" t="n">
-        <v>0.272585</v>
+        <v>0.272558</v>
       </c>
       <c r="O30" s="31" t="n">
         <v>0.6626510174407112</v>
@@ -4671,7 +4670,7 @@
       </c>
       <c r="T31" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.69, delta=0.19&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.69, delta=0.19&lt;0.30)</t>
         </is>
       </c>
       <c r="U31" s="32" t="n">
@@ -4781,7 +4780,7 @@
       </c>
       <c r="T32" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.73, delta=0.23&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.73, delta=0.23&lt;0.30)</t>
         </is>
       </c>
       <c r="U32" s="32" t="n">
@@ -4864,13 +4863,13 @@
         </is>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0.436779</v>
+        <v>0.436803</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>0.264067</v>
+        <v>0.264019</v>
       </c>
       <c r="N33" s="31" t="n">
-        <v>0.299154</v>
+        <v>0.299178</v>
       </c>
       <c r="O33" s="31" t="n">
         <v>0.4825726127876495</v>
@@ -4891,7 +4890,7 @@
       </c>
       <c r="T33" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.60, delta=0.10&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.60, delta=0.10&lt;0.30)</t>
         </is>
       </c>
       <c r="U33" s="32" t="n">
@@ -5084,13 +5083,13 @@
         </is>
       </c>
       <c r="L35" s="31" t="n">
-        <v>0.3778806238098235</v>
+        <v>0.3779060858037166</v>
       </c>
       <c r="M35" s="31" t="n">
-        <v>0.2814411786821948</v>
+        <v>0.2813902546944084</v>
       </c>
       <c r="N35" s="31" t="n">
-        <v>0.3406781975079819</v>
+        <v>0.340703659501875</v>
       </c>
       <c r="O35" s="31" t="n">
         <v>0.4642402790842933</v>
@@ -5110,7 +5109,7 @@
       </c>
       <c r="T35" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.53, delta=0.03&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.53, delta=0.03&lt;0.30)</t>
         </is>
       </c>
       <c r="U35" s="32" t="n">
@@ -5193,13 +5192,13 @@
         </is>
       </c>
       <c r="L36" s="31" t="n">
-        <v>0.459797</v>
+        <v>0.45977</v>
       </c>
       <c r="M36" s="31" t="n">
-        <v>0.220398</v>
+        <v>0.220452</v>
       </c>
       <c r="N36" s="31" t="n">
-        <v>0.319805</v>
+        <v>0.319778</v>
       </c>
       <c r="O36" s="31" t="n">
         <v>0.6744931291712692</v>
@@ -5303,13 +5302,13 @@
         </is>
       </c>
       <c r="L37" s="31" t="n">
-        <v>0.3846617080054454</v>
+        <v>0.3846877251006374</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>0.2892306494942386</v>
+        <v>0.2891786153038545</v>
       </c>
       <c r="N37" s="31" t="n">
-        <v>0.326107642500316</v>
+        <v>0.3261336595955081</v>
       </c>
       <c r="O37" s="31" t="n">
         <v>0.4329010012935023</v>
@@ -5631,13 +5630,13 @@
         </is>
       </c>
       <c r="L40" s="31" t="n">
-        <v>0.455399</v>
+        <v>0.455364</v>
       </c>
       <c r="M40" s="31" t="n">
-        <v>0.255901</v>
+        <v>0.255971</v>
       </c>
       <c r="N40" s="31" t="n">
-        <v>0.2887</v>
+        <v>0.288665</v>
       </c>
       <c r="O40" s="31" t="n">
         <v>0.4998597255701074</v>
@@ -5658,7 +5657,7 @@
       </c>
       <c r="T40" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.67, delta=0.17&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.67, delta=0.17&lt;0.30)</t>
         </is>
       </c>
       <c r="U40" s="32" t="n">
@@ -5741,13 +5740,13 @@
         </is>
       </c>
       <c r="L41" s="31" t="n">
-        <v>0.3562294018228677</v>
+        <v>0.3562553942733552</v>
       </c>
       <c r="M41" s="31" t="n">
-        <v>0.2885062220759475</v>
+        <v>0.2884542371749724</v>
       </c>
       <c r="N41" s="31" t="n">
-        <v>0.3552643761011849</v>
+        <v>0.3552903685516724</v>
       </c>
       <c r="O41" s="31" t="n">
         <v>0.4381085945823797</v>
@@ -5851,13 +5850,13 @@
         </is>
       </c>
       <c r="L42" s="31" t="n">
-        <v>0.4936</v>
+        <v>0.493624</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>0.277401</v>
+        <v>0.277352</v>
       </c>
       <c r="N42" s="31" t="n">
-        <v>0.228999</v>
+        <v>0.229024</v>
       </c>
       <c r="O42" s="31" t="n">
         <v>0.3963885637853248</v>
@@ -5961,13 +5960,13 @@
         </is>
       </c>
       <c r="L43" s="31" t="n">
-        <v>0.3931238580672648</v>
+        <v>0.3930883461191027</v>
       </c>
       <c r="M43" s="31" t="n">
-        <v>0.2612093373656894</v>
+        <v>0.2612803612620135</v>
       </c>
       <c r="N43" s="31" t="n">
-        <v>0.3456668045670458</v>
+        <v>0.3456312926188838</v>
       </c>
       <c r="O43" s="31" t="n">
         <v>0.5350607893625914</v>
@@ -6070,19 +6069,19 @@
         </is>
       </c>
       <c r="L44" s="31" t="n">
-        <v>0.515298</v>
+        <v>0.515267</v>
       </c>
       <c r="M44" s="31" t="n">
-        <v>0.22885</v>
+        <v>0.228911</v>
       </c>
       <c r="N44" s="31" t="n">
-        <v>0.255852</v>
+        <v>0.255822</v>
       </c>
       <c r="O44" s="31" t="n">
         <v>0.5985032908303799</v>
       </c>
       <c r="P44" s="31" t="n">
-        <v>0.4014967091696201</v>
+        <v>0.40149670916962</v>
       </c>
       <c r="Q44" s="30" t="n">
         <v>0</v>
@@ -6180,13 +6179,13 @@
         </is>
       </c>
       <c r="L45" s="31" t="n">
-        <v>0.3301149312056603</v>
+        <v>0.3301413713435694</v>
       </c>
       <c r="M45" s="31" t="n">
-        <v>0.2966507528014525</v>
+        <v>0.2965978725256345</v>
       </c>
       <c r="N45" s="31" t="n">
-        <v>0.3732343159928871</v>
+        <v>0.3732607561307962</v>
       </c>
       <c r="O45" s="31" t="n">
         <v>0.4070079729829673</v>
@@ -6317,7 +6316,7 @@
       </c>
       <c r="T46" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Valor</t>
+          <t>[PASAR] xG Margen Insuf (2.79, delta=0.29&lt;0.30)</t>
         </is>
       </c>
       <c r="U46" s="32" t="n">
@@ -6400,13 +6399,13 @@
         </is>
       </c>
       <c r="L47" s="31" t="n">
-        <v>0.4977</v>
+        <v>0.497668</v>
       </c>
       <c r="M47" s="31" t="n">
-        <v>0.23656</v>
+        <v>0.236624</v>
       </c>
       <c r="N47" s="31" t="n">
-        <v>0.26574</v>
+        <v>0.265708</v>
       </c>
       <c r="O47" s="31" t="n">
         <v>0.5709537516820591</v>
@@ -6619,13 +6618,13 @@
         </is>
       </c>
       <c r="L49" s="31" t="n">
-        <v>0.494462</v>
+        <v>0.49443</v>
       </c>
       <c r="M49" s="31" t="n">
-        <v>0.238803</v>
+        <v>0.238868</v>
       </c>
       <c r="N49" s="31" t="n">
-        <v>0.266735</v>
+        <v>0.266703</v>
       </c>
       <c r="O49" s="31" t="n">
         <v>0.5616275155884431</v>
@@ -6947,13 +6946,13 @@
         </is>
       </c>
       <c r="L52" s="31" t="n">
-        <v>0.3799976504400017</v>
+        <v>0.3799658652700799</v>
       </c>
       <c r="M52" s="31" t="n">
-        <v>0.2447315069332119</v>
+        <v>0.2447950772730552</v>
       </c>
       <c r="N52" s="31" t="n">
-        <v>0.3752708426267864</v>
+        <v>0.3752390574568647</v>
       </c>
       <c r="O52" s="31" t="n">
         <v>0.6114688439440668</v>
@@ -7057,19 +7056,19 @@
         </is>
       </c>
       <c r="L53" s="31" t="n">
-        <v>0.479359</v>
+        <v>0.479384</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>0.271975</v>
+        <v>0.271926</v>
       </c>
       <c r="N53" s="31" t="n">
-        <v>0.248666</v>
+        <v>0.24869</v>
       </c>
       <c r="O53" s="31" t="n">
         <v>0.4283291668066846</v>
       </c>
       <c r="P53" s="31" t="n">
-        <v>0.5716708331933155</v>
+        <v>0.5716708331933154</v>
       </c>
       <c r="Q53" s="30" t="n">
         <v>2</v>
@@ -7302,7 +7301,7 @@
       </c>
       <c r="T55" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (1X2 Priorizado)</t>
+          <t>[PASAR] xG Margen Insuf (2.80, delta=0.30&lt;0.30)</t>
         </is>
       </c>
       <c r="U55" s="32" t="n">
@@ -7385,13 +7384,13 @@
         </is>
       </c>
       <c r="L56" s="31" t="n">
-        <v>0.460271</v>
+        <v>0.460246</v>
       </c>
       <c r="M56" s="31" t="n">
-        <v>0.214691</v>
+        <v>0.214741</v>
       </c>
       <c r="N56" s="31" t="n">
-        <v>0.325037</v>
+        <v>0.325012</v>
       </c>
       <c r="O56" s="31" t="n">
         <v>0.7039103277145289</v>
@@ -7495,13 +7494,13 @@
         </is>
       </c>
       <c r="L57" s="31" t="n">
-        <v>0.465529</v>
+        <v>0.465495</v>
       </c>
       <c r="M57" s="31" t="n">
-        <v>0.245298</v>
+        <v>0.245365</v>
       </c>
       <c r="N57" s="31" t="n">
-        <v>0.289173</v>
+        <v>0.28914</v>
       </c>
       <c r="O57" s="31" t="n">
         <v>0.545657589335549</v>
@@ -7604,13 +7603,13 @@
         </is>
       </c>
       <c r="L58" s="31" t="n">
-        <v>0.506894</v>
+        <v>0.506918</v>
       </c>
       <c r="M58" s="31" t="n">
-        <v>0.271056</v>
+        <v>0.271008</v>
       </c>
       <c r="N58" s="31" t="n">
-        <v>0.22205</v>
+        <v>0.222074</v>
       </c>
       <c r="O58" s="31" t="n">
         <v>0.4128232474368506</v>
@@ -7714,13 +7713,13 @@
         </is>
       </c>
       <c r="L59" s="31" t="n">
-        <v>0.5734322988906213</v>
+        <v>0.5734549578692216</v>
       </c>
       <c r="M59" s="31" t="n">
-        <v>0.2543605121061134</v>
+        <v>0.2543151941489126</v>
       </c>
       <c r="N59" s="31" t="n">
-        <v>0.1722071890032654</v>
+        <v>0.1722298479818657</v>
       </c>
       <c r="O59" s="31" t="n">
         <v>0.4463974102627131</v>
@@ -7824,13 +7823,13 @@
         </is>
       </c>
       <c r="L60" s="31" t="n">
-        <v>0.3574387363194203</v>
+        <v>0.357464418558816</v>
       </c>
       <c r="M60" s="31" t="n">
-        <v>0.28416828227082</v>
+        <v>0.2841169177920285</v>
       </c>
       <c r="N60" s="31" t="n">
-        <v>0.3583929814097598</v>
+        <v>0.3584186636491555</v>
       </c>
       <c r="O60" s="31" t="n">
         <v>0.4546459849409152</v>
@@ -7934,13 +7933,13 @@
         </is>
       </c>
       <c r="L61" s="31" t="n">
-        <v>0.461934</v>
+        <v>0.461959</v>
       </c>
       <c r="M61" s="31" t="n">
-        <v>0.28327</v>
+        <v>0.28322</v>
       </c>
       <c r="N61" s="31" t="n">
-        <v>0.254796</v>
+        <v>0.254821</v>
       </c>
       <c r="O61" s="31" t="n">
         <v>0.3922601733778666</v>
@@ -8044,13 +8043,13 @@
         </is>
       </c>
       <c r="L62" s="31" t="n">
-        <v>0.426467</v>
+        <v>0.426493</v>
       </c>
       <c r="M62" s="31" t="n">
-        <v>0.315158</v>
+        <v>0.315107</v>
       </c>
       <c r="N62" s="31" t="n">
-        <v>0.258375</v>
+        <v>0.2584</v>
       </c>
       <c r="O62" s="31" t="n">
         <v>0.297629510143734</v>
@@ -8143,13 +8142,13 @@
         </is>
       </c>
       <c r="L63" s="31" t="n">
-        <v>0.50986</v>
+        <v>0.509884</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>0.269912</v>
+        <v>0.269864</v>
       </c>
       <c r="N63" s="31" t="n">
-        <v>0.220229</v>
+        <v>0.220253</v>
       </c>
       <c r="O63" s="31" t="n">
         <v>0.4153291784124106</v>
@@ -8249,19 +8248,19 @@
         </is>
       </c>
       <c r="L64" s="31" t="n">
-        <v>0.464668</v>
+        <v>0.464638</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>0.233267</v>
+        <v>0.233328</v>
       </c>
       <c r="N64" s="31" t="n">
-        <v>0.302065</v>
+        <v>0.302034</v>
       </c>
       <c r="O64" s="31" t="n">
         <v>0.606252855964858</v>
       </c>
       <c r="P64" s="31" t="n">
-        <v>0.3937471440351421</v>
+        <v>0.393747144035142</v>
       </c>
       <c r="Q64" s="30" t="n">
         <v>4</v>
@@ -8359,13 +8358,13 @@
         </is>
       </c>
       <c r="L65" s="31" t="n">
-        <v>0.3548897391662117</v>
+        <v>0.3549156187649966</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>0.2868572289386647</v>
+        <v>0.2868054697410951</v>
       </c>
       <c r="N65" s="31" t="n">
-        <v>0.3582530318951235</v>
+        <v>0.3582789114939084</v>
       </c>
       <c r="O65" s="31" t="n">
         <v>0.4443332923376039</v>
@@ -8469,13 +8468,13 @@
         </is>
       </c>
       <c r="L66" s="31" t="n">
-        <v>0.513982</v>
+        <v>0.513956</v>
       </c>
       <c r="M66" s="31" t="n">
-        <v>0.213058</v>
+        <v>0.213109</v>
       </c>
       <c r="N66" s="31" t="n">
-        <v>0.272961</v>
+        <v>0.272935</v>
       </c>
       <c r="O66" s="31" t="n">
         <v>0.6853780312818094</v>
@@ -8579,13 +8578,13 @@
         </is>
       </c>
       <c r="L67" s="31" t="n">
-        <v>0.482585</v>
+        <v>0.48256</v>
       </c>
       <c r="M67" s="31" t="n">
-        <v>0.214515</v>
+        <v>0.214566</v>
       </c>
       <c r="N67" s="31" t="n">
-        <v>0.302899</v>
+        <v>0.302874</v>
       </c>
       <c r="O67" s="31" t="n">
         <v>0.6959966261239385</v>
@@ -8689,13 +8688,13 @@
         </is>
       </c>
       <c r="L68" s="31" t="n">
-        <v>0.456183</v>
+        <v>0.456158</v>
       </c>
       <c r="M68" s="31" t="n">
-        <v>0.21416</v>
+        <v>0.214209</v>
       </c>
       <c r="N68" s="31" t="n">
-        <v>0.329658</v>
+        <v>0.329633</v>
       </c>
       <c r="O68" s="31" t="n">
         <v>0.7078930653966972</v>
@@ -8799,19 +8798,19 @@
         </is>
       </c>
       <c r="L69" s="31" t="n">
-        <v>0.5375070563966498</v>
+        <v>0.5137389999999999</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>0.2174204946633362</v>
+        <v>0.209967</v>
       </c>
       <c r="N69" s="31" t="n">
-        <v>0.2450724489400141</v>
+        <v>0.276294</v>
       </c>
       <c r="O69" s="31" t="n">
-        <v>0.673639038286969</v>
+        <v>0.7026839774429058</v>
       </c>
       <c r="P69" s="31" t="n">
-        <v>0.326360961713031</v>
+        <v>0.2973160225570943</v>
       </c>
       <c r="Q69" s="30" t="n">
         <v>3</v>
@@ -8856,7 +8855,7 @@
         <v/>
       </c>
       <c r="AB69" s="34" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8292</v>
       </c>
       <c r="AC69" s="30" t="inlineStr">
         <is>
@@ -8909,13 +8908,13 @@
         </is>
       </c>
       <c r="L70" s="31" t="n">
-        <v>0.5162318271319581</v>
+        <v>0.5162038289823252</v>
       </c>
       <c r="M70" s="31" t="n">
-        <v>0.2236016837629775</v>
+        <v>0.2236576800622434</v>
       </c>
       <c r="N70" s="31" t="n">
-        <v>0.2601664891050643</v>
+        <v>0.2601384909554314</v>
       </c>
       <c r="O70" s="31" t="n">
         <v>0.6595672583678465</v>
@@ -9019,13 +9018,13 @@
         </is>
       </c>
       <c r="L71" s="31" t="n">
-        <v>0.47758</v>
+        <v>0.477551</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>0.228588</v>
+        <v>0.228647</v>
       </c>
       <c r="N71" s="31" t="n">
-        <v>0.293832</v>
+        <v>0.293802</v>
       </c>
       <c r="O71" s="31" t="n">
         <v>0.6243503202999419</v>
@@ -9125,13 +9124,13 @@
         </is>
       </c>
       <c r="L72" s="31" t="n">
-        <v>0.436052</v>
+        <v>0.436076</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>0.265765</v>
+        <v>0.265717</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>0.298183</v>
+        <v>0.298207</v>
       </c>
       <c r="O72" s="31" t="n">
         <v>0.4754011830978497</v>
@@ -9231,19 +9230,19 @@
         </is>
       </c>
       <c r="L73" s="31" t="n">
-        <v>0.441475</v>
+        <v>0.441497</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>0.248012</v>
+        <v>0.247968</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>0.310512</v>
+        <v>0.310534</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>0.5544961797151675</v>
+        <v>0.5544961797151676</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>0.4455038202848325</v>
+        <v>0.4455038202848324</v>
       </c>
       <c r="Q73" s="30" t="n">
         <v>1</v>
@@ -9337,19 +9336,19 @@
         </is>
       </c>
       <c r="L74" s="31" t="n">
-        <v>0.3759587398249099</v>
+        <v>0.3908938483465888</v>
       </c>
       <c r="M74" s="31" t="n">
-        <v>0.2316108652053599</v>
+        <v>0.2178199788892485</v>
       </c>
       <c r="N74" s="31" t="n">
-        <v>0.3924303949697302</v>
+        <v>0.3912861727641627</v>
       </c>
       <c r="O74" s="31" t="n">
-        <v>0.6733716590854798</v>
+        <v>0.7396962481117284</v>
       </c>
       <c r="P74" s="31" t="n">
-        <v>0.3266283409145201</v>
+        <v>0.2603037518882716</v>
       </c>
       <c r="Q74" s="30" t="n">
         <v>0</v>
@@ -9394,7 +9393,7 @@
         <v/>
       </c>
       <c r="AB74" s="34" t="n">
-        <v>0.9306</v>
+        <v>0.9058</v>
       </c>
       <c r="AC74" s="30" t="inlineStr">
         <is>
@@ -9445,13 +9444,13 @@
         </is>
       </c>
       <c r="L75" s="31" t="n">
-        <v>0.5162318271319581</v>
+        <v>0.5162038289823252</v>
       </c>
       <c r="M75" s="31" t="n">
-        <v>0.2236016837629775</v>
+        <v>0.2236576800622434</v>
       </c>
       <c r="N75" s="31" t="n">
-        <v>0.2601664891050643</v>
+        <v>0.2601384909554314</v>
       </c>
       <c r="O75" s="31" t="n">
         <v>0.6595672583678465</v>
@@ -9554,13 +9553,13 @@
         </is>
       </c>
       <c r="L76" s="31" t="n">
-        <v>0.518254</v>
+        <v>0.5182290000000001</v>
       </c>
       <c r="M76" s="31" t="n">
-        <v>0.211558</v>
+        <v>0.211609</v>
       </c>
       <c r="N76" s="31" t="n">
-        <v>0.270187</v>
+        <v>0.270162</v>
       </c>
       <c r="O76" s="31" t="n">
         <v>0.690539118596024</v>
@@ -9660,13 +9659,13 @@
         </is>
       </c>
       <c r="L77" s="31" t="n">
-        <v>0.442728</v>
+        <v>0.4427</v>
       </c>
       <c r="M77" s="31" t="n">
-        <v>0.224985</v>
+        <v>0.225041</v>
       </c>
       <c r="N77" s="31" t="n">
-        <v>0.332287</v>
+        <v>0.332259</v>
       </c>
       <c r="O77" s="31" t="n">
         <v>0.6558913692263365</v>
@@ -9770,13 +9769,13 @@
         </is>
       </c>
       <c r="L78" s="31" t="n">
-        <v>0.459283</v>
+        <v>0.459254</v>
       </c>
       <c r="M78" s="31" t="n">
-        <v>0.226374</v>
+        <v>0.226431</v>
       </c>
       <c r="N78" s="31" t="n">
-        <v>0.314343</v>
+        <v>0.314314</v>
       </c>
       <c r="O78" s="31" t="n">
         <v>0.6437684226844578</v>
@@ -9870,19 +9869,19 @@
         </is>
       </c>
       <c r="L79" s="31" t="n">
-        <v>0.3664922331532478</v>
+        <v>0.3665162999071583</v>
       </c>
       <c r="M79" s="31" t="n">
-        <v>0.2674715221985613</v>
+        <v>0.2674233886907404</v>
       </c>
       <c r="N79" s="31" t="n">
-        <v>0.3660362446481908</v>
+        <v>0.3660603114021013</v>
       </c>
       <c r="O79" s="31" t="n">
         <v>0.5224005312757404</v>
       </c>
       <c r="P79" s="31" t="n">
-        <v>0.4775994687242597</v>
+        <v>0.4775994687242596</v>
       </c>
       <c r="Q79" s="30" t="n">
         <v>0</v>
@@ -9976,13 +9975,13 @@
         </is>
       </c>
       <c r="L80" s="31" t="n">
-        <v>0.3822885660488354</v>
+        <v>0.3823121996880964</v>
       </c>
       <c r="M80" s="31" t="n">
-        <v>0.2638650255530964</v>
+        <v>0.2638177582745744</v>
       </c>
       <c r="N80" s="31" t="n">
-        <v>0.3538464083980681</v>
+        <v>0.3538700420373291</v>
       </c>
       <c r="O80" s="31" t="n">
         <v>0.537191674357519</v>
@@ -10082,16 +10081,16 @@
         </is>
       </c>
       <c r="L81" s="31" t="n">
-        <v>0.431117</v>
+        <v>0.431138</v>
       </c>
       <c r="M81" s="31" t="n">
-        <v>0.241987</v>
+        <v>0.241945</v>
       </c>
       <c r="N81" s="31" t="n">
-        <v>0.326896</v>
+        <v>0.326917</v>
       </c>
       <c r="O81" s="31" t="n">
-        <v>0.5860389248216261</v>
+        <v>0.5860389248216262</v>
       </c>
       <c r="P81" s="31" t="n">
         <v>0.4139610751783738</v>
@@ -10192,13 +10191,13 @@
         </is>
       </c>
       <c r="L82" s="31" t="n">
-        <v>0.518254</v>
+        <v>0.5182290000000001</v>
       </c>
       <c r="M82" s="31" t="n">
-        <v>0.211558</v>
+        <v>0.211609</v>
       </c>
       <c r="N82" s="31" t="n">
-        <v>0.270187</v>
+        <v>0.270162</v>
       </c>
       <c r="O82" s="31" t="n">
         <v>0.690539118596024</v>
@@ -10293,13 +10292,13 @@
         </is>
       </c>
       <c r="L83" s="31" t="n">
-        <v>0.442728</v>
+        <v>0.4427</v>
       </c>
       <c r="M83" s="31" t="n">
-        <v>0.224985</v>
+        <v>0.225041</v>
       </c>
       <c r="N83" s="31" t="n">
-        <v>0.332287</v>
+        <v>0.332259</v>
       </c>
       <c r="O83" s="31" t="n">
         <v>0.6558913692263365</v>
@@ -10399,13 +10398,13 @@
         </is>
       </c>
       <c r="L84" s="31" t="n">
-        <v>0.3666619926508228</v>
+        <v>0.3666860193374752</v>
       </c>
       <c r="M84" s="31" t="n">
-        <v>0.267131566738302</v>
+        <v>0.2670835133649971</v>
       </c>
       <c r="N84" s="31" t="n">
-        <v>0.3662064406108753</v>
+        <v>0.3662304672975277</v>
       </c>
       <c r="O84" s="31" t="n">
         <v>0.5238432985648792</v>
@@ -10505,13 +10504,13 @@
         </is>
       </c>
       <c r="L85" s="31" t="n">
-        <v>0.494556</v>
+        <v>0.494578</v>
       </c>
       <c r="M85" s="31" t="n">
-        <v>0.242589</v>
+        <v>0.242545</v>
       </c>
       <c r="N85" s="31" t="n">
-        <v>0.262855</v>
+        <v>0.262877</v>
       </c>
       <c r="O85" s="31" t="n">
         <v>0.554841106162472</v>
@@ -10613,13 +10612,13 @@
         </is>
       </c>
       <c r="L86" s="31" t="n">
-        <v>0.441581</v>
+        <v>0.441604</v>
       </c>
       <c r="M86" s="31" t="n">
-        <v>0.25751</v>
+        <v>0.257463</v>
       </c>
       <c r="N86" s="31" t="n">
-        <v>0.300909</v>
+        <v>0.300933</v>
       </c>
       <c r="O86" s="31" t="n">
         <v>0.5102846778231006</v>
@@ -10721,13 +10720,13 @@
         </is>
       </c>
       <c r="L87" s="31" t="n">
-        <v>0.3958686053381169</v>
+        <v>0.3958417490805526</v>
       </c>
       <c r="M87" s="31" t="n">
-        <v>0.2275557042245653</v>
+        <v>0.227609416739694</v>
       </c>
       <c r="N87" s="31" t="n">
-        <v>0.3765756904373178</v>
+        <v>0.3765488341797535</v>
       </c>
       <c r="O87" s="31" t="n">
         <v>0.692701292413594</v>
@@ -10823,13 +10822,13 @@
         </is>
       </c>
       <c r="L88" s="31" t="n">
-        <v>0.428793</v>
+        <v>0.428802</v>
       </c>
       <c r="M88" s="31" t="n">
-        <v>0.219855</v>
+        <v>0.219837</v>
       </c>
       <c r="N88" s="31" t="n">
-        <v>0.351352</v>
+        <v>0.351361</v>
       </c>
       <c r="O88" s="31" t="n">
         <v>0.6884717147660365</v>
@@ -10931,13 +10930,13 @@
         </is>
       </c>
       <c r="L89" s="31" t="n">
-        <v>0.349919</v>
+        <v>0.349928</v>
       </c>
       <c r="M89" s="31" t="n">
-        <v>0.224855</v>
+        <v>0.224837</v>
       </c>
       <c r="N89" s="31" t="n">
-        <v>0.425226</v>
+        <v>0.425236</v>
       </c>
       <c r="O89" s="31" t="n">
         <v>0.6639022170684276</v>
@@ -11039,19 +11038,19 @@
         </is>
       </c>
       <c r="L90" s="31" t="n">
-        <v>0.3996490176352145</v>
+        <v>0.399673031451362</v>
       </c>
       <c r="M90" s="31" t="n">
-        <v>0.2667843924687136</v>
+        <v>0.2667363648364188</v>
       </c>
       <c r="N90" s="31" t="n">
-        <v>0.3335665898960719</v>
+        <v>0.3335906037122193</v>
       </c>
       <c r="O90" s="31" t="n">
         <v>0.5219188975037713</v>
       </c>
       <c r="P90" s="31" t="n">
-        <v>0.4780811024962288</v>
+        <v>0.4780811024962287</v>
       </c>
       <c r="Q90" s="30" t="n">
         <v>1</v>
@@ -11151,13 +11150,13 @@
         </is>
       </c>
       <c r="L91" s="31" t="n">
-        <v>0.466859</v>
+        <v>0.466868</v>
       </c>
       <c r="M91" s="31" t="n">
-        <v>0.226953</v>
+        <v>0.226934</v>
       </c>
       <c r="N91" s="31" t="n">
-        <v>0.306188</v>
+        <v>0.306198</v>
       </c>
       <c r="O91" s="31" t="n">
         <v>0.642169075997571</v>
@@ -11259,13 +11258,13 @@
         </is>
       </c>
       <c r="L92" s="31" t="n">
-        <v>0.487891</v>
+        <v>0.487864</v>
       </c>
       <c r="M92" s="31" t="n">
-        <v>0.217696</v>
+        <v>0.217749</v>
       </c>
       <c r="N92" s="31" t="n">
-        <v>0.294413</v>
+        <v>0.294387</v>
       </c>
       <c r="O92" s="31" t="n">
         <v>0.6764492201281175</v>
@@ -11367,13 +11366,13 @@
         </is>
       </c>
       <c r="L93" s="31" t="n">
-        <v>0.429886</v>
+        <v>0.429895</v>
       </c>
       <c r="M93" s="31" t="n">
-        <v>0.220044</v>
+        <v>0.220026</v>
       </c>
       <c r="N93" s="31" t="n">
-        <v>0.35007</v>
+        <v>0.350079</v>
       </c>
       <c r="O93" s="31" t="n">
         <v>0.6873848456576175</v>
@@ -11475,13 +11474,13 @@
         </is>
       </c>
       <c r="L94" s="31" t="n">
-        <v>0.487216</v>
+        <v>0.487225</v>
       </c>
       <c r="M94" s="31" t="n">
-        <v>0.226545</v>
+        <v>0.226525</v>
       </c>
       <c r="N94" s="31" t="n">
-        <v>0.28624</v>
+        <v>0.286249</v>
       </c>
       <c r="O94" s="31" t="n">
         <v>0.634300558214799</v>
@@ -11567,13 +11566,13 @@
         </is>
       </c>
       <c r="F95" s="29" t="n">
-        <v>1.89</v>
+        <v>1.28</v>
       </c>
       <c r="G95" s="29" t="n">
-        <v>3.41</v>
+        <v>4.66</v>
       </c>
       <c r="H95" s="29" t="n">
-        <v>4.68</v>
+        <v>18.23</v>
       </c>
       <c r="I95" s="29" t="n"/>
       <c r="J95" s="29" t="n"/>
@@ -11583,25 +11582,25 @@
         </is>
       </c>
       <c r="L95" s="31" t="n">
-        <v>0.483256</v>
+        <v>0.483227</v>
       </c>
       <c r="M95" s="31" t="n">
-        <v>0.226898</v>
+        <v>0.226956</v>
       </c>
       <c r="N95" s="31" t="n">
-        <v>0.289845</v>
+        <v>0.289816</v>
       </c>
       <c r="O95" s="31" t="n">
         <v>0.6302198486764455</v>
       </c>
       <c r="P95" s="31" t="n">
-        <v>0.3697801513235545</v>
+        <v>0.3697801513235544</v>
       </c>
       <c r="Q95" s="35" t="n"/>
       <c r="R95" s="35" t="n"/>
       <c r="S95" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (29%&lt;33%)</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T95" s="28" t="inlineStr">
@@ -11671,13 +11670,13 @@
         </is>
       </c>
       <c r="F96" s="29" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="G96" s="29" t="n">
         <v>3.17</v>
       </c>
       <c r="H96" s="29" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="I96" s="29" t="n">
         <v>2.07</v>
@@ -11691,13 +11690,13 @@
         </is>
       </c>
       <c r="L96" s="31" t="n">
-        <v>0.444886</v>
+        <v>0.444856</v>
       </c>
       <c r="M96" s="31" t="n">
-        <v>0.230066</v>
+        <v>0.230125</v>
       </c>
       <c r="N96" s="31" t="n">
-        <v>0.325048</v>
+        <v>0.325019</v>
       </c>
       <c r="O96" s="31" t="n">
         <v>0.6295043800536333</v>
@@ -11778,13 +11777,13 @@
         </is>
       </c>
       <c r="F97" s="29" t="n">
-        <v>2.48</v>
+        <v>2.29</v>
       </c>
       <c r="G97" s="29" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="H97" s="29" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="I97" s="29" t="n"/>
       <c r="J97" s="29" t="n"/>
@@ -11794,13 +11793,13 @@
         </is>
       </c>
       <c r="L97" s="31" t="n">
-        <v>0.5154086240810365</v>
+        <v>0.5154327452571092</v>
       </c>
       <c r="M97" s="31" t="n">
-        <v>0.2687683529110076</v>
+        <v>0.268720110558862</v>
       </c>
       <c r="N97" s="31" t="n">
-        <v>0.215823023007956</v>
+        <v>0.2158471441840288</v>
       </c>
       <c r="O97" s="31" t="n">
         <v>0.4462706911952379</v>
@@ -11897,25 +11896,30 @@
         </is>
       </c>
       <c r="L98" s="31" t="n">
-        <v>0.477986</v>
+        <v>0.450514</v>
       </c>
       <c r="M98" s="31" t="n">
-        <v>0.214848</v>
+        <v>0.199854</v>
       </c>
       <c r="N98" s="31" t="n">
-        <v>0.307166</v>
+        <v>0.349632</v>
       </c>
       <c r="O98" s="31" t="n">
-        <v>0.6963520928617232</v>
+        <v>0.7817409540483304</v>
       </c>
       <c r="P98" s="31" t="n">
-        <v>0.3036479071382768</v>
-      </c>
-      <c r="Q98" s="35" t="n"/>
-      <c r="R98" s="35" t="n"/>
-      <c r="S98" s="28">
-        <f>IF(OR(Q98="",R98=""),"[APOSTAR] LOCAL",IF(Q98&gt;R98,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+        <v>0.2182590459516696</v>
+      </c>
+      <c r="Q98" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R98" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" s="28" t="inlineStr">
+        <is>
+          <t>[PERDIDA] LOCAL</t>
+        </is>
       </c>
       <c r="T98" s="28" t="inlineStr">
         <is>
@@ -11949,7 +11953,7 @@
         <v/>
       </c>
       <c r="AB98" s="34" t="n">
-        <v>0.8167</v>
+        <v>0.7733</v>
       </c>
       <c r="AC98" s="30" t="inlineStr">
         <is>
@@ -11984,13 +11988,13 @@
         </is>
       </c>
       <c r="F99" s="29" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="G99" s="29" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="H99" s="29" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="I99" s="29" t="n"/>
       <c r="J99" s="29" t="n"/>
@@ -12000,13 +12004,13 @@
         </is>
       </c>
       <c r="L99" s="31" t="n">
-        <v>0.474014</v>
+        <v>0.473978</v>
       </c>
       <c r="M99" s="31" t="n">
-        <v>0.258841</v>
+        <v>0.258912</v>
       </c>
       <c r="N99" s="31" t="n">
-        <v>0.267145</v>
+        <v>0.267109</v>
       </c>
       <c r="O99" s="31" t="n">
         <v>0.4771663073686631</v>
@@ -12018,7 +12022,7 @@
       <c r="R99" s="35" t="n"/>
       <c r="S99" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.033&lt;0.080)</t>
+          <t>[PASAR] EV Insuf (0.047&lt;0.080)</t>
         </is>
       </c>
       <c r="T99" s="28" t="inlineStr">
@@ -12108,13 +12112,13 @@
         </is>
       </c>
       <c r="L100" s="31" t="n">
-        <v>0.3993915632237725</v>
+        <v>0.3994009931944392</v>
       </c>
       <c r="M100" s="31" t="n">
-        <v>0.232987014908538</v>
+        <v>0.2329681549672047</v>
       </c>
       <c r="N100" s="31" t="n">
-        <v>0.3676214218676895</v>
+        <v>0.3676308518383561</v>
       </c>
       <c r="O100" s="31" t="n">
         <v>0.6703629857151495</v>
@@ -12216,25 +12220,30 @@
         </is>
       </c>
       <c r="L101" s="31" t="n">
-        <v>0.453616</v>
+        <v>0.478911</v>
       </c>
       <c r="M101" s="31" t="n">
-        <v>0.237596</v>
+        <v>0.221722</v>
       </c>
       <c r="N101" s="31" t="n">
-        <v>0.308788</v>
+        <v>0.299368</v>
       </c>
       <c r="O101" s="31" t="n">
-        <v>0.5933963385823751</v>
+        <v>0.6638038731229567</v>
       </c>
       <c r="P101" s="31" t="n">
-        <v>0.4066036614176248</v>
-      </c>
-      <c r="Q101" s="35" t="n"/>
-      <c r="R101" s="35" t="n"/>
-      <c r="S101" s="28">
-        <f>IF(OR(Q101="",R101=""),"[APOSTAR] LOCAL",IF(Q101&gt;R101,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+        <v>0.3361961268770433</v>
+      </c>
+      <c r="Q101" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R101" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" s="28" t="inlineStr">
+        <is>
+          <t>[GANADA] LOCAL</t>
+        </is>
       </c>
       <c r="T101" s="28" t="inlineStr">
         <is>
@@ -12268,7 +12277,7 @@
         <v/>
       </c>
       <c r="AB101" s="34" t="n">
-        <v>0.7782</v>
+        <v>0.7889</v>
       </c>
       <c r="AC101" s="30" t="inlineStr">
         <is>
@@ -12303,13 +12312,13 @@
         </is>
       </c>
       <c r="F102" s="29" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="G102" s="29" t="n">
-        <v>4.77</v>
+        <v>2.92</v>
       </c>
       <c r="H102" s="29" t="n">
-        <v>9.779999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="I102" s="29" t="n">
         <v>1.93</v>
@@ -12323,13 +12332,13 @@
         </is>
       </c>
       <c r="L102" s="31" t="n">
-        <v>0.5663147973463485</v>
+        <v>0.5662821398952622</v>
       </c>
       <c r="M102" s="31" t="n">
-        <v>0.2380797601822919</v>
+        <v>0.2381450750844643</v>
       </c>
       <c r="N102" s="31" t="n">
-        <v>0.1956054424713596</v>
+        <v>0.1955727850202735</v>
       </c>
       <c r="O102" s="31" t="n">
         <v>0.5267138998639872</v>
@@ -12346,7 +12355,7 @@
       </c>
       <c r="T102" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Valor</t>
+          <t>[PASAR] xG Margen Insuf (2.78, delta=0.28&lt;0.30)</t>
         </is>
       </c>
       <c r="U102" s="32" t="n">
@@ -12421,22 +12430,26 @@
         </is>
       </c>
       <c r="L103" s="31" t="n">
-        <v>0.3689656880715366</v>
+        <v>0.3457634471517051</v>
       </c>
       <c r="M103" s="31" t="n">
-        <v>0.2960101675412269</v>
+        <v>0.266392885382093</v>
       </c>
       <c r="N103" s="31" t="n">
-        <v>0.3350241443872364</v>
+        <v>0.3878436674662018</v>
       </c>
       <c r="O103" s="31" t="n">
-        <v>0.4097861749290452</v>
+        <v>0.5254035034935817</v>
       </c>
       <c r="P103" s="31" t="n">
-        <v>0.5902138250709547</v>
-      </c>
-      <c r="Q103" s="35" t="n"/>
-      <c r="R103" s="35" t="n"/>
+        <v>0.4745964965064183</v>
+      </c>
+      <c r="Q103" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="30" t="n">
+        <v>3</v>
+      </c>
       <c r="S103" s="28" t="inlineStr">
         <is>
           <t>[PASAR] Sin Cuotas</t>
@@ -12474,7 +12487,7 @@
         <v/>
       </c>
       <c r="AB103" s="34" t="n">
-        <v>0.6372</v>
+        <v>0.6571</v>
       </c>
       <c r="AC103" s="30" t="inlineStr">
         <is>
@@ -12509,13 +12522,13 @@
         </is>
       </c>
       <c r="F104" s="29" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G104" s="29" t="n">
-        <v>3.99</v>
+        <v>3.94</v>
       </c>
       <c r="H104" s="29" t="n">
-        <v>5.91</v>
+        <v>5.8</v>
       </c>
       <c r="I104" s="29" t="n">
         <v>1.83</v>
@@ -12529,13 +12542,13 @@
         </is>
       </c>
       <c r="L104" s="31" t="n">
-        <v>0.518011</v>
+        <v>0.517981</v>
       </c>
       <c r="M104" s="31" t="n">
-        <v>0.225553</v>
+        <v>0.225612</v>
       </c>
       <c r="N104" s="31" t="n">
-        <v>0.256436</v>
+        <v>0.256407</v>
       </c>
       <c r="O104" s="31" t="n">
         <v>0.6141062694228666</v>
@@ -12617,16 +12630,16 @@
         </is>
       </c>
       <c r="F105" s="29" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G105" s="29" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="H105" s="29" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="I105" s="29" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="J105" s="29" t="n">
         <v>1.83</v>
@@ -12637,13 +12650,13 @@
         </is>
       </c>
       <c r="L105" s="31" t="n">
-        <v>0.5492606578971941</v>
+        <v>0.5492294420724316</v>
       </c>
       <c r="M105" s="31" t="n">
-        <v>0.2319231664305118</v>
+        <v>0.2319855980800367</v>
       </c>
       <c r="N105" s="31" t="n">
-        <v>0.2188161756722942</v>
+        <v>0.2187849598475317</v>
       </c>
       <c r="O105" s="31" t="n">
         <v>0.5810405925258193</v>
@@ -12724,13 +12737,13 @@
         </is>
       </c>
       <c r="F106" s="29" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="G106" s="29" t="n">
-        <v>3.76</v>
+        <v>5.51</v>
       </c>
       <c r="H106" s="29" t="n">
-        <v>6.13</v>
+        <v>21.55</v>
       </c>
       <c r="I106" s="29" t="n"/>
       <c r="J106" s="29" t="n"/>
@@ -12740,13 +12753,13 @@
         </is>
       </c>
       <c r="L106" s="31" t="n">
-        <v>0.5183748905984021</v>
+        <v>0.5183983985553006</v>
       </c>
       <c r="M106" s="31" t="n">
-        <v>0.259841450751463</v>
+        <v>0.2597944348376662</v>
       </c>
       <c r="N106" s="31" t="n">
-        <v>0.2217836586501349</v>
+        <v>0.2218071666070332</v>
       </c>
       <c r="O106" s="31" t="n">
         <v>0.4844492602992937</v>
@@ -12844,13 +12857,13 @@
         </is>
       </c>
       <c r="L107" s="31" t="n">
-        <v>0.509002</v>
+        <v>0.509023</v>
       </c>
       <c r="M107" s="31" t="n">
-        <v>0.236182</v>
+        <v>0.236141</v>
       </c>
       <c r="N107" s="31" t="n">
-        <v>0.254816</v>
+        <v>0.254837</v>
       </c>
       <c r="O107" s="31" t="n">
         <v>0.5770269103124676</v>
@@ -12952,13 +12965,13 @@
         </is>
       </c>
       <c r="L108" s="31" t="n">
-        <v>0.466264</v>
+        <v>0.466273</v>
       </c>
       <c r="M108" s="31" t="n">
-        <v>0.221153</v>
+        <v>0.221135</v>
       </c>
       <c r="N108" s="31" t="n">
-        <v>0.312583</v>
+        <v>0.312592</v>
       </c>
       <c r="O108" s="31" t="n">
         <v>0.6723378196207546</v>
@@ -13064,13 +13077,13 @@
         </is>
       </c>
       <c r="L109" s="31" t="n">
-        <v>0.442531</v>
+        <v>0.442506</v>
       </c>
       <c r="M109" s="31" t="n">
-        <v>0.214755</v>
+        <v>0.214805</v>
       </c>
       <c r="N109" s="31" t="n">
-        <v>0.342714</v>
+        <v>0.342689</v>
       </c>
       <c r="O109" s="31" t="n">
         <v>0.7081521294456694</v>
@@ -13172,13 +13185,13 @@
         </is>
       </c>
       <c r="L110" s="31" t="n">
-        <v>0.5564058544729272</v>
+        <v>0.5564289591644533</v>
       </c>
       <c r="M110" s="31" t="n">
-        <v>0.2582842926994595</v>
+        <v>0.2582380833164074</v>
       </c>
       <c r="N110" s="31" t="n">
-        <v>0.1853098528276132</v>
+        <v>0.1853329575191393</v>
       </c>
       <c r="O110" s="31" t="n">
         <v>0.4497533845612681</v>
@@ -13263,7 +13276,7 @@
         <v>3.49</v>
       </c>
       <c r="G111" s="29" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="H111" s="29" t="n">
         <v>2.07</v>
@@ -13363,13 +13376,13 @@
         </is>
       </c>
       <c r="F112" s="29" t="n">
-        <v>3.16</v>
+        <v>2.94</v>
       </c>
       <c r="G112" s="29" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="H112" s="29" t="n">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="I112" s="29" t="n"/>
       <c r="J112" s="29" t="n"/>
@@ -13379,13 +13392,13 @@
         </is>
       </c>
       <c r="L112" s="31" t="n">
-        <v>0.3333326837740704</v>
+        <v>0.3333452995346447</v>
       </c>
       <c r="M112" s="31" t="n">
-        <v>0.2768377365086844</v>
+        <v>0.2768125049875358</v>
       </c>
       <c r="N112" s="31" t="n">
-        <v>0.3898295797172452</v>
+        <v>0.3898421954778195</v>
       </c>
       <c r="O112" s="31" t="n">
         <v>0.4735064796585714</v>
@@ -13397,7 +13410,7 @@
       <c r="R112" s="35" t="n"/>
       <c r="S112" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.053&lt;0.120)</t>
+          <t>[PASAR] EV Insuf (0.045&lt;0.120)</t>
         </is>
       </c>
       <c r="T112" s="28" t="inlineStr">
@@ -13467,10 +13480,10 @@
         </is>
       </c>
       <c r="F113" s="29" t="n">
-        <v>8.06</v>
+        <v>8.08</v>
       </c>
       <c r="G113" s="29" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="H113" s="29" t="n">
         <v>1.3</v>
@@ -13571,13 +13584,13 @@
         </is>
       </c>
       <c r="F114" s="29" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="G114" s="29" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="H114" s="29" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="I114" s="29" t="n"/>
       <c r="J114" s="29" t="n"/>
@@ -13605,7 +13618,7 @@
       <c r="R114" s="35" t="n"/>
       <c r="S114" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.038&lt;0.080)</t>
+          <t>[PASAR] EV Insuf (0.062&lt;0.080)</t>
         </is>
       </c>
       <c r="T114" s="28" t="inlineStr">
@@ -13778,13 +13791,13 @@
         </is>
       </c>
       <c r="F116" s="29" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="G116" s="29" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="H116" s="29" t="n">
-        <v>6.14</v>
+        <v>6.2</v>
       </c>
       <c r="I116" s="29" t="n"/>
       <c r="J116" s="29" t="n"/>
@@ -13882,13 +13895,13 @@
         </is>
       </c>
       <c r="F117" s="29" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="G117" s="29" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="H117" s="29" t="n">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="I117" s="29" t="n"/>
       <c r="J117" s="29" t="n"/>
@@ -14109,13 +14122,13 @@
         </is>
       </c>
       <c r="L119" s="31" t="n">
-        <v>0.3888341022581325</v>
+        <v>0.388859915461245</v>
       </c>
       <c r="M119" s="31" t="n">
-        <v>0.2862072184034586</v>
+        <v>0.2861555919972337</v>
       </c>
       <c r="N119" s="31" t="n">
-        <v>0.3249586793384088</v>
+        <v>0.3249844925415213</v>
       </c>
       <c r="O119" s="31" t="n">
         <v>0.4438155267438119</v>
@@ -14320,13 +14333,13 @@
         </is>
       </c>
       <c r="L121" s="31" t="n">
-        <v>0.3980929690869996</v>
+        <v>0.3981045687317345</v>
       </c>
       <c r="M121" s="31" t="n">
-        <v>0.2586017920120435</v>
+        <v>0.2585785927225737</v>
       </c>
       <c r="N121" s="31" t="n">
-        <v>0.3433052389009569</v>
+        <v>0.3433168385456918</v>
       </c>
       <c r="O121" s="31" t="n">
         <v>0.5506715830807075</v>
@@ -14427,13 +14440,13 @@
         </is>
       </c>
       <c r="L122" s="31" t="n">
-        <v>0.43794</v>
+        <v>0.437952</v>
       </c>
       <c r="M122" s="31" t="n">
-        <v>0.262175</v>
+        <v>0.262151</v>
       </c>
       <c r="N122" s="31" t="n">
-        <v>0.299884</v>
+        <v>0.299896</v>
       </c>
       <c r="O122" s="31" t="n">
         <v>0.4828233891977304</v>
@@ -14450,7 +14463,7 @@
       </c>
       <c r="T122" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] xG Margen Insuf (2.61, delta=0.11&lt;0.25)</t>
+          <t>[PASAR] xG Margen Insuf (2.61, delta=0.11&lt;0.30)</t>
         </is>
       </c>
       <c r="U122" s="32" t="n">
@@ -14531,13 +14544,13 @@
         </is>
       </c>
       <c r="L123" s="31" t="n">
-        <v>0.5489449484467983</v>
+        <v>0.5489562062163815</v>
       </c>
       <c r="M123" s="31" t="n">
-        <v>0.2470220433885786</v>
+        <v>0.2469995278494123</v>
       </c>
       <c r="N123" s="31" t="n">
-        <v>0.2040330081646231</v>
+        <v>0.2040442659342062</v>
       </c>
       <c r="O123" s="31" t="n">
         <v>0.5066134159402413</v>
@@ -14619,19 +14632,19 @@
         </is>
       </c>
       <c r="F124" s="29" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G124" s="29" t="n">
-        <v>3.79</v>
+        <v>3.86</v>
       </c>
       <c r="H124" s="29" t="n">
-        <v>4.35</v>
+        <v>4.45</v>
       </c>
       <c r="I124" s="29" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="J124" s="29" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="K124" s="30" t="inlineStr">
         <is>
@@ -14726,9 +14739,15 @@
           <t>Aldosivi</t>
         </is>
       </c>
-      <c r="F125" s="29" t="n"/>
-      <c r="G125" s="29" t="n"/>
-      <c r="H125" s="29" t="n"/>
+      <c r="F125" s="29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G125" s="29" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H125" s="29" t="n">
+        <v>5.89</v>
+      </c>
       <c r="I125" s="29" t="n"/>
       <c r="J125" s="29" t="n"/>
       <c r="K125" s="30" t="inlineStr">
@@ -14737,13 +14756,13 @@
         </is>
       </c>
       <c r="L125" s="31" t="n">
-        <v>0.471476</v>
+        <v>0.471501</v>
       </c>
       <c r="M125" s="31" t="n">
-        <v>0.28589</v>
+        <v>0.28584</v>
       </c>
       <c r="N125" s="31" t="n">
-        <v>0.242634</v>
+        <v>0.242659</v>
       </c>
       <c r="O125" s="31" t="n">
         <v>0.377017356090305</v>
@@ -14755,7 +14774,7 @@
       <c r="R125" s="35" t="n"/>
       <c r="S125" s="28" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T125" s="28" t="inlineStr">
@@ -14877,7 +14896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15012,17 +15031,17 @@
       </c>
       <c r="B5" s="42" t="inlineStr">
         <is>
-          <t>San Lorenzo vs Defensa y Justicia</t>
+          <t>Chapecoense vs Gremio</t>
         </is>
       </c>
       <c r="C5" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E5" s="43" t="n">
@@ -15030,15 +15049,15 @@
       </c>
       <c r="F5" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="G5" s="45" t="n">
-        <v>6750</v>
+        <v>-2500</v>
       </c>
       <c r="H5" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I5" s="43" t="n">
@@ -15046,35 +15065,35 @@
       </c>
       <c r="J5" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K5" s="45" t="n">
-        <v>6750</v>
+        <v>-2500</v>
       </c>
       <c r="L5" s="46" t="n">
         <v>0</v>
       </c>
       <c r="M5" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N5" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="47" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="B6" s="48" t="inlineStr">
         <is>
-          <t>Central Córdoba (santiago del Estero) vs Deportivo Riestra</t>
+          <t>San Lorenzo vs Defensa y Justicia</t>
         </is>
       </c>
       <c r="C6" s="47" t="inlineStr">
@@ -15084,45 +15103,45 @@
       </c>
       <c r="D6" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E6" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="F6" s="44" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G6" s="45" t="n">
-        <v>4750</v>
+      <c r="G6" s="51" t="n">
+        <v>6750</v>
       </c>
       <c r="H6" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I6" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J6" s="44" t="inlineStr">
+      <c r="J6" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K6" s="45" t="n">
-        <v>4750</v>
+      <c r="K6" s="51" t="n">
+        <v>6750</v>
       </c>
       <c r="L6" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="M6" s="44" t="inlineStr">
+      <c r="M6" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N6" s="44" t="inlineStr">
+      <c r="N6" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -15131,17 +15150,17 @@
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="B7" s="42" t="inlineStr">
         <is>
-          <t>Goztepe vs Galatasaray</t>
+          <t>Central Córdoba (santiago del Estero) vs Deportivo Riestra</t>
         </is>
       </c>
       <c r="C7" s="41" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D7" s="42" t="inlineStr">
@@ -15154,10 +15173,12 @@
       </c>
       <c r="F7" s="50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="G7" s="49" t="n"/>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G7" s="51" t="n">
+        <v>4750</v>
+      </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -15168,36 +15189,40 @@
       </c>
       <c r="J7" s="50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K7" s="49" t="n"/>
-      <c r="L7" s="49" t="n"/>
-      <c r="M7" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K7" s="51" t="n">
+        <v>4750</v>
+      </c>
+      <c r="L7" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N7" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="47" t="inlineStr">
         <is>
-          <t>20/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="B8" s="48" t="inlineStr">
         <is>
-          <t>AFC Bournemouth vs Manchester United</t>
+          <t>Goztepe vs Galatasaray</t>
         </is>
       </c>
       <c r="C8" s="47" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D8" s="48" t="inlineStr">
@@ -15208,14 +15233,12 @@
       <c r="E8" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="F8" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G8" s="52" t="n">
-        <v>-2500</v>
-      </c>
+      <c r="F8" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G8" s="49" t="n"/>
       <c r="H8" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -15224,85 +15247,83 @@
       <c r="I8" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J8" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K8" s="52" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L8" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N8" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J8" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="41" t="inlineStr">
         <is>
-          <t>21/03/2026</t>
+          <t>20/03/2026</t>
         </is>
       </c>
       <c r="B9" s="42" t="inlineStr">
         <is>
-          <t>Atlético Tucumán vs Gimnasia la Plata</t>
+          <t>AFC Bournemouth vs Manchester United</t>
         </is>
       </c>
       <c r="C9" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.041&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="E9" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F9" s="44" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G9" s="45" t="n">
+        <v>-2500</v>
+      </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I9" s="43" t="n">
-        <v>1779.49</v>
+        <v>2500</v>
       </c>
       <c r="J9" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K9" s="45" t="n">
-        <v>2064.21</v>
-      </c>
-      <c r="L9" s="49" t="n"/>
-      <c r="M9" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-2500</v>
+      </c>
+      <c r="L9" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N9" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15335,7 @@
       </c>
       <c r="B10" s="48" t="inlineStr">
         <is>
-          <t>Banfield vs Tigre</t>
+          <t>Atlético Tucumán vs Gimnasia la Plata</t>
         </is>
       </c>
       <c r="C10" s="47" t="inlineStr">
@@ -15324,45 +15345,43 @@
       </c>
       <c r="D10" s="48" t="inlineStr">
         <is>
+          <t>[PASAR] EV Insuf (0.041&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="48" t="inlineStr">
+        <is>
           <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
-      <c r="E10" s="49" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F10" s="44" t="inlineStr">
+      <c r="I10" s="49" t="n">
+        <v>1781.72</v>
+      </c>
+      <c r="J10" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G10" s="45" t="n">
-        <v>2886.76</v>
-      </c>
-      <c r="H10" s="48" t="inlineStr">
-        <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I10" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J10" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K10" s="45" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L10" s="52" t="n">
-        <v>-2113.24</v>
-      </c>
-      <c r="M10" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N10" s="44" t="inlineStr">
+      <c r="K10" s="51" t="n">
+        <v>2066.8</v>
+      </c>
+      <c r="L10" s="49" t="n"/>
+      <c r="M10" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -15376,12 +15395,12 @@
       </c>
       <c r="B11" s="42" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion vs Liverpool</t>
+          <t>Banfield vs Tigre</t>
         </is>
       </c>
       <c r="C11" s="41" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D11" s="42" t="inlineStr">
@@ -15390,15 +15409,15 @@
         </is>
       </c>
       <c r="E11" s="43" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F11" s="44" t="inlineStr">
+        <v>1443.38</v>
+      </c>
+      <c r="F11" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G11" s="45" t="n">
-        <v>5625</v>
+      <c r="G11" s="51" t="n">
+        <v>2886.76</v>
       </c>
       <c r="H11" s="42" t="inlineStr">
         <is>
@@ -15408,23 +15427,23 @@
       <c r="I11" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J11" s="44" t="inlineStr">
+      <c r="J11" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K11" s="45" t="n">
-        <v>5625</v>
-      </c>
-      <c r="L11" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="44" t="inlineStr">
+      <c r="K11" s="51" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L11" s="45" t="n">
+        <v>-2113.24</v>
+      </c>
+      <c r="M11" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N11" s="44" t="inlineStr">
+      <c r="N11" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -15438,12 +15457,12 @@
       </c>
       <c r="B12" s="48" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs Unión (santa Fe)</t>
+          <t>Brighton &amp; Hove Albion vs Liverpool</t>
         </is>
       </c>
       <c r="C12" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D12" s="48" t="inlineStr">
@@ -15452,15 +15471,15 @@
         </is>
       </c>
       <c r="E12" s="49" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F12" s="44" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="F12" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G12" s="45" t="n">
-        <v>2742.42</v>
+      <c r="G12" s="51" t="n">
+        <v>5625</v>
       </c>
       <c r="H12" s="48" t="inlineStr">
         <is>
@@ -15470,23 +15489,23 @@
       <c r="I12" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J12" s="44" t="inlineStr">
+      <c r="J12" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K12" s="45" t="n">
-        <v>4750</v>
-      </c>
-      <c r="L12" s="52" t="n">
-        <v>-2007.58</v>
-      </c>
-      <c r="M12" s="44" t="inlineStr">
+      <c r="K12" s="51" t="n">
+        <v>5625</v>
+      </c>
+      <c r="L12" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N12" s="44" t="inlineStr">
+      <c r="N12" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -15500,7 +15519,7 @@
       </c>
       <c r="B13" s="42" t="inlineStr">
         <is>
-          <t>Newell's Old Boys vs Gimnasia (mendoza)</t>
+          <t>Defensa y Justicia vs Unión (santa Fe)</t>
         </is>
       </c>
       <c r="C13" s="41" t="inlineStr">
@@ -15510,47 +15529,47 @@
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E13" s="43" t="n">
         <v>1443.38</v>
       </c>
-      <c r="F13" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G13" s="52" t="n">
-        <v>-1443.38</v>
+      <c r="F13" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="n">
+        <v>2742.42</v>
       </c>
       <c r="H13" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I13" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J13" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K13" s="52" t="n">
-        <v>-2500</v>
+      <c r="J13" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K13" s="51" t="n">
+        <v>4750</v>
       </c>
       <c r="L13" s="45" t="n">
-        <v>1056.62</v>
-      </c>
-      <c r="M13" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N13" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>-2007.58</v>
+      </c>
+      <c r="M13" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N13" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -15562,33 +15581,33 @@
       </c>
       <c r="B14" s="48" t="inlineStr">
         <is>
-          <t>Viking fk vs Molde</t>
+          <t>Newell's Old Boys vs Gimnasia (mendoza)</t>
         </is>
       </c>
       <c r="C14" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D14" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E14" s="49" t="n">
-        <v>2500</v>
+        <v>1443.38</v>
       </c>
       <c r="F14" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="G14" s="45" t="n">
-        <v>2250</v>
+        <v>-1443.38</v>
       </c>
       <c r="H14" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I14" s="49" t="n">
@@ -15596,40 +15615,40 @@
       </c>
       <c r="J14" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K14" s="45" t="n">
-        <v>2250</v>
-      </c>
-      <c r="L14" s="46" t="n">
-        <v>0</v>
+        <v>-2500</v>
+      </c>
+      <c r="L14" s="51" t="n">
+        <v>1056.62</v>
       </c>
       <c r="M14" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N14" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="41" t="inlineStr">
         <is>
-          <t>22/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="B15" s="42" t="inlineStr">
         <is>
-          <t>Aston Villa vs West Ham United</t>
+          <t>Viking fk vs Molde</t>
         </is>
       </c>
       <c r="C15" s="41" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D15" s="42" t="inlineStr">
@@ -15638,15 +15657,15 @@
         </is>
       </c>
       <c r="E15" s="43" t="n">
-        <v>1308.71</v>
-      </c>
-      <c r="F15" s="44" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G15" s="45" t="n">
-        <v>1361.06</v>
+      <c r="G15" s="51" t="n">
+        <v>2250</v>
       </c>
       <c r="H15" s="42" t="inlineStr">
         <is>
@@ -15654,25 +15673,25 @@
         </is>
       </c>
       <c r="I15" s="43" t="n">
-        <v>2266.75</v>
-      </c>
-      <c r="J15" s="44" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="J15" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K15" s="45" t="n">
-        <v>2357.42</v>
-      </c>
-      <c r="L15" s="52" t="n">
-        <v>-996.36</v>
-      </c>
-      <c r="M15" s="44" t="inlineStr">
+      <c r="K15" s="51" t="n">
+        <v>2250</v>
+      </c>
+      <c r="L15" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N15" s="44" t="inlineStr">
+      <c r="N15" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -15686,12 +15705,12 @@
       </c>
       <c r="B16" s="48" t="inlineStr">
         <is>
-          <t>Corinthians vs Flamengo</t>
+          <t>Aston Villa vs West Ham United</t>
         </is>
       </c>
       <c r="C16" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D16" s="48" t="inlineStr">
@@ -15700,15 +15719,15 @@
         </is>
       </c>
       <c r="E16" s="49" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F16" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G16" s="52" t="n">
-        <v>-1443.38</v>
+        <v>1308.71</v>
+      </c>
+      <c r="F16" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="n">
+        <v>1361.06</v>
       </c>
       <c r="H16" s="48" t="inlineStr">
         <is>
@@ -15716,27 +15735,27 @@
         </is>
       </c>
       <c r="I16" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J16" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K16" s="52" t="n">
-        <v>-2500</v>
+        <v>2266.75</v>
+      </c>
+      <c r="J16" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K16" s="51" t="n">
+        <v>2357.42</v>
       </c>
       <c r="L16" s="45" t="n">
-        <v>1056.62</v>
-      </c>
-      <c r="M16" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N16" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+        <v>-996.36</v>
+      </c>
+      <c r="M16" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N16" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -15748,7 +15767,7 @@
       </c>
       <c r="B17" s="42" t="inlineStr">
         <is>
-          <t>Remo vs Bahia</t>
+          <t>Corinthians vs Flamengo</t>
         </is>
       </c>
       <c r="C17" s="41" t="inlineStr">
@@ -15766,11 +15785,11 @@
       </c>
       <c r="F17" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="G17" s="45" t="n">
-        <v>3882.69</v>
+        <v>-1443.38</v>
       </c>
       <c r="H17" s="42" t="inlineStr">
         <is>
@@ -15782,23 +15801,23 @@
       </c>
       <c r="J17" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K17" s="45" t="n">
-        <v>6725</v>
-      </c>
-      <c r="L17" s="52" t="n">
-        <v>-2842.31</v>
+        <v>-2500</v>
+      </c>
+      <c r="L17" s="51" t="n">
+        <v>1056.62</v>
       </c>
       <c r="M17" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="N17" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -15810,12 +15829,12 @@
       </c>
       <c r="B18" s="48" t="inlineStr">
         <is>
-          <t>Rosenborg vs Valerenga</t>
+          <t>Remo vs Bahia</t>
         </is>
       </c>
       <c r="C18" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D18" s="48" t="inlineStr">
@@ -15824,15 +15843,15 @@
         </is>
       </c>
       <c r="E18" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G18" s="52" t="n">
-        <v>-2500</v>
+        <v>1443.38</v>
+      </c>
+      <c r="F18" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="n">
+        <v>3882.69</v>
       </c>
       <c r="H18" s="48" t="inlineStr">
         <is>
@@ -15842,25 +15861,25 @@
       <c r="I18" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J18" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K18" s="52" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N18" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J18" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K18" s="51" t="n">
+        <v>6725</v>
+      </c>
+      <c r="L18" s="45" t="n">
+        <v>-2842.31</v>
+      </c>
+      <c r="M18" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N18" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -15872,7 +15891,7 @@
       </c>
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>Sandefjord vs Sarpsborg fk</t>
+          <t>Rosenborg vs Valerenga</t>
         </is>
       </c>
       <c r="C19" s="41" t="inlineStr">
@@ -15882,45 +15901,47 @@
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.054&lt;0.120)</t>
-        </is>
-      </c>
-      <c r="E19" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F19" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G19" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E19" s="43" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F19" s="44" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G19" s="45" t="n">
+        <v>-2500</v>
+      </c>
       <c r="H19" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I19" s="43" t="n">
-        <v>1259.61</v>
+        <v>2500</v>
       </c>
       <c r="J19" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K19" s="45" t="n">
-        <v>2708.16</v>
-      </c>
-      <c r="L19" s="49" t="n"/>
-      <c r="M19" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-2500</v>
+      </c>
+      <c r="L19" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N19" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -15932,55 +15953,53 @@
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Sarmiento (junín) vs Aldosivi</t>
+          <t>Sandefjord vs Sarpsborg fk</t>
         </is>
       </c>
       <c r="C20" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E20" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F20" s="44" t="inlineStr">
+          <t>[PASAR] EV Insuf (0.054&lt;0.120)</t>
+        </is>
+      </c>
+      <c r="E20" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="48" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I20" s="49" t="n">
+        <v>1259.61</v>
+      </c>
+      <c r="J20" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G20" s="45" t="n">
-        <v>3150</v>
-      </c>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I20" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J20" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K20" s="45" t="n">
-        <v>3150</v>
-      </c>
-      <c r="L20" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N20" s="44" t="inlineStr">
+      <c r="K20" s="51" t="n">
+        <v>2708.16</v>
+      </c>
+      <c r="L20" s="49" t="n"/>
+      <c r="M20" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -15994,55 +16013,55 @@
       </c>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur vs Nottingham Forest</t>
+          <t>Sarmiento (junín) vs Aldosivi</t>
         </is>
       </c>
       <c r="C21" s="41" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D21" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E21" s="43" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F21" s="44" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="F21" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G21" s="45" t="n">
-        <v>3464.11</v>
+      <c r="G21" s="51" t="n">
+        <v>3150</v>
       </c>
       <c r="H21" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I21" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J21" s="44" t="inlineStr">
+      <c r="J21" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K21" s="45" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L21" s="52" t="n">
-        <v>-2535.89</v>
-      </c>
-      <c r="M21" s="44" t="inlineStr">
+      <c r="K21" s="51" t="n">
+        <v>3150</v>
+      </c>
+      <c r="L21" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N21" s="44" t="inlineStr">
+      <c r="N21" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16056,55 +16075,55 @@
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Vitória vs Mirassol</t>
+          <t>Tottenham Hotspur vs Nottingham Forest</t>
         </is>
       </c>
       <c r="C22" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E22" s="49" t="n">
         <v>1443.38</v>
       </c>
-      <c r="F22" s="44" t="inlineStr">
+      <c r="F22" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G22" s="45" t="n">
-        <v>2237.24</v>
+      <c r="G22" s="51" t="n">
+        <v>3464.11</v>
       </c>
       <c r="H22" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I22" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J22" s="44" t="inlineStr">
+      <c r="J22" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K22" s="45" t="n">
-        <v>3875</v>
-      </c>
-      <c r="L22" s="52" t="n">
-        <v>-1637.76</v>
-      </c>
-      <c r="M22" s="44" t="inlineStr">
+      <c r="K22" s="51" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L22" s="45" t="n">
+        <v>-2535.89</v>
+      </c>
+      <c r="M22" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N22" s="44" t="inlineStr">
+      <c r="N22" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16113,17 +16132,17 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="41" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs San Lorenzo</t>
+          <t>Vitória vs Mirassol</t>
         </is>
       </c>
       <c r="C23" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D23" s="42" t="inlineStr">
@@ -16132,15 +16151,15 @@
         </is>
       </c>
       <c r="E23" s="43" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F23" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G23" s="52" t="n">
-        <v>-2500</v>
+        <v>1443.38</v>
+      </c>
+      <c r="F23" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G23" s="51" t="n">
+        <v>2237.24</v>
       </c>
       <c r="H23" s="42" t="inlineStr">
         <is>
@@ -16150,60 +16169,60 @@
       <c r="I23" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J23" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K23" s="52" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L23" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N23" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J23" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K23" s="51" t="n">
+        <v>3875</v>
+      </c>
+      <c r="L23" s="45" t="n">
+        <v>-1637.76</v>
+      </c>
+      <c r="M23" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N23" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="47" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Bahia vs Athletico Paranaense</t>
+          <t>Deportivo Riestra vs San Lorenzo</t>
         </is>
       </c>
       <c r="C24" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E24" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E24" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F24" s="44" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G24" s="45" t="n">
+        <v>-2500</v>
+      </c>
       <c r="H24" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16214,21 +16233,23 @@
       </c>
       <c r="J24" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K24" s="45" t="n">
-        <v>8900</v>
-      </c>
-      <c r="L24" s="49" t="n"/>
-      <c r="M24" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>-2500</v>
+      </c>
+      <c r="L24" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N24" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -16240,7 +16261,7 @@
       </c>
       <c r="B25" s="42" t="inlineStr">
         <is>
-          <t>Botafogo vs Mirassol</t>
+          <t>Bahia vs Athletico Paranaense</t>
         </is>
       </c>
       <c r="C25" s="41" t="inlineStr">
@@ -16272,13 +16293,13 @@
       <c r="I25" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J25" s="44" t="inlineStr">
+      <c r="J25" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K25" s="45" t="n">
-        <v>3775</v>
+      <c r="K25" s="51" t="n">
+        <v>8900</v>
       </c>
       <c r="L25" s="49" t="n"/>
       <c r="M25" s="41" t="inlineStr">
@@ -16286,7 +16307,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N25" s="44" t="inlineStr">
+      <c r="N25" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16300,7 +16321,7 @@
       </c>
       <c r="B26" s="48" t="inlineStr">
         <is>
-          <t>Coritiba vs Vasco da Gama</t>
+          <t>Botafogo vs Mirassol</t>
         </is>
       </c>
       <c r="C26" s="47" t="inlineStr">
@@ -16310,7 +16331,7 @@
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E26" s="49" t="inlineStr">
@@ -16332,13 +16353,13 @@
       <c r="I26" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J26" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K26" s="52" t="n">
-        <v>-2500</v>
+      <c r="J26" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K26" s="51" t="n">
+        <v>3775</v>
       </c>
       <c r="L26" s="49" t="n"/>
       <c r="M26" s="47" t="inlineStr">
@@ -16346,9 +16367,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N26" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N26" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -16360,7 +16381,7 @@
       </c>
       <c r="B27" s="42" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Coritiba vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C27" s="41" t="inlineStr">
@@ -16370,7 +16391,7 @@
       </c>
       <c r="D27" s="42" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E27" s="43" t="inlineStr">
@@ -16394,11 +16415,11 @@
       </c>
       <c r="J27" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K27" s="45" t="n">
-        <v>12075</v>
+        <v>-2500</v>
       </c>
       <c r="L27" s="49" t="n"/>
       <c r="M27" s="41" t="inlineStr">
@@ -16408,7 +16429,7 @@
       </c>
       <c r="N27" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -16420,7 +16441,7 @@
       </c>
       <c r="B28" s="48" t="inlineStr">
         <is>
-          <t>Internacional vs São Paulo</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C28" s="47" t="inlineStr">
@@ -16430,7 +16451,7 @@
       </c>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E28" s="49" t="inlineStr">
@@ -16452,13 +16473,13 @@
       <c r="I28" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J28" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K28" s="52" t="n">
-        <v>-2500</v>
+      <c r="J28" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K28" s="51" t="n">
+        <v>12075</v>
       </c>
       <c r="L28" s="49" t="n"/>
       <c r="M28" s="47" t="inlineStr">
@@ -16466,26 +16487,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N28" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N28" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B29" s="42" t="inlineStr">
         <is>
-          <t>Barracas Central vs Sarmiento (junin)</t>
+          <t>Internacional vs São Paulo</t>
         </is>
       </c>
       <c r="C29" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D29" s="42" t="inlineStr">
@@ -16512,12 +16533,12 @@
       <c r="I29" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J29" s="51" t="inlineStr">
+      <c r="J29" s="44" t="inlineStr">
         <is>
           <t>PERDIDA</t>
         </is>
       </c>
-      <c r="K29" s="52" t="n">
+      <c r="K29" s="45" t="n">
         <v>-2500</v>
       </c>
       <c r="L29" s="49" t="n"/>
@@ -16526,7 +16547,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N29" s="51" t="inlineStr">
+      <c r="N29" s="44" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -16535,35 +16556,35 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="47" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B30" s="48" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Barracas Central vs Sarmiento (junin)</t>
         </is>
       </c>
       <c r="C30" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E30" s="49" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F30" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G30" s="45" t="n">
-        <v>4929.59</v>
-      </c>
+          <t>[PERDIDA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" s="49" t="n"/>
       <c r="H30" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16574,35 +16595,33 @@
       </c>
       <c r="J30" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K30" s="45" t="n">
-        <v>12075</v>
-      </c>
-      <c r="L30" s="52" t="n">
-        <v>-7145.41</v>
-      </c>
-      <c r="M30" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+        <v>-2500</v>
+      </c>
+      <c r="L30" s="49" t="n"/>
+      <c r="M30" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B31" s="42" t="inlineStr">
         <is>
-          <t>Palmeiras vs Grêmio</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C31" s="41" t="inlineStr">
@@ -16612,20 +16631,20 @@
       </c>
       <c r="D31" s="42" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E31" s="43" t="n">
+        <v>1020.62</v>
+      </c>
+      <c r="F31" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G31" s="51" t="n">
+        <v>4929.59</v>
+      </c>
       <c r="H31" s="42" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16634,21 +16653,23 @@
       <c r="I31" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J31" s="44" t="inlineStr">
+      <c r="J31" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K31" s="45" t="n">
-        <v>12575</v>
-      </c>
-      <c r="L31" s="49" t="n"/>
-      <c r="M31" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N31" s="44" t="inlineStr">
+      <c r="K31" s="51" t="n">
+        <v>12075</v>
+      </c>
+      <c r="L31" s="45" t="n">
+        <v>-7145.41</v>
+      </c>
+      <c r="M31" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N31" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16662,7 +16683,7 @@
       </c>
       <c r="B32" s="48" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino vs Flamengo</t>
+          <t>Palmeiras vs Grêmio</t>
         </is>
       </c>
       <c r="C32" s="47" t="inlineStr">
@@ -16694,13 +16715,13 @@
       <c r="I32" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J32" s="44" t="inlineStr">
+      <c r="J32" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K32" s="45" t="n">
-        <v>8550</v>
+      <c r="K32" s="51" t="n">
+        <v>12575</v>
       </c>
       <c r="L32" s="49" t="n"/>
       <c r="M32" s="47" t="inlineStr">
@@ -16708,7 +16729,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N32" s="44" t="inlineStr">
+      <c r="N32" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16722,7 +16743,7 @@
       </c>
       <c r="B33" s="42" t="inlineStr">
         <is>
-          <t>Santos vs Remo</t>
+          <t>Red Bull Bragantino vs Flamengo</t>
         </is>
       </c>
       <c r="C33" s="41" t="inlineStr">
@@ -16754,13 +16775,13 @@
       <c r="I33" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J33" s="44" t="inlineStr">
+      <c r="J33" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K33" s="45" t="n">
-        <v>12625</v>
+      <c r="K33" s="51" t="n">
+        <v>8550</v>
       </c>
       <c r="L33" s="49" t="n"/>
       <c r="M33" s="41" t="inlineStr">
@@ -16768,7 +16789,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N33" s="44" t="inlineStr">
+      <c r="N33" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16777,17 +16798,17 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="47" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B34" s="48" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
+          <t>Santos vs Remo</t>
         </is>
       </c>
       <c r="C34" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D34" s="48" t="inlineStr">
@@ -16814,13 +16835,13 @@
       <c r="I34" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J34" s="44" t="inlineStr">
+      <c r="J34" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K34" s="45" t="n">
-        <v>7750</v>
+      <c r="K34" s="51" t="n">
+        <v>12625</v>
       </c>
       <c r="L34" s="49" t="n"/>
       <c r="M34" s="47" t="inlineStr">
@@ -16828,7 +16849,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" s="44" t="inlineStr">
+      <c r="N34" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16837,35 +16858,35 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="41" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B35" s="42" t="inlineStr">
         <is>
-          <t>Palmeiras vs Gremio</t>
+          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
         </is>
       </c>
       <c r="C35" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D35" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E35" s="43" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F35" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G35" s="45" t="n">
-        <v>6900</v>
-      </c>
+          <t>[GANADA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="49" t="n"/>
       <c r="H35" s="42" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16874,23 +16895,21 @@
       <c r="I35" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J35" s="44" t="inlineStr">
+      <c r="J35" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K35" s="45" t="n">
-        <v>13800</v>
-      </c>
-      <c r="L35" s="52" t="n">
-        <v>-6900</v>
-      </c>
-      <c r="M35" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N35" s="44" t="inlineStr">
+      <c r="K35" s="51" t="n">
+        <v>7750</v>
+      </c>
+      <c r="L35" s="49" t="n"/>
+      <c r="M35" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -16899,35 +16918,35 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="47" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B36" s="48" t="inlineStr">
         <is>
-          <t>Genclerbirligi vs Goztepe</t>
+          <t>Palmeiras vs Gremio</t>
         </is>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E36" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E36" s="49" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F36" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G36" s="51" t="n">
+        <v>6900</v>
+      </c>
       <c r="H36" s="48" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -16936,23 +16955,25 @@
       <c r="I36" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J36" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K36" s="52" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L36" s="49" t="n"/>
-      <c r="M36" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N36" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J36" s="50" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K36" s="51" t="n">
+        <v>13800</v>
+      </c>
+      <c r="L36" s="45" t="n">
+        <v>-6900</v>
+      </c>
+      <c r="M36" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N36" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -16964,17 +16985,17 @@
       </c>
       <c r="B37" s="42" t="inlineStr">
         <is>
-          <t>Independiente vs Racing Club</t>
+          <t>Genclerbirligi vs Goztepe</t>
         </is>
       </c>
       <c r="C37" s="41" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D37" s="42" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E37" s="43" t="inlineStr">
@@ -16998,11 +17019,11 @@
       </c>
       <c r="J37" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K37" s="45" t="n">
-        <v>11575</v>
+        <v>-2500</v>
       </c>
       <c r="L37" s="49" t="n"/>
       <c r="M37" s="41" t="inlineStr">
@@ -17012,7 +17033,7 @@
       </c>
       <c r="N37" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -17024,17 +17045,17 @@
       </c>
       <c r="B38" s="48" t="inlineStr">
         <is>
-          <t>Kasimpasa vs Kayserispor</t>
+          <t>Independiente vs Racing Club</t>
         </is>
       </c>
       <c r="C38" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.055&lt;0.080)</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E38" s="49" t="inlineStr">
@@ -17054,15 +17075,15 @@
         </is>
       </c>
       <c r="I38" s="49" t="n">
-        <v>2186.56</v>
-      </c>
-      <c r="J38" s="44" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="J38" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K38" s="45" t="n">
-        <v>2755.07</v>
+      <c r="K38" s="51" t="n">
+        <v>11575</v>
       </c>
       <c r="L38" s="49" t="n"/>
       <c r="M38" s="47" t="inlineStr">
@@ -17070,7 +17091,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N38" s="44" t="inlineStr">
+      <c r="N38" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -17084,7 +17105,7 @@
       </c>
       <c r="B39" s="42" t="inlineStr">
         <is>
-          <t>Trabzonspor vs Galatasaray</t>
+          <t>Kasimpasa vs Kayserispor</t>
         </is>
       </c>
       <c r="C39" s="41" t="inlineStr">
@@ -17094,7 +17115,7 @@
       </c>
       <c r="D39" s="42" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.055&lt;0.080)</t>
         </is>
       </c>
       <c r="E39" s="43" t="inlineStr">
@@ -17114,15 +17135,15 @@
         </is>
       </c>
       <c r="I39" s="43" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J39" s="44" t="inlineStr">
+        <v>2187.37</v>
+      </c>
+      <c r="J39" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K39" s="45" t="n">
-        <v>6050</v>
+      <c r="K39" s="51" t="n">
+        <v>2756.09</v>
       </c>
       <c r="L39" s="49" t="n"/>
       <c r="M39" s="41" t="inlineStr">
@@ -17130,7 +17151,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N39" s="44" t="inlineStr">
+      <c r="N39" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -17139,12 +17160,12 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="47" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B40" s="48" t="inlineStr">
         <is>
-          <t>Antalyaspor vs Eyupspor</t>
+          <t>Trabzonspor vs Galatasaray</t>
         </is>
       </c>
       <c r="C40" s="47" t="inlineStr">
@@ -17154,7 +17175,7 @@
       </c>
       <c r="D40" s="48" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.077&lt;0.080)</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E40" s="49" t="inlineStr">
@@ -17176,13 +17197,13 @@
       <c r="I40" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J40" s="44" t="inlineStr">
+      <c r="J40" s="50" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K40" s="45" t="n">
-        <v>3025</v>
+      <c r="K40" s="51" t="n">
+        <v>6050</v>
       </c>
       <c r="L40" s="49" t="n"/>
       <c r="M40" s="47" t="inlineStr">
@@ -17190,7 +17211,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N40" s="44" t="inlineStr">
+      <c r="N40" s="50" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -17204,25 +17225,27 @@
       </c>
       <c r="B41" s="42" t="inlineStr">
         <is>
-          <t>Bahia vs Palmeiras</t>
+          <t>Antalyaspor vs Eyupspor</t>
         </is>
       </c>
       <c r="C41" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D41" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E41" s="43" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F41" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[PASAR] EV Insuf (0.077&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="49" t="n"/>
@@ -17236,19 +17259,21 @@
       </c>
       <c r="J41" s="50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K41" s="49" t="n"/>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K41" s="51" t="n">
+        <v>3025</v>
+      </c>
       <c r="L41" s="49" t="n"/>
       <c r="M41" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N41" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N41" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -17260,12 +17285,12 @@
       </c>
       <c r="B42" s="48" t="inlineStr">
         <is>
-          <t>Central Córdoba (santiago del Estero) vs Newell's Old Boys</t>
+          <t>Bahia vs Palmeiras</t>
         </is>
       </c>
       <c r="C42" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D42" s="48" t="inlineStr">
@@ -17274,9 +17299,9 @@
         </is>
       </c>
       <c r="E42" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F42" s="50" t="inlineStr">
+        <v>1443.38</v>
+      </c>
+      <c r="F42" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17290,7 +17315,7 @@
       <c r="I42" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J42" s="50" t="inlineStr">
+      <c r="J42" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17316,12 +17341,12 @@
       </c>
       <c r="B43" s="42" t="inlineStr">
         <is>
-          <t>Chapecoense vs Vitoria</t>
+          <t>Central Córdoba (santiago del Estero) vs Newell's Old Boys</t>
         </is>
       </c>
       <c r="C43" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D43" s="42" t="inlineStr">
@@ -17330,9 +17355,9 @@
         </is>
       </c>
       <c r="E43" s="43" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F43" s="50" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="F43" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17346,7 +17371,7 @@
       <c r="I43" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J43" s="50" t="inlineStr">
+      <c r="J43" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17372,7 +17397,7 @@
       </c>
       <c r="B44" s="48" t="inlineStr">
         <is>
-          <t>Corinthians vs Internacional</t>
+          <t>Chapecoense vs Vitoria</t>
         </is>
       </c>
       <c r="C44" s="47" t="inlineStr">
@@ -17382,7 +17407,7 @@
       </c>
       <c r="D44" s="48" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.033&lt;0.080)</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E44" s="49" t="inlineStr">
@@ -17390,9 +17415,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="F44" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G44" s="49" t="n"/>
@@ -17402,23 +17427,25 @@
         </is>
       </c>
       <c r="I44" s="49" t="n">
-        <v>1413.16</v>
-      </c>
-      <c r="J44" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K44" s="49" t="n"/>
+        <v>2500</v>
+      </c>
+      <c r="J44" s="44" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K44" s="45" t="n">
+        <v>-2500</v>
+      </c>
       <c r="L44" s="49" t="n"/>
       <c r="M44" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N44" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N44" s="44" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -17430,17 +17457,17 @@
       </c>
       <c r="B45" s="42" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük vs Caykur Rizespor</t>
+          <t>Corinthians vs Internacional</t>
         </is>
       </c>
       <c r="C45" s="41" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D45" s="42" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.047&lt;0.080)</t>
         </is>
       </c>
       <c r="E45" s="43" t="inlineStr">
@@ -17448,9 +17475,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="F45" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="G45" s="49" t="n"/>
@@ -17460,25 +17487,23 @@
         </is>
       </c>
       <c r="I45" s="43" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J45" s="44" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K45" s="45" t="n">
-        <v>5675</v>
-      </c>
+        <v>1962.45</v>
+      </c>
+      <c r="J45" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K45" s="49" t="n"/>
       <c r="L45" s="49" t="n"/>
       <c r="M45" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N45" s="44" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N45" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17490,7 +17515,7 @@
       </c>
       <c r="B46" s="48" t="inlineStr">
         <is>
-          <t>Fenerbahce vs Besiktas</t>
+          <t>Fatih Karagümrük vs Caykur Rizespor</t>
         </is>
       </c>
       <c r="C46" s="47" t="inlineStr">
@@ -17500,15 +17525,17 @@
       </c>
       <c r="D46" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E46" s="49" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F46" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E46" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G46" s="49" t="n"/>
@@ -17522,19 +17549,21 @@
       </c>
       <c r="J46" s="50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K46" s="49" t="n"/>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K46" s="51" t="n">
+        <v>5675</v>
+      </c>
       <c r="L46" s="49" t="n"/>
       <c r="M46" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N46" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N46" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -17546,25 +17575,27 @@
       </c>
       <c r="B47" s="42" t="inlineStr">
         <is>
-          <t>Mirassol vs Red Bull Bragantino</t>
+          <t>Fenerbahce vs Besiktas</t>
         </is>
       </c>
       <c r="C47" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D47" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E47" s="43" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F47" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G47" s="49" t="n"/>
@@ -17578,19 +17609,21 @@
       </c>
       <c r="J47" s="50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K47" s="49" t="n"/>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K47" s="51" t="n">
+        <v>4225</v>
+      </c>
       <c r="L47" s="49" t="n"/>
       <c r="M47" s="41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N47" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N47" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -17602,27 +17635,25 @@
       </c>
       <c r="B48" s="48" t="inlineStr">
         <is>
-          <t>Samsunspor vs Konyaspor</t>
+          <t>Mirassol vs Red Bull Bragantino</t>
         </is>
       </c>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D48" s="48" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E48" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E48" s="49" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F48" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
         </is>
       </c>
       <c r="G48" s="49" t="n"/>
@@ -17634,45 +17665,43 @@
       <c r="I48" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J48" s="51" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K48" s="52" t="n">
-        <v>-2500</v>
-      </c>
+      <c r="J48" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K48" s="49" t="n"/>
       <c r="L48" s="49" t="n"/>
       <c r="M48" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N48" s="51" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N48" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="41" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B49" s="42" t="inlineStr">
         <is>
-          <t>Vasco da Gama vs Botafogo</t>
+          <t>Samsunspor vs Konyaspor</t>
         </is>
       </c>
       <c r="C49" s="41" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D49" s="42" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E49" s="43" t="inlineStr">
@@ -17688,7 +17717,7 @@
       <c r="G49" s="49" t="n"/>
       <c r="H49" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I49" s="43" t="n">
@@ -17696,11 +17725,11 @@
       </c>
       <c r="J49" s="44" t="inlineStr">
         <is>
-          <t>GANADA</t>
+          <t>PERDIDA</t>
         </is>
       </c>
       <c r="K49" s="45" t="n">
-        <v>7200</v>
+        <v>-2500</v>
       </c>
       <c r="L49" s="49" t="n"/>
       <c r="M49" s="41" t="inlineStr">
@@ -17710,43 +17739,45 @@
       </c>
       <c r="N49" s="44" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="47" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B50" s="48" t="inlineStr">
         <is>
-          <t>Hamkam vs Sk Brann</t>
+          <t>Vasco da Gama vs Botafogo</t>
         </is>
       </c>
       <c r="C50" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D50" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E50" s="49" t="n">
-        <v>1767.77</v>
-      </c>
-      <c r="F50" s="50" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] VISITA</t>
+        </is>
+      </c>
+      <c r="E50" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G50" s="49" t="n"/>
       <c r="H50" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I50" s="49" t="n">
@@ -17754,19 +17785,21 @@
       </c>
       <c r="J50" s="50" t="inlineStr">
         <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K50" s="49" t="n"/>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K50" s="51" t="n">
+        <v>7200</v>
+      </c>
       <c r="L50" s="49" t="n"/>
       <c r="M50" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N50" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N50" s="50" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -17778,25 +17811,23 @@
       </c>
       <c r="B51" s="42" t="inlineStr">
         <is>
-          <t>Kocaelispor vs Istanbul Basaksehir</t>
+          <t>Hamkam vs Sk Brann</t>
         </is>
       </c>
       <c r="C51" s="41" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D51" s="42" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.053&lt;0.120)</t>
-        </is>
-      </c>
-      <c r="E51" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" s="50" t="inlineStr">
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E51" s="43" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F51" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17808,9 +17839,9 @@
         </is>
       </c>
       <c r="I51" s="43" t="n">
-        <v>1234.52</v>
-      </c>
-      <c r="J51" s="50" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="J51" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17836,17 +17867,17 @@
       </c>
       <c r="B52" s="48" t="inlineStr">
         <is>
-          <t>Molde vs Lillestrom</t>
+          <t>Kocaelispor vs Istanbul Basaksehir</t>
         </is>
       </c>
       <c r="C52" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D52" s="48" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.038&lt;0.080)</t>
+          <t>[PASAR] EV Insuf (0.045&lt;0.120)</t>
         </is>
       </c>
       <c r="E52" s="49" t="inlineStr">
@@ -17854,7 +17885,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="50" t="inlineStr">
+      <c r="F52" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17862,13 +17893,13 @@
       <c r="G52" s="49" t="n"/>
       <c r="H52" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I52" s="49" t="n">
-        <v>1643.96</v>
-      </c>
-      <c r="J52" s="50" t="inlineStr">
+        <v>1332.65</v>
+      </c>
+      <c r="J52" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17894,7 +17925,7 @@
       </c>
       <c r="B53" s="42" t="inlineStr">
         <is>
-          <t>Sarpsborg fk vs Ik Start</t>
+          <t>Molde vs Lillestrom</t>
         </is>
       </c>
       <c r="C53" s="41" t="inlineStr">
@@ -17904,13 +17935,15 @@
       </c>
       <c r="D53" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E53" s="43" t="n">
-        <v>1767.77</v>
-      </c>
-      <c r="F53" s="50" t="inlineStr">
+          <t>[PASAR] EV Insuf (0.062&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E53" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17918,13 +17951,13 @@
       <c r="G53" s="49" t="n"/>
       <c r="H53" s="42" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I53" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J53" s="50" t="inlineStr">
+      <c r="J53" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17945,12 +17978,12 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="47" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B54" s="48" t="inlineStr">
         <is>
-          <t>Aalesund vs Fredrikstad</t>
+          <t>Sarpsborg fk vs Ik Start</t>
         </is>
       </c>
       <c r="C54" s="47" t="inlineStr">
@@ -17960,13 +17993,13 @@
       </c>
       <c r="D54" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E54" s="49" t="n">
         <v>1767.77</v>
       </c>
-      <c r="F54" s="50" t="inlineStr">
+      <c r="F54" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17974,13 +18007,13 @@
       <c r="G54" s="49" t="n"/>
       <c r="H54" s="48" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I54" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J54" s="50" t="inlineStr">
+      <c r="J54" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -18001,17 +18034,17 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="41" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B55" s="42" t="inlineStr">
         <is>
-          <t>Goztepe vs Galatasaray</t>
+          <t>Aalesund vs Fredrikstad</t>
         </is>
       </c>
       <c r="C55" s="41" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D55" s="42" t="inlineStr">
@@ -18020,9 +18053,9 @@
         </is>
       </c>
       <c r="E55" s="43" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F55" s="50" t="inlineStr">
+        <v>1767.77</v>
+      </c>
+      <c r="F55" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -18036,7 +18069,7 @@
       <c r="I55" s="43" t="n">
         <v>2500</v>
       </c>
-      <c r="J55" s="50" t="inlineStr">
+      <c r="J55" s="52" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -18054,100 +18087,132 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="A57" s="53" t="inlineStr">
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="47" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="48" t="inlineStr">
+        <is>
+          <t>Goztepe vs Galatasaray</t>
+        </is>
+      </c>
+      <c r="C56" s="47" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="D56" s="48" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F56" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G56" s="49" t="n"/>
+      <c r="H56" s="48" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I56" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J56" s="52" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K56" s="49" t="n"/>
+      <c r="L56" s="49" t="n"/>
+      <c r="M56" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="53" t="inlineStr">
         <is>
           <t>RESUMEN COMPARATIVO DE RENDIMIENTO</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="37" t="inlineStr">
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="37" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B58" s="38" t="inlineStr">
+      <c r="B59" s="38" t="inlineStr">
         <is>
           <t>Opcion 1 (Activa)</t>
         </is>
       </c>
-      <c r="D58" s="39" t="inlineStr">
+      <c r="D59" s="39" t="inlineStr">
         <is>
           <t>Opcion 4 (Shadow)</t>
         </is>
       </c>
-      <c r="F58" s="40" t="inlineStr">
+      <c r="F59" s="40" t="inlineStr">
         <is>
           <t>Mejor</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" s="54" t="inlineStr">
-        <is>
-          <t>N apuestas liquidadas</t>
-        </is>
-      </c>
-      <c r="B59" s="55" t="n">
-        <v>18</v>
-      </c>
-      <c r="C59" s="55" t="n">
-        <v>18</v>
-      </c>
-      <c r="D59" s="55" t="n">
-        <v>38</v>
-      </c>
-      <c r="E59" s="55" t="n">
-        <v>38</v>
-      </c>
-      <c r="F59" s="56" t="inlineStr">
-        <is>
-          <t>=</t>
         </is>
       </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="54" t="inlineStr">
         <is>
-          <t>Ganadas</t>
-        </is>
-      </c>
-      <c r="B60" s="57" t="n">
-        <v>13</v>
-      </c>
-      <c r="C60" s="57" t="n">
-        <v>13</v>
-      </c>
-      <c r="D60" s="58" t="n">
-        <v>28</v>
-      </c>
-      <c r="E60" s="58" t="n">
-        <v>28</v>
-      </c>
-      <c r="F60" s="59" t="inlineStr">
-        <is>
-          <t>Op4</t>
+          <t>N apuestas liquidadas</t>
+        </is>
+      </c>
+      <c r="B60" s="55" t="n">
+        <v>19</v>
+      </c>
+      <c r="C60" s="55" t="n">
+        <v>19</v>
+      </c>
+      <c r="D60" s="55" t="n">
+        <v>41</v>
+      </c>
+      <c r="E60" s="55" t="n">
+        <v>41</v>
+      </c>
+      <c r="F60" s="56" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="54" t="inlineStr">
         <is>
-          <t>Hit rate</t>
-        </is>
-      </c>
-      <c r="B61" s="60" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="C61" s="60" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="D61" s="61" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="E61" s="61" t="n">
-        <v>0.7368421052631579</v>
+          <t>Ganadas</t>
+        </is>
+      </c>
+      <c r="B61" s="57" t="n">
+        <v>13</v>
+      </c>
+      <c r="C61" s="57" t="n">
+        <v>13</v>
+      </c>
+      <c r="D61" s="58" t="n">
+        <v>29</v>
+      </c>
+      <c r="E61" s="58" t="n">
+        <v>29</v>
       </c>
       <c r="F61" s="59" t="inlineStr">
         <is>
@@ -18158,77 +18223,101 @@
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="54" t="inlineStr">
         <is>
-          <t>Volumen apostado</t>
-        </is>
-      </c>
-      <c r="B62" s="46" t="n">
-        <v>33682.99000000001</v>
-      </c>
-      <c r="C62" s="46" t="n">
-        <v>33682.99000000001</v>
-      </c>
-      <c r="D62" s="46" t="n">
-        <v>92492.41</v>
-      </c>
-      <c r="E62" s="46" t="n">
-        <v>92492.41</v>
-      </c>
-      <c r="F62" s="56" t="inlineStr">
-        <is>
-          <t>=</t>
+          <t>Hit rate</t>
+        </is>
+      </c>
+      <c r="B62" s="60" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="C62" s="60" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="D62" s="61" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="E62" s="61" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="F62" s="59" t="inlineStr">
+        <is>
+          <t>Op4</t>
         </is>
       </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="54" t="inlineStr">
         <is>
-          <t>P/L neto</t>
-        </is>
-      </c>
-      <c r="B63" s="52" t="n">
-        <v>40542.11</v>
-      </c>
-      <c r="C63" s="52" t="n">
-        <v>40542.11</v>
-      </c>
-      <c r="D63" s="45" t="n">
-        <v>159409.86</v>
-      </c>
-      <c r="E63" s="45" t="n">
-        <v>159409.86</v>
-      </c>
-      <c r="F63" s="59" t="inlineStr">
-        <is>
-          <t>Op4</t>
+          <t>Volumen apostado</t>
+        </is>
+      </c>
+      <c r="B63" s="46" t="n">
+        <v>36182.99000000001</v>
+      </c>
+      <c r="C63" s="46" t="n">
+        <v>36182.99000000001</v>
+      </c>
+      <c r="D63" s="46" t="n">
+        <v>99995.45</v>
+      </c>
+      <c r="E63" s="46" t="n">
+        <v>99995.45</v>
+      </c>
+      <c r="F63" s="56" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="54" t="inlineStr">
         <is>
+          <t>P/L neto</t>
+        </is>
+      </c>
+      <c r="B64" s="45" t="n">
+        <v>38042.11</v>
+      </c>
+      <c r="C64" s="45" t="n">
+        <v>38042.11</v>
+      </c>
+      <c r="D64" s="51" t="n">
+        <v>158638.47</v>
+      </c>
+      <c r="E64" s="51" t="n">
+        <v>158638.47</v>
+      </c>
+      <c r="F64" s="59" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="17" customHeight="1">
+      <c r="A65" s="54" t="inlineStr">
+        <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="B64" s="60" t="n">
-        <v>1.203637503677672</v>
-      </c>
-      <c r="C64" s="60" t="n">
-        <v>1.203637503677672</v>
-      </c>
-      <c r="D64" s="61" t="n">
-        <v>1.723491257282624</v>
-      </c>
-      <c r="E64" s="61" t="n">
-        <v>1.723491257282624</v>
-      </c>
-      <c r="F64" s="59" t="inlineStr">
+      <c r="B65" s="60" t="n">
+        <v>1.051381049493145</v>
+      </c>
+      <c r="C65" s="60" t="n">
+        <v>1.051381049493145</v>
+      </c>
+      <c r="D65" s="61" t="n">
+        <v>1.586456883788212</v>
+      </c>
+      <c r="E65" s="61" t="n">
+        <v>1.586456883788212</v>
+      </c>
+      <c r="F65" s="59" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="62" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="62" t="inlineStr">
         <is>
           <t>Verde = celda ganadora en ese KPI / partido   |   Rojo = celda perdedora   |   Amarillo en Resultado = pendiente de liquidar   |   Op1 activa desde V4.3: empates bloqueados + xG Margen O/U + Camino 2B (desacuerdo) + Camino 3 (alta conv.)</t>
         </is>
@@ -18236,13 +18325,13 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A67:N67"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A57:N57"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="L3:N3"/>
-    <mergeCell ref="A66:N66"/>
+    <mergeCell ref="A58:N58"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18345,25 +18434,25 @@
         </is>
       </c>
       <c r="B3" s="63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C3" s="63" t="n">
         <v>11</v>
       </c>
       <c r="D3" s="63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" s="64" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.6875</v>
       </c>
       <c r="F3" s="65" t="n">
-        <v>48644.04</v>
+        <v>44700.66</v>
       </c>
       <c r="G3" s="64" t="n">
-        <v>2.709391952482641</v>
+        <v>2.041383471158922</v>
       </c>
       <c r="H3" s="65" t="n">
-        <v>17953.86</v>
+        <v>21897.24</v>
       </c>
     </row>
     <row r="4">
@@ -18429,25 +18518,25 @@
         </is>
       </c>
       <c r="B6" s="63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="63" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="64" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>4343.33</v>
+        <v>6782.64</v>
       </c>
       <c r="G6" s="64" t="n">
-        <v>0.6762882456440839</v>
+        <v>0.8623079250617874</v>
       </c>
       <c r="H6" s="65" t="n">
-        <v>6422.3</v>
+        <v>7865.68</v>
       </c>
     </row>
     <row r="7">
@@ -18457,31 +18546,31 @@
         </is>
       </c>
       <c r="B7" s="66" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C7" s="66" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" s="66" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E7" s="67" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="F7" s="68" t="n">
-        <v>95233.99000000001</v>
+        <v>93729.92</v>
       </c>
       <c r="G7" s="67" t="n">
-        <v>1.576675435173506</v>
+        <v>1.424715207954943</v>
       </c>
       <c r="H7" s="68" t="n">
-        <v>60401.77</v>
+        <v>65788.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="69" t="inlineStr">
         <is>
-          <t>Generado: 05/04/2026 15:35</t>
+          <t>Generado: 05/04/2026 18:55</t>
         </is>
       </c>
     </row>

--- a/Backtest_Modelo.xlsx
+++ b/Backtest_Modelo.xlsx
@@ -393,10 +393,10 @@
     <xf numFmtId="4" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -902,7 +902,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 05/04/2026 23:29   |   Bankroll: $100,000.00</t>
+          <t>Generado: 06/04/2026 23:37   |   Bankroll: $100,000.00</t>
         </is>
       </c>
     </row>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>96353.4267</v>
+        <v>90015.9267</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>96353.4267</v>
+        <v>90015.9267</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1.319177540195834</v>
+        <v>1.117647558316291</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1.319177540195834</v>
+        <v>1.117647558316291</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>0</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>73040.53</v>
+        <v>80540.53</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>73040.53</v>
+        <v>80540.53</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>0</v>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
@@ -1009,14 +1009,14 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>% Acierto P  (col. Acierto, 57/83 partidos)</t>
+          <t>% Acierto P  (col. Acierto, 61/91 partidos)</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.6867469879518072</v>
+        <v>0.6703296703296703</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.6867469879518072</v>
+        <v>0.6703296703296703</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1030,11 +1030,11 @@
           <t>% Acierto $  (apuestas ganadoras / total apostado)</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
-        <v>0.5652173913043478</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0.5652173913043478</v>
+      <c r="B11" s="9" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.5294117647058824</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>0</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.6259821896280775</v>
+        <v>0.5998707175177763</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.6259821896280775</v>
+        <v>0.5998707175177763</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>0</v>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>3.9584</v>
+        <v>3.6233</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>3.9584</v>
+        <v>3.6233</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.0001</v>
+        <v>0.0003</v>
       </c>
       <c r="D15" s="17" t="n">
         <v>1</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>0.5926209053377396</v>
+        <v>0.5950443055293947</v>
       </c>
       <c r="C18" s="20" t="n">
-        <v>0.5926209053377396</v>
+        <v>0.5950443055293947</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>0.6407704356028928</v>
+        <v>0.6253766856469403</v>
       </c>
       <c r="C19" s="20" t="n">
-        <v>0.6407704356028928</v>
+        <v>0.6253766856469403</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>-0.04814953026515323</v>
+        <v>-0.03033238011754558</v>
       </c>
       <c r="C20" s="20" t="n">
-        <v>-0.04814953026515323</v>
+        <v>-0.03033238011754558</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC146"/>
+  <dimension ref="A1:AC167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="L2" s="33" t="n">
-        <v>0.3730826893905395</v>
+        <v>0.3731194757087563</v>
       </c>
       <c r="M2" s="33" t="n">
-        <v>0.2319300728990054</v>
+        <v>0.2318565002625718</v>
       </c>
       <c r="N2" s="33" t="n">
-        <v>0.3949872377104551</v>
+        <v>0.3950240240286719</v>
       </c>
       <c r="O2" s="33" t="n">
         <v>0.6814484819251414</v>
@@ -1677,13 +1677,13 @@
         </is>
       </c>
       <c r="L3" s="33" t="n">
-        <v>0.431334</v>
+        <v>0.431368</v>
       </c>
       <c r="M3" s="33" t="n">
-        <v>0.219666</v>
+        <v>0.219598</v>
       </c>
       <c r="N3" s="33" t="n">
-        <v>0.349</v>
+        <v>0.349034</v>
       </c>
       <c r="O3" s="33" t="n">
         <v>0.6945766824354072</v>
@@ -2006,19 +2006,19 @@
         </is>
       </c>
       <c r="L6" s="33" t="n">
-        <v>0.3943289003108972</v>
+        <v>0.424287</v>
       </c>
       <c r="M6" s="33" t="n">
-        <v>0.2302752748517164</v>
+        <v>0.221277</v>
       </c>
       <c r="N6" s="33" t="n">
-        <v>0.3753958248373864</v>
+        <v>0.354436</v>
       </c>
       <c r="O6" s="33" t="n">
-        <v>0.6892851554850581</v>
+        <v>0.6871128073697615</v>
       </c>
       <c r="P6" s="33" t="n">
-        <v>0.310714844514942</v>
+        <v>0.3128871926302385</v>
       </c>
       <c r="Q6" s="32" t="n">
         <v>2</v>
@@ -2026,10 +2026,9 @@
       <c r="R6" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="S6" s="30" t="inlineStr">
-        <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
+      <c r="S6" s="30">
+        <f>IF(OR(Q6="",R6=""),"[APOSTAR] LOCAL",IF(Q6&gt;R6,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T6" s="30" t="inlineStr">
         <is>
@@ -2037,7 +2036,7 @@
         </is>
       </c>
       <c r="U6" s="34" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="V6" s="34" t="n">
         <v>0</v>
@@ -2063,7 +2062,7 @@
         <v/>
       </c>
       <c r="AB6" s="36" t="n">
-        <v>0.7618</v>
+        <v>0.7674</v>
       </c>
       <c r="AC6" s="32" t="inlineStr">
         <is>
@@ -2116,13 +2115,13 @@
         </is>
       </c>
       <c r="L7" s="33" t="n">
-        <v>0.432698</v>
+        <v>0.432734</v>
       </c>
       <c r="M7" s="33" t="n">
-        <v>0.224605</v>
+        <v>0.224532</v>
       </c>
       <c r="N7" s="33" t="n">
-        <v>0.342698</v>
+        <v>0.342734</v>
       </c>
       <c r="O7" s="33" t="n">
         <v>0.6698908319120198</v>
@@ -2226,19 +2225,19 @@
         </is>
       </c>
       <c r="L8" s="33" t="n">
-        <v>0.356957</v>
+        <v>0.3838877205916895</v>
       </c>
       <c r="M8" s="33" t="n">
-        <v>0.215152</v>
+        <v>0.2260032781359762</v>
       </c>
       <c r="N8" s="33" t="n">
-        <v>0.427891</v>
+        <v>0.3901090012723342</v>
       </c>
       <c r="O8" s="33" t="n">
-        <v>0.717250170972745</v>
+        <v>0.7091842177634944</v>
       </c>
       <c r="P8" s="33" t="n">
-        <v>0.282749829027255</v>
+        <v>0.2908157822365056</v>
       </c>
       <c r="Q8" s="32" t="n">
         <v>2</v>
@@ -2246,9 +2245,10 @@
       <c r="R8" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="S8" s="30">
-        <f>IF(OR(Q8="",R8=""),"[APOSTAR] VISITA",IF(Q8&lt;R8,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S8" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
       </c>
       <c r="T8" s="30" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="U8" s="34" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="V8" s="34" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v/>
       </c>
       <c r="AB8" s="36" t="n">
-        <v>0.8819</v>
+        <v>0.8854</v>
       </c>
       <c r="AC8" s="32" t="inlineStr">
         <is>
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="L9" s="33" t="n">
-        <v>0.389866940388378</v>
+        <v>0.3899029348898337</v>
       </c>
       <c r="M9" s="33" t="n">
-        <v>0.2300291219194187</v>
+        <v>0.2299571329165074</v>
       </c>
       <c r="N9" s="33" t="n">
-        <v>0.3801039376922033</v>
+        <v>0.3801399321936589</v>
       </c>
       <c r="O9" s="33" t="n">
         <v>0.69063707873453</v>
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="L10" s="33" t="n">
-        <v>0.3865513820130155</v>
+        <v>0.386585642935619</v>
       </c>
       <c r="M10" s="33" t="n">
-        <v>0.2258944253536193</v>
+        <v>0.2258259035084124</v>
       </c>
       <c r="N10" s="33" t="n">
-        <v>0.3875541926333652</v>
+        <v>0.3875884535559687</v>
       </c>
       <c r="O10" s="33" t="n">
         <v>0.7100415726316365</v>
@@ -2555,19 +2555,19 @@
         </is>
       </c>
       <c r="L11" s="33" t="n">
-        <v>0.432882</v>
+        <v>0.432916</v>
       </c>
       <c r="M11" s="33" t="n">
-        <v>0.219693</v>
+        <v>0.219625</v>
       </c>
       <c r="N11" s="33" t="n">
-        <v>0.347425</v>
+        <v>0.347459</v>
       </c>
       <c r="O11" s="33" t="n">
         <v>0.6942200394125083</v>
       </c>
       <c r="P11" s="33" t="n">
-        <v>0.3057799605874916</v>
+        <v>0.3057799605874917</v>
       </c>
       <c r="Q11" s="32" t="n">
         <v>5</v>
@@ -2655,13 +2655,13 @@
         </is>
       </c>
       <c r="L12" s="33" t="n">
-        <v>0.506363</v>
+        <v>0.506332</v>
       </c>
       <c r="M12" s="33" t="n">
-        <v>0.187001</v>
+        <v>0.187064</v>
       </c>
       <c r="N12" s="33" t="n">
-        <v>0.306636</v>
+        <v>0.306605</v>
       </c>
       <c r="O12" s="33" t="n">
         <v>0.831747426350389</v>
@@ -3071,13 +3071,13 @@
         </is>
       </c>
       <c r="L16" s="33" t="n">
-        <v>0.458923</v>
+        <v>0.458892</v>
       </c>
       <c r="M16" s="33" t="n">
-        <v>0.190136</v>
+        <v>0.190199</v>
       </c>
       <c r="N16" s="33" t="n">
-        <v>0.35094</v>
+        <v>0.350909</v>
       </c>
       <c r="O16" s="33" t="n">
         <v>0.8317576399381373</v>
@@ -3167,13 +3167,13 @@
         </is>
       </c>
       <c r="L17" s="33" t="n">
-        <v>0.348748</v>
+        <v>0.348713</v>
       </c>
       <c r="M17" s="33" t="n">
-        <v>0.195498</v>
+        <v>0.195569</v>
       </c>
       <c r="N17" s="33" t="n">
-        <v>0.455754</v>
+        <v>0.455718</v>
       </c>
       <c r="O17" s="33" t="n">
         <v>0.8077569920766402</v>
@@ -3257,10 +3257,10 @@
         </is>
       </c>
       <c r="F18" s="31" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="G18" s="31" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="H18" s="31" t="n">
         <v>1.64</v>
@@ -3273,13 +3273,13 @@
         </is>
       </c>
       <c r="L18" s="33" t="n">
-        <v>0.442618</v>
+        <v>0.442585</v>
       </c>
       <c r="M18" s="33" t="n">
-        <v>0.192026</v>
+        <v>0.192091</v>
       </c>
       <c r="N18" s="33" t="n">
-        <v>0.365357</v>
+        <v>0.365324</v>
       </c>
       <c r="O18" s="33" t="n">
         <v>0.8255343688857609</v>
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L19" s="33" t="n">
-        <v>0.446078</v>
+        <v>0.446045</v>
       </c>
       <c r="M19" s="33" t="n">
-        <v>0.192357</v>
+        <v>0.192423</v>
       </c>
       <c r="N19" s="33" t="n">
-        <v>0.361565</v>
+        <v>0.361532</v>
       </c>
       <c r="O19" s="33" t="n">
         <v>0.8236626971734087</v>
@@ -3994,13 +3994,13 @@
         </is>
       </c>
       <c r="L25" s="33" t="n">
-        <v>0.424911</v>
+        <v>0.424948</v>
       </c>
       <c r="M25" s="33" t="n">
-        <v>0.225635</v>
+        <v>0.225561</v>
       </c>
       <c r="N25" s="33" t="n">
-        <v>0.349454</v>
+        <v>0.349491</v>
       </c>
       <c r="O25" s="33" t="n">
         <v>0.6659072410848628</v>
@@ -4103,13 +4103,13 @@
         </is>
       </c>
       <c r="L26" s="33" t="n">
-        <v>0.397878495599691</v>
+        <v>0.3979147246188666</v>
       </c>
       <c r="M26" s="33" t="n">
-        <v>0.2305303406840633</v>
+        <v>0.2304578826457123</v>
       </c>
       <c r="N26" s="33" t="n">
-        <v>0.3715911637162457</v>
+        <v>0.3716273927354211</v>
       </c>
       <c r="O26" s="33" t="n">
         <v>0.6878381974505104</v>
@@ -4322,13 +4322,13 @@
         </is>
       </c>
       <c r="L28" s="33" t="n">
-        <v>0.436187</v>
+        <v>0.436219</v>
       </c>
       <c r="M28" s="33" t="n">
-        <v>0.216415</v>
+        <v>0.21635</v>
       </c>
       <c r="N28" s="33" t="n">
-        <v>0.347398</v>
+        <v>0.347431</v>
       </c>
       <c r="O28" s="33" t="n">
         <v>0.709955455946658</v>
@@ -4760,13 +4760,13 @@
         </is>
       </c>
       <c r="L32" s="33" t="n">
-        <v>0.427083</v>
+        <v>0.427086</v>
       </c>
       <c r="M32" s="33" t="n">
-        <v>0.145834</v>
+        <v>0.145829</v>
       </c>
       <c r="N32" s="33" t="n">
-        <v>0.427083</v>
+        <v>0.427086</v>
       </c>
       <c r="O32" s="33" t="n">
         <v>0.9644378138836682</v>
@@ -4870,19 +4870,19 @@
         </is>
       </c>
       <c r="L33" s="33" t="n">
-        <v>0.3901796849963756</v>
+        <v>0.3902174830277121</v>
       </c>
       <c r="M33" s="33" t="n">
-        <v>0.2345045215958767</v>
+        <v>0.2344289255332035</v>
       </c>
       <c r="N33" s="33" t="n">
-        <v>0.3753157934077477</v>
+        <v>0.3753535914390843</v>
       </c>
       <c r="O33" s="33" t="n">
         <v>0.6696077735528496</v>
       </c>
       <c r="P33" s="33" t="n">
-        <v>0.3303922264471503</v>
+        <v>0.3303922264471504</v>
       </c>
       <c r="Q33" s="32" t="n">
         <v>1</v>
@@ -5090,13 +5090,13 @@
         </is>
       </c>
       <c r="L35" s="33" t="n">
-        <v>0.3917683742862499</v>
+        <v>0.3918037847473589</v>
       </c>
       <c r="M35" s="33" t="n">
-        <v>0.2286090882402792</v>
+        <v>0.2285382673180611</v>
       </c>
       <c r="N35" s="33" t="n">
-        <v>0.3796225374734709</v>
+        <v>0.3796579479345799</v>
       </c>
       <c r="O35" s="33" t="n">
         <v>0.6972413909234073</v>
@@ -5309,13 +5309,13 @@
         </is>
       </c>
       <c r="L37" s="33" t="n">
-        <v>0.3850464797022863</v>
+        <v>0.3850825863759373</v>
       </c>
       <c r="M37" s="33" t="n">
-        <v>0.2303142078952086</v>
+        <v>0.2302419945479065</v>
       </c>
       <c r="N37" s="33" t="n">
-        <v>0.384639312402505</v>
+        <v>0.3846754190761561</v>
       </c>
       <c r="O37" s="33" t="n">
         <v>0.6893754755750047</v>
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L38" s="33" t="n">
-        <v>0.474079</v>
+        <v>0.474086</v>
       </c>
       <c r="M38" s="33" t="n">
-        <v>0.173035</v>
+        <v>0.173021</v>
       </c>
       <c r="N38" s="33" t="n">
-        <v>0.352886</v>
+        <v>0.352893</v>
       </c>
       <c r="O38" s="33" t="n">
         <v>0.8939984342088939</v>
@@ -5747,13 +5747,13 @@
         </is>
       </c>
       <c r="L41" s="33" t="n">
-        <v>0.3855092436896441</v>
+        <v>0.3855470531965907</v>
       </c>
       <c r="M41" s="33" t="n">
-        <v>0.2345560622160211</v>
+        <v>0.2344804432021277</v>
       </c>
       <c r="N41" s="33" t="n">
-        <v>0.3799346940943348</v>
+        <v>0.3799725036012815</v>
       </c>
       <c r="O41" s="33" t="n">
         <v>0.6695132949325856</v>
@@ -5857,13 +5857,13 @@
         </is>
       </c>
       <c r="L42" s="33" t="n">
-        <v>0.429746</v>
+        <v>0.429782</v>
       </c>
       <c r="M42" s="33" t="n">
-        <v>0.222698</v>
+        <v>0.222627</v>
       </c>
       <c r="N42" s="33" t="n">
-        <v>0.347556</v>
+        <v>0.347591</v>
       </c>
       <c r="O42" s="33" t="n">
         <v>0.6797895124991777</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="L45" s="33" t="n">
-        <v>0.347557</v>
+        <v>0.347592</v>
       </c>
       <c r="M45" s="33" t="n">
-        <v>0.221326</v>
+        <v>0.221257</v>
       </c>
       <c r="N45" s="33" t="n">
-        <v>0.431116</v>
+        <v>0.431151</v>
       </c>
       <c r="O45" s="33" t="n">
         <v>0.6863860244237964</v>
@@ -6295,19 +6295,19 @@
         </is>
       </c>
       <c r="L46" s="33" t="n">
-        <v>0.382704</v>
+        <v>0.382712</v>
       </c>
       <c r="M46" s="33" t="n">
-        <v>0.176487</v>
+        <v>0.176471</v>
       </c>
       <c r="N46" s="33" t="n">
-        <v>0.440809</v>
+        <v>0.440817</v>
       </c>
       <c r="O46" s="33" t="n">
         <v>0.8836044250835575</v>
       </c>
       <c r="P46" s="33" t="n">
-        <v>0.1163955749164424</v>
+        <v>0.1163955749164425</v>
       </c>
       <c r="Q46" s="32" t="n">
         <v>3</v>
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L50" s="33" t="n">
-        <v>0.491013</v>
+        <v>0.491019</v>
       </c>
       <c r="M50" s="33" t="n">
-        <v>0.169284</v>
+        <v>0.169272</v>
       </c>
       <c r="N50" s="33" t="n">
-        <v>0.339703</v>
+        <v>0.339709</v>
       </c>
       <c r="O50" s="33" t="n">
         <v>0.905433144594896</v>
@@ -6841,13 +6841,13 @@
         </is>
       </c>
       <c r="L51" s="33" t="n">
-        <v>0.448099</v>
+        <v>0.448105</v>
       </c>
       <c r="M51" s="33" t="n">
-        <v>0.170857</v>
+        <v>0.170844</v>
       </c>
       <c r="N51" s="33" t="n">
-        <v>0.381044</v>
+        <v>0.38105</v>
       </c>
       <c r="O51" s="33" t="n">
         <v>0.9055076819692618</v>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="L53" s="33" t="n">
-        <v>0.440633</v>
+        <v>0.440669</v>
       </c>
       <c r="M53" s="33" t="n">
-        <v>0.224108</v>
+        <v>0.224036</v>
       </c>
       <c r="N53" s="33" t="n">
-        <v>0.335259</v>
+        <v>0.335295</v>
       </c>
       <c r="O53" s="33" t="n">
         <v>0.6708339200603624</v>
@@ -7168,13 +7168,13 @@
         </is>
       </c>
       <c r="L54" s="33" t="n">
-        <v>0.474486</v>
+        <v>0.474494</v>
       </c>
       <c r="M54" s="33" t="n">
-        <v>0.174169</v>
+        <v>0.174154</v>
       </c>
       <c r="N54" s="33" t="n">
-        <v>0.351345</v>
+        <v>0.351352</v>
       </c>
       <c r="O54" s="33" t="n">
         <v>0.889287248387998</v>
@@ -7604,19 +7604,19 @@
         </is>
       </c>
       <c r="L58" s="33" t="n">
-        <v>0.430669</v>
+        <v>0.43782</v>
       </c>
       <c r="M58" s="33" t="n">
-        <v>0.229007</v>
+        <v>0.225469</v>
       </c>
       <c r="N58" s="33" t="n">
-        <v>0.340324</v>
+        <v>0.33671</v>
       </c>
       <c r="O58" s="33" t="n">
-        <v>0.6484369584010296</v>
+        <v>0.6642844500495885</v>
       </c>
       <c r="P58" s="33" t="n">
-        <v>0.3515630415989705</v>
+        <v>0.3357155499504115</v>
       </c>
       <c r="Q58" s="32" t="n">
         <v>1</v>
@@ -7661,7 +7661,7 @@
         <v/>
       </c>
       <c r="AB58" s="36" t="n">
-        <v>1.0038</v>
+        <v>0.9829</v>
       </c>
       <c r="AC58" s="32" t="inlineStr">
         <is>
@@ -7714,13 +7714,13 @@
         </is>
       </c>
       <c r="L59" s="33" t="n">
-        <v>0.515767</v>
+        <v>0.515798</v>
       </c>
       <c r="M59" s="33" t="n">
-        <v>0.207203</v>
+        <v>0.207141</v>
       </c>
       <c r="N59" s="33" t="n">
-        <v>0.27703</v>
+        <v>0.277061</v>
       </c>
       <c r="O59" s="33" t="n">
         <v>0.7248856060553114</v>
@@ -7824,13 +7824,13 @@
         </is>
       </c>
       <c r="L60" s="33" t="n">
-        <v>0.430783</v>
+        <v>0.430818</v>
       </c>
       <c r="M60" s="33" t="n">
-        <v>0.221189</v>
+        <v>0.22112</v>
       </c>
       <c r="N60" s="33" t="n">
-        <v>0.348028</v>
+        <v>0.348063</v>
       </c>
       <c r="O60" s="33" t="n">
         <v>0.6871126506588848</v>
@@ -7933,13 +7933,13 @@
         </is>
       </c>
       <c r="L61" s="33" t="n">
-        <v>0.435043</v>
+        <v>0.435078</v>
       </c>
       <c r="M61" s="33" t="n">
-        <v>0.222512</v>
+        <v>0.222441</v>
       </c>
       <c r="N61" s="33" t="n">
-        <v>0.342445</v>
+        <v>0.342481</v>
       </c>
       <c r="O61" s="33" t="n">
         <v>0.6798816771154758</v>
@@ -8043,19 +8043,19 @@
         </is>
       </c>
       <c r="L62" s="33" t="n">
-        <v>0.3915826617318239</v>
+        <v>0.3916219553229459</v>
       </c>
       <c r="M62" s="33" t="n">
-        <v>0.2383684230215259</v>
+        <v>0.238289835839282</v>
       </c>
       <c r="N62" s="33" t="n">
-        <v>0.3700489152466502</v>
+        <v>0.3700882088377722</v>
       </c>
       <c r="O62" s="33" t="n">
         <v>0.6513935760302454</v>
       </c>
       <c r="P62" s="33" t="n">
-        <v>0.3486064239697547</v>
+        <v>0.3486064239697546</v>
       </c>
       <c r="Q62" s="32" t="n">
         <v>1</v>
@@ -8143,19 +8143,19 @@
         </is>
       </c>
       <c r="L63" s="33" t="n">
-        <v>0.435949</v>
+        <v>0.442844</v>
       </c>
       <c r="M63" s="33" t="n">
-        <v>0.22222</v>
+        <v>0.218925</v>
       </c>
       <c r="N63" s="33" t="n">
-        <v>0.341831</v>
+        <v>0.338231</v>
       </c>
       <c r="O63" s="33" t="n">
-        <v>0.6811720714969456</v>
+        <v>0.6959106749065054</v>
       </c>
       <c r="P63" s="33" t="n">
-        <v>0.3188279285030543</v>
+        <v>0.3040893250934946</v>
       </c>
       <c r="Q63" s="32" t="n">
         <v>2</v>
@@ -8200,7 +8200,7 @@
         <v/>
       </c>
       <c r="AB63" s="36" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.842</v>
       </c>
       <c r="AC63" s="32" t="inlineStr">
         <is>
@@ -13187,8 +13187,12 @@
       <c r="P110" s="33" t="n">
         <v>0.3088247085805371</v>
       </c>
-      <c r="Q110" s="37" t="n"/>
-      <c r="R110" s="37" t="n"/>
+      <c r="Q110" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R110" s="32" t="n">
+        <v>2</v>
+      </c>
       <c r="S110" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Riesgo/Beneficio</t>
@@ -13289,11 +13293,16 @@
       <c r="P111" s="33" t="n">
         <v>0.09751991066831002</v>
       </c>
-      <c r="Q111" s="37" t="n"/>
-      <c r="R111" s="37" t="n"/>
-      <c r="S111" s="30">
-        <f>IF(OR(Q111="",R111=""),"[APOSTAR] LOCAL",IF(Q111&gt;R111,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+      <c r="Q111" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R111" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="S111" s="30" t="inlineStr">
+        <is>
+          <t>[PERDIDA] LOCAL</t>
+        </is>
       </c>
       <c r="T111" s="30" t="inlineStr">
         <is>
@@ -13390,11 +13399,16 @@
       <c r="P112" s="33" t="n">
         <v>0.1728348193737792</v>
       </c>
-      <c r="Q112" s="37" t="n"/>
-      <c r="R112" s="37" t="n"/>
-      <c r="S112" s="30">
-        <f>IF(OR(Q112="",R112=""),"[APOSTAR] VISITA",IF(Q112&lt;R112,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="Q112" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" s="30" t="inlineStr">
+        <is>
+          <t>[PERDIDA] VISITA</t>
+        </is>
       </c>
       <c r="T112" s="30" t="inlineStr">
         <is>
@@ -13491,8 +13505,12 @@
       <c r="P113" s="33" t="n">
         <v>0.09476615677355756</v>
       </c>
-      <c r="Q113" s="37" t="n"/>
-      <c r="R113" s="37" t="n"/>
+      <c r="Q113" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="S113" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Riesgo/Beneficio</t>
@@ -13593,11 +13611,16 @@
       <c r="P114" s="33" t="n">
         <v>0.06386809670053707</v>
       </c>
-      <c r="Q114" s="37" t="n"/>
-      <c r="R114" s="37" t="n"/>
-      <c r="S114" s="30">
-        <f>IF(OR(Q114="",R114=""),"[APOSTAR] VISITA",IF(Q114&lt;R114,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="Q114" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S114" s="30" t="inlineStr">
+        <is>
+          <t>[GANADA] VISITA</t>
+        </is>
       </c>
       <c r="T114" s="30" t="inlineStr">
         <is>
@@ -13694,11 +13717,16 @@
       <c r="P115" s="33" t="n">
         <v>0.05851054229051283</v>
       </c>
-      <c r="Q115" s="37" t="n"/>
-      <c r="R115" s="37" t="n"/>
-      <c r="S115" s="30">
-        <f>IF(OR(Q115="",R115=""),"[APOSTAR] VISITA",IF(Q115&lt;R115,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="Q115" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S115" s="30" t="inlineStr">
+        <is>
+          <t>[PERDIDA] VISITA</t>
+        </is>
       </c>
       <c r="T115" s="30" t="inlineStr">
         <is>
@@ -13795,8 +13823,12 @@
       <c r="P116" s="33" t="n">
         <v>0.1131178115719779</v>
       </c>
-      <c r="Q116" s="37" t="n"/>
-      <c r="R116" s="37" t="n"/>
+      <c r="Q116" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R116" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="S116" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Riesgo/Beneficio</t>
@@ -13897,11 +13929,16 @@
       <c r="P117" s="33" t="n">
         <v>0.09758564820482256</v>
       </c>
-      <c r="Q117" s="37" t="n"/>
-      <c r="R117" s="37" t="n"/>
-      <c r="S117" s="30">
-        <f>IF(OR(Q117="",R117=""),"[APOSTAR] LOCAL",IF(Q117&gt;R117,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+      <c r="Q117" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="S117" s="30" t="inlineStr">
+        <is>
+          <t>[PERDIDA] LOCAL</t>
+        </is>
       </c>
       <c r="T117" s="30" t="inlineStr">
         <is>
@@ -13968,13 +14005,13 @@
         </is>
       </c>
       <c r="F118" s="31" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="G118" s="31" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="H118" s="31" t="n">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="I118" s="31" t="n">
         <v>1.82</v>
@@ -13988,13 +14025,13 @@
         </is>
       </c>
       <c r="L118" s="33" t="n">
-        <v>0.424409</v>
+        <v>0.424413</v>
       </c>
       <c r="M118" s="33" t="n">
-        <v>0.156027</v>
+        <v>0.156018</v>
       </c>
       <c r="N118" s="33" t="n">
-        <v>0.419565</v>
+        <v>0.419569</v>
       </c>
       <c r="O118" s="33" t="n">
         <v>0.9353755849059086</v>
@@ -14104,8 +14141,12 @@
       <c r="P119" s="33" t="n">
         <v>0.3000240064760311</v>
       </c>
-      <c r="Q119" s="37" t="n"/>
-      <c r="R119" s="37" t="n"/>
+      <c r="Q119" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R119" s="32" t="n">
+        <v>0</v>
+      </c>
       <c r="S119" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
@@ -14176,13 +14217,13 @@
         </is>
       </c>
       <c r="F120" s="31" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="G120" s="31" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="H120" s="31" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="I120" s="31" t="n">
         <v>1.84</v>
@@ -14196,13 +14237,13 @@
         </is>
       </c>
       <c r="L120" s="33" t="n">
-        <v>0.461996</v>
+        <v>0.462003</v>
       </c>
       <c r="M120" s="33" t="n">
-        <v>0.172404</v>
+        <v>0.172391</v>
       </c>
       <c r="N120" s="33" t="n">
-        <v>0.3656</v>
+        <v>0.365606</v>
       </c>
       <c r="O120" s="33" t="n">
         <v>0.8983203327620296</v>
@@ -14281,10 +14322,10 @@
         </is>
       </c>
       <c r="F121" s="31" t="n">
-        <v>5.09</v>
+        <v>5.07</v>
       </c>
       <c r="G121" s="31" t="n">
-        <v>4.04</v>
+        <v>4.02</v>
       </c>
       <c r="H121" s="31" t="n">
         <v>1.64</v>
@@ -14297,13 +14338,13 @@
         </is>
       </c>
       <c r="L121" s="33" t="n">
-        <v>0.442618</v>
+        <v>0.442585</v>
       </c>
       <c r="M121" s="33" t="n">
-        <v>0.192026</v>
+        <v>0.192091</v>
       </c>
       <c r="N121" s="33" t="n">
-        <v>0.365357</v>
+        <v>0.365324</v>
       </c>
       <c r="O121" s="33" t="n">
         <v>0.8255343688857609</v>
@@ -14402,13 +14443,13 @@
         </is>
       </c>
       <c r="L122" s="33" t="n">
-        <v>0.458923</v>
+        <v>0.458892</v>
       </c>
       <c r="M122" s="33" t="n">
-        <v>0.190136</v>
+        <v>0.190199</v>
       </c>
       <c r="N122" s="33" t="n">
-        <v>0.35094</v>
+        <v>0.350909</v>
       </c>
       <c r="O122" s="33" t="n">
         <v>0.8317576399381373</v>
@@ -14504,13 +14545,13 @@
         </is>
       </c>
       <c r="L123" s="33" t="n">
-        <v>0.476124</v>
+        <v>0.476091</v>
       </c>
       <c r="M123" s="33" t="n">
-        <v>0.191568</v>
+        <v>0.191634</v>
       </c>
       <c r="N123" s="33" t="n">
-        <v>0.332308</v>
+        <v>0.332275</v>
       </c>
       <c r="O123" s="33" t="n">
         <v>0.8212521396243118</v>
@@ -14590,19 +14631,19 @@
         </is>
       </c>
       <c r="F124" s="31" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="G124" s="31" t="n">
-        <v>3.86</v>
+        <v>3.77</v>
       </c>
       <c r="H124" s="31" t="n">
-        <v>4.44</v>
+        <v>4.34</v>
       </c>
       <c r="I124" s="31" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J124" s="31" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="K124" s="32" t="inlineStr">
         <is>
@@ -14705,13 +14746,13 @@
         </is>
       </c>
       <c r="L125" s="33" t="n">
-        <v>0.449095</v>
+        <v>0.449062</v>
       </c>
       <c r="M125" s="33" t="n">
-        <v>0.192727</v>
+        <v>0.192793</v>
       </c>
       <c r="N125" s="33" t="n">
-        <v>0.358178</v>
+        <v>0.358145</v>
       </c>
       <c r="O125" s="33" t="n">
         <v>0.8216013050648159</v>
@@ -14791,13 +14832,13 @@
         </is>
       </c>
       <c r="F126" s="31" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G126" s="31" t="n">
-        <v>4.94</v>
+        <v>4.77</v>
       </c>
       <c r="H126" s="31" t="n">
-        <v>8.56</v>
+        <v>8.19</v>
       </c>
       <c r="I126" s="31" t="n"/>
       <c r="J126" s="31" t="n"/>
@@ -14893,10 +14934,10 @@
         </is>
       </c>
       <c r="F127" s="31" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G127" s="31" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="H127" s="31" t="n">
         <v>6.01</v>
@@ -14909,13 +14950,13 @@
         </is>
       </c>
       <c r="L127" s="33" t="n">
-        <v>0.430508</v>
+        <v>0.430544</v>
       </c>
       <c r="M127" s="33" t="n">
-        <v>0.223689</v>
+        <v>0.223617</v>
       </c>
       <c r="N127" s="33" t="n">
-        <v>0.345803</v>
+        <v>0.345839</v>
       </c>
       <c r="O127" s="33" t="n">
         <v>0.674774666543377</v>
@@ -14995,13 +15036,13 @@
         </is>
       </c>
       <c r="F128" s="31" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="G128" s="31" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="H128" s="31" t="n">
-        <v>3.78</v>
+        <v>3.69</v>
       </c>
       <c r="I128" s="31" t="n"/>
       <c r="J128" s="31" t="n"/>
@@ -15011,13 +15052,13 @@
         </is>
       </c>
       <c r="L128" s="33" t="n">
-        <v>0.425987</v>
+        <v>0.426023</v>
       </c>
       <c r="M128" s="33" t="n">
-        <v>0.223414</v>
+        <v>0.223343</v>
       </c>
       <c r="N128" s="33" t="n">
-        <v>0.350599</v>
+        <v>0.350634</v>
       </c>
       <c r="O128" s="33" t="n">
         <v>0.6767318585475198</v>
@@ -15037,7 +15078,7 @@
         </is>
       </c>
       <c r="U128" s="34" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
       <c r="V128" s="34" t="n">
         <v>0</v>
@@ -15202,7 +15243,7 @@
         </is>
       </c>
       <c r="F130" s="31" t="n">
-        <v>4.47</v>
+        <v>4.48</v>
       </c>
       <c r="G130" s="31" t="n">
         <v>4.19</v>
@@ -15303,9 +15344,15 @@
           <t>Instituto (córdoba)</t>
         </is>
       </c>
-      <c r="F131" s="31" t="n"/>
-      <c r="G131" s="31" t="n"/>
-      <c r="H131" s="31" t="n"/>
+      <c r="F131" s="31" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G131" s="31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H131" s="31" t="n">
+        <v>3.07</v>
+      </c>
       <c r="I131" s="31" t="n"/>
       <c r="J131" s="31" t="n"/>
       <c r="K131" s="32" t="inlineStr">
@@ -15314,13 +15361,13 @@
         </is>
       </c>
       <c r="L131" s="33" t="n">
-        <v>0.3987778425454901</v>
+        <v>0.3988149221165253</v>
       </c>
       <c r="M131" s="33" t="n">
-        <v>0.2326096196445088</v>
+        <v>0.2325354605024384</v>
       </c>
       <c r="N131" s="33" t="n">
-        <v>0.3686125378100011</v>
+        <v>0.3686496173810364</v>
       </c>
       <c r="O131" s="33" t="n">
         <v>0.677939061194281</v>
@@ -15330,18 +15377,17 @@
       </c>
       <c r="Q131" s="37" t="n"/>
       <c r="R131" s="37" t="n"/>
-      <c r="S131" s="30" t="inlineStr">
+      <c r="S131" s="30">
+        <f>IF(OR(Q131="",R131=""),"[APOSTAR] LOCAL",IF(Q131&gt;R131,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T131" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Sin Cuotas</t>
         </is>
       </c>
-      <c r="T131" s="30" t="inlineStr">
-        <is>
-          <t>[PASAR] Sin Cuotas</t>
-        </is>
-      </c>
       <c r="U131" s="34" t="n">
-        <v>0</v>
+        <v>1443.38</v>
       </c>
       <c r="V131" s="34" t="n">
         <v>0</v>
@@ -15403,10 +15449,10 @@
         <v>2.3</v>
       </c>
       <c r="G132" s="31" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="H132" s="31" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="I132" s="31" t="n"/>
       <c r="J132" s="31" t="n"/>
@@ -15416,13 +15462,13 @@
         </is>
       </c>
       <c r="L132" s="33" t="n">
-        <v>0.471192</v>
+        <v>0.471224</v>
       </c>
       <c r="M132" s="33" t="n">
-        <v>0.212956</v>
+        <v>0.212892</v>
       </c>
       <c r="N132" s="33" t="n">
-        <v>0.315853</v>
+        <v>0.315885</v>
       </c>
       <c r="O132" s="33" t="n">
         <v>0.7180025760599492</v>
@@ -15442,7 +15488,7 @@
         </is>
       </c>
       <c r="U132" s="34" t="n">
-        <v>1767.77</v>
+        <v>1443.38</v>
       </c>
       <c r="V132" s="34" t="n">
         <v>0</v>
@@ -15501,10 +15547,10 @@
         </is>
       </c>
       <c r="F133" s="31" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="G133" s="31" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="H133" s="31" t="n">
         <v>2.46</v>
@@ -15543,7 +15589,7 @@
         </is>
       </c>
       <c r="U133" s="34" t="n">
-        <v>1020.62</v>
+        <v>1118.03</v>
       </c>
       <c r="V133" s="34" t="n">
         <v>0</v>
@@ -15601,9 +15647,15 @@
           <t>Argentinos Juniors</t>
         </is>
       </c>
-      <c r="F134" s="31" t="n"/>
-      <c r="G134" s="31" t="n"/>
-      <c r="H134" s="31" t="n"/>
+      <c r="F134" s="31" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G134" s="31" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H134" s="31" t="n">
+        <v>3.13</v>
+      </c>
       <c r="I134" s="31" t="n"/>
       <c r="J134" s="31" t="n"/>
       <c r="K134" s="32" t="inlineStr">
@@ -15612,13 +15664,13 @@
         </is>
       </c>
       <c r="L134" s="33" t="n">
-        <v>0.3966795097402527</v>
+        <v>0.396715346992891</v>
       </c>
       <c r="M134" s="33" t="n">
-        <v>0.2295945475878384</v>
+        <v>0.2295228730825617</v>
       </c>
       <c r="N134" s="33" t="n">
-        <v>0.3737259426719089</v>
+        <v>0.3737617799245473</v>
       </c>
       <c r="O134" s="33" t="n">
         <v>0.6923430160030771</v>
@@ -15630,7 +15682,7 @@
       <c r="R134" s="37" t="n"/>
       <c r="S134" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
         </is>
       </c>
       <c r="T134" s="30" t="inlineStr">
@@ -15698,19 +15750,19 @@
         </is>
       </c>
       <c r="F135" s="31" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="G135" s="31" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="H135" s="31" t="n">
-        <v>3.66</v>
+        <v>4.09</v>
       </c>
       <c r="I135" s="31" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="J135" s="31" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="K135" s="32" t="inlineStr">
         <is>
@@ -15744,7 +15796,7 @@
         </is>
       </c>
       <c r="U135" s="34" t="n">
-        <v>1020.62</v>
+        <v>1118.03</v>
       </c>
       <c r="V135" s="34" t="n">
         <v>0</v>
@@ -15813,13 +15865,13 @@
         </is>
       </c>
       <c r="L136" s="33" t="n">
-        <v>0.463119</v>
+        <v>0.463086</v>
       </c>
       <c r="M136" s="33" t="n">
-        <v>0.192731</v>
+        <v>0.192798</v>
       </c>
       <c r="N136" s="33" t="n">
-        <v>0.34415</v>
+        <v>0.344116</v>
       </c>
       <c r="O136" s="33" t="n">
         <v>0.8191108446117275</v>
@@ -15909,13 +15961,13 @@
         </is>
       </c>
       <c r="L137" s="33" t="n">
-        <v>0.442848</v>
+        <v>0.442816</v>
       </c>
       <c r="M137" s="33" t="n">
-        <v>0.191895</v>
+        <v>0.19196</v>
       </c>
       <c r="N137" s="33" t="n">
-        <v>0.365257</v>
+        <v>0.365224</v>
       </c>
       <c r="O137" s="33" t="n">
         <v>0.8260980760230097</v>
@@ -16005,19 +16057,19 @@
         </is>
       </c>
       <c r="L138" s="33" t="n">
-        <v>0.412393</v>
+        <v>0.428223</v>
       </c>
       <c r="M138" s="33" t="n">
-        <v>0.175214</v>
+        <v>0.188214</v>
       </c>
       <c r="N138" s="33" t="n">
-        <v>0.412393</v>
+        <v>0.383563</v>
       </c>
       <c r="O138" s="33" t="n">
-        <v>0.859193612624773</v>
+        <v>0.8321970267658978</v>
       </c>
       <c r="P138" s="33" t="n">
-        <v>0.1408063873752269</v>
+        <v>0.1678029732341022</v>
       </c>
       <c r="Q138" s="37" t="n"/>
       <c r="R138" s="37" t="n"/>
@@ -16058,7 +16110,7 @@
         <v/>
       </c>
       <c r="AB138" s="36" t="n">
-        <v>0.3921</v>
+        <v>0.8417</v>
       </c>
       <c r="AC138" s="32" t="inlineStr">
         <is>
@@ -16091,13 +16143,13 @@
         </is>
       </c>
       <c r="F139" s="31" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G139" s="31" t="n">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
       <c r="H139" s="31" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="I139" s="31" t="n"/>
       <c r="J139" s="31" t="n"/>
@@ -16193,19 +16245,19 @@
         </is>
       </c>
       <c r="F140" s="31" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="G140" s="31" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="H140" s="31" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="I140" s="31" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J140" s="31" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="K140" s="32" t="inlineStr">
         <is>
@@ -16229,9 +16281,10 @@
       </c>
       <c r="Q140" s="37" t="n"/>
       <c r="R140" s="37" t="n"/>
-      <c r="S140" s="30">
-        <f>IF(OR(Q140="",R140=""),"[APOSTAR] VISITA",IF(Q140&lt;R140,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S140" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] EV Insuf (0.070&lt;0.080)</t>
+        </is>
       </c>
       <c r="T140" s="30" t="inlineStr">
         <is>
@@ -16239,7 +16292,7 @@
         </is>
       </c>
       <c r="U140" s="34" t="n">
-        <v>1020.62</v>
+        <v>0</v>
       </c>
       <c r="V140" s="34" t="n">
         <v>0</v>
@@ -16298,13 +16351,13 @@
         </is>
       </c>
       <c r="F141" s="31" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="G141" s="31" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="H141" s="31" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I141" s="31" t="n">
         <v>1.99</v>
@@ -16344,7 +16397,7 @@
         </is>
       </c>
       <c r="U141" s="34" t="n">
-        <v>1020.62</v>
+        <v>1118.03</v>
       </c>
       <c r="V141" s="34" t="n">
         <v>0</v>
@@ -16403,13 +16456,13 @@
         </is>
       </c>
       <c r="F142" s="31" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="G142" s="31" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="H142" s="31" t="n">
-        <v>3.28</v>
+        <v>3.41</v>
       </c>
       <c r="I142" s="31" t="n"/>
       <c r="J142" s="31" t="n"/>
@@ -16445,7 +16498,7 @@
         </is>
       </c>
       <c r="U142" s="34" t="n">
-        <v>1020.62</v>
+        <v>1118.03</v>
       </c>
       <c r="V142" s="34" t="n">
         <v>0</v>
@@ -16503,9 +16556,15 @@
           <t>Kristiansund bk</t>
         </is>
       </c>
-      <c r="F143" s="31" t="n"/>
-      <c r="G143" s="31" t="n"/>
-      <c r="H143" s="31" t="n"/>
+      <c r="F143" s="31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G143" s="31" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="H143" s="31" t="n">
+        <v>7.27</v>
+      </c>
       <c r="I143" s="31" t="n"/>
       <c r="J143" s="31" t="n"/>
       <c r="K143" s="32" t="inlineStr">
@@ -16514,25 +16573,25 @@
         </is>
       </c>
       <c r="L143" s="33" t="n">
-        <v>0.458318</v>
+        <v>0.476807</v>
       </c>
       <c r="M143" s="33" t="n">
-        <v>0.175342</v>
+        <v>0.175305</v>
       </c>
       <c r="N143" s="33" t="n">
-        <v>0.366341</v>
+        <v>0.347888</v>
       </c>
       <c r="O143" s="33" t="n">
-        <v>0.8869225802309257</v>
+        <v>0.8840338278652803</v>
       </c>
       <c r="P143" s="33" t="n">
-        <v>0.1130774197690743</v>
+        <v>0.1159661721347198</v>
       </c>
       <c r="Q143" s="37" t="n"/>
       <c r="R143" s="37" t="n"/>
       <c r="S143" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T143" s="30" t="inlineStr">
@@ -16567,7 +16626,7 @@
         <v/>
       </c>
       <c r="AB143" s="36" t="n">
-        <v>1.735</v>
+        <v>1.7401</v>
       </c>
       <c r="AC143" s="32" t="inlineStr">
         <is>
@@ -16599,9 +16658,15 @@
           <t>Bodo/glimt</t>
         </is>
       </c>
-      <c r="F144" s="31" t="n"/>
-      <c r="G144" s="31" t="n"/>
-      <c r="H144" s="31" t="n"/>
+      <c r="F144" s="31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="G144" s="31" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="H144" s="31" t="n">
+        <v>1.98</v>
+      </c>
       <c r="I144" s="31" t="n"/>
       <c r="J144" s="31" t="n"/>
       <c r="K144" s="32" t="inlineStr">
@@ -16610,34 +16675,33 @@
         </is>
       </c>
       <c r="L144" s="33" t="n">
-        <v>0.362556</v>
+        <v>0.353908</v>
       </c>
       <c r="M144" s="33" t="n">
-        <v>0.172101</v>
+        <v>0.171703</v>
       </c>
       <c r="N144" s="33" t="n">
-        <v>0.465343</v>
+        <v>0.474389</v>
       </c>
       <c r="O144" s="33" t="n">
-        <v>0.8990878084260638</v>
+        <v>0.8992250126845134</v>
       </c>
       <c r="P144" s="33" t="n">
-        <v>0.1009121915739362</v>
+        <v>0.1007749873154866</v>
       </c>
       <c r="Q144" s="37" t="n"/>
       <c r="R144" s="37" t="n"/>
-      <c r="S144" s="30" t="inlineStr">
+      <c r="S144" s="30">
+        <f>IF(OR(Q144="",R144=""),"[APOSTAR] LOCAL",IF(Q144&gt;R144,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T144" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Sin Cuotas</t>
         </is>
       </c>
-      <c r="T144" s="30" t="inlineStr">
-        <is>
-          <t>[PASAR] Sin Cuotas</t>
-        </is>
-      </c>
       <c r="U144" s="34" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="V144" s="34" t="n">
         <v>0</v>
@@ -16663,7 +16727,7 @@
         <v/>
       </c>
       <c r="AB144" s="36" t="n">
-        <v>1.6327</v>
+        <v>1.6059</v>
       </c>
       <c r="AC144" s="32" t="inlineStr">
         <is>
@@ -16696,13 +16760,13 @@
         </is>
       </c>
       <c r="F145" s="31" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="G145" s="31" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="H145" s="31" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="I145" s="31" t="n"/>
       <c r="J145" s="31" t="n"/>
@@ -16738,7 +16802,7 @@
         </is>
       </c>
       <c r="U145" s="34" t="n">
-        <v>1020.62</v>
+        <v>1118.03</v>
       </c>
       <c r="V145" s="34" t="n">
         <v>0</v>
@@ -16774,64 +16838,58 @@
     </row>
     <row r="146">
       <c r="A146" s="29" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B146" s="30" t="inlineStr">
         <is>
-          <t>2026-04-12estudiantesderiocuartobarracascentral</t>
+          <t>2026-04-12aalesundkfumoslo</t>
         </is>
       </c>
       <c r="C146" s="30" t="inlineStr">
         <is>
-          <t>Estudiantes de Rio Cuarto vs Barracas Central</t>
+          <t>Aalesund vs Kfum Oslo</t>
         </is>
       </c>
       <c r="D146" s="30" t="inlineStr">
         <is>
-          <t>Estudiantes de Rio Cuarto</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="E146" s="30" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
-        </is>
-      </c>
-      <c r="F146" s="31" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="G146" s="31" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H146" s="31" t="n">
-        <v>3.65</v>
-      </c>
+          <t>Kfum Oslo</t>
+        </is>
+      </c>
+      <c r="F146" s="31" t="n"/>
+      <c r="G146" s="31" t="n"/>
+      <c r="H146" s="31" t="n"/>
       <c r="I146" s="31" t="n"/>
       <c r="J146" s="31" t="n"/>
       <c r="K146" s="32" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="L146" s="33" t="n">
-        <v>0.3963134205509635</v>
+        <v>0.412239</v>
       </c>
       <c r="M146" s="33" t="n">
-        <v>0.2290691920280968</v>
+        <v>0.156922</v>
       </c>
       <c r="N146" s="33" t="n">
-        <v>0.3746173874209397</v>
+        <v>0.430839</v>
       </c>
       <c r="O146" s="33" t="n">
-        <v>0.6948441594527209</v>
+        <v>0.9322324834348802</v>
       </c>
       <c r="P146" s="33" t="n">
-        <v>0.3051558405472792</v>
+        <v>0.06776751656511987</v>
       </c>
       <c r="Q146" s="37" t="n"/>
       <c r="R146" s="37" t="n"/>
       <c r="S146" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+          <t>[PASAR] Sin Cuotas</t>
         </is>
       </c>
       <c r="T146" s="30" t="inlineStr">
@@ -16866,9 +16924,2126 @@
         <v/>
       </c>
       <c r="AB146" s="36" t="n">
+        <v>1.3333</v>
+      </c>
+      <c r="AC146" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B147" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12athleticoparanaensechapecoense</t>
+        </is>
+      </c>
+      <c r="C147" s="30" t="inlineStr">
+        <is>
+          <t>Athletico Paranaense vs Chapecoense</t>
+        </is>
+      </c>
+      <c r="D147" s="30" t="inlineStr">
+        <is>
+          <t>Athletico Paranaense</t>
+        </is>
+      </c>
+      <c r="E147" s="30" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F147" s="31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G147" s="31" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H147" s="31" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="I147" s="31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J147" s="31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K147" s="32" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="L147" s="33" t="n">
+        <v>0.463893</v>
+      </c>
+      <c r="M147" s="33" t="n">
+        <v>0.177381</v>
+      </c>
+      <c r="N147" s="33" t="n">
+        <v>0.358726</v>
+      </c>
+      <c r="O147" s="33" t="n">
+        <v>0.8815683491777673</v>
+      </c>
+      <c r="P147" s="33" t="n">
+        <v>0.1184316508222327</v>
+      </c>
+      <c r="Q147" s="37" t="n"/>
+      <c r="R147" s="37" t="n"/>
+      <c r="S147" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Riesgo/Beneficio</t>
+        </is>
+      </c>
+      <c r="T147" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
+      </c>
+      <c r="U147" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" s="30">
+        <f>IF(L147="","",IF((MAX(L147,M147,N147)-MEDIAN(L147,M147,N147))&gt;0.05,IF(OR(Q147="",R147=""),"[PREDICCION] "&amp;IF(L147=MAX(L147,M147,N147),"LOCAL",IF(M147=MAX(L147,M147,N147),"EMPATE","VISITA")),IF(L147=MAX(L147,M147,N147),IF(Q147&gt;R147,"[ACIERTO]","[FALLO]"),IF(M147=MAX(L147,M147,N147),IF(Q147=R147,"[ACIERTO]","[FALLO]"),IF(Q147&lt;R147,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X147" s="34">
+        <f>IFERROR(IF(U147=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S147)),U147*(IF(ISNUMBER(SEARCH("LOCAL",S147)),F147,IF(ISNUMBER(SEARCH("EMPATE",S147)),G147,H147))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S147)),-U147,0))),0)+IFERROR(IF(V147=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T147)),V147*(IF(ISNUMBER(SEARCH("OVER",T147)),I147,J147)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T147)),-V147,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y147" s="34">
+        <f>Y146+X147</f>
+        <v/>
+      </c>
+      <c r="Z147" s="35">
+        <f>IF(OR(Q147="",R147=""),"",(L147-IF(Q147&gt;R147,1,0))^2+(M147-IF(Q147=R147,1,0))^2+(N147-IF(Q147&lt;R147,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA147" s="35">
+        <f>IF(OR(Q147="",R147="",F147="",F147=0,G147="",G147=0,H147="",H147=0),"",((1/F147/(1/F147+1/G147+1/H147))-IF(Q147&gt;R147,1,0))^2+((1/G147/(1/F147+1/G147+1/H147))-IF(Q147=R147,1,0))^2+((1/H147/(1/F147+1/G147+1/H147))-IF(Q147&lt;R147,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB147" s="36" t="n">
+        <v>1.2345</v>
+      </c>
+      <c r="AC147" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B148" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12atleticotucumantigre</t>
+        </is>
+      </c>
+      <c r="C148" s="30" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman vs Tigre</t>
+        </is>
+      </c>
+      <c r="D148" s="30" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman</t>
+        </is>
+      </c>
+      <c r="E148" s="30" t="inlineStr">
+        <is>
+          <t>Tigre</t>
+        </is>
+      </c>
+      <c r="F148" s="31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G148" s="31" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="H148" s="31" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I148" s="31" t="n"/>
+      <c r="J148" s="31" t="n"/>
+      <c r="K148" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L148" s="33" t="n">
+        <v>0.3986006826387638</v>
+      </c>
+      <c r="M148" s="33" t="n">
+        <v>0.2330114755931314</v>
+      </c>
+      <c r="N148" s="33" t="n">
+        <v>0.3683878417681047</v>
+      </c>
+      <c r="O148" s="33" t="n">
+        <v>0.6757078738015533</v>
+      </c>
+      <c r="P148" s="33" t="n">
+        <v>0.3242921261984467</v>
+      </c>
+      <c r="Q148" s="37" t="n"/>
+      <c r="R148" s="37" t="n"/>
+      <c r="S148" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] EV Insuf (0.088&lt;0.120)</t>
+        </is>
+      </c>
+      <c r="T148" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U148" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" s="30">
+        <f>IF(L148="","",IF((MAX(L148,M148,N148)-MEDIAN(L148,M148,N148))&gt;0.05,IF(OR(Q148="",R148=""),"[PREDICCION] "&amp;IF(L148=MAX(L148,M148,N148),"LOCAL",IF(M148=MAX(L148,M148,N148),"EMPATE","VISITA")),IF(L148=MAX(L148,M148,N148),IF(Q148&gt;R148,"[ACIERTO]","[FALLO]"),IF(M148=MAX(L148,M148,N148),IF(Q148=R148,"[ACIERTO]","[FALLO]"),IF(Q148&lt;R148,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X148" s="34">
+        <f>IFERROR(IF(U148=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S148)),U148*(IF(ISNUMBER(SEARCH("LOCAL",S148)),F148,IF(ISNUMBER(SEARCH("EMPATE",S148)),G148,H148))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S148)),-U148,0))),0)+IFERROR(IF(V148=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T148)),V148*(IF(ISNUMBER(SEARCH("OVER",T148)),I148,J148)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T148)),-V148,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y148" s="34">
+        <f>Y147+X148</f>
+        <v/>
+      </c>
+      <c r="Z148" s="35">
+        <f>IF(OR(Q148="",R148=""),"",(L148-IF(Q148&gt;R148,1,0))^2+(M148-IF(Q148=R148,1,0))^2+(N148-IF(Q148&lt;R148,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA148" s="35">
+        <f>IF(OR(Q148="",R148="",F148="",F148=0,G148="",G148=0,H148="",H148=0),"",((1/F148/(1/F148+1/G148+1/H148))-IF(Q148&gt;R148,1,0))^2+((1/G148/(1/F148+1/G148+1/H148))-IF(Q148=R148,1,0))^2+((1/H148/(1/F148+1/G148+1/H148))-IF(Q148&lt;R148,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB148" s="36" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="AC148" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B149" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12botafogocoritiba</t>
+        </is>
+      </c>
+      <c r="C149" s="30" t="inlineStr">
+        <is>
+          <t>Botafogo vs Coritiba</t>
+        </is>
+      </c>
+      <c r="D149" s="30" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="E149" s="30" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F149" s="31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G149" s="31" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="H149" s="31" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="I149" s="31" t="n"/>
+      <c r="J149" s="31" t="n"/>
+      <c r="K149" s="32" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="L149" s="33" t="n">
+        <v>0.441492</v>
+      </c>
+      <c r="M149" s="33" t="n">
+        <v>0.183811</v>
+      </c>
+      <c r="N149" s="33" t="n">
+        <v>0.374697</v>
+      </c>
+      <c r="O149" s="33" t="n">
+        <v>0.8569284695318948</v>
+      </c>
+      <c r="P149" s="33" t="n">
+        <v>0.1430715304681051</v>
+      </c>
+      <c r="Q149" s="37" t="n"/>
+      <c r="R149" s="37" t="n"/>
+      <c r="S149" s="30">
+        <f>IF(OR(Q149="",R149=""),"[APOSTAR] VISITA",IF(Q149&lt;R149,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T149" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U149" s="34" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="V149" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" s="30">
+        <f>IF(L149="","",IF((MAX(L149,M149,N149)-MEDIAN(L149,M149,N149))&gt;0.05,IF(OR(Q149="",R149=""),"[PREDICCION] "&amp;IF(L149=MAX(L149,M149,N149),"LOCAL",IF(M149=MAX(L149,M149,N149),"EMPATE","VISITA")),IF(L149=MAX(L149,M149,N149),IF(Q149&gt;R149,"[ACIERTO]","[FALLO]"),IF(M149=MAX(L149,M149,N149),IF(Q149=R149,"[ACIERTO]","[FALLO]"),IF(Q149&lt;R149,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X149" s="34">
+        <f>IFERROR(IF(U149=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S149)),U149*(IF(ISNUMBER(SEARCH("LOCAL",S149)),F149,IF(ISNUMBER(SEARCH("EMPATE",S149)),G149,H149))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S149)),-U149,0))),0)+IFERROR(IF(V149=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T149)),V149*(IF(ISNUMBER(SEARCH("OVER",T149)),I149,J149)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T149)),-V149,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y149" s="34">
+        <f>Y148+X149</f>
+        <v/>
+      </c>
+      <c r="Z149" s="35">
+        <f>IF(OR(Q149="",R149=""),"",(L149-IF(Q149&gt;R149,1,0))^2+(M149-IF(Q149=R149,1,0))^2+(N149-IF(Q149&lt;R149,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA149" s="35">
+        <f>IF(OR(Q149="",R149="",F149="",F149=0,G149="",G149=0,H149="",H149=0),"",((1/F149/(1/F149+1/G149+1/H149))-IF(Q149&gt;R149,1,0))^2+((1/G149/(1/F149+1/G149+1/H149))-IF(Q149=R149,1,0))^2+((1/H149/(1/F149+1/G149+1/H149))-IF(Q149&lt;R149,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB149" s="36" t="n">
+        <v>1.1562</v>
+      </c>
+      <c r="AC149" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B150" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12chelseamanchestercity</t>
+        </is>
+      </c>
+      <c r="C150" s="30" t="inlineStr">
+        <is>
+          <t>Chelsea vs Manchester City</t>
+        </is>
+      </c>
+      <c r="D150" s="30" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="E150" s="30" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="F150" s="31" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G150" s="31" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="H150" s="31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I150" s="31" t="n"/>
+      <c r="J150" s="31" t="n"/>
+      <c r="K150" s="32" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="L150" s="33" t="n">
+        <v>0.370878</v>
+      </c>
+      <c r="M150" s="33" t="n">
+        <v>0.181249</v>
+      </c>
+      <c r="N150" s="33" t="n">
+        <v>0.447873</v>
+      </c>
+      <c r="O150" s="33" t="n">
+        <v>0.8692174436264934</v>
+      </c>
+      <c r="P150" s="33" t="n">
+        <v>0.1307825563735065</v>
+      </c>
+      <c r="Q150" s="37" t="n"/>
+      <c r="R150" s="37" t="n"/>
+      <c r="S150" s="30">
+        <f>IF(OR(Q150="",R150=""),"[APOSTAR] LOCAL",IF(Q150&gt;R150,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T150" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U150" s="34" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="V150" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" s="30">
+        <f>IF(L150="","",IF((MAX(L150,M150,N150)-MEDIAN(L150,M150,N150))&gt;0.05,IF(OR(Q150="",R150=""),"[PREDICCION] "&amp;IF(L150=MAX(L150,M150,N150),"LOCAL",IF(M150=MAX(L150,M150,N150),"EMPATE","VISITA")),IF(L150=MAX(L150,M150,N150),IF(Q150&gt;R150,"[ACIERTO]","[FALLO]"),IF(M150=MAX(L150,M150,N150),IF(Q150=R150,"[ACIERTO]","[FALLO]"),IF(Q150&lt;R150,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X150" s="34">
+        <f>IFERROR(IF(U150=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S150)),U150*(IF(ISNUMBER(SEARCH("LOCAL",S150)),F150,IF(ISNUMBER(SEARCH("EMPATE",S150)),G150,H150))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S150)),-U150,0))),0)+IFERROR(IF(V150=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T150)),V150*(IF(ISNUMBER(SEARCH("OVER",T150)),I150,J150)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T150)),-V150,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y150" s="34">
+        <f>Y149+X150</f>
+        <v/>
+      </c>
+      <c r="Z150" s="35">
+        <f>IF(OR(Q150="",R150=""),"",(L150-IF(Q150&gt;R150,1,0))^2+(M150-IF(Q150=R150,1,0))^2+(N150-IF(Q150&lt;R150,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA150" s="35">
+        <f>IF(OR(Q150="",R150="",F150="",F150=0,G150="",G150=0,H150="",H150=0),"",((1/F150/(1/F150+1/G150+1/H150))-IF(Q150&gt;R150,1,0))^2+((1/G150/(1/F150+1/G150+1/H150))-IF(Q150=R150,1,0))^2+((1/H150/(1/F150+1/G150+1/H150))-IF(Q150&lt;R150,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB150" s="36" t="n">
+        <v>1.3041</v>
+      </c>
+      <c r="AC150" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B151" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12corinthianspalmeiras</t>
+        </is>
+      </c>
+      <c r="C151" s="30" t="inlineStr">
+        <is>
+          <t>Corinthians vs Palmeiras</t>
+        </is>
+      </c>
+      <c r="D151" s="30" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="E151" s="30" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="F151" s="31" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G151" s="31" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="H151" s="31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I151" s="31" t="n"/>
+      <c r="J151" s="31" t="n"/>
+      <c r="K151" s="32" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="L151" s="33" t="n">
+        <v>0.363484</v>
+      </c>
+      <c r="M151" s="33" t="n">
+        <v>0.195095</v>
+      </c>
+      <c r="N151" s="33" t="n">
+        <v>0.441421</v>
+      </c>
+      <c r="O151" s="33" t="n">
+        <v>0.8055400750928456</v>
+      </c>
+      <c r="P151" s="33" t="n">
+        <v>0.1944599249071544</v>
+      </c>
+      <c r="Q151" s="37" t="n"/>
+      <c r="R151" s="37" t="n"/>
+      <c r="S151" s="30">
+        <f>IF(OR(Q151="",R151=""),"[APOSTAR] VISITA",IF(Q151&lt;R151,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T151" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U151" s="34" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="V151" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" s="30">
+        <f>IF(L151="","",IF((MAX(L151,M151,N151)-MEDIAN(L151,M151,N151))&gt;0.05,IF(OR(Q151="",R151=""),"[PREDICCION] "&amp;IF(L151=MAX(L151,M151,N151),"LOCAL",IF(M151=MAX(L151,M151,N151),"EMPATE","VISITA")),IF(L151=MAX(L151,M151,N151),IF(Q151&gt;R151,"[ACIERTO]","[FALLO]"),IF(M151=MAX(L151,M151,N151),IF(Q151=R151,"[ACIERTO]","[FALLO]"),IF(Q151&lt;R151,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X151" s="34">
+        <f>IFERROR(IF(U151=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S151)),U151*(IF(ISNUMBER(SEARCH("LOCAL",S151)),F151,IF(ISNUMBER(SEARCH("EMPATE",S151)),G151,H151))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S151)),-U151,0))),0)+IFERROR(IF(V151=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T151)),V151*(IF(ISNUMBER(SEARCH("OVER",T151)),I151,J151)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T151)),-V151,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y151" s="34">
+        <f>Y150+X151</f>
+        <v/>
+      </c>
+      <c r="Z151" s="35">
+        <f>IF(OR(Q151="",R151=""),"",(L151-IF(Q151&gt;R151,1,0))^2+(M151-IF(Q151=R151,1,0))^2+(N151-IF(Q151&lt;R151,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA151" s="35">
+        <f>IF(OR(Q151="",R151="",F151="",F151=0,G151="",G151=0,H151="",H151=0),"",((1/F151/(1/F151+1/G151+1/H151))-IF(Q151&gt;R151,1,0))^2+((1/G151/(1/F151+1/G151+1/H151))-IF(Q151=R151,1,0))^2+((1/H151/(1/F151+1/G151+1/H151))-IF(Q151&lt;R151,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB151" s="36" t="n">
+        <v>1.2647</v>
+      </c>
+      <c r="AC151" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B152" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12cruzeiroredbullbragantino</t>
+        </is>
+      </c>
+      <c r="C152" s="30" t="inlineStr">
+        <is>
+          <t>Cruzeiro vs Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="D152" s="30" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="E152" s="30" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="F152" s="31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G152" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H152" s="31" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="I152" s="31" t="n"/>
+      <c r="J152" s="31" t="n"/>
+      <c r="K152" s="32" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="L152" s="33" t="n">
+        <v>0.455166</v>
+      </c>
+      <c r="M152" s="33" t="n">
+        <v>0.190811</v>
+      </c>
+      <c r="N152" s="33" t="n">
+        <v>0.354024</v>
+      </c>
+      <c r="O152" s="33" t="n">
+        <v>0.8238327445501378</v>
+      </c>
+      <c r="P152" s="33" t="n">
+        <v>0.1761672554498623</v>
+      </c>
+      <c r="Q152" s="37" t="n"/>
+      <c r="R152" s="37" t="n"/>
+      <c r="S152" s="30">
+        <f>IF(OR(Q152="",R152=""),"[APOSTAR] VISITA",IF(Q152&lt;R152,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T152" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U152" s="34" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="V152" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" s="30">
+        <f>IF(L152="","",IF((MAX(L152,M152,N152)-MEDIAN(L152,M152,N152))&gt;0.05,IF(OR(Q152="",R152=""),"[PREDICCION] "&amp;IF(L152=MAX(L152,M152,N152),"LOCAL",IF(M152=MAX(L152,M152,N152),"EMPATE","VISITA")),IF(L152=MAX(L152,M152,N152),IF(Q152&gt;R152,"[ACIERTO]","[FALLO]"),IF(M152=MAX(L152,M152,N152),IF(Q152=R152,"[ACIERTO]","[FALLO]"),IF(Q152&lt;R152,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X152" s="34">
+        <f>IFERROR(IF(U152=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S152)),U152*(IF(ISNUMBER(SEARCH("LOCAL",S152)),F152,IF(ISNUMBER(SEARCH("EMPATE",S152)),G152,H152))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S152)),-U152,0))),0)+IFERROR(IF(V152=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T152)),V152*(IF(ISNUMBER(SEARCH("OVER",T152)),I152,J152)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T152)),-V152,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y152" s="34">
+        <f>Y151+X152</f>
+        <v/>
+      </c>
+      <c r="Z152" s="35">
+        <f>IF(OR(Q152="",R152=""),"",(L152-IF(Q152&gt;R152,1,0))^2+(M152-IF(Q152=R152,1,0))^2+(N152-IF(Q152&lt;R152,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA152" s="35">
+        <f>IF(OR(Q152="",R152="",F152="",F152=0,G152="",G152=0,H152="",H152=0),"",((1/F152/(1/F152+1/G152+1/H152))-IF(Q152&gt;R152,1,0))^2+((1/G152/(1/F152+1/G152+1/H152))-IF(Q152=R152,1,0))^2+((1/H152/(1/F152+1/G152+1/H152))-IF(Q152&lt;R152,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB152" s="36" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="AC152" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B153" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12crystalpalacenewcastleunited</t>
+        </is>
+      </c>
+      <c r="C153" s="30" t="inlineStr">
+        <is>
+          <t>Crystal Palace vs Newcastle United</t>
+        </is>
+      </c>
+      <c r="D153" s="30" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="E153" s="30" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="F153" s="31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G153" s="31" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="H153" s="31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I153" s="31" t="n"/>
+      <c r="J153" s="31" t="n"/>
+      <c r="K153" s="32" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="L153" s="33" t="n">
+        <v>0.375809</v>
+      </c>
+      <c r="M153" s="33" t="n">
+        <v>0.182174</v>
+      </c>
+      <c r="N153" s="33" t="n">
+        <v>0.442017</v>
+      </c>
+      <c r="O153" s="33" t="n">
+        <v>0.8657991460674097</v>
+      </c>
+      <c r="P153" s="33" t="n">
+        <v>0.1342008539325902</v>
+      </c>
+      <c r="Q153" s="37" t="n"/>
+      <c r="R153" s="37" t="n"/>
+      <c r="S153" s="30">
+        <f>IF(OR(Q153="",R153=""),"[APOSTAR] VISITA",IF(Q153&lt;R153,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T153" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U153" s="34" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="V153" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="30">
+        <f>IF(L153="","",IF((MAX(L153,M153,N153)-MEDIAN(L153,M153,N153))&gt;0.05,IF(OR(Q153="",R153=""),"[PREDICCION] "&amp;IF(L153=MAX(L153,M153,N153),"LOCAL",IF(M153=MAX(L153,M153,N153),"EMPATE","VISITA")),IF(L153=MAX(L153,M153,N153),IF(Q153&gt;R153,"[ACIERTO]","[FALLO]"),IF(M153=MAX(L153,M153,N153),IF(Q153=R153,"[ACIERTO]","[FALLO]"),IF(Q153&lt;R153,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X153" s="34">
+        <f>IFERROR(IF(U153=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S153)),U153*(IF(ISNUMBER(SEARCH("LOCAL",S153)),F153,IF(ISNUMBER(SEARCH("EMPATE",S153)),G153,H153))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S153)),-U153,0))),0)+IFERROR(IF(V153=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T153)),V153*(IF(ISNUMBER(SEARCH("OVER",T153)),I153,J153)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T153)),-V153,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y153" s="34">
+        <f>Y152+X153</f>
+        <v/>
+      </c>
+      <c r="Z153" s="35">
+        <f>IF(OR(Q153="",R153=""),"",(L153-IF(Q153&gt;R153,1,0))^2+(M153-IF(Q153=R153,1,0))^2+(N153-IF(Q153&lt;R153,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA153" s="35">
+        <f>IF(OR(Q153="",R153="",F153="",F153=0,G153="",G153=0,H153="",H153=0),"",((1/F153/(1/F153+1/G153+1/H153))-IF(Q153&gt;R153,1,0))^2+((1/G153/(1/F153+1/G153+1/H153))-IF(Q153=R153,1,0))^2+((1/H153/(1/F153+1/G153+1/H153))-IF(Q153&lt;R153,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB153" s="36" t="n">
+        <v>1.4124</v>
+      </c>
+      <c r="AC153" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="29" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B154" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12estudiantesderiocuartobarracascentral</t>
+        </is>
+      </c>
+      <c r="C154" s="30" t="inlineStr">
+        <is>
+          <t>Estudiantes de Rio Cuarto vs Barracas Central</t>
+        </is>
+      </c>
+      <c r="D154" s="30" t="inlineStr">
+        <is>
+          <t>Estudiantes de Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="E154" s="30" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F154" s="31" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G154" s="31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H154" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I154" s="31" t="n"/>
+      <c r="J154" s="31" t="n"/>
+      <c r="K154" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L154" s="33" t="n">
+        <v>0.3963490381212049</v>
+      </c>
+      <c r="M154" s="33" t="n">
+        <v>0.228997956887614</v>
+      </c>
+      <c r="N154" s="33" t="n">
+        <v>0.3746530049911811</v>
+      </c>
+      <c r="O154" s="33" t="n">
+        <v>0.6948441594527209</v>
+      </c>
+      <c r="P154" s="33" t="n">
+        <v>0.3051558405472792</v>
+      </c>
+      <c r="Q154" s="37" t="n"/>
+      <c r="R154" s="37" t="n"/>
+      <c r="S154" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="T154" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U154" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" s="30">
+        <f>IF(L154="","",IF((MAX(L154,M154,N154)-MEDIAN(L154,M154,N154))&gt;0.05,IF(OR(Q154="",R154=""),"[PREDICCION] "&amp;IF(L154=MAX(L154,M154,N154),"LOCAL",IF(M154=MAX(L154,M154,N154),"EMPATE","VISITA")),IF(L154=MAX(L154,M154,N154),IF(Q154&gt;R154,"[ACIERTO]","[FALLO]"),IF(M154=MAX(L154,M154,N154),IF(Q154=R154,"[ACIERTO]","[FALLO]"),IF(Q154&lt;R154,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X154" s="34">
+        <f>IFERROR(IF(U154=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S154)),U154*(IF(ISNUMBER(SEARCH("LOCAL",S154)),F154,IF(ISNUMBER(SEARCH("EMPATE",S154)),G154,H154))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S154)),-U154,0))),0)+IFERROR(IF(V154=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T154)),V154*(IF(ISNUMBER(SEARCH("OVER",T154)),I154,J154)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T154)),-V154,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y154" s="34">
+        <f>Y153+X154</f>
+        <v/>
+      </c>
+      <c r="Z154" s="35">
+        <f>IF(OR(Q154="",R154=""),"",(L154-IF(Q154&gt;R154,1,0))^2+(M154-IF(Q154=R154,1,0))^2+(N154-IF(Q154&lt;R154,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA154" s="35">
+        <f>IF(OR(Q154="",R154="",F154="",F154=0,G154="",G154=0,H154="",H154=0),"",((1/F154/(1/F154+1/G154+1/H154))-IF(Q154&gt;R154,1,0))^2+((1/G154/(1/F154+1/G154+1/H154))-IF(Q154=R154,1,0))^2+((1/H154/(1/F154+1/G154+1/H154))-IF(Q154&lt;R154,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB154" s="36" t="n">
         <v>0.9323</v>
       </c>
-      <c r="AC146" s="32" t="inlineStr">
+      <c r="AC154" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B155" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12fredrikstadvalerenga</t>
+        </is>
+      </c>
+      <c r="C155" s="30" t="inlineStr">
+        <is>
+          <t>Fredrikstad vs Valerenga</t>
+        </is>
+      </c>
+      <c r="D155" s="30" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="E155" s="30" t="inlineStr">
+        <is>
+          <t>Valerenga</t>
+        </is>
+      </c>
+      <c r="F155" s="31" t="n"/>
+      <c r="G155" s="31" t="n"/>
+      <c r="H155" s="31" t="n"/>
+      <c r="I155" s="31" t="n"/>
+      <c r="J155" s="31" t="n"/>
+      <c r="K155" s="32" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="L155" s="33" t="n">
+        <v>0.459754</v>
+      </c>
+      <c r="M155" s="33" t="n">
+        <v>0.169717</v>
+      </c>
+      <c r="N155" s="33" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="O155" s="33" t="n">
+        <v>0.9088598664214891</v>
+      </c>
+      <c r="P155" s="33" t="n">
+        <v>0.09114013357851096</v>
+      </c>
+      <c r="Q155" s="37" t="n"/>
+      <c r="R155" s="37" t="n"/>
+      <c r="S155" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T155" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U155" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" s="30">
+        <f>IF(L155="","",IF((MAX(L155,M155,N155)-MEDIAN(L155,M155,N155))&gt;0.05,IF(OR(Q155="",R155=""),"[PREDICCION] "&amp;IF(L155=MAX(L155,M155,N155),"LOCAL",IF(M155=MAX(L155,M155,N155),"EMPATE","VISITA")),IF(L155=MAX(L155,M155,N155),IF(Q155&gt;R155,"[ACIERTO]","[FALLO]"),IF(M155=MAX(L155,M155,N155),IF(Q155=R155,"[ACIERTO]","[FALLO]"),IF(Q155&lt;R155,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X155" s="34">
+        <f>IFERROR(IF(U155=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S155)),U155*(IF(ISNUMBER(SEARCH("LOCAL",S155)),F155,IF(ISNUMBER(SEARCH("EMPATE",S155)),G155,H155))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S155)),-U155,0))),0)+IFERROR(IF(V155=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T155)),V155*(IF(ISNUMBER(SEARCH("OVER",T155)),I155,J155)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T155)),-V155,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y155" s="34">
+        <f>Y154+X155</f>
+        <v/>
+      </c>
+      <c r="Z155" s="35">
+        <f>IF(OR(Q155="",R155=""),"",(L155-IF(Q155&gt;R155,1,0))^2+(M155-IF(Q155=R155,1,0))^2+(N155-IF(Q155&lt;R155,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA155" s="35">
+        <f>IF(OR(Q155="",R155="",F155="",F155=0,G155="",G155=0,H155="",H155=0),"",((1/F155/(1/F155+1/G155+1/H155))-IF(Q155&gt;R155,1,0))^2+((1/G155/(1/F155+1/G155+1/H155))-IF(Q155=R155,1,0))^2+((1/H155/(1/F155+1/G155+1/H155))-IF(Q155&lt;R155,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB155" s="36" t="n">
+        <v>1.6803</v>
+      </c>
+      <c r="AC155" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B156" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12galatasaraykocaelispor</t>
+        </is>
+      </c>
+      <c r="C156" s="30" t="inlineStr">
+        <is>
+          <t>Galatasaray vs Kocaelispor</t>
+        </is>
+      </c>
+      <c r="D156" s="30" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="E156" s="30" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="F156" s="31" t="n"/>
+      <c r="G156" s="31" t="n"/>
+      <c r="H156" s="31" t="n"/>
+      <c r="I156" s="31" t="n"/>
+      <c r="J156" s="31" t="n"/>
+      <c r="K156" s="32" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="L156" s="33" t="n">
+        <v>0.506282</v>
+      </c>
+      <c r="M156" s="33" t="n">
+        <v>0.184489</v>
+      </c>
+      <c r="N156" s="33" t="n">
+        <v>0.309229</v>
+      </c>
+      <c r="O156" s="33" t="n">
+        <v>0.8436747050240128</v>
+      </c>
+      <c r="P156" s="33" t="n">
+        <v>0.1563252949759873</v>
+      </c>
+      <c r="Q156" s="37" t="n"/>
+      <c r="R156" s="37" t="n"/>
+      <c r="S156" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T156" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U156" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" s="30">
+        <f>IF(L156="","",IF((MAX(L156,M156,N156)-MEDIAN(L156,M156,N156))&gt;0.05,IF(OR(Q156="",R156=""),"[PREDICCION] "&amp;IF(L156=MAX(L156,M156,N156),"LOCAL",IF(M156=MAX(L156,M156,N156),"EMPATE","VISITA")),IF(L156=MAX(L156,M156,N156),IF(Q156&gt;R156,"[ACIERTO]","[FALLO]"),IF(M156=MAX(L156,M156,N156),IF(Q156=R156,"[ACIERTO]","[FALLO]"),IF(Q156&lt;R156,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X156" s="34">
+        <f>IFERROR(IF(U156=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S156)),U156*(IF(ISNUMBER(SEARCH("LOCAL",S156)),F156,IF(ISNUMBER(SEARCH("EMPATE",S156)),G156,H156))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S156)),-U156,0))),0)+IFERROR(IF(V156=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T156)),V156*(IF(ISNUMBER(SEARCH("OVER",T156)),I156,J156)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T156)),-V156,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y156" s="34">
+        <f>Y155+X156</f>
+        <v/>
+      </c>
+      <c r="Z156" s="35">
+        <f>IF(OR(Q156="",R156=""),"",(L156-IF(Q156&gt;R156,1,0))^2+(M156-IF(Q156=R156,1,0))^2+(N156-IF(Q156&lt;R156,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA156" s="35">
+        <f>IF(OR(Q156="",R156="",F156="",F156=0,G156="",G156=0,H156="",H156=0),"",((1/F156/(1/F156+1/G156+1/H156))-IF(Q156&gt;R156,1,0))^2+((1/G156/(1/F156+1/G156+1/H156))-IF(Q156=R156,1,0))^2+((1/H156/(1/F156+1/G156+1/H156))-IF(Q156&lt;R156,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB156" s="36" t="n">
+        <v>1.3341</v>
+      </c>
+      <c r="AC156" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B157" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12goztepekasimpasa</t>
+        </is>
+      </c>
+      <c r="C157" s="30" t="inlineStr">
+        <is>
+          <t>Goztepe vs Kasimpasa</t>
+        </is>
+      </c>
+      <c r="D157" s="30" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="E157" s="30" t="inlineStr">
+        <is>
+          <t>Kasimpasa</t>
+        </is>
+      </c>
+      <c r="F157" s="31" t="n"/>
+      <c r="G157" s="31" t="n"/>
+      <c r="H157" s="31" t="n"/>
+      <c r="I157" s="31" t="n"/>
+      <c r="J157" s="31" t="n"/>
+      <c r="K157" s="32" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="L157" s="33" t="n">
+        <v>0.459856</v>
+      </c>
+      <c r="M157" s="33" t="n">
+        <v>0.193695</v>
+      </c>
+      <c r="N157" s="33" t="n">
+        <v>0.346449</v>
+      </c>
+      <c r="O157" s="33" t="n">
+        <v>0.8156480867340589</v>
+      </c>
+      <c r="P157" s="33" t="n">
+        <v>0.1843519132659412</v>
+      </c>
+      <c r="Q157" s="37" t="n"/>
+      <c r="R157" s="37" t="n"/>
+      <c r="S157" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T157" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U157" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" s="30">
+        <f>IF(L157="","",IF((MAX(L157,M157,N157)-MEDIAN(L157,M157,N157))&gt;0.05,IF(OR(Q157="",R157=""),"[PREDICCION] "&amp;IF(L157=MAX(L157,M157,N157),"LOCAL",IF(M157=MAX(L157,M157,N157),"EMPATE","VISITA")),IF(L157=MAX(L157,M157,N157),IF(Q157&gt;R157,"[ACIERTO]","[FALLO]"),IF(M157=MAX(L157,M157,N157),IF(Q157=R157,"[ACIERTO]","[FALLO]"),IF(Q157&lt;R157,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X157" s="34">
+        <f>IFERROR(IF(U157=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S157)),U157*(IF(ISNUMBER(SEARCH("LOCAL",S157)),F157,IF(ISNUMBER(SEARCH("EMPATE",S157)),G157,H157))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S157)),-U157,0))),0)+IFERROR(IF(V157=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T157)),V157*(IF(ISNUMBER(SEARCH("OVER",T157)),I157,J157)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T157)),-V157,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y157" s="34">
+        <f>Y156+X157</f>
+        <v/>
+      </c>
+      <c r="Z157" s="35">
+        <f>IF(OR(Q157="",R157=""),"",(L157-IF(Q157&gt;R157,1,0))^2+(M157-IF(Q157=R157,1,0))^2+(N157-IF(Q157&lt;R157,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA157" s="35">
+        <f>IF(OR(Q157="",R157="",F157="",F157=0,G157="",G157=0,H157="",H157=0),"",((1/F157/(1/F157+1/G157+1/H157))-IF(Q157&gt;R157,1,0))^2+((1/G157/(1/F157+1/G157+1/H157))-IF(Q157=R157,1,0))^2+((1/H157/(1/F157+1/G157+1/H157))-IF(Q157&lt;R157,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB157" s="36" t="n">
+        <v>1.3197</v>
+      </c>
+      <c r="AC157" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B158" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12huracanrosariocentral</t>
+        </is>
+      </c>
+      <c r="C158" s="30" t="inlineStr">
+        <is>
+          <t>Huracan vs Rosario Central</t>
+        </is>
+      </c>
+      <c r="D158" s="30" t="inlineStr">
+        <is>
+          <t>Huracan</t>
+        </is>
+      </c>
+      <c r="E158" s="30" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="F158" s="31" t="n"/>
+      <c r="G158" s="31" t="n"/>
+      <c r="H158" s="31" t="n"/>
+      <c r="I158" s="31" t="n"/>
+      <c r="J158" s="31" t="n"/>
+      <c r="K158" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L158" s="33" t="n">
+        <v>0.3961158482117325</v>
+      </c>
+      <c r="M158" s="33" t="n">
+        <v>0.2332738112541244</v>
+      </c>
+      <c r="N158" s="33" t="n">
+        <v>0.3706103405341432</v>
+      </c>
+      <c r="O158" s="33" t="n">
+        <v>0.6746814648322969</v>
+      </c>
+      <c r="P158" s="33" t="n">
+        <v>0.3253185351677031</v>
+      </c>
+      <c r="Q158" s="37" t="n"/>
+      <c r="R158" s="37" t="n"/>
+      <c r="S158" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T158" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U158" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V158" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" s="30">
+        <f>IF(L158="","",IF((MAX(L158,M158,N158)-MEDIAN(L158,M158,N158))&gt;0.05,IF(OR(Q158="",R158=""),"[PREDICCION] "&amp;IF(L158=MAX(L158,M158,N158),"LOCAL",IF(M158=MAX(L158,M158,N158),"EMPATE","VISITA")),IF(L158=MAX(L158,M158,N158),IF(Q158&gt;R158,"[ACIERTO]","[FALLO]"),IF(M158=MAX(L158,M158,N158),IF(Q158=R158,"[ACIERTO]","[FALLO]"),IF(Q158&lt;R158,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X158" s="34">
+        <f>IFERROR(IF(U158=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S158)),U158*(IF(ISNUMBER(SEARCH("LOCAL",S158)),F158,IF(ISNUMBER(SEARCH("EMPATE",S158)),G158,H158))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S158)),-U158,0))),0)+IFERROR(IF(V158=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T158)),V158*(IF(ISNUMBER(SEARCH("OVER",T158)),I158,J158)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T158)),-V158,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y158" s="34">
+        <f>Y157+X158</f>
+        <v/>
+      </c>
+      <c r="Z158" s="35">
+        <f>IF(OR(Q158="",R158=""),"",(L158-IF(Q158&gt;R158,1,0))^2+(M158-IF(Q158=R158,1,0))^2+(N158-IF(Q158&lt;R158,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA158" s="35">
+        <f>IF(OR(Q158="",R158="",F158="",F158=0,G158="",G158=0,H158="",H158=0),"",((1/F158/(1/F158+1/G158+1/H158))-IF(Q158&gt;R158,1,0))^2+((1/G158/(1/F158+1/G158+1/H158))-IF(Q158=R158,1,0))^2+((1/H158/(1/F158+1/G158+1/H158))-IF(Q158&lt;R158,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB158" s="36" t="n">
+        <v>0.8921</v>
+      </c>
+      <c r="AC158" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B159" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12konyasporfatihkaragumruk</t>
+        </is>
+      </c>
+      <c r="C159" s="30" t="inlineStr">
+        <is>
+          <t>Konyaspor vs Fatih Karagümrük</t>
+        </is>
+      </c>
+      <c r="D159" s="30" t="inlineStr">
+        <is>
+          <t>Konyaspor</t>
+        </is>
+      </c>
+      <c r="E159" s="30" t="inlineStr">
+        <is>
+          <t>Fatih Karagümrük</t>
+        </is>
+      </c>
+      <c r="F159" s="31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G159" s="31" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="H159" s="31" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="I159" s="31" t="n"/>
+      <c r="J159" s="31" t="n"/>
+      <c r="K159" s="32" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="L159" s="33" t="n">
+        <v>0.470203</v>
+      </c>
+      <c r="M159" s="33" t="n">
+        <v>0.194426</v>
+      </c>
+      <c r="N159" s="33" t="n">
+        <v>0.335371</v>
+      </c>
+      <c r="O159" s="33" t="n">
+        <v>0.8098303351519444</v>
+      </c>
+      <c r="P159" s="33" t="n">
+        <v>0.1901696648480556</v>
+      </c>
+      <c r="Q159" s="37" t="n"/>
+      <c r="R159" s="37" t="n"/>
+      <c r="S159" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Riesgo/Beneficio</t>
+        </is>
+      </c>
+      <c r="T159" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U159" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V159" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" s="30">
+        <f>IF(L159="","",IF((MAX(L159,M159,N159)-MEDIAN(L159,M159,N159))&gt;0.05,IF(OR(Q159="",R159=""),"[PREDICCION] "&amp;IF(L159=MAX(L159,M159,N159),"LOCAL",IF(M159=MAX(L159,M159,N159),"EMPATE","VISITA")),IF(L159=MAX(L159,M159,N159),IF(Q159&gt;R159,"[ACIERTO]","[FALLO]"),IF(M159=MAX(L159,M159,N159),IF(Q159=R159,"[ACIERTO]","[FALLO]"),IF(Q159&lt;R159,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X159" s="34">
+        <f>IFERROR(IF(U159=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S159)),U159*(IF(ISNUMBER(SEARCH("LOCAL",S159)),F159,IF(ISNUMBER(SEARCH("EMPATE",S159)),G159,H159))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S159)),-U159,0))),0)+IFERROR(IF(V159=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T159)),V159*(IF(ISNUMBER(SEARCH("OVER",T159)),I159,J159)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T159)),-V159,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y159" s="34">
+        <f>Y158+X159</f>
+        <v/>
+      </c>
+      <c r="Z159" s="35">
+        <f>IF(OR(Q159="",R159=""),"",(L159-IF(Q159&gt;R159,1,0))^2+(M159-IF(Q159=R159,1,0))^2+(N159-IF(Q159&lt;R159,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA159" s="35">
+        <f>IF(OR(Q159="",R159="",F159="",F159=0,G159="",G159=0,H159="",H159=0),"",((1/F159/(1/F159+1/G159+1/H159))-IF(Q159&gt;R159,1,0))^2+((1/G159/(1/F159+1/G159+1/H159))-IF(Q159=R159,1,0))^2+((1/H159/(1/F159+1/G159+1/H159))-IF(Q159&lt;R159,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB159" s="36" t="n">
+        <v>1.2653</v>
+      </c>
+      <c r="AC159" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B160" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12moldehamkam</t>
+        </is>
+      </c>
+      <c r="C160" s="30" t="inlineStr">
+        <is>
+          <t>Molde vs Hamkam</t>
+        </is>
+      </c>
+      <c r="D160" s="30" t="inlineStr">
+        <is>
+          <t>Molde</t>
+        </is>
+      </c>
+      <c r="E160" s="30" t="inlineStr">
+        <is>
+          <t>Hamkam</t>
+        </is>
+      </c>
+      <c r="F160" s="31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G160" s="31" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="H160" s="31" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I160" s="31" t="n"/>
+      <c r="J160" s="31" t="n"/>
+      <c r="K160" s="32" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="L160" s="33" t="n">
+        <v>0.450245</v>
+      </c>
+      <c r="M160" s="33" t="n">
+        <v>0.176204</v>
+      </c>
+      <c r="N160" s="33" t="n">
+        <v>0.37355</v>
+      </c>
+      <c r="O160" s="33" t="n">
+        <v>0.8841170701918618</v>
+      </c>
+      <c r="P160" s="33" t="n">
+        <v>0.1158829298081381</v>
+      </c>
+      <c r="Q160" s="37" t="n"/>
+      <c r="R160" s="37" t="n"/>
+      <c r="S160" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Riesgo/Beneficio</t>
+        </is>
+      </c>
+      <c r="T160" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U160" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V160" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W160" s="30">
+        <f>IF(L160="","",IF((MAX(L160,M160,N160)-MEDIAN(L160,M160,N160))&gt;0.05,IF(OR(Q160="",R160=""),"[PREDICCION] "&amp;IF(L160=MAX(L160,M160,N160),"LOCAL",IF(M160=MAX(L160,M160,N160),"EMPATE","VISITA")),IF(L160=MAX(L160,M160,N160),IF(Q160&gt;R160,"[ACIERTO]","[FALLO]"),IF(M160=MAX(L160,M160,N160),IF(Q160=R160,"[ACIERTO]","[FALLO]"),IF(Q160&lt;R160,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X160" s="34">
+        <f>IFERROR(IF(U160=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S160)),U160*(IF(ISNUMBER(SEARCH("LOCAL",S160)),F160,IF(ISNUMBER(SEARCH("EMPATE",S160)),G160,H160))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S160)),-U160,0))),0)+IFERROR(IF(V160=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T160)),V160*(IF(ISNUMBER(SEARCH("OVER",T160)),I160,J160)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T160)),-V160,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y160" s="34">
+        <f>Y159+X160</f>
+        <v/>
+      </c>
+      <c r="Z160" s="35">
+        <f>IF(OR(Q160="",R160=""),"",(L160-IF(Q160&gt;R160,1,0))^2+(M160-IF(Q160=R160,1,0))^2+(N160-IF(Q160&lt;R160,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA160" s="35">
+        <f>IF(OR(Q160="",R160="",F160="",F160=0,G160="",G160=0,H160="",H160=0),"",((1/F160/(1/F160+1/G160+1/H160))-IF(Q160&gt;R160,1,0))^2+((1/G160/(1/F160+1/G160+1/H160))-IF(Q160=R160,1,0))^2+((1/H160/(1/F160+1/G160+1/H160))-IF(Q160&lt;R160,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB160" s="36" t="n">
+        <v>1.6797</v>
+      </c>
+      <c r="AC160" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B161" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12newellsoldboyssanlorenzo</t>
+        </is>
+      </c>
+      <c r="C161" s="30" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys vs San Lorenzo</t>
+        </is>
+      </c>
+      <c r="D161" s="30" t="inlineStr">
+        <is>
+          <t>Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="E161" s="30" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="F161" s="31" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G161" s="31" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H161" s="31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="I161" s="31" t="n"/>
+      <c r="J161" s="31" t="n"/>
+      <c r="K161" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L161" s="33" t="n">
+        <v>0.3830342891436993</v>
+      </c>
+      <c r="M161" s="33" t="n">
+        <v>0.2343441625542087</v>
+      </c>
+      <c r="N161" s="33" t="n">
+        <v>0.3826215483020922</v>
+      </c>
+      <c r="O161" s="33" t="n">
+        <v>0.6701744125591808</v>
+      </c>
+      <c r="P161" s="33" t="n">
+        <v>0.3298255874408193</v>
+      </c>
+      <c r="Q161" s="37" t="n"/>
+      <c r="R161" s="37" t="n"/>
+      <c r="S161" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="T161" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U161" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V161" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" s="30">
+        <f>IF(L161="","",IF((MAX(L161,M161,N161)-MEDIAN(L161,M161,N161))&gt;0.05,IF(OR(Q161="",R161=""),"[PREDICCION] "&amp;IF(L161=MAX(L161,M161,N161),"LOCAL",IF(M161=MAX(L161,M161,N161),"EMPATE","VISITA")),IF(L161=MAX(L161,M161,N161),IF(Q161&gt;R161,"[ACIERTO]","[FALLO]"),IF(M161=MAX(L161,M161,N161),IF(Q161=R161,"[ACIERTO]","[FALLO]"),IF(Q161&lt;R161,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X161" s="34">
+        <f>IFERROR(IF(U161=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S161)),U161*(IF(ISNUMBER(SEARCH("LOCAL",S161)),F161,IF(ISNUMBER(SEARCH("EMPATE",S161)),G161,H161))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S161)),-U161,0))),0)+IFERROR(IF(V161=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T161)),V161*(IF(ISNUMBER(SEARCH("OVER",T161)),I161,J161)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T161)),-V161,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y161" s="34">
+        <f>Y160+X161</f>
+        <v/>
+      </c>
+      <c r="Z161" s="35">
+        <f>IF(OR(Q161="",R161=""),"",(L161-IF(Q161&gt;R161,1,0))^2+(M161-IF(Q161=R161,1,0))^2+(N161-IF(Q161&lt;R161,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA161" s="35">
+        <f>IF(OR(Q161="",R161="",F161="",F161=0,G161="",G161=0,H161="",H161=0),"",((1/F161/(1/F161+1/G161+1/H161))-IF(Q161&gt;R161,1,0))^2+((1/G161/(1/F161+1/G161+1/H161))-IF(Q161=R161,1,0))^2+((1/H161/(1/F161+1/G161+1/H161))-IF(Q161&lt;R161,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB161" s="36" t="n">
+        <v>0.8489</v>
+      </c>
+      <c r="AC161" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B162" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12nottinghamforestastonvilla</t>
+        </is>
+      </c>
+      <c r="C162" s="30" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="D162" s="30" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="E162" s="30" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F162" s="31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G162" s="31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="H162" s="31" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="I162" s="31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J162" s="31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K162" s="32" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="L162" s="33" t="n">
+        <v>0.443102</v>
+      </c>
+      <c r="M162" s="33" t="n">
+        <v>0.182968</v>
+      </c>
+      <c r="N162" s="33" t="n">
+        <v>0.373929</v>
+      </c>
+      <c r="O162" s="33" t="n">
+        <v>0.8623934161136466</v>
+      </c>
+      <c r="P162" s="33" t="n">
+        <v>0.1376065838863534</v>
+      </c>
+      <c r="Q162" s="37" t="n"/>
+      <c r="R162" s="37" t="n"/>
+      <c r="S162" s="30">
+        <f>IF(OR(Q162="",R162=""),"[APOSTAR] LOCAL",IF(Q162&gt;R162,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T162" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
+      </c>
+      <c r="U162" s="34" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="V162" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" s="30">
+        <f>IF(L162="","",IF((MAX(L162,M162,N162)-MEDIAN(L162,M162,N162))&gt;0.05,IF(OR(Q162="",R162=""),"[PREDICCION] "&amp;IF(L162=MAX(L162,M162,N162),"LOCAL",IF(M162=MAX(L162,M162,N162),"EMPATE","VISITA")),IF(L162=MAX(L162,M162,N162),IF(Q162&gt;R162,"[ACIERTO]","[FALLO]"),IF(M162=MAX(L162,M162,N162),IF(Q162=R162,"[ACIERTO]","[FALLO]"),IF(Q162&lt;R162,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X162" s="34">
+        <f>IFERROR(IF(U162=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S162)),U162*(IF(ISNUMBER(SEARCH("LOCAL",S162)),F162,IF(ISNUMBER(SEARCH("EMPATE",S162)),G162,H162))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S162)),-U162,0))),0)+IFERROR(IF(V162=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T162)),V162*(IF(ISNUMBER(SEARCH("OVER",T162)),I162,J162)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T162)),-V162,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y162" s="34">
+        <f>Y161+X162</f>
+        <v/>
+      </c>
+      <c r="Z162" s="35">
+        <f>IF(OR(Q162="",R162=""),"",(L162-IF(Q162&gt;R162,1,0))^2+(M162-IF(Q162=R162,1,0))^2+(N162-IF(Q162&lt;R162,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA162" s="35">
+        <f>IF(OR(Q162="",R162="",F162="",F162=0,G162="",G162=0,H162="",H162=0),"",((1/F162/(1/F162+1/G162+1/H162))-IF(Q162&gt;R162,1,0))^2+((1/G162/(1/F162+1/G162+1/H162))-IF(Q162=R162,1,0))^2+((1/H162/(1/F162+1/G162+1/H162))-IF(Q162&lt;R162,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB162" s="36" t="n">
+        <v>1.4079</v>
+      </c>
+      <c r="AC162" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B163" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12platensegimnasiamendoza</t>
+        </is>
+      </c>
+      <c r="C163" s="30" t="inlineStr">
+        <is>
+          <t>Platense vs Gimnasia Mendoza</t>
+        </is>
+      </c>
+      <c r="D163" s="30" t="inlineStr">
+        <is>
+          <t>Platense</t>
+        </is>
+      </c>
+      <c r="E163" s="30" t="inlineStr">
+        <is>
+          <t>Gimnasia Mendoza</t>
+        </is>
+      </c>
+      <c r="F163" s="31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G163" s="31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="H163" s="31" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="I163" s="31" t="n"/>
+      <c r="J163" s="31" t="n"/>
+      <c r="K163" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L163" s="33" t="n">
+        <v>0.3844437277119686</v>
+      </c>
+      <c r="M163" s="33" t="n">
+        <v>0.2288833200513232</v>
+      </c>
+      <c r="N163" s="33" t="n">
+        <v>0.3866729522367082</v>
+      </c>
+      <c r="O163" s="33" t="n">
+        <v>0.6957337538044741</v>
+      </c>
+      <c r="P163" s="33" t="n">
+        <v>0.3042662461955258</v>
+      </c>
+      <c r="Q163" s="37" t="n"/>
+      <c r="R163" s="37" t="n"/>
+      <c r="S163" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="T163" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U163" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V163" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" s="30">
+        <f>IF(L163="","",IF((MAX(L163,M163,N163)-MEDIAN(L163,M163,N163))&gt;0.05,IF(OR(Q163="",R163=""),"[PREDICCION] "&amp;IF(L163=MAX(L163,M163,N163),"LOCAL",IF(M163=MAX(L163,M163,N163),"EMPATE","VISITA")),IF(L163=MAX(L163,M163,N163),IF(Q163&gt;R163,"[ACIERTO]","[FALLO]"),IF(M163=MAX(L163,M163,N163),IF(Q163=R163,"[ACIERTO]","[FALLO]"),IF(Q163&lt;R163,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X163" s="34">
+        <f>IFERROR(IF(U163=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S163)),U163*(IF(ISNUMBER(SEARCH("LOCAL",S163)),F163,IF(ISNUMBER(SEARCH("EMPATE",S163)),G163,H163))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S163)),-U163,0))),0)+IFERROR(IF(V163=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T163)),V163*(IF(ISNUMBER(SEARCH("OVER",T163)),I163,J163)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T163)),-V163,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y163" s="34">
+        <f>Y162+X163</f>
+        <v/>
+      </c>
+      <c r="Z163" s="35">
+        <f>IF(OR(Q163="",R163=""),"",(L163-IF(Q163&gt;R163,1,0))^2+(M163-IF(Q163=R163,1,0))^2+(N163-IF(Q163&lt;R163,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA163" s="35">
+        <f>IF(OR(Q163="",R163="",F163="",F163=0,G163="",G163=0,H163="",H163=0),"",((1/F163/(1/F163+1/G163+1/H163))-IF(Q163&gt;R163,1,0))^2+((1/G163/(1/F163+1/G163+1/H163))-IF(Q163=R163,1,0))^2+((1/H163/(1/F163+1/G163+1/H163))-IF(Q163&lt;R163,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB163" s="36" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AC163" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B164" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12racingclubriverplate</t>
+        </is>
+      </c>
+      <c r="C164" s="30" t="inlineStr">
+        <is>
+          <t>Racing Club vs River Plate</t>
+        </is>
+      </c>
+      <c r="D164" s="30" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="E164" s="30" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="F164" s="31" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="G164" s="31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H164" s="31" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I164" s="31" t="n"/>
+      <c r="J164" s="31" t="n"/>
+      <c r="K164" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L164" s="33" t="n">
+        <v>0.3840412192698343</v>
+      </c>
+      <c r="M164" s="33" t="n">
+        <v>0.2362788326047079</v>
+      </c>
+      <c r="N164" s="33" t="n">
+        <v>0.3796799481254578</v>
+      </c>
+      <c r="O164" s="33" t="n">
+        <v>0.6611191377960927</v>
+      </c>
+      <c r="P164" s="33" t="n">
+        <v>0.3388808622039073</v>
+      </c>
+      <c r="Q164" s="37" t="n"/>
+      <c r="R164" s="37" t="n"/>
+      <c r="S164" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="T164" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U164" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V164" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" s="30">
+        <f>IF(L164="","",IF((MAX(L164,M164,N164)-MEDIAN(L164,M164,N164))&gt;0.05,IF(OR(Q164="",R164=""),"[PREDICCION] "&amp;IF(L164=MAX(L164,M164,N164),"LOCAL",IF(M164=MAX(L164,M164,N164),"EMPATE","VISITA")),IF(L164=MAX(L164,M164,N164),IF(Q164&gt;R164,"[ACIERTO]","[FALLO]"),IF(M164=MAX(L164,M164,N164),IF(Q164=R164,"[ACIERTO]","[FALLO]"),IF(Q164&lt;R164,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X164" s="34">
+        <f>IFERROR(IF(U164=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S164)),U164*(IF(ISNUMBER(SEARCH("LOCAL",S164)),F164,IF(ISNUMBER(SEARCH("EMPATE",S164)),G164,H164))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S164)),-U164,0))),0)+IFERROR(IF(V164=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T164)),V164*(IF(ISNUMBER(SEARCH("OVER",T164)),I164,J164)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T164)),-V164,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y164" s="34">
+        <f>Y163+X164</f>
+        <v/>
+      </c>
+      <c r="Z164" s="35">
+        <f>IF(OR(Q164="",R164=""),"",(L164-IF(Q164&gt;R164,1,0))^2+(M164-IF(Q164=R164,1,0))^2+(N164-IF(Q164&lt;R164,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA164" s="35">
+        <f>IF(OR(Q164="",R164="",F164="",F164=0,G164="",G164=0,H164="",H164=0),"",((1/F164/(1/F164+1/G164+1/H164))-IF(Q164&gt;R164,1,0))^2+((1/G164/(1/F164+1/G164+1/H164))-IF(Q164=R164,1,0))^2+((1/H164/(1/F164+1/G164+1/H164))-IF(Q164&lt;R164,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB164" s="36" t="n">
+        <v>0.8295</v>
+      </c>
+      <c r="AC164" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B165" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12rosenborgsarpsborgfk</t>
+        </is>
+      </c>
+      <c r="C165" s="30" t="inlineStr">
+        <is>
+          <t>Rosenborg vs Sarpsborg fk</t>
+        </is>
+      </c>
+      <c r="D165" s="30" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="E165" s="30" t="inlineStr">
+        <is>
+          <t>Sarpsborg fk</t>
+        </is>
+      </c>
+      <c r="F165" s="31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G165" s="31" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H165" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I165" s="31" t="n"/>
+      <c r="J165" s="31" t="n"/>
+      <c r="K165" s="32" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="L165" s="33" t="n">
+        <v>0.47527</v>
+      </c>
+      <c r="M165" s="33" t="n">
+        <v>0.170333</v>
+      </c>
+      <c r="N165" s="33" t="n">
+        <v>0.354397</v>
+      </c>
+      <c r="O165" s="33" t="n">
+        <v>0.9044490721974714</v>
+      </c>
+      <c r="P165" s="33" t="n">
+        <v>0.09555092780252858</v>
+      </c>
+      <c r="Q165" s="37" t="n"/>
+      <c r="R165" s="37" t="n"/>
+      <c r="S165" s="30">
+        <f>IF(OR(Q165="",R165=""),"[APOSTAR] VISITA",IF(Q165&lt;R165,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T165" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U165" s="34" t="n">
+        <v>2500</v>
+      </c>
+      <c r="V165" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" s="30">
+        <f>IF(L165="","",IF((MAX(L165,M165,N165)-MEDIAN(L165,M165,N165))&gt;0.05,IF(OR(Q165="",R165=""),"[PREDICCION] "&amp;IF(L165=MAX(L165,M165,N165),"LOCAL",IF(M165=MAX(L165,M165,N165),"EMPATE","VISITA")),IF(L165=MAX(L165,M165,N165),IF(Q165&gt;R165,"[ACIERTO]","[FALLO]"),IF(M165=MAX(L165,M165,N165),IF(Q165=R165,"[ACIERTO]","[FALLO]"),IF(Q165&lt;R165,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X165" s="34">
+        <f>IFERROR(IF(U165=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S165)),U165*(IF(ISNUMBER(SEARCH("LOCAL",S165)),F165,IF(ISNUMBER(SEARCH("EMPATE",S165)),G165,H165))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S165)),-U165,0))),0)+IFERROR(IF(V165=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T165)),V165*(IF(ISNUMBER(SEARCH("OVER",T165)),I165,J165)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T165)),-V165,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y165" s="34">
+        <f>Y164+X165</f>
+        <v/>
+      </c>
+      <c r="Z165" s="35">
+        <f>IF(OR(Q165="",R165=""),"",(L165-IF(Q165&gt;R165,1,0))^2+(M165-IF(Q165=R165,1,0))^2+(N165-IF(Q165&lt;R165,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA165" s="35">
+        <f>IF(OR(Q165="",R165="",F165="",F165=0,G165="",G165=0,H165="",H165=0),"",((1/F165/(1/F165+1/G165+1/H165))-IF(Q165&gt;R165,1,0))^2+((1/G165/(1/F165+1/G165+1/H165))-IF(Q165=R165,1,0))^2+((1/H165/(1/F165+1/G165+1/H165))-IF(Q165&lt;R165,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB165" s="36" t="n">
+        <v>1.5859</v>
+      </c>
+      <c r="AC165" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B166" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12skbrannsandefjord</t>
+        </is>
+      </c>
+      <c r="C166" s="30" t="inlineStr">
+        <is>
+          <t>Sk Brann vs Sandefjord</t>
+        </is>
+      </c>
+      <c r="D166" s="30" t="inlineStr">
+        <is>
+          <t>Sk Brann</t>
+        </is>
+      </c>
+      <c r="E166" s="30" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F166" s="31" t="n"/>
+      <c r="G166" s="31" t="n"/>
+      <c r="H166" s="31" t="n"/>
+      <c r="I166" s="31" t="n"/>
+      <c r="J166" s="31" t="n"/>
+      <c r="K166" s="32" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="L166" s="33" t="n">
+        <v>0.475423</v>
+      </c>
+      <c r="M166" s="33" t="n">
+        <v>0.170079</v>
+      </c>
+      <c r="N166" s="33" t="n">
+        <v>0.354498</v>
+      </c>
+      <c r="O166" s="33" t="n">
+        <v>0.9054048614108229</v>
+      </c>
+      <c r="P166" s="33" t="n">
+        <v>0.09459513858917706</v>
+      </c>
+      <c r="Q166" s="37" t="n"/>
+      <c r="R166" s="37" t="n"/>
+      <c r="S166" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T166" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U166" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V166" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W166" s="30">
+        <f>IF(L166="","",IF((MAX(L166,M166,N166)-MEDIAN(L166,M166,N166))&gt;0.05,IF(OR(Q166="",R166=""),"[PREDICCION] "&amp;IF(L166=MAX(L166,M166,N166),"LOCAL",IF(M166=MAX(L166,M166,N166),"EMPATE","VISITA")),IF(L166=MAX(L166,M166,N166),IF(Q166&gt;R166,"[ACIERTO]","[FALLO]"),IF(M166=MAX(L166,M166,N166),IF(Q166=R166,"[ACIERTO]","[FALLO]"),IF(Q166&lt;R166,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X166" s="34">
+        <f>IFERROR(IF(U166=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S166)),U166*(IF(ISNUMBER(SEARCH("LOCAL",S166)),F166,IF(ISNUMBER(SEARCH("EMPATE",S166)),G166,H166))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S166)),-U166,0))),0)+IFERROR(IF(V166=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T166)),V166*(IF(ISNUMBER(SEARCH("OVER",T166)),I166,J166)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T166)),-V166,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y166" s="34">
+        <f>Y165+X166</f>
+        <v/>
+      </c>
+      <c r="Z166" s="35">
+        <f>IF(OR(Q166="",R166=""),"",(L166-IF(Q166&gt;R166,1,0))^2+(M166-IF(Q166=R166,1,0))^2+(N166-IF(Q166&lt;R166,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA166" s="35">
+        <f>IF(OR(Q166="",R166="",F166="",F166=0,G166="",G166=0,H166="",H166=0),"",((1/F166/(1/F166+1/G166+1/H166))-IF(Q166&gt;R166,1,0))^2+((1/G166/(1/F166+1/G166+1/H166))-IF(Q166=R166,1,0))^2+((1/H166/(1/F166+1/G166+1/H166))-IF(Q166&lt;R166,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB166" s="36" t="n">
+        <v>1.5249</v>
+      </c>
+      <c r="AC166" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="29" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B167" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-12sunderlandtottenhamhotspur</t>
+        </is>
+      </c>
+      <c r="C167" s="30" t="inlineStr">
+        <is>
+          <t>Sunderland vs Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="D167" s="30" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="E167" s="30" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="F167" s="31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G167" s="31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H167" s="31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I167" s="31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J167" s="31" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="K167" s="32" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="L167" s="33" t="n">
+        <v>0.412971</v>
+      </c>
+      <c r="M167" s="33" t="n">
+        <v>0.174381</v>
+      </c>
+      <c r="N167" s="33" t="n">
+        <v>0.412648</v>
+      </c>
+      <c r="O167" s="33" t="n">
+        <v>0.8693498833775939</v>
+      </c>
+      <c r="P167" s="33" t="n">
+        <v>0.1306501166224062</v>
+      </c>
+      <c r="Q167" s="37" t="n"/>
+      <c r="R167" s="37" t="n"/>
+      <c r="S167" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="T167" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Valor</t>
+        </is>
+      </c>
+      <c r="U167" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W167" s="30">
+        <f>IF(L167="","",IF((MAX(L167,M167,N167)-MEDIAN(L167,M167,N167))&gt;0.05,IF(OR(Q167="",R167=""),"[PREDICCION] "&amp;IF(L167=MAX(L167,M167,N167),"LOCAL",IF(M167=MAX(L167,M167,N167),"EMPATE","VISITA")),IF(L167=MAX(L167,M167,N167),IF(Q167&gt;R167,"[ACIERTO]","[FALLO]"),IF(M167=MAX(L167,M167,N167),IF(Q167=R167,"[ACIERTO]","[FALLO]"),IF(Q167&lt;R167,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X167" s="34">
+        <f>IFERROR(IF(U167=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S167)),U167*(IF(ISNUMBER(SEARCH("LOCAL",S167)),F167,IF(ISNUMBER(SEARCH("EMPATE",S167)),G167,H167))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S167)),-U167,0))),0)+IFERROR(IF(V167=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T167)),V167*(IF(ISNUMBER(SEARCH("OVER",T167)),I167,J167)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T167)),-V167,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y167" s="34">
+        <f>Y166+X167</f>
+        <v/>
+      </c>
+      <c r="Z167" s="35">
+        <f>IF(OR(Q167="",R167=""),"",(L167-IF(Q167&gt;R167,1,0))^2+(M167-IF(Q167=R167,1,0))^2+(N167-IF(Q167&lt;R167,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA167" s="35">
+        <f>IF(OR(Q167="",R167="",F167="",F167=0,G167="",G167=0,H167="",H167=0),"",((1/F167/(1/F167+1/G167+1/H167))-IF(Q167&gt;R167,1,0))^2+((1/G167/(1/F167+1/G167+1/H167))-IF(Q167=R167,1,0))^2+((1/H167/(1/F167+1/G167+1/H167))-IF(Q167&lt;R167,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB167" s="36" t="n">
+        <v>1.3796</v>
+      </c>
+      <c r="AC167" s="32" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -16876,7 +19051,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AC1"/>
-  <conditionalFormatting sqref="A2:R146">
+  <conditionalFormatting sqref="A2:R167">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$K2="Argentina"</formula>
     </cfRule>
@@ -16893,7 +19068,7 @@
       <formula>$K2="Inglaterra"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S146">
+  <conditionalFormatting sqref="S2:S167">
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("[GANADA]",S2))</formula>
     </cfRule>
@@ -16907,7 +19082,7 @@
       <formula>ISNUMBER(SEARCH("[APOSTAR]",S2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T146">
+  <conditionalFormatting sqref="T2:T167">
     <cfRule type="expression" priority="10" dxfId="5" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("[GANADA]",T2))</formula>
     </cfRule>
@@ -16921,7 +19096,7 @@
       <formula>ISNUMBER(SEARCH("[APOSTAR]",T2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X146">
+  <conditionalFormatting sqref="X2:X167">
     <cfRule type="expression" priority="14" dxfId="5" stopIfTrue="1">
       <formula>X2&gt;0</formula>
     </cfRule>
@@ -16929,7 +19104,7 @@
       <formula>X2&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W146">
+  <conditionalFormatting sqref="W2:W167">
     <cfRule type="expression" priority="16" dxfId="5" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("[ACIERTO]",W2))</formula>
     </cfRule>
@@ -16953,7 +19128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17148,7 +19323,7 @@
       </c>
       <c r="B6" s="50" t="inlineStr">
         <is>
-          <t>San Lorenzo vs Defensa y Justicia</t>
+          <t>Instituto (córdoba) vs Independiente</t>
         </is>
       </c>
       <c r="C6" s="48" t="inlineStr">
@@ -17158,7 +19333,7 @@
       </c>
       <c r="D6" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E6" s="49" t="n">
@@ -17170,35 +19345,33 @@
         </is>
       </c>
       <c r="G6" s="52" t="n">
-        <v>6750</v>
+        <v>4075</v>
       </c>
       <c r="H6" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I6" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J6" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K6" s="52" t="n">
-        <v>6750</v>
-      </c>
-      <c r="L6" s="53" t="n">
-        <v>0</v>
-      </c>
+          <t>[PASAR] Shadow-EV (0.052&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="I6" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="49" t="n"/>
+      <c r="L6" s="49" t="n"/>
       <c r="M6" s="51" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N6" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N6" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17226,7 +19399,7 @@
       <c r="E7" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="F7" s="54" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17240,7 +19413,7 @@
       <c r="I7" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J7" s="54" t="inlineStr">
+      <c r="J7" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -17552,7 +19725,7 @@
       <c r="K12" s="52" t="n">
         <v>6975</v>
       </c>
-      <c r="L12" s="53" t="n">
+      <c r="L12" s="54" t="n">
         <v>0</v>
       </c>
       <c r="M12" s="51" t="inlineStr">
@@ -17614,7 +19787,7 @@
       <c r="K13" s="47" t="n">
         <v>-2500</v>
       </c>
-      <c r="L13" s="53" t="n">
+      <c r="L13" s="54" t="n">
         <v>0</v>
       </c>
       <c r="M13" s="46" t="inlineStr">
@@ -18222,7 +20395,7 @@
       <c r="K23" s="47" t="n">
         <v>-2500</v>
       </c>
-      <c r="L23" s="53" t="n">
+      <c r="L23" s="54" t="n">
         <v>0</v>
       </c>
       <c r="M23" s="46" t="inlineStr">
@@ -18530,7 +20703,7 @@
       <c r="K28" s="52" t="n">
         <v>4375</v>
       </c>
-      <c r="L28" s="53" t="n">
+      <c r="L28" s="54" t="n">
         <v>0</v>
       </c>
       <c r="M28" s="51" t="inlineStr">
@@ -20122,15 +22295,17 @@
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E55" s="45" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F55" s="54" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[PERDIDA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E55" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G55" s="49" t="n"/>
@@ -20142,21 +22317,23 @@
       <c r="I55" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J55" s="54" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K55" s="49" t="n"/>
+      <c r="J55" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K55" s="47" t="n">
+        <v>-2500</v>
+      </c>
       <c r="L55" s="49" t="n"/>
       <c r="M55" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N55" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N55" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -20168,53 +22345,55 @@
       </c>
       <c r="B56" s="50" t="inlineStr">
         <is>
-          <t>Kocaelispor vs Istanbul Basaksehir</t>
+          <t>Molde vs Lillestrom</t>
         </is>
       </c>
       <c r="C56" s="48" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D56" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E56" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F56" s="54" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] VISITA</t>
+        </is>
+      </c>
+      <c r="E56" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G56" s="49" t="n"/>
       <c r="H56" s="50" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I56" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="54" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K56" s="49" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I56" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J56" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K56" s="52" t="n">
+        <v>5175</v>
+      </c>
       <c r="L56" s="49" t="n"/>
       <c r="M56" s="48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N56" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N56" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -20226,7 +22405,7 @@
       </c>
       <c r="B57" s="44" t="inlineStr">
         <is>
-          <t>Molde vs Lillestrom</t>
+          <t>Sarpsborg fk vs Ik Start</t>
         </is>
       </c>
       <c r="C57" s="43" t="inlineStr">
@@ -20236,15 +22415,17 @@
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E57" s="45" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F57" s="54" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[PERDIDA] VISITA</t>
+        </is>
+      </c>
+      <c r="E57" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F57" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G57" s="49" t="n"/>
@@ -20256,33 +22437,35 @@
       <c r="I57" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J57" s="54" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K57" s="49" t="n"/>
+      <c r="J57" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K57" s="47" t="n">
+        <v>-2500</v>
+      </c>
       <c r="L57" s="49" t="n"/>
       <c r="M57" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N57" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N57" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="48" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B58" s="50" t="inlineStr">
         <is>
-          <t>Sarpsborg fk vs Ik Start</t>
+          <t>Kfum Oslo vs Sandefjord</t>
         </is>
       </c>
       <c r="C58" s="48" t="inlineStr">
@@ -20296,9 +22479,9 @@
         </is>
       </c>
       <c r="E58" s="49" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F58" s="54" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="F58" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20312,7 +22495,7 @@
       <c r="I58" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J58" s="54" t="inlineStr">
+      <c r="J58" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20333,17 +22516,17 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="43" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B59" s="44" t="inlineStr">
         <is>
-          <t>Valerenga vs Viking fk</t>
+          <t>Goztepe vs Galatasaray</t>
         </is>
       </c>
       <c r="C59" s="43" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D59" s="44" t="inlineStr">
@@ -20352,9 +22535,9 @@
         </is>
       </c>
       <c r="E59" s="45" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F59" s="54" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="F59" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20362,15 +22545,13 @@
       <c r="G59" s="49" t="n"/>
       <c r="H59" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I59" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" s="54" t="inlineStr">
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I59" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J59" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20391,17 +22572,17 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="48" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B60" s="50" t="inlineStr">
         <is>
-          <t>Kfum Oslo vs Sandefjord</t>
+          <t>West Ham United vs Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="C60" s="48" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D60" s="50" t="inlineStr">
@@ -20412,7 +22593,7 @@
       <c r="E60" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="F60" s="54" t="inlineStr">
+      <c r="F60" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20420,13 +22601,15 @@
       <c r="G60" s="49" t="n"/>
       <c r="H60" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I60" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J60" s="54" t="inlineStr">
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I60" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20447,28 +22630,28 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="43" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B61" s="44" t="inlineStr">
         <is>
-          <t>Goztepe vs Galatasaray</t>
+          <t>Boca Juniors vs Independiente</t>
         </is>
       </c>
       <c r="C61" s="43" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D61" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E61" s="45" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F61" s="54" t="inlineStr">
+        <v>1443.38</v>
+      </c>
+      <c r="F61" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20476,13 +22659,13 @@
       <c r="G61" s="49" t="n"/>
       <c r="H61" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I61" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J61" s="54" t="inlineStr">
+      <c r="J61" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20503,28 +22686,28 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="48" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="50" t="inlineStr">
         <is>
-          <t>West Ham United vs Wolverhampton Wanderers</t>
+          <t>Deportivo Riestra vs Instituto (córdoba)</t>
         </is>
       </c>
       <c r="C62" s="48" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D62" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E62" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F62" s="54" t="inlineStr">
+        <v>1443.38</v>
+      </c>
+      <c r="F62" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20532,15 +22715,13 @@
       <c r="G62" s="49" t="n"/>
       <c r="H62" s="50" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I62" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="54" t="inlineStr">
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I62" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J62" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20566,7 +22747,7 @@
       </c>
       <c r="B63" s="44" t="inlineStr">
         <is>
-          <t>Boca Juniors vs Independiente</t>
+          <t>Estudiantes de la Plata vs Union (santa Fe)</t>
         </is>
       </c>
       <c r="C63" s="43" t="inlineStr">
@@ -20576,13 +22757,13 @@
       </c>
       <c r="D63" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E63" s="45" t="n">
-        <v>1767.77</v>
-      </c>
-      <c r="F63" s="54" t="inlineStr">
+        <v>1443.38</v>
+      </c>
+      <c r="F63" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20590,13 +22771,15 @@
       <c r="G63" s="49" t="n"/>
       <c r="H63" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I63" s="45" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J63" s="54" t="inlineStr">
+          <t>[PASAR] Shadow-Floor (33%&lt;33%)</t>
+        </is>
+      </c>
+      <c r="I63" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20622,12 +22805,12 @@
       </c>
       <c r="B64" s="50" t="inlineStr">
         <is>
-          <t>Estudiantes de la Plata vs Union (santa Fe)</t>
+          <t>Fluminense vs Flamengo</t>
         </is>
       </c>
       <c r="C64" s="48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D64" s="50" t="inlineStr">
@@ -20636,9 +22819,9 @@
         </is>
       </c>
       <c r="E64" s="49" t="n">
-        <v>1767.77</v>
-      </c>
-      <c r="F64" s="54" t="inlineStr">
+        <v>1118.03</v>
+      </c>
+      <c r="F64" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20646,15 +22829,13 @@
       <c r="G64" s="49" t="n"/>
       <c r="H64" s="50" t="inlineStr">
         <is>
-          <t>[PASAR] Shadow-Floor (33%&lt;33%)</t>
-        </is>
-      </c>
-      <c r="I64" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="54" t="inlineStr">
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I64" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J64" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20680,7 +22861,7 @@
       </c>
       <c r="B65" s="44" t="inlineStr">
         <is>
-          <t>Fluminense vs Flamengo</t>
+          <t>Internacional vs Gremio</t>
         </is>
       </c>
       <c r="C65" s="43" t="inlineStr">
@@ -20690,13 +22871,13 @@
       </c>
       <c r="D65" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E65" s="45" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F65" s="54" t="inlineStr">
+        <v>1118.03</v>
+      </c>
+      <c r="F65" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20704,13 +22885,13 @@
       <c r="G65" s="49" t="n"/>
       <c r="H65" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I65" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J65" s="54" t="inlineStr">
+      <c r="J65" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20736,7 +22917,7 @@
       </c>
       <c r="B66" s="50" t="inlineStr">
         <is>
-          <t>Internacional vs Gremio</t>
+          <t>Mirassol vs Bahia</t>
         </is>
       </c>
       <c r="C66" s="48" t="inlineStr">
@@ -20746,13 +22927,15 @@
       </c>
       <c r="D66" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E66" s="49" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F66" s="54" t="inlineStr">
+          <t>[PASAR] EV Insuf (0.070&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E66" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20766,7 +22949,7 @@
       <c r="I66" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J66" s="54" t="inlineStr">
+      <c r="J66" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20792,7 +22975,7 @@
       </c>
       <c r="B67" s="44" t="inlineStr">
         <is>
-          <t>Mirassol vs Bahia</t>
+          <t>Remo vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C67" s="43" t="inlineStr">
@@ -20802,13 +22985,13 @@
       </c>
       <c r="D67" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E67" s="45" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F67" s="54" t="inlineStr">
+        <v>1118.03</v>
+      </c>
+      <c r="F67" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20816,13 +22999,13 @@
       <c r="G67" s="49" t="n"/>
       <c r="H67" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I67" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J67" s="54" t="inlineStr">
+      <c r="J67" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20848,7 +23031,7 @@
       </c>
       <c r="B68" s="50" t="inlineStr">
         <is>
-          <t>Remo vs Vasco da Gama</t>
+          <t>Santos vs Atlético-mg</t>
         </is>
       </c>
       <c r="C68" s="48" t="inlineStr">
@@ -20858,13 +23041,13 @@
       </c>
       <c r="D68" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E68" s="49" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F68" s="54" t="inlineStr">
+        <v>1118.03</v>
+      </c>
+      <c r="F68" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20872,13 +23055,13 @@
       <c r="G68" s="49" t="n"/>
       <c r="H68" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I68" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J68" s="54" t="inlineStr">
+      <c r="J68" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20904,23 +23087,23 @@
       </c>
       <c r="B69" s="44" t="inlineStr">
         <is>
-          <t>Santos vs Atlético-mg</t>
+          <t>Viking fk vs Bodo/glimt</t>
         </is>
       </c>
       <c r="C69" s="43" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D69" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E69" s="45" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F69" s="54" t="inlineStr">
+        <v>2500</v>
+      </c>
+      <c r="F69" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20928,13 +23111,13 @@
       <c r="G69" s="49" t="n"/>
       <c r="H69" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I69" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J69" s="54" t="inlineStr">
+      <c r="J69" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20974,9 +23157,9 @@
         </is>
       </c>
       <c r="E70" s="49" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F70" s="54" t="inlineStr">
+        <v>1118.03</v>
+      </c>
+      <c r="F70" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -20990,7 +23173,7 @@
       <c r="I70" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J70" s="54" t="inlineStr">
+      <c r="J70" s="53" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>
@@ -21008,181 +23191,577 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="18" customHeight="1">
-      <c r="A72" s="55" t="inlineStr">
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="43" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="44" t="inlineStr">
+        <is>
+          <t>Botafogo vs Coritiba</t>
+        </is>
+      </c>
+      <c r="C71" s="43" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D71" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E71" s="45" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F71" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G71" s="49" t="n"/>
+      <c r="H71" s="44" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I71" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K71" s="49" t="n"/>
+      <c r="L71" s="49" t="n"/>
+      <c r="M71" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="48" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="50" t="inlineStr">
+        <is>
+          <t>Chelsea vs Manchester City</t>
+        </is>
+      </c>
+      <c r="C72" s="48" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="D72" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E72" s="49" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F72" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G72" s="49" t="n"/>
+      <c r="H72" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I72" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J72" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K72" s="49" t="n"/>
+      <c r="L72" s="49" t="n"/>
+      <c r="M72" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="43" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="44" t="inlineStr">
+        <is>
+          <t>Corinthians vs Palmeiras</t>
+        </is>
+      </c>
+      <c r="C73" s="43" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D73" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E73" s="45" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F73" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G73" s="49" t="n"/>
+      <c r="H73" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I73" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J73" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K73" s="49" t="n"/>
+      <c r="L73" s="49" t="n"/>
+      <c r="M73" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="48" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="50" t="inlineStr">
+        <is>
+          <t>Cruzeiro vs Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="C74" s="48" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="D74" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E74" s="49" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F74" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G74" s="49" t="n"/>
+      <c r="H74" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I74" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J74" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K74" s="49" t="n"/>
+      <c r="L74" s="49" t="n"/>
+      <c r="M74" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="43" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="44" t="inlineStr">
+        <is>
+          <t>Crystal Palace vs Newcastle United</t>
+        </is>
+      </c>
+      <c r="C75" s="43" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="D75" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E75" s="45" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F75" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G75" s="49" t="n"/>
+      <c r="H75" s="44" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I75" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K75" s="49" t="n"/>
+      <c r="L75" s="49" t="n"/>
+      <c r="M75" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="48" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="50" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C76" s="48" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="D76" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E76" s="49" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F76" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G76" s="49" t="n"/>
+      <c r="H76" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I76" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J76" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K76" s="49" t="n"/>
+      <c r="L76" s="49" t="n"/>
+      <c r="M76" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="43" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="44" t="inlineStr">
+        <is>
+          <t>Rosenborg vs Sarpsborg fk</t>
+        </is>
+      </c>
+      <c r="C77" s="43" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="D77" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E77" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F77" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G77" s="49" t="n"/>
+      <c r="H77" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I77" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J77" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K77" s="49" t="n"/>
+      <c r="L77" s="49" t="n"/>
+      <c r="M77" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="55" t="inlineStr">
         <is>
           <t>RESUMEN COMPARATIVO DE RENDIMIENTO</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="39" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="39" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B73" s="40" t="inlineStr">
+      <c r="B80" s="40" t="inlineStr">
         <is>
           <t>Opcion 1 (Activa)</t>
         </is>
       </c>
-      <c r="D73" s="41" t="inlineStr">
+      <c r="D80" s="41" t="inlineStr">
         <is>
           <t>Opcion 4 (Shadow)</t>
         </is>
       </c>
-      <c r="F73" s="42" t="inlineStr">
+      <c r="F80" s="42" t="inlineStr">
         <is>
           <t>Mejor</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="56" t="inlineStr">
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="56" t="inlineStr">
         <is>
           <t>N apuestas liquidadas</t>
         </is>
       </c>
-      <c r="B74" s="57" t="n">
+      <c r="B81" s="57" t="n">
         <v>23</v>
       </c>
-      <c r="C74" s="57" t="n">
+      <c r="C81" s="57" t="n">
         <v>23</v>
       </c>
-      <c r="D74" s="57" t="n">
-        <v>40</v>
-      </c>
-      <c r="E74" s="57" t="n">
-        <v>40</v>
-      </c>
-      <c r="F74" s="58" t="inlineStr">
+      <c r="D81" s="57" t="n">
+        <v>42</v>
+      </c>
+      <c r="E81" s="57" t="n">
+        <v>42</v>
+      </c>
+      <c r="F81" s="58" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="56" t="inlineStr">
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="56" t="inlineStr">
         <is>
           <t>Ganadas</t>
         </is>
       </c>
-      <c r="B75" s="59" t="n">
+      <c r="B82" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="C75" s="59" t="n">
+      <c r="C82" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="D75" s="60" t="n">
+      <c r="D82" s="60" t="n">
         <v>25</v>
       </c>
-      <c r="E75" s="60" t="n">
+      <c r="E82" s="60" t="n">
         <v>25</v>
       </c>
-      <c r="F75" s="61" t="inlineStr">
+      <c r="F82" s="61" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" s="56" t="inlineStr">
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" s="56" t="inlineStr">
         <is>
           <t>Hit rate</t>
         </is>
       </c>
-      <c r="B76" s="62" t="n">
+      <c r="B83" s="62" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="C76" s="62" t="n">
+      <c r="C83" s="62" t="n">
         <v>0.5217391304347826</v>
       </c>
-      <c r="D76" s="63" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E76" s="63" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="F76" s="61" t="inlineStr">
+      <c r="D83" s="63" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="E83" s="63" t="n">
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="F83" s="61" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" s="56" t="inlineStr">
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" s="56" t="inlineStr">
         <is>
           <t>Volumen apostado</t>
         </is>
       </c>
-      <c r="B77" s="53" t="n">
+      <c r="B84" s="54" t="n">
         <v>37220.99000000001</v>
       </c>
-      <c r="C77" s="53" t="n">
+      <c r="C84" s="54" t="n">
         <v>37220.99000000001</v>
       </c>
-      <c r="D77" s="53" t="n">
-        <v>99687.37</v>
-      </c>
-      <c r="E77" s="53" t="n">
-        <v>99687.37</v>
-      </c>
-      <c r="F77" s="58" t="inlineStr">
+      <c r="D84" s="54" t="n">
+        <v>104687.37</v>
+      </c>
+      <c r="E84" s="54" t="n">
+        <v>104687.37</v>
+      </c>
+      <c r="F84" s="58" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="56" t="inlineStr">
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="56" t="inlineStr">
         <is>
           <t>P/L neto</t>
         </is>
       </c>
-      <c r="B78" s="47" t="n">
-        <v>35608.43000000001</v>
-      </c>
-      <c r="C78" s="47" t="n">
-        <v>35608.43000000001</v>
-      </c>
-      <c r="D78" s="52" t="n">
-        <v>147081.09</v>
-      </c>
-      <c r="E78" s="52" t="n">
-        <v>147081.09</v>
-      </c>
-      <c r="F78" s="61" t="inlineStr">
+      <c r="B85" s="47" t="n">
+        <v>32933.43000000001</v>
+      </c>
+      <c r="C85" s="47" t="n">
+        <v>32933.43000000001</v>
+      </c>
+      <c r="D85" s="52" t="n">
+        <v>140506.09</v>
+      </c>
+      <c r="E85" s="52" t="n">
+        <v>140506.09</v>
+      </c>
+      <c r="F85" s="61" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="56" t="inlineStr">
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="56" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="B79" s="62" t="n">
-        <v>0.9566760583208561</v>
-      </c>
-      <c r="C79" s="62" t="n">
-        <v>0.9566760583208561</v>
-      </c>
-      <c r="D79" s="63" t="n">
-        <v>1.475423516539758</v>
-      </c>
-      <c r="E79" s="63" t="n">
-        <v>1.475423516539758</v>
-      </c>
-      <c r="F79" s="61" t="inlineStr">
+      <c r="B86" s="62" t="n">
+        <v>0.8848080075247865</v>
+      </c>
+      <c r="C86" s="62" t="n">
+        <v>0.8848080075247865</v>
+      </c>
+      <c r="D86" s="63" t="n">
+        <v>1.34214939204223</v>
+      </c>
+      <c r="E86" s="63" t="n">
+        <v>1.34214939204223</v>
+      </c>
+      <c r="F86" s="61" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="64" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="64" t="inlineStr">
         <is>
           <t>Verde = celda ganadora en ese KPI / partido   |   Rojo = celda perdedora   |   Amarillo en Resultado = pendiente de liquidar   |   Op1 activa desde V4.3: empates bloqueados + xG Margen O/U + Camino 2B (desacuerdo) + Camino 3 (alta conv.)</t>
         </is>
@@ -21190,11 +23769,11 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A79:N79"/>
     <mergeCell ref="D3:G3"/>
+    <mergeCell ref="A88:N88"/>
     <mergeCell ref="H3:K3"/>
     <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A72:N72"/>
-    <mergeCell ref="A81:N81"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A1:N1"/>
@@ -21283,10 +23862,10 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="F2" s="67" t="n">
-        <v>24540.99</v>
+        <v>21865.99</v>
       </c>
       <c r="G2" s="66" t="n">
-        <v>1.166644307681191</v>
+        <v>1.039478568175573</v>
       </c>
       <c r="H2" s="67" t="n">
         <v>21035.54</v>
@@ -21355,25 +23934,25 @@
         </is>
       </c>
       <c r="B5" s="65" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" s="65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F5" s="67" t="n">
-        <v>687.5</v>
+        <v>-475</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>0.09166666666666666</v>
+        <v>-0.038</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>7500</v>
+        <v>12500</v>
       </c>
     </row>
     <row r="6">
@@ -21383,25 +23962,25 @@
         </is>
       </c>
       <c r="B6" s="65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="65" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="66" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="67" t="n">
-        <v>6782.64</v>
+        <v>4282.64</v>
       </c>
       <c r="G6" s="66" t="n">
-        <v>0.8623079250617874</v>
+        <v>0.4131555479235323</v>
       </c>
       <c r="H6" s="67" t="n">
-        <v>7865.68</v>
+        <v>10365.68</v>
       </c>
     </row>
     <row r="7">
@@ -21411,31 +23990,31 @@
         </is>
       </c>
       <c r="B7" s="68" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C7" s="68" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="68" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E7" s="69" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="F7" s="70" t="n">
-        <v>96353.42999999999</v>
+        <v>90015.92999999999</v>
       </c>
       <c r="G7" s="69" t="n">
-        <v>1.319177540195834</v>
+        <v>1.117647558316291</v>
       </c>
       <c r="H7" s="70" t="n">
-        <v>73040.53</v>
+        <v>80540.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="71" t="inlineStr">
         <is>
-          <t>Generado: 05/04/2026 23:29</t>
+          <t>Generado: 06/04/2026 23:37</t>
         </is>
       </c>
     </row>

--- a/Backtest_Modelo.xlsx
+++ b/Backtest_Modelo.xlsx
@@ -902,7 +902,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 06/04/2026 23:37   |   Bankroll: $100,000.00</t>
+          <t>Generado: 08/04/2026 13:30   |   Bankroll: $100,000.00</t>
         </is>
       </c>
     </row>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>90015.9267</v>
+        <v>95915.9267</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>90015.9267</v>
+        <v>95915.9267</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1.117647558316291</v>
+        <v>1.155049548696281</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1.117647558316291</v>
+        <v>1.155049548696281</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>0</v>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>80540.53</v>
+        <v>83040.53</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>80540.53</v>
+        <v>83040.53</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>0</v>
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>0</v>
@@ -1009,14 +1009,14 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>% Acierto P  (col. Acierto, 61/91 partidos)</t>
+          <t>% Acierto P  (col. Acierto, 61/92 partidos)</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.6703296703296703</v>
+        <v>0.6630434782608695</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>0.6703296703296703</v>
+        <v>0.6630434782608695</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>0</v>
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>0.5998707175177763</v>
+        <v>0.600752508361204</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>0.5998707175177763</v>
+        <v>0.600752508361204</v>
       </c>
       <c r="D12" s="13" t="n">
         <v>0</v>
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>3.6233</v>
+        <v>3.7614</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>3.6233</v>
+        <v>3.7614</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="B15" s="16" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
       <c r="D15" s="17" t="n">
         <v>1</v>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="B18" s="19" t="n">
-        <v>0.5950443055293947</v>
+        <v>0.5950175242282342</v>
       </c>
       <c r="C18" s="20" t="n">
-        <v>0.5950443055293947</v>
+        <v>0.5950175242282342</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B19" s="19" t="n">
-        <v>0.6253766856469403</v>
+        <v>0.6262751916648202</v>
       </c>
       <c r="C19" s="20" t="n">
-        <v>0.6253766856469403</v>
+        <v>0.6262751916648202</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>-0.03033238011754558</v>
+        <v>-0.03125766743658598</v>
       </c>
       <c r="C20" s="20" t="n">
-        <v>-0.03033238011754558</v>
+        <v>-0.03125766743658598</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC167"/>
+  <dimension ref="A1:AC174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3051,19 +3051,19 @@
         </is>
       </c>
       <c r="F16" s="31" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="G16" s="31" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="H16" s="31" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="I16" s="31" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="J16" s="31" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="K16" s="32" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
       <c r="R16" s="37" t="n"/>
       <c r="S16" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.074&lt;0.080)</t>
+          <t>[PASAR] EV Insuf (0.060&lt;0.080)</t>
         </is>
       </c>
       <c r="T16" s="30" t="inlineStr">
@@ -3257,16 +3257,20 @@
         </is>
       </c>
       <c r="F18" s="31" t="n">
-        <v>5.07</v>
+        <v>4.54</v>
       </c>
       <c r="G18" s="31" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="H18" s="31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I18" s="31" t="n"/>
-      <c r="J18" s="31" t="n"/>
+        <v>1.85</v>
+      </c>
+      <c r="I18" s="31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J18" s="31" t="n">
+        <v>1.99</v>
+      </c>
       <c r="K18" s="32" t="inlineStr">
         <is>
           <t>Turquia</t>
@@ -3295,7 +3299,7 @@
       </c>
       <c r="T18" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U18" s="34" t="n">
@@ -4760,13 +4764,13 @@
         </is>
       </c>
       <c r="L32" s="33" t="n">
-        <v>0.427086</v>
+        <v>0.427089</v>
       </c>
       <c r="M32" s="33" t="n">
-        <v>0.145829</v>
+        <v>0.145822</v>
       </c>
       <c r="N32" s="33" t="n">
-        <v>0.427086</v>
+        <v>0.427089</v>
       </c>
       <c r="O32" s="33" t="n">
         <v>0.9644378138836682</v>
@@ -5419,13 +5423,13 @@
         </is>
       </c>
       <c r="L38" s="33" t="n">
-        <v>0.474086</v>
+        <v>0.474096</v>
       </c>
       <c r="M38" s="33" t="n">
-        <v>0.173021</v>
+        <v>0.173</v>
       </c>
       <c r="N38" s="33" t="n">
-        <v>0.352893</v>
+        <v>0.352904</v>
       </c>
       <c r="O38" s="33" t="n">
         <v>0.8939984342088939</v>
@@ -6295,13 +6299,13 @@
         </is>
       </c>
       <c r="L46" s="33" t="n">
-        <v>0.382712</v>
+        <v>0.382723</v>
       </c>
       <c r="M46" s="33" t="n">
-        <v>0.176471</v>
+        <v>0.176449</v>
       </c>
       <c r="N46" s="33" t="n">
-        <v>0.440817</v>
+        <v>0.440828</v>
       </c>
       <c r="O46" s="33" t="n">
         <v>0.8836044250835575</v>
@@ -6732,13 +6736,13 @@
         </is>
       </c>
       <c r="L50" s="33" t="n">
-        <v>0.491019</v>
+        <v>0.491029</v>
       </c>
       <c r="M50" s="33" t="n">
-        <v>0.169272</v>
+        <v>0.169253</v>
       </c>
       <c r="N50" s="33" t="n">
-        <v>0.339709</v>
+        <v>0.339718</v>
       </c>
       <c r="O50" s="33" t="n">
         <v>0.905433144594896</v>
@@ -6841,13 +6845,13 @@
         </is>
       </c>
       <c r="L51" s="33" t="n">
-        <v>0.448105</v>
+        <v>0.448115</v>
       </c>
       <c r="M51" s="33" t="n">
-        <v>0.170844</v>
+        <v>0.170825</v>
       </c>
       <c r="N51" s="33" t="n">
-        <v>0.38105</v>
+        <v>0.38106</v>
       </c>
       <c r="O51" s="33" t="n">
         <v>0.9055076819692618</v>
@@ -7168,13 +7172,13 @@
         </is>
       </c>
       <c r="L54" s="33" t="n">
-        <v>0.474494</v>
+        <v>0.474505</v>
       </c>
       <c r="M54" s="33" t="n">
-        <v>0.174154</v>
+        <v>0.174133</v>
       </c>
       <c r="N54" s="33" t="n">
-        <v>0.351352</v>
+        <v>0.351363</v>
       </c>
       <c r="O54" s="33" t="n">
         <v>0.889287248387998</v>
@@ -14039,8 +14043,12 @@
       <c r="P118" s="33" t="n">
         <v>0.06462441509409138</v>
       </c>
-      <c r="Q118" s="37" t="n"/>
-      <c r="R118" s="37" t="n"/>
+      <c r="Q118" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R118" s="32" t="n">
+        <v>3</v>
+      </c>
       <c r="S118" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
@@ -14251,11 +14259,16 @@
       <c r="P120" s="33" t="n">
         <v>0.1016796672379705</v>
       </c>
-      <c r="Q120" s="37" t="n"/>
-      <c r="R120" s="37" t="n"/>
-      <c r="S120" s="30">
-        <f>IF(OR(Q120="",R120=""),"[APOSTAR] VISITA",IF(Q120&lt;R120,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="Q120" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="R120" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S120" s="30" t="inlineStr">
+        <is>
+          <t>[GANADA] VISITA</t>
+        </is>
       </c>
       <c r="T120" s="30" t="inlineStr">
         <is>
@@ -14322,16 +14335,20 @@
         </is>
       </c>
       <c r="F121" s="31" t="n">
-        <v>5.07</v>
+        <v>4.54</v>
       </c>
       <c r="G121" s="31" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="H121" s="31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I121" s="31" t="n"/>
-      <c r="J121" s="31" t="n"/>
+        <v>1.85</v>
+      </c>
+      <c r="I121" s="31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J121" s="31" t="n">
+        <v>1.99</v>
+      </c>
       <c r="K121" s="32" t="inlineStr">
         <is>
           <t>Turquia</t>
@@ -14360,7 +14377,7 @@
       </c>
       <c r="T121" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U121" s="34" t="n">
@@ -14423,19 +14440,19 @@
         </is>
       </c>
       <c r="F122" s="31" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="G122" s="31" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="H122" s="31" t="n">
-        <v>2.94</v>
+        <v>3.08</v>
       </c>
       <c r="I122" s="31" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="J122" s="31" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="K122" s="32" t="inlineStr">
         <is>
@@ -14461,7 +14478,7 @@
       <c r="R122" s="37" t="n"/>
       <c r="S122" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.074&lt;0.080)</t>
+          <t>[PASAR] EV Insuf (0.060&lt;0.080)</t>
         </is>
       </c>
       <c r="T122" s="30" t="inlineStr">
@@ -14529,13 +14546,13 @@
         </is>
       </c>
       <c r="F123" s="31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="G123" s="31" t="n">
-        <v>5.98</v>
+        <v>5.89</v>
       </c>
       <c r="H123" s="31" t="n">
-        <v>9.449999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I123" s="31" t="n"/>
       <c r="J123" s="31" t="n"/>
@@ -14631,13 +14648,13 @@
         </is>
       </c>
       <c r="F124" s="31" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G124" s="31" t="n">
         <v>3.77</v>
       </c>
       <c r="H124" s="31" t="n">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="I124" s="31" t="n">
         <v>1.88</v>
@@ -14735,11 +14752,21 @@
           <t>Trabzonspor</t>
         </is>
       </c>
-      <c r="F125" s="31" t="n"/>
-      <c r="G125" s="31" t="n"/>
-      <c r="H125" s="31" t="n"/>
-      <c r="I125" s="31" t="n"/>
-      <c r="J125" s="31" t="n"/>
+      <c r="F125" s="31" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G125" s="31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H125" s="31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="I125" s="31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J125" s="31" t="n">
+        <v>1.93</v>
+      </c>
       <c r="K125" s="32" t="inlineStr">
         <is>
           <t>Turquia</t>
@@ -14762,18 +14789,17 @@
       </c>
       <c r="Q125" s="37" t="n"/>
       <c r="R125" s="37" t="n"/>
-      <c r="S125" s="30" t="inlineStr">
-        <is>
-          <t>[PASAR] Sin Cuotas</t>
-        </is>
+      <c r="S125" s="30">
+        <f>IF(OR(Q125="",R125=""),"[APOSTAR] LOCAL",IF(Q125&gt;R125,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
       </c>
       <c r="T125" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U125" s="34" t="n">
-        <v>0</v>
+        <v>1767.77</v>
       </c>
       <c r="V125" s="34" t="n">
         <v>0</v>
@@ -14832,13 +14858,13 @@
         </is>
       </c>
       <c r="F126" s="31" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G126" s="31" t="n">
-        <v>4.77</v>
+        <v>4.71</v>
       </c>
       <c r="H126" s="31" t="n">
-        <v>8.19</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I126" s="31" t="n"/>
       <c r="J126" s="31" t="n"/>
@@ -14934,13 +14960,13 @@
         </is>
       </c>
       <c r="F127" s="31" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G127" s="31" t="n">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="H127" s="31" t="n">
-        <v>6.01</v>
+        <v>6.03</v>
       </c>
       <c r="I127" s="31" t="n"/>
       <c r="J127" s="31" t="n"/>
@@ -15036,13 +15062,13 @@
         </is>
       </c>
       <c r="F128" s="31" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="G128" s="31" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="H128" s="31" t="n">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="I128" s="31" t="n"/>
       <c r="J128" s="31" t="n"/>
@@ -15078,7 +15104,7 @@
         </is>
       </c>
       <c r="U128" s="34" t="n">
-        <v>1443.38</v>
+        <v>1767.77</v>
       </c>
       <c r="V128" s="34" t="n">
         <v>0</v>
@@ -15137,13 +15163,13 @@
         </is>
       </c>
       <c r="F129" s="31" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="G129" s="31" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="H129" s="31" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="I129" s="31" t="n">
         <v>2.01</v>
@@ -15345,13 +15371,13 @@
         </is>
       </c>
       <c r="F131" s="31" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="G131" s="31" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="H131" s="31" t="n">
-        <v>3.07</v>
+        <v>3.09</v>
       </c>
       <c r="I131" s="31" t="n"/>
       <c r="J131" s="31" t="n"/>
@@ -15387,7 +15413,7 @@
         </is>
       </c>
       <c r="U131" s="34" t="n">
-        <v>1443.38</v>
+        <v>1767.77</v>
       </c>
       <c r="V131" s="34" t="n">
         <v>0</v>
@@ -15446,13 +15472,13 @@
         </is>
       </c>
       <c r="F132" s="31" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G132" s="31" t="n">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="H132" s="31" t="n">
-        <v>4.46</v>
+        <v>4.42</v>
       </c>
       <c r="I132" s="31" t="n"/>
       <c r="J132" s="31" t="n"/>
@@ -15478,9 +15504,10 @@
       </c>
       <c r="Q132" s="37" t="n"/>
       <c r="R132" s="37" t="n"/>
-      <c r="S132" s="30">
-        <f>IF(OR(Q132="",R132=""),"[APOSTAR] LOCAL",IF(Q132&gt;R132,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
-        <v/>
+      <c r="S132" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] EV Insuf (0.056&lt;0.080)</t>
+        </is>
       </c>
       <c r="T132" s="30" t="inlineStr">
         <is>
@@ -15488,7 +15515,7 @@
         </is>
       </c>
       <c r="U132" s="34" t="n">
-        <v>1443.38</v>
+        <v>0</v>
       </c>
       <c r="V132" s="34" t="n">
         <v>0</v>
@@ -15547,13 +15574,13 @@
         </is>
       </c>
       <c r="F133" s="31" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="G133" s="31" t="n">
         <v>3.11</v>
       </c>
       <c r="H133" s="31" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="I133" s="31" t="n"/>
       <c r="J133" s="31" t="n"/>
@@ -15648,13 +15675,13 @@
         </is>
       </c>
       <c r="F134" s="31" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="G134" s="31" t="n">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="H134" s="31" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="I134" s="31" t="n"/>
       <c r="J134" s="31" t="n"/>
@@ -15753,16 +15780,16 @@
         <v>1.88</v>
       </c>
       <c r="G135" s="31" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="H135" s="31" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="I135" s="31" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="J135" s="31" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="K135" s="32" t="inlineStr">
         <is>
@@ -15854,11 +15881,21 @@
           <t>Genclerbirligi</t>
         </is>
       </c>
-      <c r="F136" s="31" t="n"/>
-      <c r="G136" s="31" t="n"/>
-      <c r="H136" s="31" t="n"/>
-      <c r="I136" s="31" t="n"/>
-      <c r="J136" s="31" t="n"/>
+      <c r="F136" s="31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G136" s="31" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H136" s="31" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="I136" s="31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J136" s="31" t="n">
+        <v>2</v>
+      </c>
       <c r="K136" s="32" t="inlineStr">
         <is>
           <t>Turquia</t>
@@ -15883,12 +15920,12 @@
       <c r="R136" s="37" t="n"/>
       <c r="S136" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T136" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U136" s="34" t="n">
@@ -15950,9 +15987,15 @@
           <t>Fenerbahce</t>
         </is>
       </c>
-      <c r="F137" s="31" t="n"/>
-      <c r="G137" s="31" t="n"/>
-      <c r="H137" s="31" t="n"/>
+      <c r="F137" s="31" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G137" s="31" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H137" s="31" t="n">
+        <v>1.47</v>
+      </c>
       <c r="I137" s="31" t="n"/>
       <c r="J137" s="31" t="n"/>
       <c r="K137" s="32" t="inlineStr">
@@ -15977,18 +16020,17 @@
       </c>
       <c r="Q137" s="37" t="n"/>
       <c r="R137" s="37" t="n"/>
-      <c r="S137" s="30" t="inlineStr">
+      <c r="S137" s="30">
+        <f>IF(OR(Q137="",R137=""),"[APOSTAR] LOCAL",IF(Q137&gt;R137,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T137" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Sin Cuotas</t>
         </is>
       </c>
-      <c r="T137" s="30" t="inlineStr">
-        <is>
-          <t>[PASAR] Sin Cuotas</t>
-        </is>
-      </c>
       <c r="U137" s="34" t="n">
-        <v>0</v>
+        <v>1767.77</v>
       </c>
       <c r="V137" s="34" t="n">
         <v>0</v>
@@ -16046,9 +16088,15 @@
           <t>Ik Start</t>
         </is>
       </c>
-      <c r="F138" s="31" t="n"/>
-      <c r="G138" s="31" t="n"/>
-      <c r="H138" s="31" t="n"/>
+      <c r="F138" s="31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G138" s="31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="H138" s="31" t="n">
+        <v>5.06</v>
+      </c>
       <c r="I138" s="31" t="n"/>
       <c r="J138" s="31" t="n"/>
       <c r="K138" s="32" t="inlineStr">
@@ -16057,13 +16105,13 @@
         </is>
       </c>
       <c r="L138" s="33" t="n">
-        <v>0.428223</v>
+        <v>0.428238</v>
       </c>
       <c r="M138" s="33" t="n">
-        <v>0.188214</v>
+        <v>0.188183</v>
       </c>
       <c r="N138" s="33" t="n">
-        <v>0.383563</v>
+        <v>0.383579</v>
       </c>
       <c r="O138" s="33" t="n">
         <v>0.8321970267658978</v>
@@ -16075,7 +16123,7 @@
       <c r="R138" s="37" t="n"/>
       <c r="S138" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T138" s="30" t="inlineStr">
@@ -16146,10 +16194,10 @@
         <v>1.59</v>
       </c>
       <c r="G139" s="31" t="n">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="H139" s="31" t="n">
-        <v>5.35</v>
+        <v>5.34</v>
       </c>
       <c r="I139" s="31" t="n"/>
       <c r="J139" s="31" t="n"/>
@@ -16245,13 +16293,13 @@
         </is>
       </c>
       <c r="F140" s="31" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="G140" s="31" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="H140" s="31" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="I140" s="31" t="n">
         <v>1.96</v>
@@ -16283,7 +16331,7 @@
       <c r="R140" s="37" t="n"/>
       <c r="S140" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.070&lt;0.080)</t>
+          <t>[PASAR] EV Insuf (0.075&lt;0.080)</t>
         </is>
       </c>
       <c r="T140" s="30" t="inlineStr">
@@ -16456,13 +16504,13 @@
         </is>
       </c>
       <c r="F142" s="31" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="G142" s="31" t="n">
         <v>3.17</v>
       </c>
       <c r="H142" s="31" t="n">
-        <v>3.41</v>
+        <v>3.38</v>
       </c>
       <c r="I142" s="31" t="n"/>
       <c r="J142" s="31" t="n"/>
@@ -16557,13 +16605,13 @@
         </is>
       </c>
       <c r="F143" s="31" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="G143" s="31" t="n">
-        <v>5.01</v>
+        <v>5.12</v>
       </c>
       <c r="H143" s="31" t="n">
-        <v>7.27</v>
+        <v>7.57</v>
       </c>
       <c r="I143" s="31" t="n"/>
       <c r="J143" s="31" t="n"/>
@@ -16573,13 +16621,13 @@
         </is>
       </c>
       <c r="L143" s="33" t="n">
-        <v>0.476807</v>
+        <v>0.476818</v>
       </c>
       <c r="M143" s="33" t="n">
-        <v>0.175305</v>
+        <v>0.175282</v>
       </c>
       <c r="N143" s="33" t="n">
-        <v>0.347888</v>
+        <v>0.347899</v>
       </c>
       <c r="O143" s="33" t="n">
         <v>0.8840338278652803</v>
@@ -16659,13 +16707,13 @@
         </is>
       </c>
       <c r="F144" s="31" t="n">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="G144" s="31" t="n">
-        <v>4.26</v>
+        <v>4.33</v>
       </c>
       <c r="H144" s="31" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="I144" s="31" t="n"/>
       <c r="J144" s="31" t="n"/>
@@ -16675,13 +16723,13 @@
         </is>
       </c>
       <c r="L144" s="33" t="n">
-        <v>0.353908</v>
+        <v>0.353918</v>
       </c>
       <c r="M144" s="33" t="n">
-        <v>0.171703</v>
+        <v>0.171683</v>
       </c>
       <c r="N144" s="33" t="n">
-        <v>0.474389</v>
+        <v>0.474399</v>
       </c>
       <c r="O144" s="33" t="n">
         <v>0.8992250126845134</v>
@@ -16860,9 +16908,15 @@
           <t>Kfum Oslo</t>
         </is>
       </c>
-      <c r="F146" s="31" t="n"/>
-      <c r="G146" s="31" t="n"/>
-      <c r="H146" s="31" t="n"/>
+      <c r="F146" s="31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G146" s="31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H146" s="31" t="n">
+        <v>2.41</v>
+      </c>
       <c r="I146" s="31" t="n"/>
       <c r="J146" s="31" t="n"/>
       <c r="K146" s="32" t="inlineStr">
@@ -16871,25 +16925,25 @@
         </is>
       </c>
       <c r="L146" s="33" t="n">
-        <v>0.412239</v>
+        <v>0.409741</v>
       </c>
       <c r="M146" s="33" t="n">
-        <v>0.156922</v>
+        <v>0.160468</v>
       </c>
       <c r="N146" s="33" t="n">
-        <v>0.430839</v>
+        <v>0.429791</v>
       </c>
       <c r="O146" s="33" t="n">
-        <v>0.9322324834348802</v>
+        <v>0.9197610406248048</v>
       </c>
       <c r="P146" s="33" t="n">
-        <v>0.06776751656511987</v>
+        <v>0.08023895937519526</v>
       </c>
       <c r="Q146" s="37" t="n"/>
       <c r="R146" s="37" t="n"/>
       <c r="S146" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
         </is>
       </c>
       <c r="T146" s="30" t="inlineStr">
@@ -16924,7 +16978,7 @@
         <v/>
       </c>
       <c r="AB146" s="36" t="n">
-        <v>1.3333</v>
+        <v>1.3995</v>
       </c>
       <c r="AC146" s="32" t="inlineStr">
         <is>
@@ -16957,19 +17011,19 @@
         </is>
       </c>
       <c r="F147" s="31" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G147" s="31" t="n">
-        <v>3.97</v>
+        <v>4.01</v>
       </c>
       <c r="H147" s="31" t="n">
-        <v>5.87</v>
+        <v>6.02</v>
       </c>
       <c r="I147" s="31" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J147" s="31" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="K147" s="32" t="inlineStr">
         <is>
@@ -17063,13 +17117,13 @@
         </is>
       </c>
       <c r="F148" s="31" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="G148" s="31" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="H148" s="31" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="I148" s="31" t="n"/>
       <c r="J148" s="31" t="n"/>
@@ -17097,7 +17151,7 @@
       <c r="R148" s="37" t="n"/>
       <c r="S148" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.088&lt;0.120)</t>
+          <t>[PASAR] EV Insuf (0.084&lt;0.120)</t>
         </is>
       </c>
       <c r="T148" s="30" t="inlineStr">
@@ -17165,10 +17219,10 @@
         </is>
       </c>
       <c r="F149" s="31" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G149" s="31" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="H149" s="31" t="n">
         <v>4.72</v>
@@ -17266,13 +17320,13 @@
         </is>
       </c>
       <c r="F150" s="31" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="G150" s="31" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="H150" s="31" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="I150" s="31" t="n"/>
       <c r="J150" s="31" t="n"/>
@@ -17308,7 +17362,7 @@
         </is>
       </c>
       <c r="U150" s="34" t="n">
-        <v>1443.38</v>
+        <v>1767.77</v>
       </c>
       <c r="V150" s="34" t="n">
         <v>0</v>
@@ -17468,13 +17522,13 @@
         </is>
       </c>
       <c r="F152" s="31" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G152" s="31" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="H152" s="31" t="n">
-        <v>4.32</v>
+        <v>4.38</v>
       </c>
       <c r="I152" s="31" t="n"/>
       <c r="J152" s="31" t="n"/>
@@ -17569,13 +17623,13 @@
         </is>
       </c>
       <c r="F153" s="31" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="G153" s="31" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="H153" s="31" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="I153" s="31" t="n"/>
       <c r="J153" s="31" t="n"/>
@@ -17601,9 +17655,10 @@
       </c>
       <c r="Q153" s="37" t="n"/>
       <c r="R153" s="37" t="n"/>
-      <c r="S153" s="30">
-        <f>IF(OR(Q153="",R153=""),"[APOSTAR] VISITA",IF(Q153&lt;R153,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
-        <v/>
+      <c r="S153" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] EV Insuf (0.043&lt;0.080)</t>
+        </is>
       </c>
       <c r="T153" s="30" t="inlineStr">
         <is>
@@ -17611,7 +17666,7 @@
         </is>
       </c>
       <c r="U153" s="34" t="n">
-        <v>1443.38</v>
+        <v>0</v>
       </c>
       <c r="V153" s="34" t="n">
         <v>0</v>
@@ -17670,13 +17725,13 @@
         </is>
       </c>
       <c r="F154" s="31" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="G154" s="31" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H154" s="31" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="I154" s="31" t="n"/>
       <c r="J154" s="31" t="n"/>
@@ -17771,9 +17826,15 @@
           <t>Valerenga</t>
         </is>
       </c>
-      <c r="F155" s="31" t="n"/>
-      <c r="G155" s="31" t="n"/>
-      <c r="H155" s="31" t="n"/>
+      <c r="F155" s="31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G155" s="31" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="H155" s="31" t="n">
+        <v>2.81</v>
+      </c>
       <c r="I155" s="31" t="n"/>
       <c r="J155" s="31" t="n"/>
       <c r="K155" s="32" t="inlineStr">
@@ -17782,13 +17843,13 @@
         </is>
       </c>
       <c r="L155" s="33" t="n">
-        <v>0.459754</v>
+        <v>0.459763</v>
       </c>
       <c r="M155" s="33" t="n">
-        <v>0.169717</v>
+        <v>0.169698</v>
       </c>
       <c r="N155" s="33" t="n">
-        <v>0.37053</v>
+        <v>0.370539</v>
       </c>
       <c r="O155" s="33" t="n">
         <v>0.9088598664214891</v>
@@ -17798,18 +17859,17 @@
       </c>
       <c r="Q155" s="37" t="n"/>
       <c r="R155" s="37" t="n"/>
-      <c r="S155" s="30" t="inlineStr">
+      <c r="S155" s="30">
+        <f>IF(OR(Q155="",R155=""),"[APOSTAR] LOCAL",IF(Q155&gt;R155,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T155" s="30" t="inlineStr">
         <is>
           <t>[PASAR] Sin Cuotas</t>
         </is>
       </c>
-      <c r="T155" s="30" t="inlineStr">
-        <is>
-          <t>[PASAR] Sin Cuotas</t>
-        </is>
-      </c>
       <c r="U155" s="34" t="n">
-        <v>0</v>
+        <v>1767.77</v>
       </c>
       <c r="V155" s="34" t="n">
         <v>0</v>
@@ -18156,16 +18216,20 @@
         </is>
       </c>
       <c r="F159" s="31" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G159" s="31" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="H159" s="31" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="I159" s="31" t="n"/>
-      <c r="J159" s="31" t="n"/>
+        <v>5.24</v>
+      </c>
+      <c r="I159" s="31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J159" s="31" t="n">
+        <v>1.81</v>
+      </c>
       <c r="K159" s="32" t="inlineStr">
         <is>
           <t>Turquia</t>
@@ -18195,7 +18259,7 @@
       </c>
       <c r="T159" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Sin Valor</t>
         </is>
       </c>
       <c r="U159" s="34" t="n">
@@ -18258,13 +18322,13 @@
         </is>
       </c>
       <c r="F160" s="31" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G160" s="31" t="n">
-        <v>4.34</v>
+        <v>4.27</v>
       </c>
       <c r="H160" s="31" t="n">
-        <v>5.35</v>
+        <v>5.21</v>
       </c>
       <c r="I160" s="31" t="n"/>
       <c r="J160" s="31" t="n"/>
@@ -18274,13 +18338,13 @@
         </is>
       </c>
       <c r="L160" s="33" t="n">
-        <v>0.450245</v>
+        <v>0.450256</v>
       </c>
       <c r="M160" s="33" t="n">
-        <v>0.176204</v>
+        <v>0.176182</v>
       </c>
       <c r="N160" s="33" t="n">
-        <v>0.37355</v>
+        <v>0.373562</v>
       </c>
       <c r="O160" s="33" t="n">
         <v>0.8841170701918618</v>
@@ -18360,13 +18424,13 @@
         </is>
       </c>
       <c r="F161" s="31" t="n">
-        <v>2.93</v>
+        <v>2.73</v>
       </c>
       <c r="G161" s="31" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="H161" s="31" t="n">
-        <v>2.79</v>
+        <v>3.07</v>
       </c>
       <c r="I161" s="31" t="n"/>
       <c r="J161" s="31" t="n"/>
@@ -18462,16 +18526,16 @@
         </is>
       </c>
       <c r="F162" s="31" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="G162" s="31" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="H162" s="31" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="I162" s="31" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="J162" s="31" t="n">
         <v>1.88</v>
@@ -18508,7 +18572,7 @@
         </is>
       </c>
       <c r="U162" s="34" t="n">
-        <v>1443.38</v>
+        <v>1767.77</v>
       </c>
       <c r="V162" s="34" t="n">
         <v>0</v>
@@ -18567,13 +18631,13 @@
         </is>
       </c>
       <c r="F163" s="31" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G163" s="31" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="H163" s="31" t="n">
-        <v>4.41</v>
+        <v>4.57</v>
       </c>
       <c r="I163" s="31" t="n"/>
       <c r="J163" s="31" t="n"/>
@@ -18672,10 +18736,10 @@
         <v>2.67</v>
       </c>
       <c r="G164" s="31" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="H164" s="31" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="I164" s="31" t="n"/>
       <c r="J164" s="31" t="n"/>
@@ -18771,13 +18835,13 @@
         </is>
       </c>
       <c r="F165" s="31" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="G165" s="31" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="H165" s="31" t="n">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="I165" s="31" t="n"/>
       <c r="J165" s="31" t="n"/>
@@ -18787,13 +18851,13 @@
         </is>
       </c>
       <c r="L165" s="33" t="n">
-        <v>0.47527</v>
+        <v>0.47528</v>
       </c>
       <c r="M165" s="33" t="n">
-        <v>0.170333</v>
+        <v>0.170314</v>
       </c>
       <c r="N165" s="33" t="n">
-        <v>0.354397</v>
+        <v>0.354407</v>
       </c>
       <c r="O165" s="33" t="n">
         <v>0.9044490721974714</v>
@@ -18804,7 +18868,7 @@
       <c r="Q165" s="37" t="n"/>
       <c r="R165" s="37" t="n"/>
       <c r="S165" s="30">
-        <f>IF(OR(Q165="",R165=""),"[APOSTAR] VISITA",IF(Q165&lt;R165,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <f>IF(OR(Q165="",R165=""),"[APOSTAR] LOCAL",IF(Q165&gt;R165,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
         <v/>
       </c>
       <c r="T165" s="30" t="inlineStr">
@@ -18813,7 +18877,7 @@
         </is>
       </c>
       <c r="U165" s="34" t="n">
-        <v>2500</v>
+        <v>1767.77</v>
       </c>
       <c r="V165" s="34" t="n">
         <v>0</v>
@@ -18871,9 +18935,15 @@
           <t>Sandefjord</t>
         </is>
       </c>
-      <c r="F166" s="31" t="n"/>
-      <c r="G166" s="31" t="n"/>
-      <c r="H166" s="31" t="n"/>
+      <c r="F166" s="31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G166" s="31" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="H166" s="31" t="n">
+        <v>5.58</v>
+      </c>
       <c r="I166" s="31" t="n"/>
       <c r="J166" s="31" t="n"/>
       <c r="K166" s="32" t="inlineStr">
@@ -18882,25 +18952,25 @@
         </is>
       </c>
       <c r="L166" s="33" t="n">
-        <v>0.475423</v>
+        <v>0.454556</v>
       </c>
       <c r="M166" s="33" t="n">
-        <v>0.170079</v>
+        <v>0.17239</v>
       </c>
       <c r="N166" s="33" t="n">
-        <v>0.354498</v>
+        <v>0.373054</v>
       </c>
       <c r="O166" s="33" t="n">
-        <v>0.9054048614108229</v>
+        <v>0.8990198324910278</v>
       </c>
       <c r="P166" s="33" t="n">
-        <v>0.09459513858917706</v>
+        <v>0.1009801675089722</v>
       </c>
       <c r="Q166" s="37" t="n"/>
       <c r="R166" s="37" t="n"/>
       <c r="S166" s="30" t="inlineStr">
         <is>
-          <t>[PASAR] Sin Cuotas</t>
+          <t>[PASAR] Riesgo/Beneficio</t>
         </is>
       </c>
       <c r="T166" s="30" t="inlineStr">
@@ -18935,7 +19005,7 @@
         <v/>
       </c>
       <c r="AB166" s="36" t="n">
-        <v>1.5249</v>
+        <v>1.5462</v>
       </c>
       <c r="AC166" s="32" t="inlineStr">
         <is>
@@ -18968,19 +19038,19 @@
         </is>
       </c>
       <c r="F167" s="31" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="G167" s="31" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="H167" s="31" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="I167" s="31" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="J167" s="31" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="K167" s="32" t="inlineStr">
         <is>
@@ -19049,9 +19119,710 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" s="29" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B168" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-13caykurrizesporgaziantepfk</t>
+        </is>
+      </c>
+      <c r="C168" s="30" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor vs Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="D168" s="30" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="E168" s="30" t="inlineStr">
+        <is>
+          <t>Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="F168" s="31" t="n"/>
+      <c r="G168" s="31" t="n"/>
+      <c r="H168" s="31" t="n"/>
+      <c r="I168" s="31" t="n"/>
+      <c r="J168" s="31" t="n"/>
+      <c r="K168" s="32" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="L168" s="33" t="n">
+        <v>0.462929</v>
+      </c>
+      <c r="M168" s="33" t="n">
+        <v>0.187596</v>
+      </c>
+      <c r="N168" s="33" t="n">
+        <v>0.349474</v>
+      </c>
+      <c r="O168" s="33" t="n">
+        <v>0.8426036069310784</v>
+      </c>
+      <c r="P168" s="33" t="n">
+        <v>0.1573963930689216</v>
+      </c>
+      <c r="Q168" s="37" t="n"/>
+      <c r="R168" s="37" t="n"/>
+      <c r="S168" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T168" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U168" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" s="30">
+        <f>IF(L168="","",IF((MAX(L168,M168,N168)-MEDIAN(L168,M168,N168))&gt;0.05,IF(OR(Q168="",R168=""),"[PREDICCION] "&amp;IF(L168=MAX(L168,M168,N168),"LOCAL",IF(M168=MAX(L168,M168,N168),"EMPATE","VISITA")),IF(L168=MAX(L168,M168,N168),IF(Q168&gt;R168,"[ACIERTO]","[FALLO]"),IF(M168=MAX(L168,M168,N168),IF(Q168=R168,"[ACIERTO]","[FALLO]"),IF(Q168&lt;R168,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X168" s="34">
+        <f>IFERROR(IF(U168=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S168)),U168*(IF(ISNUMBER(SEARCH("LOCAL",S168)),F168,IF(ISNUMBER(SEARCH("EMPATE",S168)),G168,H168))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S168)),-U168,0))),0)+IFERROR(IF(V168=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T168)),V168*(IF(ISNUMBER(SEARCH("OVER",T168)),I168,J168)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T168)),-V168,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y168" s="34">
+        <f>Y167+X168</f>
+        <v/>
+      </c>
+      <c r="Z168" s="35">
+        <f>IF(OR(Q168="",R168=""),"",(L168-IF(Q168&gt;R168,1,0))^2+(M168-IF(Q168=R168,1,0))^2+(N168-IF(Q168&lt;R168,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA168" s="35">
+        <f>IF(OR(Q168="",R168="",F168="",F168=0,G168="",G168=0,H168="",H168=0),"",((1/F168/(1/F168+1/G168+1/H168))-IF(Q168&gt;R168,1,0))^2+((1/G168/(1/F168+1/G168+1/H168))-IF(Q168=R168,1,0))^2+((1/H168/(1/F168+1/G168+1/H168))-IF(Q168&lt;R168,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB168" s="36" t="n">
+        <v>1.3593</v>
+      </c>
+      <c r="AC168" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="29" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B169" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-13defensayjusticiatallerescordoba</t>
+        </is>
+      </c>
+      <c r="C169" s="30" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia vs Talleres (córdoba)</t>
+        </is>
+      </c>
+      <c r="D169" s="30" t="inlineStr">
+        <is>
+          <t>Defensa y Justicia</t>
+        </is>
+      </c>
+      <c r="E169" s="30" t="inlineStr">
+        <is>
+          <t>Talleres (córdoba)</t>
+        </is>
+      </c>
+      <c r="F169" s="31" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G169" s="31" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="H169" s="31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I169" s="31" t="n"/>
+      <c r="J169" s="31" t="n"/>
+      <c r="K169" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L169" s="33" t="n">
+        <v>0.3943531681145134</v>
+      </c>
+      <c r="M169" s="33" t="n">
+        <v>0.2321980137792769</v>
+      </c>
+      <c r="N169" s="33" t="n">
+        <v>0.3734488181062096</v>
+      </c>
+      <c r="O169" s="33" t="n">
+        <v>0.6798820498619095</v>
+      </c>
+      <c r="P169" s="33" t="n">
+        <v>0.3201179501380905</v>
+      </c>
+      <c r="Q169" s="37" t="n"/>
+      <c r="R169" s="37" t="n"/>
+      <c r="S169" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="T169" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U169" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" s="30">
+        <f>IF(L169="","",IF((MAX(L169,M169,N169)-MEDIAN(L169,M169,N169))&gt;0.05,IF(OR(Q169="",R169=""),"[PREDICCION] "&amp;IF(L169=MAX(L169,M169,N169),"LOCAL",IF(M169=MAX(L169,M169,N169),"EMPATE","VISITA")),IF(L169=MAX(L169,M169,N169),IF(Q169&gt;R169,"[ACIERTO]","[FALLO]"),IF(M169=MAX(L169,M169,N169),IF(Q169=R169,"[ACIERTO]","[FALLO]"),IF(Q169&lt;R169,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X169" s="34">
+        <f>IFERROR(IF(U169=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S169)),U169*(IF(ISNUMBER(SEARCH("LOCAL",S169)),F169,IF(ISNUMBER(SEARCH("EMPATE",S169)),G169,H169))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S169)),-U169,0))),0)+IFERROR(IF(V169=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T169)),V169*(IF(ISNUMBER(SEARCH("OVER",T169)),I169,J169)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T169)),-V169,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y169" s="34">
+        <f>Y168+X169</f>
+        <v/>
+      </c>
+      <c r="Z169" s="35">
+        <f>IF(OR(Q169="",R169=""),"",(L169-IF(Q169&gt;R169,1,0))^2+(M169-IF(Q169=R169,1,0))^2+(N169-IF(Q169&lt;R169,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA169" s="35">
+        <f>IF(OR(Q169="",R169="",F169="",F169=0,G169="",G169=0,H169="",H169=0),"",((1/F169/(1/F169+1/G169+1/H169))-IF(Q169&gt;R169,1,0))^2+((1/G169/(1/F169+1/G169+1/H169))-IF(Q169=R169,1,0))^2+((1/H169/(1/F169+1/G169+1/H169))-IF(Q169&lt;R169,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB169" s="36" t="n">
+        <v>0.8088</v>
+      </c>
+      <c r="AC169" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="29" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B170" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-13eyupsporsamsunspor</t>
+        </is>
+      </c>
+      <c r="C170" s="30" t="inlineStr">
+        <is>
+          <t>Eyupspor vs Samsunspor</t>
+        </is>
+      </c>
+      <c r="D170" s="30" t="inlineStr">
+        <is>
+          <t>Eyupspor</t>
+        </is>
+      </c>
+      <c r="E170" s="30" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="F170" s="31" t="n"/>
+      <c r="G170" s="31" t="n"/>
+      <c r="H170" s="31" t="n"/>
+      <c r="I170" s="31" t="n"/>
+      <c r="J170" s="31" t="n"/>
+      <c r="K170" s="32" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="L170" s="33" t="n">
+        <v>0.424572</v>
+      </c>
+      <c r="M170" s="33" t="n">
+        <v>0.193451</v>
+      </c>
+      <c r="N170" s="33" t="n">
+        <v>0.381977</v>
+      </c>
+      <c r="O170" s="33" t="n">
+        <v>0.8203906149832714</v>
+      </c>
+      <c r="P170" s="33" t="n">
+        <v>0.1796093850167286</v>
+      </c>
+      <c r="Q170" s="37" t="n"/>
+      <c r="R170" s="37" t="n"/>
+      <c r="S170" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="T170" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U170" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V170" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" s="30">
+        <f>IF(L170="","",IF((MAX(L170,M170,N170)-MEDIAN(L170,M170,N170))&gt;0.05,IF(OR(Q170="",R170=""),"[PREDICCION] "&amp;IF(L170=MAX(L170,M170,N170),"LOCAL",IF(M170=MAX(L170,M170,N170),"EMPATE","VISITA")),IF(L170=MAX(L170,M170,N170),IF(Q170&gt;R170,"[ACIERTO]","[FALLO]"),IF(M170=MAX(L170,M170,N170),IF(Q170=R170,"[ACIERTO]","[FALLO]"),IF(Q170&lt;R170,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X170" s="34">
+        <f>IFERROR(IF(U170=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S170)),U170*(IF(ISNUMBER(SEARCH("LOCAL",S170)),F170,IF(ISNUMBER(SEARCH("EMPATE",S170)),G170,H170))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S170)),-U170,0))),0)+IFERROR(IF(V170=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T170)),V170*(IF(ISNUMBER(SEARCH("OVER",T170)),I170,J170)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T170)),-V170,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y170" s="34">
+        <f>Y169+X170</f>
+        <v/>
+      </c>
+      <c r="Z170" s="35">
+        <f>IF(OR(Q170="",R170=""),"",(L170-IF(Q170&gt;R170,1,0))^2+(M170-IF(Q170=R170,1,0))^2+(N170-IF(Q170&lt;R170,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA170" s="35">
+        <f>IF(OR(Q170="",R170="",F170="",F170=0,G170="",G170=0,H170="",H170=0),"",((1/F170/(1/F170+1/G170+1/H170))-IF(Q170&gt;R170,1,0))^2+((1/G170/(1/F170+1/G170+1/H170))-IF(Q170=R170,1,0))^2+((1/H170/(1/F170+1/G170+1/H170))-IF(Q170&lt;R170,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB170" s="36" t="n">
+        <v>1.3173</v>
+      </c>
+      <c r="AC170" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="29" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B171" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-13lanusbanfield</t>
+        </is>
+      </c>
+      <c r="C171" s="30" t="inlineStr">
+        <is>
+          <t>Lanus vs Banfield</t>
+        </is>
+      </c>
+      <c r="D171" s="30" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E171" s="30" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="F171" s="31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G171" s="31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H171" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I171" s="31" t="n"/>
+      <c r="J171" s="31" t="n"/>
+      <c r="K171" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L171" s="33" t="n">
+        <v>0.450239</v>
+      </c>
+      <c r="M171" s="33" t="n">
+        <v>0.218435</v>
+      </c>
+      <c r="N171" s="33" t="n">
+        <v>0.331326</v>
+      </c>
+      <c r="O171" s="33" t="n">
+        <v>0.6966201773216166</v>
+      </c>
+      <c r="P171" s="33" t="n">
+        <v>0.3033798226783834</v>
+      </c>
+      <c r="Q171" s="37" t="n"/>
+      <c r="R171" s="37" t="n"/>
+      <c r="S171" s="30">
+        <f>IF(OR(Q171="",R171=""),"[APOSTAR] VISITA",IF(Q171&lt;R171,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T171" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U171" s="34" t="n">
+        <v>2500</v>
+      </c>
+      <c r="V171" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" s="30">
+        <f>IF(L171="","",IF((MAX(L171,M171,N171)-MEDIAN(L171,M171,N171))&gt;0.05,IF(OR(Q171="",R171=""),"[PREDICCION] "&amp;IF(L171=MAX(L171,M171,N171),"LOCAL",IF(M171=MAX(L171,M171,N171),"EMPATE","VISITA")),IF(L171=MAX(L171,M171,N171),IF(Q171&gt;R171,"[ACIERTO]","[FALLO]"),IF(M171=MAX(L171,M171,N171),IF(Q171=R171,"[ACIERTO]","[FALLO]"),IF(Q171&lt;R171,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X171" s="34">
+        <f>IFERROR(IF(U171=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S171)),U171*(IF(ISNUMBER(SEARCH("LOCAL",S171)),F171,IF(ISNUMBER(SEARCH("EMPATE",S171)),G171,H171))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S171)),-U171,0))),0)+IFERROR(IF(V171=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T171)),V171*(IF(ISNUMBER(SEARCH("OVER",T171)),I171,J171)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T171)),-V171,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y171" s="34">
+        <f>Y170+X171</f>
+        <v/>
+      </c>
+      <c r="Z171" s="35">
+        <f>IF(OR(Q171="",R171=""),"",(L171-IF(Q171&gt;R171,1,0))^2+(M171-IF(Q171=R171,1,0))^2+(N171-IF(Q171&lt;R171,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA171" s="35">
+        <f>IF(OR(Q171="",R171="",F171="",F171=0,G171="",G171=0,H171="",H171=0),"",((1/F171/(1/F171+1/G171+1/H171))-IF(Q171&gt;R171,1,0))^2+((1/G171/(1/F171+1/G171+1/H171))-IF(Q171=R171,1,0))^2+((1/H171/(1/F171+1/G171+1/H171))-IF(Q171&lt;R171,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB171" s="36" t="n">
+        <v>0.9307</v>
+      </c>
+      <c r="AC171" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="29" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B172" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-13manchesterunitedleedsunited</t>
+        </is>
+      </c>
+      <c r="C172" s="30" t="inlineStr">
+        <is>
+          <t>Manchester United vs Leeds United</t>
+        </is>
+      </c>
+      <c r="D172" s="30" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="E172" s="30" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="F172" s="31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G172" s="31" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H172" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I172" s="31" t="n"/>
+      <c r="J172" s="31" t="n"/>
+      <c r="K172" s="32" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="L172" s="33" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="M172" s="33" t="n">
+        <v>0.180529</v>
+      </c>
+      <c r="N172" s="33" t="n">
+        <v>0.361761</v>
+      </c>
+      <c r="O172" s="33" t="n">
+        <v>0.8711350590571894</v>
+      </c>
+      <c r="P172" s="33" t="n">
+        <v>0.1288649409428107</v>
+      </c>
+      <c r="Q172" s="37" t="n"/>
+      <c r="R172" s="37" t="n"/>
+      <c r="S172" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Riesgo/Beneficio</t>
+        </is>
+      </c>
+      <c r="T172" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U172" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V172" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W172" s="30">
+        <f>IF(L172="","",IF((MAX(L172,M172,N172)-MEDIAN(L172,M172,N172))&gt;0.05,IF(OR(Q172="",R172=""),"[PREDICCION] "&amp;IF(L172=MAX(L172,M172,N172),"LOCAL",IF(M172=MAX(L172,M172,N172),"EMPATE","VISITA")),IF(L172=MAX(L172,M172,N172),IF(Q172&gt;R172,"[ACIERTO]","[FALLO]"),IF(M172=MAX(L172,M172,N172),IF(Q172=R172,"[ACIERTO]","[FALLO]"),IF(Q172&lt;R172,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X172" s="34">
+        <f>IFERROR(IF(U172=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S172)),U172*(IF(ISNUMBER(SEARCH("LOCAL",S172)),F172,IF(ISNUMBER(SEARCH("EMPATE",S172)),G172,H172))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S172)),-U172,0))),0)+IFERROR(IF(V172=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T172)),V172*(IF(ISNUMBER(SEARCH("OVER",T172)),I172,J172)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T172)),-V172,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y172" s="34">
+        <f>Y171+X172</f>
+        <v/>
+      </c>
+      <c r="Z172" s="35">
+        <f>IF(OR(Q172="",R172=""),"",(L172-IF(Q172&gt;R172,1,0))^2+(M172-IF(Q172=R172,1,0))^2+(N172-IF(Q172&lt;R172,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA172" s="35">
+        <f>IF(OR(Q172="",R172="",F172="",F172=0,G172="",G172=0,H172="",H172=0),"",((1/F172/(1/F172+1/G172+1/H172))-IF(Q172&gt;R172,1,0))^2+((1/G172/(1/F172+1/G172+1/H172))-IF(Q172=R172,1,0))^2+((1/H172/(1/F172+1/G172+1/H172))-IF(Q172&lt;R172,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB172" s="36" t="n">
+        <v>1.3167</v>
+      </c>
+      <c r="AC172" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="29" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B173" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-13sarmientojuningimnasialaplata</t>
+        </is>
+      </c>
+      <c r="C173" s="30" t="inlineStr">
+        <is>
+          <t>Sarmiento (junin) vs Gimnasia la Plata</t>
+        </is>
+      </c>
+      <c r="D173" s="30" t="inlineStr">
+        <is>
+          <t>Sarmiento (junin)</t>
+        </is>
+      </c>
+      <c r="E173" s="30" t="inlineStr">
+        <is>
+          <t>Gimnasia la Plata</t>
+        </is>
+      </c>
+      <c r="F173" s="31" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="G173" s="31" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H173" s="31" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="I173" s="31" t="n"/>
+      <c r="J173" s="31" t="n"/>
+      <c r="K173" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L173" s="33" t="n">
+        <v>0.425266</v>
+      </c>
+      <c r="M173" s="33" t="n">
+        <v>0.224613</v>
+      </c>
+      <c r="N173" s="33" t="n">
+        <v>0.350121</v>
+      </c>
+      <c r="O173" s="33" t="n">
+        <v>0.6705515747078269</v>
+      </c>
+      <c r="P173" s="33" t="n">
+        <v>0.3294484252921732</v>
+      </c>
+      <c r="Q173" s="37" t="n"/>
+      <c r="R173" s="37" t="n"/>
+      <c r="S173" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] EV Insuf (0.059&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="T173" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U173" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V173" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" s="30">
+        <f>IF(L173="","",IF((MAX(L173,M173,N173)-MEDIAN(L173,M173,N173))&gt;0.05,IF(OR(Q173="",R173=""),"[PREDICCION] "&amp;IF(L173=MAX(L173,M173,N173),"LOCAL",IF(M173=MAX(L173,M173,N173),"EMPATE","VISITA")),IF(L173=MAX(L173,M173,N173),IF(Q173&gt;R173,"[ACIERTO]","[FALLO]"),IF(M173=MAX(L173,M173,N173),IF(Q173=R173,"[ACIERTO]","[FALLO]"),IF(Q173&lt;R173,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X173" s="34">
+        <f>IFERROR(IF(U173=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S173)),U173*(IF(ISNUMBER(SEARCH("LOCAL",S173)),F173,IF(ISNUMBER(SEARCH("EMPATE",S173)),G173,H173))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S173)),-U173,0))),0)+IFERROR(IF(V173=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T173)),V173*(IF(ISNUMBER(SEARCH("OVER",T173)),I173,J173)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T173)),-V173,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y173" s="34">
+        <f>Y172+X173</f>
+        <v/>
+      </c>
+      <c r="Z173" s="35">
+        <f>IF(OR(Q173="",R173=""),"",(L173-IF(Q173&gt;R173,1,0))^2+(M173-IF(Q173=R173,1,0))^2+(N173-IF(Q173&lt;R173,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA173" s="35">
+        <f>IF(OR(Q173="",R173="",F173="",F173=0,G173="",G173=0,H173="",H173=0),"",((1/F173/(1/F173+1/G173+1/H173))-IF(Q173&gt;R173,1,0))^2+((1/G173/(1/F173+1/G173+1/H173))-IF(Q173=R173,1,0))^2+((1/H173/(1/F173+1/G173+1/H173))-IF(Q173&lt;R173,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB173" s="36" t="n">
+        <v>0.8578</v>
+      </c>
+      <c r="AC173" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="29" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B174" s="30" t="inlineStr">
+        <is>
+          <t>2026-04-14velezsarsfieldcentralcordobasantiagodelestero</t>
+        </is>
+      </c>
+      <c r="C174" s="30" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield vs Central Córdoba (santiago del Estero)</t>
+        </is>
+      </c>
+      <c r="D174" s="30" t="inlineStr">
+        <is>
+          <t>Velez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E174" s="30" t="inlineStr">
+        <is>
+          <t>Central Córdoba (santiago del Estero)</t>
+        </is>
+      </c>
+      <c r="F174" s="31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G174" s="31" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="H174" s="31" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="I174" s="31" t="n"/>
+      <c r="J174" s="31" t="n"/>
+      <c r="K174" s="32" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="L174" s="33" t="n">
+        <v>0.457788</v>
+      </c>
+      <c r="M174" s="33" t="n">
+        <v>0.214576</v>
+      </c>
+      <c r="N174" s="33" t="n">
+        <v>0.327636</v>
+      </c>
+      <c r="O174" s="33" t="n">
+        <v>0.7139585800856334</v>
+      </c>
+      <c r="P174" s="33" t="n">
+        <v>0.2860414199143665</v>
+      </c>
+      <c r="Q174" s="37" t="n"/>
+      <c r="R174" s="37" t="n"/>
+      <c r="S174" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Riesgo/Beneficio</t>
+        </is>
+      </c>
+      <c r="T174" s="30" t="inlineStr">
+        <is>
+          <t>[PASAR] Sin Cuotas</t>
+        </is>
+      </c>
+      <c r="U174" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V174" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" s="30">
+        <f>IF(L174="","",IF((MAX(L174,M174,N174)-MEDIAN(L174,M174,N174))&gt;0.05,IF(OR(Q174="",R174=""),"[PREDICCION] "&amp;IF(L174=MAX(L174,M174,N174),"LOCAL",IF(M174=MAX(L174,M174,N174),"EMPATE","VISITA")),IF(L174=MAX(L174,M174,N174),IF(Q174&gt;R174,"[ACIERTO]","[FALLO]"),IF(M174=MAX(L174,M174,N174),IF(Q174=R174,"[ACIERTO]","[FALLO]"),IF(Q174&lt;R174,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
+        <v/>
+      </c>
+      <c r="X174" s="34">
+        <f>IFERROR(IF(U174=0,0,IF(ISNUMBER(SEARCH("[GANADA]",S174)),U174*(IF(ISNUMBER(SEARCH("LOCAL",S174)),F174,IF(ISNUMBER(SEARCH("EMPATE",S174)),G174,H174))-1),IF(ISNUMBER(SEARCH("[PERDIDA]",S174)),-U174,0))),0)+IFERROR(IF(V174=0,0,IF(ISNUMBER(SEARCH("[GANADA]",T174)),V174*(IF(ISNUMBER(SEARCH("OVER",T174)),I174,J174)-1),IF(ISNUMBER(SEARCH("[PERDIDA]",T174)),-V174,0))),0)</f>
+        <v/>
+      </c>
+      <c r="Y174" s="34">
+        <f>Y173+X174</f>
+        <v/>
+      </c>
+      <c r="Z174" s="35">
+        <f>IF(OR(Q174="",R174=""),"",(L174-IF(Q174&gt;R174,1,0))^2+(M174-IF(Q174=R174,1,0))^2+(N174-IF(Q174&lt;R174,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AA174" s="35">
+        <f>IF(OR(Q174="",R174="",F174="",F174=0,G174="",G174=0,H174="",H174=0),"",((1/F174/(1/F174+1/G174+1/H174))-IF(Q174&gt;R174,1,0))^2+((1/G174/(1/F174+1/G174+1/H174))-IF(Q174=R174,1,0))^2+((1/H174/(1/F174+1/G174+1/H174))-IF(Q174&lt;R174,1,0))^2)</f>
+        <v/>
+      </c>
+      <c r="AB174" s="36" t="n">
+        <v>1.0542</v>
+      </c>
+      <c r="AC174" s="32" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AC1"/>
-  <conditionalFormatting sqref="A2:R167">
+  <conditionalFormatting sqref="A2:R174">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$K2="Argentina"</formula>
     </cfRule>
@@ -19068,7 +19839,7 @@
       <formula>$K2="Inglaterra"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S167">
+  <conditionalFormatting sqref="S2:S174">
     <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("[GANADA]",S2))</formula>
     </cfRule>
@@ -19082,7 +19853,7 @@
       <formula>ISNUMBER(SEARCH("[APOSTAR]",S2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T167">
+  <conditionalFormatting sqref="T2:T174">
     <cfRule type="expression" priority="10" dxfId="5" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("[GANADA]",T2))</formula>
     </cfRule>
@@ -19096,7 +19867,7 @@
       <formula>ISNUMBER(SEARCH("[APOSTAR]",T2))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X167">
+  <conditionalFormatting sqref="X2:X174">
     <cfRule type="expression" priority="14" dxfId="5" stopIfTrue="1">
       <formula>X2&gt;0</formula>
     </cfRule>
@@ -19104,7 +19875,7 @@
       <formula>X2&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W167">
+  <conditionalFormatting sqref="W2:W174">
     <cfRule type="expression" priority="16" dxfId="5" stopIfTrue="1">
       <formula>ISNUMBER(SEARCH("[ACIERTO]",W2))</formula>
     </cfRule>
@@ -19128,7 +19899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -19383,7 +20154,7 @@
       </c>
       <c r="B7" s="44" t="inlineStr">
         <is>
-          <t>Goztepe vs Galatasaray</t>
+          <t>Caykur Rizespor vs Samsunspor</t>
         </is>
       </c>
       <c r="C7" s="43" t="inlineStr">
@@ -19393,11 +20164,13 @@
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E7" s="45" t="n">
-        <v>2500</v>
+          <t>[PASAR] EV Insuf (0.060&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E7" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F7" s="53" t="inlineStr">
         <is>
@@ -19407,7 +20180,7 @@
       <c r="G7" s="49" t="n"/>
       <c r="H7" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I7" s="45" t="n">
@@ -19434,62 +20207,56 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="48" t="inlineStr">
         <is>
-          <t>21/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="B8" s="50" t="inlineStr">
         <is>
-          <t>Atlético Tucumán vs Gimnasia la Plata</t>
+          <t>Goztepe vs Galatasaray</t>
         </is>
       </c>
       <c r="C8" s="48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D8" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E8" s="49" t="n">
-        <v>1767.77</v>
-      </c>
-      <c r="F8" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G8" s="47" t="n">
-        <v>-1767.77</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G8" s="49" t="n"/>
       <c r="H8" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I8" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J8" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K8" s="47" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L8" s="52" t="n">
-        <v>732.23</v>
-      </c>
-      <c r="M8" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N8" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J8" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K8" s="49" t="n"/>
+      <c r="L8" s="49" t="n"/>
+      <c r="M8" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19501,55 +20268,57 @@
       </c>
       <c r="B9" s="44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion vs Liverpool</t>
+          <t>Atlético Tucumán vs Gimnasia la Plata</t>
         </is>
       </c>
       <c r="C9" s="43" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D9" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E9" s="45" t="n">
         <v>1767.77</v>
       </c>
-      <c r="F9" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G9" s="52" t="n">
-        <v>3977.48</v>
+      <c r="F9" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G9" s="47" t="n">
+        <v>-1767.77</v>
       </c>
       <c r="H9" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I9" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="49" t="n"/>
-      <c r="L9" s="49" t="n"/>
-      <c r="M9" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N9" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I9" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J9" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K9" s="47" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L9" s="52" t="n">
+        <v>732.23</v>
+      </c>
+      <c r="M9" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N9" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -19561,12 +20330,12 @@
       </c>
       <c r="B10" s="50" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs Unión (santa Fe)</t>
+          <t>Brighton &amp; Hove Albion vs Liverpool</t>
         </is>
       </c>
       <c r="C10" s="48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D10" s="50" t="inlineStr">
@@ -19583,35 +20352,33 @@
         </is>
       </c>
       <c r="G10" s="52" t="n">
-        <v>3358.76</v>
+        <v>3977.48</v>
       </c>
       <c r="H10" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I10" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J10" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K10" s="52" t="n">
-        <v>4750</v>
-      </c>
-      <c r="L10" s="47" t="n">
-        <v>-1391.24</v>
-      </c>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I10" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="49" t="n"/>
+      <c r="L10" s="49" t="n"/>
       <c r="M10" s="51" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N10" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N10" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19623,12 +20390,12 @@
       </c>
       <c r="B11" s="44" t="inlineStr">
         <is>
-          <t>Everton vs Chelsea</t>
+          <t>Defensa y Justicia vs Unión (santa Fe)</t>
         </is>
       </c>
       <c r="C11" s="43" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D11" s="44" t="inlineStr">
@@ -19645,7 +20412,7 @@
         </is>
       </c>
       <c r="G11" s="52" t="n">
-        <v>4596.2</v>
+        <v>3358.76</v>
       </c>
       <c r="H11" s="44" t="inlineStr">
         <is>
@@ -19661,10 +20428,10 @@
         </is>
       </c>
       <c r="K11" s="52" t="n">
-        <v>6500</v>
+        <v>4750</v>
       </c>
       <c r="L11" s="47" t="n">
-        <v>-1903.8</v>
+        <v>-1391.24</v>
       </c>
       <c r="M11" s="51" t="inlineStr">
         <is>
@@ -19685,21 +20452,21 @@
       </c>
       <c r="B12" s="50" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino vs Botafogo</t>
+          <t>Everton vs Chelsea</t>
         </is>
       </c>
       <c r="C12" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D12" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E12" s="49" t="n">
-        <v>2500</v>
+        <v>1767.77</v>
       </c>
       <c r="F12" s="51" t="inlineStr">
         <is>
@@ -19707,11 +20474,11 @@
         </is>
       </c>
       <c r="G12" s="52" t="n">
-        <v>6975</v>
+        <v>4596.2</v>
       </c>
       <c r="H12" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I12" s="49" t="n">
@@ -19723,10 +20490,10 @@
         </is>
       </c>
       <c r="K12" s="52" t="n">
-        <v>6975</v>
-      </c>
-      <c r="L12" s="54" t="n">
-        <v>0</v>
+        <v>6500</v>
+      </c>
+      <c r="L12" s="47" t="n">
+        <v>-1903.8</v>
       </c>
       <c r="M12" s="51" t="inlineStr">
         <is>
@@ -19747,12 +20514,12 @@
       </c>
       <c r="B13" s="44" t="inlineStr">
         <is>
-          <t>Viking fk vs Molde</t>
+          <t>Red Bull Bragantino vs Botafogo</t>
         </is>
       </c>
       <c r="C13" s="43" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D13" s="44" t="inlineStr">
@@ -19763,13 +20530,13 @@
       <c r="E13" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="F13" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G13" s="47" t="n">
-        <v>-2500</v>
+      <c r="F13" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G13" s="52" t="n">
+        <v>6975</v>
       </c>
       <c r="H13" s="44" t="inlineStr">
         <is>
@@ -19779,42 +20546,42 @@
       <c r="I13" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J13" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K13" s="47" t="n">
-        <v>-2500</v>
+      <c r="J13" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K13" s="52" t="n">
+        <v>6975</v>
       </c>
       <c r="L13" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="M13" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N13" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="M13" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N13" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="48" t="inlineStr">
         <is>
-          <t>22/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="B14" s="50" t="inlineStr">
         <is>
-          <t>Athletico Paranaense vs Coritiba</t>
+          <t>Viking fk vs Molde</t>
         </is>
       </c>
       <c r="C14" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D14" s="50" t="inlineStr">
@@ -19823,7 +20590,7 @@
         </is>
       </c>
       <c r="E14" s="49" t="n">
-        <v>944.91</v>
+        <v>2500</v>
       </c>
       <c r="F14" s="46" t="inlineStr">
         <is>
@@ -19831,7 +20598,7 @@
         </is>
       </c>
       <c r="G14" s="47" t="n">
-        <v>-944.91</v>
+        <v>-2500</v>
       </c>
       <c r="H14" s="50" t="inlineStr">
         <is>
@@ -19849,8 +20616,8 @@
       <c r="K14" s="47" t="n">
         <v>-2500</v>
       </c>
-      <c r="L14" s="52" t="n">
-        <v>1555.09</v>
+      <c r="L14" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="46" t="inlineStr">
         <is>
@@ -19871,7 +20638,7 @@
       </c>
       <c r="B15" s="44" t="inlineStr">
         <is>
-          <t>Corinthians vs Flamengo</t>
+          <t>Athletico Paranaense vs Coritiba</t>
         </is>
       </c>
       <c r="C15" s="43" t="inlineStr">
@@ -19881,7 +20648,7 @@
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E15" s="45" t="n">
@@ -19897,29 +20664,31 @@
       </c>
       <c r="H15" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I15" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="49" t="n"/>
-      <c r="L15" s="49" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I15" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J15" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K15" s="47" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L15" s="52" t="n">
+        <v>1555.09</v>
+      </c>
       <c r="M15" s="46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N15" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N15" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -19931,7 +20700,7 @@
       </c>
       <c r="B16" s="50" t="inlineStr">
         <is>
-          <t>Cruzeiro vs Santos</t>
+          <t>Corinthians vs Flamengo</t>
         </is>
       </c>
       <c r="C16" s="48" t="inlineStr">
@@ -19941,7 +20710,7 @@
       </c>
       <c r="D16" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E16" s="49" t="n">
@@ -19957,31 +20726,29 @@
       </c>
       <c r="H16" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I16" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J16" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K16" s="47" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L16" s="52" t="n">
-        <v>1555.09</v>
-      </c>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I16" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="49" t="n"/>
+      <c r="L16" s="49" t="n"/>
       <c r="M16" s="46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N16" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N16" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19993,12 +20760,12 @@
       </c>
       <c r="B17" s="44" t="inlineStr">
         <is>
-          <t>Fredrikstad vs Kfum Oslo</t>
+          <t>Cruzeiro vs Santos</t>
         </is>
       </c>
       <c r="C17" s="43" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D17" s="44" t="inlineStr">
@@ -20007,7 +20774,7 @@
         </is>
       </c>
       <c r="E17" s="45" t="n">
-        <v>1250</v>
+        <v>944.91</v>
       </c>
       <c r="F17" s="46" t="inlineStr">
         <is>
@@ -20015,33 +20782,35 @@
         </is>
       </c>
       <c r="G17" s="47" t="n">
-        <v>-1250</v>
+        <v>-944.91</v>
       </c>
       <c r="H17" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I17" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K17" s="49" t="n"/>
-      <c r="L17" s="49" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I17" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J17" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K17" s="47" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L17" s="52" t="n">
+        <v>1555.09</v>
+      </c>
       <c r="M17" s="46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N17" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N17" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -20053,12 +20822,12 @@
       </c>
       <c r="B18" s="50" t="inlineStr">
         <is>
-          <t>Newcastle United vs Sunderland</t>
+          <t>Fredrikstad vs Kfum Oslo</t>
         </is>
       </c>
       <c r="C18" s="48" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D18" s="50" t="inlineStr">
@@ -20067,15 +20836,15 @@
         </is>
       </c>
       <c r="E18" s="49" t="n">
-        <v>1767.77</v>
-      </c>
-      <c r="F18" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G18" s="52" t="n">
-        <v>8131.74</v>
+        <v>1250</v>
+      </c>
+      <c r="F18" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G18" s="47" t="n">
+        <v>-1250</v>
       </c>
       <c r="H18" s="50" t="inlineStr">
         <is>
@@ -20094,9 +20863,9 @@
       </c>
       <c r="K18" s="49" t="n"/>
       <c r="L18" s="49" t="n"/>
-      <c r="M18" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="M18" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N18" s="48" t="inlineStr">
@@ -20113,21 +20882,21 @@
       </c>
       <c r="B19" s="44" t="inlineStr">
         <is>
-          <t>Remo vs Bahia</t>
+          <t>Newcastle United vs Sunderland</t>
         </is>
       </c>
       <c r="C19" s="43" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D19" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E19" s="45" t="n">
-        <v>944.91</v>
+        <v>1767.77</v>
       </c>
       <c r="F19" s="51" t="inlineStr">
         <is>
@@ -20135,35 +20904,33 @@
         </is>
       </c>
       <c r="G19" s="52" t="n">
-        <v>2541.81</v>
+        <v>8131.74</v>
       </c>
       <c r="H19" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I19" s="45" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J19" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K19" s="52" t="n">
-        <v>6725</v>
-      </c>
-      <c r="L19" s="47" t="n">
-        <v>-4183.19</v>
-      </c>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I19" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="49" t="n"/>
+      <c r="L19" s="49" t="n"/>
       <c r="M19" s="51" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N19" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N19" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20175,12 +20942,12 @@
       </c>
       <c r="B20" s="50" t="inlineStr">
         <is>
-          <t>Rosenborg vs Valerenga</t>
+          <t>Remo vs Bahia</t>
         </is>
       </c>
       <c r="C20" s="48" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D20" s="50" t="inlineStr">
@@ -20189,41 +20956,43 @@
         </is>
       </c>
       <c r="E20" s="49" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F20" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G20" s="47" t="n">
-        <v>-1250</v>
+        <v>944.91</v>
+      </c>
+      <c r="F20" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G20" s="52" t="n">
+        <v>2541.81</v>
       </c>
       <c r="H20" s="50" t="inlineStr">
         <is>
-          <t>[PASAR] Shadow-EV (0.061&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="I20" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K20" s="49" t="n"/>
-      <c r="L20" s="49" t="n"/>
-      <c r="M20" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N20" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I20" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J20" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K20" s="52" t="n">
+        <v>6725</v>
+      </c>
+      <c r="L20" s="47" t="n">
+        <v>-4183.19</v>
+      </c>
+      <c r="M20" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N20" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -20235,7 +21004,7 @@
       </c>
       <c r="B21" s="44" t="inlineStr">
         <is>
-          <t>Sandefjord vs Sarpsborg fk</t>
+          <t>Rosenborg vs Valerenga</t>
         </is>
       </c>
       <c r="C21" s="43" t="inlineStr">
@@ -20245,23 +21014,23 @@
       </c>
       <c r="D21" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E21" s="45" t="n">
         <v>1250</v>
       </c>
-      <c r="F21" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G21" s="52" t="n">
-        <v>2687.5</v>
+      <c r="F21" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G21" s="47" t="n">
+        <v>-1250</v>
       </c>
       <c r="H21" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+          <t>[PASAR] Shadow-EV (0.061&lt;0.080)</t>
         </is>
       </c>
       <c r="I21" s="45" t="inlineStr">
@@ -20276,9 +21045,9 @@
       </c>
       <c r="K21" s="49" t="n"/>
       <c r="L21" s="49" t="n"/>
-      <c r="M21" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="M21" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N21" s="43" t="inlineStr">
@@ -20295,29 +21064,29 @@
       </c>
       <c r="B22" s="50" t="inlineStr">
         <is>
-          <t>São Paulo vs Palmeiras</t>
+          <t>Sandefjord vs Sarpsborg fk</t>
         </is>
       </c>
       <c r="C22" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D22" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E22" s="49" t="n">
-        <v>944.91</v>
-      </c>
-      <c r="F22" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G22" s="47" t="n">
-        <v>-944.91</v>
+        <v>1250</v>
+      </c>
+      <c r="F22" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G22" s="52" t="n">
+        <v>2687.5</v>
       </c>
       <c r="H22" s="50" t="inlineStr">
         <is>
@@ -20336,9 +21105,9 @@
       </c>
       <c r="K22" s="49" t="n"/>
       <c r="L22" s="49" t="n"/>
-      <c r="M22" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="M22" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="N22" s="48" t="inlineStr">
@@ -20355,21 +21124,21 @@
       </c>
       <c r="B23" s="44" t="inlineStr">
         <is>
-          <t>Sarmiento (junín) vs Aldosivi</t>
+          <t>São Paulo vs Palmeiras</t>
         </is>
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D23" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E23" s="45" t="n">
-        <v>2500</v>
+        <v>944.91</v>
       </c>
       <c r="F23" s="46" t="inlineStr">
         <is>
@@ -20377,35 +21146,33 @@
         </is>
       </c>
       <c r="G23" s="47" t="n">
-        <v>-2500</v>
+        <v>-944.91</v>
       </c>
       <c r="H23" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I23" s="45" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J23" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K23" s="47" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L23" s="54" t="n">
-        <v>0</v>
-      </c>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I23" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="49" t="n"/>
+      <c r="L23" s="49" t="n"/>
       <c r="M23" s="46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N23" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N23" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20417,12 +21184,12 @@
       </c>
       <c r="B24" s="50" t="inlineStr">
         <is>
-          <t>Sk Brann vs Tromso</t>
+          <t>Sarmiento (junín) vs Aldosivi</t>
         </is>
       </c>
       <c r="C24" s="48" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D24" s="50" t="inlineStr">
@@ -20431,15 +21198,15 @@
         </is>
       </c>
       <c r="E24" s="49" t="n">
-        <v>1250</v>
-      </c>
-      <c r="F24" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G24" s="52" t="n">
-        <v>3000</v>
+        <v>2500</v>
+      </c>
+      <c r="F24" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G24" s="47" t="n">
+        <v>-2500</v>
       </c>
       <c r="H24" s="50" t="inlineStr">
         <is>
@@ -20449,25 +21216,25 @@
       <c r="I24" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J24" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K24" s="52" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L24" s="47" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="M24" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N24" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="J24" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K24" s="47" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L24" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N24" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -20479,12 +21246,12 @@
       </c>
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur vs Nottingham Forest</t>
+          <t>Sk Brann vs Tromso</t>
         </is>
       </c>
       <c r="C25" s="43" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D25" s="44" t="inlineStr">
@@ -20493,7 +21260,7 @@
         </is>
       </c>
       <c r="E25" s="45" t="n">
-        <v>1767.77</v>
+        <v>1250</v>
       </c>
       <c r="F25" s="51" t="inlineStr">
         <is>
@@ -20501,7 +21268,7 @@
         </is>
       </c>
       <c r="G25" s="52" t="n">
-        <v>4242.65</v>
+        <v>3000</v>
       </c>
       <c r="H25" s="44" t="inlineStr">
         <is>
@@ -20520,7 +21287,7 @@
         <v>6000</v>
       </c>
       <c r="L25" s="47" t="n">
-        <v>-1757.35</v>
+        <v>-3000</v>
       </c>
       <c r="M25" s="51" t="inlineStr">
         <is>
@@ -20541,12 +21308,12 @@
       </c>
       <c r="B26" s="50" t="inlineStr">
         <is>
-          <t>Vasco da Gama vs Grêmio</t>
+          <t>Tottenham Hotspur vs Nottingham Forest</t>
         </is>
       </c>
       <c r="C26" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D26" s="50" t="inlineStr">
@@ -20555,41 +21322,43 @@
         </is>
       </c>
       <c r="E26" s="49" t="n">
-        <v>944.91</v>
-      </c>
-      <c r="F26" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G26" s="47" t="n">
-        <v>-944.91</v>
+        <v>1767.77</v>
+      </c>
+      <c r="F26" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G26" s="52" t="n">
+        <v>4242.65</v>
       </c>
       <c r="H26" s="50" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I26" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K26" s="49" t="n"/>
-      <c r="L26" s="49" t="n"/>
-      <c r="M26" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N26" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I26" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J26" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K26" s="52" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L26" s="47" t="n">
+        <v>-1757.35</v>
+      </c>
+      <c r="M26" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N26" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -20601,7 +21370,7 @@
       </c>
       <c r="B27" s="44" t="inlineStr">
         <is>
-          <t>Vitória vs Mirassol</t>
+          <t>Vasco da Gama vs Grêmio</t>
         </is>
       </c>
       <c r="C27" s="43" t="inlineStr">
@@ -20611,64 +21380,62 @@
       </c>
       <c r="D27" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E27" s="45" t="n">
         <v>944.91</v>
       </c>
-      <c r="F27" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G27" s="52" t="n">
-        <v>1464.61</v>
+      <c r="F27" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G27" s="47" t="n">
+        <v>-944.91</v>
       </c>
       <c r="H27" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I27" s="45" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J27" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K27" s="52" t="n">
-        <v>3875</v>
-      </c>
-      <c r="L27" s="47" t="n">
-        <v>-2410.39</v>
-      </c>
-      <c r="M27" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N27" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I27" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="49" t="n"/>
+      <c r="L27" s="49" t="n"/>
+      <c r="M27" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N27" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="48" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B28" s="50" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia vs Rosario Central</t>
+          <t>Vitória vs Mirassol</t>
         </is>
       </c>
       <c r="C28" s="48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D28" s="50" t="inlineStr">
@@ -20677,7 +21444,7 @@
         </is>
       </c>
       <c r="E28" s="49" t="n">
-        <v>2500</v>
+        <v>944.91</v>
       </c>
       <c r="F28" s="51" t="inlineStr">
         <is>
@@ -20685,7 +21452,7 @@
         </is>
       </c>
       <c r="G28" s="52" t="n">
-        <v>4375</v>
+        <v>1464.61</v>
       </c>
       <c r="H28" s="50" t="inlineStr">
         <is>
@@ -20701,10 +21468,10 @@
         </is>
       </c>
       <c r="K28" s="52" t="n">
-        <v>4375</v>
-      </c>
-      <c r="L28" s="54" t="n">
-        <v>0</v>
+        <v>3875</v>
+      </c>
+      <c r="L28" s="47" t="n">
+        <v>-2410.39</v>
       </c>
       <c r="M28" s="51" t="inlineStr">
         <is>
@@ -20720,35 +21487,35 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="43" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="B29" s="44" t="inlineStr">
         <is>
-          <t>Bahia vs Athletico Paranaense</t>
+          <t>Independiente Rivadavia vs Rosario Central</t>
         </is>
       </c>
       <c r="C29" s="43" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E29" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="49" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E29" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F29" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G29" s="52" t="n">
+        <v>4375</v>
+      </c>
       <c r="H29" s="44" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -20763,12 +21530,14 @@
         </is>
       </c>
       <c r="K29" s="52" t="n">
-        <v>8900</v>
-      </c>
-      <c r="L29" s="49" t="n"/>
-      <c r="M29" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4375</v>
+      </c>
+      <c r="L29" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
       <c r="N29" s="51" t="inlineStr">
@@ -20785,7 +21554,7 @@
       </c>
       <c r="B30" s="50" t="inlineStr">
         <is>
-          <t>Botafogo vs Mirassol</t>
+          <t>Bahia vs Athletico Paranaense</t>
         </is>
       </c>
       <c r="C30" s="48" t="inlineStr">
@@ -20823,7 +21592,7 @@
         </is>
       </c>
       <c r="K30" s="52" t="n">
-        <v>3775</v>
+        <v>8900</v>
       </c>
       <c r="L30" s="49" t="n"/>
       <c r="M30" s="48" t="inlineStr">
@@ -20845,7 +21614,7 @@
       </c>
       <c r="B31" s="44" t="inlineStr">
         <is>
-          <t>Coritiba vs Vasco da Gama</t>
+          <t>Botafogo vs Mirassol</t>
         </is>
       </c>
       <c r="C31" s="43" t="inlineStr">
@@ -20855,7 +21624,7 @@
       </c>
       <c r="D31" s="44" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E31" s="45" t="inlineStr">
@@ -20877,13 +21646,13 @@
       <c r="I31" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J31" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K31" s="47" t="n">
-        <v>-2500</v>
+      <c r="J31" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K31" s="52" t="n">
+        <v>3775</v>
       </c>
       <c r="L31" s="49" t="n"/>
       <c r="M31" s="43" t="inlineStr">
@@ -20891,9 +21660,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N31" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N31" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -20905,7 +21674,7 @@
       </c>
       <c r="B32" s="50" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Coritiba vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C32" s="48" t="inlineStr">
@@ -20915,7 +21684,7 @@
       </c>
       <c r="D32" s="50" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E32" s="49" t="inlineStr">
@@ -20937,13 +21706,13 @@
       <c r="I32" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J32" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K32" s="52" t="n">
-        <v>12075</v>
+      <c r="J32" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K32" s="47" t="n">
+        <v>-2500</v>
       </c>
       <c r="L32" s="49" t="n"/>
       <c r="M32" s="48" t="inlineStr">
@@ -20951,9 +21720,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N32" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N32" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -20965,7 +21734,7 @@
       </c>
       <c r="B33" s="44" t="inlineStr">
         <is>
-          <t>Internacional vs São Paulo</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C33" s="43" t="inlineStr">
@@ -20975,7 +21744,7 @@
       </c>
       <c r="D33" s="44" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E33" s="45" t="inlineStr">
@@ -20997,13 +21766,13 @@
       <c r="I33" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J33" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K33" s="47" t="n">
-        <v>-2500</v>
+      <c r="J33" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K33" s="52" t="n">
+        <v>12075</v>
       </c>
       <c r="L33" s="49" t="n"/>
       <c r="M33" s="43" t="inlineStr">
@@ -21011,26 +21780,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N33" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N33" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B34" s="50" t="inlineStr">
         <is>
-          <t>Barracas Central vs Sarmiento (junin)</t>
+          <t>Internacional vs São Paulo</t>
         </is>
       </c>
       <c r="C34" s="48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D34" s="50" t="inlineStr">
@@ -21080,22 +21849,22 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="43" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B35" s="44" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Barracas Central vs Sarmiento (junin)</t>
         </is>
       </c>
       <c r="C35" s="43" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D35" s="44" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E35" s="45" t="inlineStr">
@@ -21117,13 +21886,13 @@
       <c r="I35" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J35" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K35" s="52" t="n">
-        <v>12075</v>
+      <c r="J35" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K35" s="47" t="n">
+        <v>-2500</v>
       </c>
       <c r="L35" s="49" t="n"/>
       <c r="M35" s="43" t="inlineStr">
@@ -21131,21 +21900,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N35" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N35" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="48" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B36" s="50" t="inlineStr">
         <is>
-          <t>Palmeiras vs Grêmio</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C36" s="48" t="inlineStr">
@@ -21183,7 +21952,7 @@
         </is>
       </c>
       <c r="K36" s="52" t="n">
-        <v>12575</v>
+        <v>12075</v>
       </c>
       <c r="L36" s="49" t="n"/>
       <c r="M36" s="48" t="inlineStr">
@@ -21205,7 +21974,7 @@
       </c>
       <c r="B37" s="44" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino vs Flamengo</t>
+          <t>Palmeiras vs Grêmio</t>
         </is>
       </c>
       <c r="C37" s="43" t="inlineStr">
@@ -21243,7 +22012,7 @@
         </is>
       </c>
       <c r="K37" s="52" t="n">
-        <v>8550</v>
+        <v>12575</v>
       </c>
       <c r="L37" s="49" t="n"/>
       <c r="M37" s="43" t="inlineStr">
@@ -21265,7 +22034,7 @@
       </c>
       <c r="B38" s="50" t="inlineStr">
         <is>
-          <t>Santos vs Remo</t>
+          <t>Red Bull Bragantino vs Flamengo</t>
         </is>
       </c>
       <c r="C38" s="48" t="inlineStr">
@@ -21303,7 +22072,7 @@
         </is>
       </c>
       <c r="K38" s="52" t="n">
-        <v>12625</v>
+        <v>8550</v>
       </c>
       <c r="L38" s="49" t="n"/>
       <c r="M38" s="48" t="inlineStr">
@@ -21320,17 +22089,17 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="43" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B39" s="44" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
+          <t>Santos vs Remo</t>
         </is>
       </c>
       <c r="C39" s="43" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D39" s="44" t="inlineStr">
@@ -21363,7 +22132,7 @@
         </is>
       </c>
       <c r="K39" s="52" t="n">
-        <v>7750</v>
+        <v>12625</v>
       </c>
       <c r="L39" s="49" t="n"/>
       <c r="M39" s="43" t="inlineStr">
@@ -21380,17 +22149,17 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="48" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B40" s="50" t="inlineStr">
         <is>
-          <t>Palmeiras vs Gremio</t>
+          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
         </is>
       </c>
       <c r="C40" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D40" s="50" t="inlineStr">
@@ -21423,7 +22192,7 @@
         </is>
       </c>
       <c r="K40" s="52" t="n">
-        <v>13800</v>
+        <v>7750</v>
       </c>
       <c r="L40" s="49" t="n"/>
       <c r="M40" s="48" t="inlineStr">
@@ -21440,22 +22209,22 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="43" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B41" s="44" t="inlineStr">
         <is>
-          <t>Genclerbirligi vs Goztepe</t>
+          <t>Palmeiras vs Gremio</t>
         </is>
       </c>
       <c r="C41" s="43" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D41" s="44" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E41" s="45" t="inlineStr">
@@ -21477,13 +22246,13 @@
       <c r="I41" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J41" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K41" s="47" t="n">
-        <v>-2500</v>
+      <c r="J41" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K41" s="52" t="n">
+        <v>13800</v>
       </c>
       <c r="L41" s="49" t="n"/>
       <c r="M41" s="43" t="inlineStr">
@@ -21491,9 +22260,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N41" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N41" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -21505,17 +22274,17 @@
       </c>
       <c r="B42" s="50" t="inlineStr">
         <is>
-          <t>Independiente vs Racing Club</t>
+          <t>Genclerbirligi vs Goztepe</t>
         </is>
       </c>
       <c r="C42" s="48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D42" s="50" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E42" s="49" t="inlineStr">
@@ -21537,13 +22306,13 @@
       <c r="I42" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J42" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K42" s="52" t="n">
-        <v>11575</v>
+      <c r="J42" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K42" s="47" t="n">
+        <v>-2500</v>
       </c>
       <c r="L42" s="49" t="n"/>
       <c r="M42" s="48" t="inlineStr">
@@ -21551,9 +22320,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N42" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N42" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -21565,17 +22334,17 @@
       </c>
       <c r="B43" s="44" t="inlineStr">
         <is>
-          <t>Kasimpasa vs Kayserispor</t>
+          <t>Independiente vs Racing Club</t>
         </is>
       </c>
       <c r="C43" s="43" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D43" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.055&lt;0.080)</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E43" s="45" t="inlineStr">
@@ -21595,7 +22364,7 @@
         </is>
       </c>
       <c r="I43" s="45" t="n">
-        <v>2187.37</v>
+        <v>2500</v>
       </c>
       <c r="J43" s="51" t="inlineStr">
         <is>
@@ -21603,7 +22372,7 @@
         </is>
       </c>
       <c r="K43" s="52" t="n">
-        <v>2756.09</v>
+        <v>11575</v>
       </c>
       <c r="L43" s="49" t="n"/>
       <c r="M43" s="43" t="inlineStr">
@@ -21625,7 +22394,7 @@
       </c>
       <c r="B44" s="50" t="inlineStr">
         <is>
-          <t>Trabzonspor vs Galatasaray</t>
+          <t>Kasimpasa vs Kayserispor</t>
         </is>
       </c>
       <c r="C44" s="48" t="inlineStr">
@@ -21635,7 +22404,7 @@
       </c>
       <c r="D44" s="50" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.055&lt;0.080)</t>
         </is>
       </c>
       <c r="E44" s="49" t="inlineStr">
@@ -21655,7 +22424,7 @@
         </is>
       </c>
       <c r="I44" s="49" t="n">
-        <v>2500</v>
+        <v>2187.37</v>
       </c>
       <c r="J44" s="51" t="inlineStr">
         <is>
@@ -21663,7 +22432,7 @@
         </is>
       </c>
       <c r="K44" s="52" t="n">
-        <v>6050</v>
+        <v>2756.09</v>
       </c>
       <c r="L44" s="49" t="n"/>
       <c r="M44" s="48" t="inlineStr">
@@ -21680,12 +22449,12 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="43" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B45" s="44" t="inlineStr">
         <is>
-          <t>Antalyaspor vs Eyupspor</t>
+          <t>Trabzonspor vs Galatasaray</t>
         </is>
       </c>
       <c r="C45" s="43" t="inlineStr">
@@ -21695,7 +22464,7 @@
       </c>
       <c r="D45" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.077&lt;0.080)</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E45" s="45" t="inlineStr">
@@ -21723,7 +22492,7 @@
         </is>
       </c>
       <c r="K45" s="52" t="n">
-        <v>3025</v>
+        <v>6050</v>
       </c>
       <c r="L45" s="49" t="n"/>
       <c r="M45" s="43" t="inlineStr">
@@ -21745,17 +22514,17 @@
       </c>
       <c r="B46" s="50" t="inlineStr">
         <is>
-          <t>Bahia vs Palmeiras</t>
+          <t>Antalyaspor vs Eyupspor</t>
         </is>
       </c>
       <c r="C46" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D46" s="50" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.077&lt;0.080)</t>
         </is>
       </c>
       <c r="E46" s="49" t="inlineStr">
@@ -21777,13 +22546,13 @@
       <c r="I46" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J46" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K46" s="47" t="n">
-        <v>-2500</v>
+      <c r="J46" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K46" s="52" t="n">
+        <v>3025</v>
       </c>
       <c r="L46" s="49" t="n"/>
       <c r="M46" s="48" t="inlineStr">
@@ -21791,9 +22560,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N46" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N46" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -21805,12 +22574,12 @@
       </c>
       <c r="B47" s="44" t="inlineStr">
         <is>
-          <t>Central Córdoba (santiago del Estero) vs Newell's Old Boys</t>
+          <t>Bahia vs Palmeiras</t>
         </is>
       </c>
       <c r="C47" s="43" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D47" s="44" t="inlineStr">
@@ -21865,12 +22634,12 @@
       </c>
       <c r="B48" s="50" t="inlineStr">
         <is>
-          <t>Chapecoense vs Vitoria</t>
+          <t>Central Córdoba (santiago del Estero) vs Newell's Old Boys</t>
         </is>
       </c>
       <c r="C48" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D48" s="50" t="inlineStr">
@@ -21925,7 +22694,7 @@
       </c>
       <c r="B49" s="44" t="inlineStr">
         <is>
-          <t>Corinthians vs Internacional</t>
+          <t>Chapecoense vs Vitoria</t>
         </is>
       </c>
       <c r="C49" s="43" t="inlineStr">
@@ -21935,7 +22704,7 @@
       </c>
       <c r="D49" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.071&lt;0.080)</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E49" s="45" t="inlineStr">
@@ -21985,17 +22754,17 @@
       </c>
       <c r="B50" s="50" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük vs Caykur Rizespor</t>
+          <t>Corinthians vs Internacional</t>
         </is>
       </c>
       <c r="C50" s="48" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D50" s="50" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.071&lt;0.080)</t>
         </is>
       </c>
       <c r="E50" s="49" t="inlineStr">
@@ -22017,13 +22786,13 @@
       <c r="I50" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J50" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K50" s="52" t="n">
-        <v>5675</v>
+      <c r="J50" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K50" s="47" t="n">
+        <v>-2500</v>
       </c>
       <c r="L50" s="49" t="n"/>
       <c r="M50" s="48" t="inlineStr">
@@ -22031,9 +22800,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N50" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N50" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -22045,7 +22814,7 @@
       </c>
       <c r="B51" s="44" t="inlineStr">
         <is>
-          <t>Fenerbahce vs Besiktas</t>
+          <t>Fatih Karagümrük vs Caykur Rizespor</t>
         </is>
       </c>
       <c r="C51" s="43" t="inlineStr">
@@ -22083,7 +22852,7 @@
         </is>
       </c>
       <c r="K51" s="52" t="n">
-        <v>4225</v>
+        <v>5675</v>
       </c>
       <c r="L51" s="49" t="n"/>
       <c r="M51" s="43" t="inlineStr">
@@ -22105,17 +22874,17 @@
       </c>
       <c r="B52" s="50" t="inlineStr">
         <is>
-          <t>Mirassol vs Red Bull Bragantino</t>
+          <t>Fenerbahce vs Besiktas</t>
         </is>
       </c>
       <c r="C52" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D52" s="50" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E52" s="49" t="inlineStr">
@@ -22137,13 +22906,13 @@
       <c r="I52" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J52" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K52" s="47" t="n">
-        <v>-2500</v>
+      <c r="J52" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K52" s="52" t="n">
+        <v>4225</v>
       </c>
       <c r="L52" s="49" t="n"/>
       <c r="M52" s="48" t="inlineStr">
@@ -22151,9 +22920,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N52" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N52" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -22165,12 +22934,12 @@
       </c>
       <c r="B53" s="44" t="inlineStr">
         <is>
-          <t>Samsunspor vs Konyaspor</t>
+          <t>Mirassol vs Red Bull Bragantino</t>
         </is>
       </c>
       <c r="C53" s="43" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D53" s="44" t="inlineStr">
@@ -22220,22 +22989,22 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="48" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B54" s="50" t="inlineStr">
         <is>
-          <t>Vasco da Gama vs Botafogo</t>
+          <t>Samsunspor vs Konyaspor</t>
         </is>
       </c>
       <c r="C54" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D54" s="50" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E54" s="49" t="inlineStr">
@@ -22251,19 +23020,19 @@
       <c r="G54" s="49" t="n"/>
       <c r="H54" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I54" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J54" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K54" s="52" t="n">
-        <v>7200</v>
+      <c r="J54" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K54" s="47" t="n">
+        <v>-2500</v>
       </c>
       <c r="L54" s="49" t="n"/>
       <c r="M54" s="48" t="inlineStr">
@@ -22271,31 +23040,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N54" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N54" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="43" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B55" s="44" t="inlineStr">
         <is>
-          <t>Hamkam vs Sk Brann</t>
+          <t>Vasco da Gama vs Botafogo</t>
         </is>
       </c>
       <c r="C55" s="43" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>[PERDIDA] LOCAL</t>
+          <t>[GANADA] VISITA</t>
         </is>
       </c>
       <c r="E55" s="45" t="inlineStr">
@@ -22311,19 +23080,19 @@
       <c r="G55" s="49" t="n"/>
       <c r="H55" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I55" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J55" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K55" s="47" t="n">
-        <v>-2500</v>
+      <c r="J55" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K55" s="52" t="n">
+        <v>7200</v>
       </c>
       <c r="L55" s="49" t="n"/>
       <c r="M55" s="43" t="inlineStr">
@@ -22331,9 +23100,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N55" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N55" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
@@ -22345,7 +23114,7 @@
       </c>
       <c r="B56" s="50" t="inlineStr">
         <is>
-          <t>Molde vs Lillestrom</t>
+          <t>Hamkam vs Sk Brann</t>
         </is>
       </c>
       <c r="C56" s="48" t="inlineStr">
@@ -22355,7 +23124,7 @@
       </c>
       <c r="D56" s="50" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[PERDIDA] LOCAL</t>
         </is>
       </c>
       <c r="E56" s="49" t="inlineStr">
@@ -22371,19 +23140,19 @@
       <c r="G56" s="49" t="n"/>
       <c r="H56" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I56" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J56" s="51" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K56" s="52" t="n">
-        <v>5175</v>
+      <c r="J56" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K56" s="47" t="n">
+        <v>-2500</v>
       </c>
       <c r="L56" s="49" t="n"/>
       <c r="M56" s="48" t="inlineStr">
@@ -22391,9 +23160,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N56" s="51" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N56" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -22405,7 +23174,7 @@
       </c>
       <c r="B57" s="44" t="inlineStr">
         <is>
-          <t>Sarpsborg fk vs Ik Start</t>
+          <t>Molde vs Lillestrom</t>
         </is>
       </c>
       <c r="C57" s="43" t="inlineStr">
@@ -22415,7 +23184,7 @@
       </c>
       <c r="D57" s="44" t="inlineStr">
         <is>
-          <t>[PERDIDA] VISITA</t>
+          <t>[GANADA] VISITA</t>
         </is>
       </c>
       <c r="E57" s="45" t="inlineStr">
@@ -22437,13 +23206,13 @@
       <c r="I57" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J57" s="46" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K57" s="47" t="n">
-        <v>-2500</v>
+      <c r="J57" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K57" s="52" t="n">
+        <v>5175</v>
       </c>
       <c r="L57" s="49" t="n"/>
       <c r="M57" s="43" t="inlineStr">
@@ -22451,21 +23220,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N57" s="46" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N57" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="48" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B58" s="50" t="inlineStr">
         <is>
-          <t>Kfum Oslo vs Sandefjord</t>
+          <t>Sarpsborg fk vs Ik Start</t>
         </is>
       </c>
       <c r="C58" s="48" t="inlineStr">
@@ -22475,15 +23244,17 @@
       </c>
       <c r="D58" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E58" s="49" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F58" s="53" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[PERDIDA] VISITA</t>
+        </is>
+      </c>
+      <c r="E58" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G58" s="49" t="n"/>
@@ -22495,99 +23266,105 @@
       <c r="I58" s="49" t="n">
         <v>2500</v>
       </c>
-      <c r="J58" s="53" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K58" s="49" t="n"/>
+      <c r="J58" s="46" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K58" s="47" t="n">
+        <v>-2500</v>
+      </c>
       <c r="L58" s="49" t="n"/>
       <c r="M58" s="48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N58" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N58" s="46" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="43" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B59" s="44" t="inlineStr">
         <is>
-          <t>Goztepe vs Galatasaray</t>
+          <t>Kfum Oslo vs Sandefjord</t>
         </is>
       </c>
       <c r="C59" s="43" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D59" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E59" s="45" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F59" s="53" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] VISITA</t>
+        </is>
+      </c>
+      <c r="E59" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G59" s="49" t="n"/>
       <c r="H59" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I59" s="45" t="n">
         <v>2500</v>
       </c>
-      <c r="J59" s="53" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K59" s="49" t="n"/>
+      <c r="J59" s="51" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K59" s="52" t="n">
+        <v>5900</v>
+      </c>
       <c r="L59" s="49" t="n"/>
       <c r="M59" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N59" s="43" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N59" s="51" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="48" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B60" s="50" t="inlineStr">
         <is>
-          <t>West Ham United vs Wolverhampton Wanderers</t>
+          <t>Goztepe vs Galatasaray</t>
         </is>
       </c>
       <c r="C60" s="48" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D60" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E60" s="49" t="n">
@@ -22601,13 +23378,11 @@
       <c r="G60" s="49" t="n"/>
       <c r="H60" s="50" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I60" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I60" s="49" t="n">
+        <v>2500</v>
       </c>
       <c r="J60" s="53" t="inlineStr">
         <is>
@@ -22630,26 +23405,28 @@
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="43" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B61" s="44" t="inlineStr">
         <is>
-          <t>Boca Juniors vs Independiente</t>
+          <t>Caykur Rizespor vs Samsunspor</t>
         </is>
       </c>
       <c r="C61" s="43" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D61" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E61" s="45" t="n">
-        <v>1443.38</v>
+          <t>[PASAR] EV Insuf (0.060&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E61" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="53" t="inlineStr">
         <is>
@@ -22686,26 +23463,26 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="48" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B62" s="50" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs Instituto (córdoba)</t>
+          <t>West Ham United vs Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="C62" s="48" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D62" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E62" s="49" t="n">
-        <v>1443.38</v>
+        <v>2500</v>
       </c>
       <c r="F62" s="53" t="inlineStr">
         <is>
@@ -22715,11 +23492,13 @@
       <c r="G62" s="49" t="n"/>
       <c r="H62" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I62" s="49" t="n">
-        <v>2500</v>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I62" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="53" t="inlineStr">
         <is>
@@ -22747,12 +23526,12 @@
       </c>
       <c r="B63" s="44" t="inlineStr">
         <is>
-          <t>Estudiantes de la Plata vs Union (santa Fe)</t>
+          <t>Alanyaspor vs Trabzonspor</t>
         </is>
       </c>
       <c r="C63" s="43" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D63" s="44" t="inlineStr">
@@ -22761,7 +23540,7 @@
         </is>
       </c>
       <c r="E63" s="45" t="n">
-        <v>1443.38</v>
+        <v>1767.77</v>
       </c>
       <c r="F63" s="53" t="inlineStr">
         <is>
@@ -22771,13 +23550,11 @@
       <c r="G63" s="49" t="n"/>
       <c r="H63" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Shadow-Floor (33%&lt;33%)</t>
-        </is>
-      </c>
-      <c r="I63" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I63" s="45" t="n">
+        <v>2500</v>
       </c>
       <c r="J63" s="53" t="inlineStr">
         <is>
@@ -22805,21 +23582,21 @@
       </c>
       <c r="B64" s="50" t="inlineStr">
         <is>
-          <t>Fluminense vs Flamengo</t>
+          <t>Boca Juniors vs Independiente</t>
         </is>
       </c>
       <c r="C64" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D64" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E64" s="49" t="n">
-        <v>1118.03</v>
+        <v>1767.77</v>
       </c>
       <c r="F64" s="53" t="inlineStr">
         <is>
@@ -22829,7 +23606,7 @@
       <c r="G64" s="49" t="n"/>
       <c r="H64" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I64" s="49" t="n">
@@ -22861,21 +23638,21 @@
       </c>
       <c r="B65" s="44" t="inlineStr">
         <is>
-          <t>Internacional vs Gremio</t>
+          <t>Deportivo Riestra vs Instituto (córdoba)</t>
         </is>
       </c>
       <c r="C65" s="43" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D65" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E65" s="45" t="n">
-        <v>1118.03</v>
+        <v>1767.77</v>
       </c>
       <c r="F65" s="53" t="inlineStr">
         <is>
@@ -22885,7 +23662,7 @@
       <c r="G65" s="49" t="n"/>
       <c r="H65" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I65" s="45" t="n">
@@ -22917,7 +23694,7 @@
       </c>
       <c r="B66" s="50" t="inlineStr">
         <is>
-          <t>Mirassol vs Bahia</t>
+          <t>Fluminense vs Flamengo</t>
         </is>
       </c>
       <c r="C66" s="48" t="inlineStr">
@@ -22927,13 +23704,11 @@
       </c>
       <c r="D66" s="50" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.070&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="E66" s="49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E66" s="49" t="n">
+        <v>1118.03</v>
       </c>
       <c r="F66" s="53" t="inlineStr">
         <is>
@@ -22943,7 +23718,7 @@
       <c r="G66" s="49" t="n"/>
       <c r="H66" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I66" s="49" t="n">
@@ -22975,7 +23750,7 @@
       </c>
       <c r="B67" s="44" t="inlineStr">
         <is>
-          <t>Remo vs Vasco da Gama</t>
+          <t>Internacional vs Gremio</t>
         </is>
       </c>
       <c r="C67" s="43" t="inlineStr">
@@ -22985,7 +23760,7 @@
       </c>
       <c r="D67" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E67" s="45" t="n">
@@ -22999,7 +23774,7 @@
       <c r="G67" s="49" t="n"/>
       <c r="H67" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I67" s="45" t="n">
@@ -23031,21 +23806,21 @@
       </c>
       <c r="B68" s="50" t="inlineStr">
         <is>
-          <t>Santos vs Atlético-mg</t>
+          <t>Kayserispor vs Fenerbahce</t>
         </is>
       </c>
       <c r="C68" s="48" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D68" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E68" s="49" t="n">
-        <v>1118.03</v>
+        <v>1767.77</v>
       </c>
       <c r="F68" s="53" t="inlineStr">
         <is>
@@ -23055,7 +23830,7 @@
       <c r="G68" s="49" t="n"/>
       <c r="H68" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I68" s="49" t="n">
@@ -23087,21 +23862,23 @@
       </c>
       <c r="B69" s="44" t="inlineStr">
         <is>
-          <t>Viking fk vs Bodo/glimt</t>
+          <t>Mirassol vs Bahia</t>
         </is>
       </c>
       <c r="C69" s="43" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D69" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E69" s="45" t="n">
-        <v>2500</v>
+          <t>[PASAR] EV Insuf (0.075&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E69" s="45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" s="53" t="inlineStr">
         <is>
@@ -23111,7 +23888,7 @@
       <c r="G69" s="49" t="n"/>
       <c r="H69" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I69" s="45" t="n">
@@ -23143,7 +23920,7 @@
       </c>
       <c r="B70" s="50" t="inlineStr">
         <is>
-          <t>Vitoria vs Sao Paulo</t>
+          <t>Remo vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C70" s="48" t="inlineStr">
@@ -23194,12 +23971,12 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="43" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="44" t="inlineStr">
         <is>
-          <t>Botafogo vs Coritiba</t>
+          <t>Santos vs Atlético-mg</t>
         </is>
       </c>
       <c r="C71" s="43" t="inlineStr">
@@ -23213,7 +23990,7 @@
         </is>
       </c>
       <c r="E71" s="45" t="n">
-        <v>1443.38</v>
+        <v>1118.03</v>
       </c>
       <c r="F71" s="53" t="inlineStr">
         <is>
@@ -23223,13 +24000,11 @@
       <c r="G71" s="49" t="n"/>
       <c r="H71" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I71" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I71" s="45" t="n">
+        <v>2500</v>
       </c>
       <c r="J71" s="53" t="inlineStr">
         <is>
@@ -23252,17 +24027,17 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="48" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B72" s="50" t="inlineStr">
         <is>
-          <t>Chelsea vs Manchester City</t>
+          <t>Viking fk vs Bodo/glimt</t>
         </is>
       </c>
       <c r="C72" s="48" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D72" s="50" t="inlineStr">
@@ -23271,7 +24046,7 @@
         </is>
       </c>
       <c r="E72" s="49" t="n">
-        <v>1443.38</v>
+        <v>2500</v>
       </c>
       <c r="F72" s="53" t="inlineStr">
         <is>
@@ -23308,12 +24083,12 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="43" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B73" s="44" t="inlineStr">
         <is>
-          <t>Corinthians vs Palmeiras</t>
+          <t>Vitoria vs Sao Paulo</t>
         </is>
       </c>
       <c r="C73" s="43" t="inlineStr">
@@ -23323,11 +24098,11 @@
       </c>
       <c r="D73" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E73" s="45" t="n">
-        <v>1443.38</v>
+        <v>1118.03</v>
       </c>
       <c r="F73" s="53" t="inlineStr">
         <is>
@@ -23337,7 +24112,7 @@
       <c r="G73" s="49" t="n"/>
       <c r="H73" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I73" s="45" t="n">
@@ -23369,7 +24144,7 @@
       </c>
       <c r="B74" s="50" t="inlineStr">
         <is>
-          <t>Cruzeiro vs Red Bull Bragantino</t>
+          <t>Botafogo vs Coritiba</t>
         </is>
       </c>
       <c r="C74" s="48" t="inlineStr">
@@ -23393,11 +24168,13 @@
       <c r="G74" s="49" t="n"/>
       <c r="H74" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I74" s="49" t="n">
-        <v>2500</v>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I74" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="53" t="inlineStr">
         <is>
@@ -23425,7 +24202,7 @@
       </c>
       <c r="B75" s="44" t="inlineStr">
         <is>
-          <t>Crystal Palace vs Newcastle United</t>
+          <t>Chelsea vs Manchester City</t>
         </is>
       </c>
       <c r="C75" s="43" t="inlineStr">
@@ -23435,11 +24212,11 @@
       </c>
       <c r="D75" s="44" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E75" s="45" t="n">
-        <v>1443.38</v>
+        <v>1767.77</v>
       </c>
       <c r="F75" s="53" t="inlineStr">
         <is>
@@ -23449,13 +24226,11 @@
       <c r="G75" s="49" t="n"/>
       <c r="H75" s="44" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I75" s="45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I75" s="45" t="n">
+        <v>2500</v>
       </c>
       <c r="J75" s="53" t="inlineStr">
         <is>
@@ -23483,17 +24258,17 @@
       </c>
       <c r="B76" s="50" t="inlineStr">
         <is>
-          <t>Nottingham Forest vs Aston Villa</t>
+          <t>Corinthians vs Palmeiras</t>
         </is>
       </c>
       <c r="C76" s="48" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D76" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E76" s="49" t="n">
@@ -23507,7 +24282,7 @@
       <c r="G76" s="49" t="n"/>
       <c r="H76" s="50" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I76" s="49" t="n">
@@ -23539,12 +24314,12 @@
       </c>
       <c r="B77" s="44" t="inlineStr">
         <is>
-          <t>Rosenborg vs Sarpsborg fk</t>
+          <t>Cruzeiro vs Red Bull Bragantino</t>
         </is>
       </c>
       <c r="C77" s="43" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D77" s="44" t="inlineStr">
@@ -23553,7 +24328,7 @@
         </is>
       </c>
       <c r="E77" s="45" t="n">
-        <v>2500</v>
+        <v>1443.38</v>
       </c>
       <c r="F77" s="53" t="inlineStr">
         <is>
@@ -23587,181 +24362,467 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="A79" s="55" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="48" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="50" t="inlineStr">
+        <is>
+          <t>Fredrikstad vs Valerenga</t>
+        </is>
+      </c>
+      <c r="C78" s="48" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="D78" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E78" s="49" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F78" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G78" s="49" t="n"/>
+      <c r="H78" s="50" t="inlineStr">
+        <is>
+          <t>[PASAR] Shadow-EV (0.049&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="I78" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K78" s="49" t="n"/>
+      <c r="L78" s="49" t="n"/>
+      <c r="M78" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="43" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="44" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C79" s="43" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="D79" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E79" s="45" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F79" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G79" s="49" t="n"/>
+      <c r="H79" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I79" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J79" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K79" s="49" t="n"/>
+      <c r="L79" s="49" t="n"/>
+      <c r="M79" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="48" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="50" t="inlineStr">
+        <is>
+          <t>Rosenborg vs Sarpsborg fk</t>
+        </is>
+      </c>
+      <c r="C80" s="48" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="D80" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E80" s="49" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F80" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G80" s="49" t="n"/>
+      <c r="H80" s="50" t="inlineStr">
+        <is>
+          <t>[PASAR] Shadow-EV (0.038&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="I80" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K80" s="49" t="n"/>
+      <c r="L80" s="49" t="n"/>
+      <c r="M80" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="43" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="44" t="inlineStr">
+        <is>
+          <t>Lanus vs Banfield</t>
+        </is>
+      </c>
+      <c r="C81" s="43" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D81" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E81" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F81" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G81" s="49" t="n"/>
+      <c r="H81" s="44" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I81" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J81" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K81" s="49" t="n"/>
+      <c r="L81" s="49" t="n"/>
+      <c r="M81" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="48" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="50" t="inlineStr">
+        <is>
+          <t>Sarmiento (junin) vs Gimnasia la Plata</t>
+        </is>
+      </c>
+      <c r="C82" s="48" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D82" s="50" t="inlineStr">
+        <is>
+          <t>[PASAR] EV Insuf (0.059&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E82" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G82" s="49" t="n"/>
+      <c r="H82" s="50" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I82" s="49" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J82" s="53" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K82" s="49" t="n"/>
+      <c r="L82" s="49" t="n"/>
+      <c r="M82" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="55" t="inlineStr">
         <is>
           <t>RESUMEN COMPARATIVO DE RENDIMIENTO</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="39" t="inlineStr">
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="39" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B80" s="40" t="inlineStr">
+      <c r="B85" s="40" t="inlineStr">
         <is>
           <t>Opcion 1 (Activa)</t>
         </is>
       </c>
-      <c r="D80" s="41" t="inlineStr">
+      <c r="D85" s="41" t="inlineStr">
         <is>
           <t>Opcion 4 (Shadow)</t>
         </is>
       </c>
-      <c r="F80" s="42" t="inlineStr">
+      <c r="F85" s="42" t="inlineStr">
         <is>
           <t>Mejor</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="56" t="inlineStr">
-        <is>
-          <t>N apuestas liquidadas</t>
-        </is>
-      </c>
-      <c r="B81" s="57" t="n">
-        <v>23</v>
-      </c>
-      <c r="C81" s="57" t="n">
-        <v>23</v>
-      </c>
-      <c r="D81" s="57" t="n">
-        <v>42</v>
-      </c>
-      <c r="E81" s="57" t="n">
-        <v>42</v>
-      </c>
-      <c r="F81" s="58" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="56" t="inlineStr">
-        <is>
-          <t>Ganadas</t>
-        </is>
-      </c>
-      <c r="B82" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="C82" s="59" t="n">
-        <v>12</v>
-      </c>
-      <c r="D82" s="60" t="n">
-        <v>25</v>
-      </c>
-      <c r="E82" s="60" t="n">
-        <v>25</v>
-      </c>
-      <c r="F82" s="61" t="inlineStr">
-        <is>
-          <t>Op4</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" s="56" t="inlineStr">
-        <is>
-          <t>Hit rate</t>
-        </is>
-      </c>
-      <c r="B83" s="62" t="n">
-        <v>0.5217391304347826</v>
-      </c>
-      <c r="C83" s="62" t="n">
-        <v>0.5217391304347826</v>
-      </c>
-      <c r="D83" s="63" t="n">
-        <v>0.5952380952380952</v>
-      </c>
-      <c r="E83" s="63" t="n">
-        <v>0.5952380952380952</v>
-      </c>
-      <c r="F83" s="61" t="inlineStr">
-        <is>
-          <t>Op4</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" s="56" t="inlineStr">
-        <is>
-          <t>Volumen apostado</t>
-        </is>
-      </c>
-      <c r="B84" s="54" t="n">
-        <v>37220.99000000001</v>
-      </c>
-      <c r="C84" s="54" t="n">
-        <v>37220.99000000001</v>
-      </c>
-      <c r="D84" s="54" t="n">
-        <v>104687.37</v>
-      </c>
-      <c r="E84" s="54" t="n">
-        <v>104687.37</v>
-      </c>
-      <c r="F84" s="58" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="56" t="inlineStr">
-        <is>
-          <t>P/L neto</t>
-        </is>
-      </c>
-      <c r="B85" s="47" t="n">
-        <v>32933.43000000001</v>
-      </c>
-      <c r="C85" s="47" t="n">
-        <v>32933.43000000001</v>
-      </c>
-      <c r="D85" s="52" t="n">
-        <v>140506.09</v>
-      </c>
-      <c r="E85" s="52" t="n">
-        <v>140506.09</v>
-      </c>
-      <c r="F85" s="61" t="inlineStr">
-        <is>
-          <t>Op4</t>
         </is>
       </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="56" t="inlineStr">
         <is>
+          <t>N apuestas liquidadas</t>
+        </is>
+      </c>
+      <c r="B86" s="57" t="n">
+        <v>23</v>
+      </c>
+      <c r="C86" s="57" t="n">
+        <v>23</v>
+      </c>
+      <c r="D86" s="57" t="n">
+        <v>43</v>
+      </c>
+      <c r="E86" s="57" t="n">
+        <v>43</v>
+      </c>
+      <c r="F86" s="58" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="56" t="inlineStr">
+        <is>
+          <t>Ganadas</t>
+        </is>
+      </c>
+      <c r="B87" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="C87" s="59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D87" s="60" t="n">
+        <v>26</v>
+      </c>
+      <c r="E87" s="60" t="n">
+        <v>26</v>
+      </c>
+      <c r="F87" s="61" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="56" t="inlineStr">
+        <is>
+          <t>Hit rate</t>
+        </is>
+      </c>
+      <c r="B88" s="62" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="C88" s="62" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="D88" s="63" t="n">
+        <v>0.6046511627906976</v>
+      </c>
+      <c r="E88" s="63" t="n">
+        <v>0.6046511627906976</v>
+      </c>
+      <c r="F88" s="61" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="56" t="inlineStr">
+        <is>
+          <t>Volumen apostado</t>
+        </is>
+      </c>
+      <c r="B89" s="54" t="n">
+        <v>37220.99000000001</v>
+      </c>
+      <c r="C89" s="54" t="n">
+        <v>37220.99000000001</v>
+      </c>
+      <c r="D89" s="54" t="n">
+        <v>107187.37</v>
+      </c>
+      <c r="E89" s="54" t="n">
+        <v>107187.37</v>
+      </c>
+      <c r="F89" s="58" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="17" customHeight="1">
+      <c r="A90" s="56" t="inlineStr">
+        <is>
+          <t>P/L neto</t>
+        </is>
+      </c>
+      <c r="B90" s="47" t="n">
+        <v>32933.43000000001</v>
+      </c>
+      <c r="C90" s="47" t="n">
+        <v>32933.43000000001</v>
+      </c>
+      <c r="D90" s="52" t="n">
+        <v>146406.09</v>
+      </c>
+      <c r="E90" s="52" t="n">
+        <v>146406.09</v>
+      </c>
+      <c r="F90" s="61" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="17" customHeight="1">
+      <c r="A91" s="56" t="inlineStr">
+        <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="B86" s="62" t="n">
+      <c r="B91" s="62" t="n">
         <v>0.8848080075247865</v>
       </c>
-      <c r="C86" s="62" t="n">
+      <c r="C91" s="62" t="n">
         <v>0.8848080075247865</v>
       </c>
-      <c r="D86" s="63" t="n">
-        <v>1.34214939204223</v>
-      </c>
-      <c r="E86" s="63" t="n">
-        <v>1.34214939204223</v>
-      </c>
-      <c r="F86" s="61" t="inlineStr">
+      <c r="D91" s="63" t="n">
+        <v>1.365889376705483</v>
+      </c>
+      <c r="E91" s="63" t="n">
+        <v>1.365889376705483</v>
+      </c>
+      <c r="F91" s="61" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="64" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="64" t="inlineStr">
         <is>
           <t>Verde = celda ganadora en ese KPI / partido   |   Rojo = celda perdedora   |   Amarillo en Resultado = pendiente de liquidar   |   Op1 activa desde V4.3: empates bloqueados + xG Margen O/U + Camino 2B (desacuerdo) + Camino 3 (alta conv.)</t>
         </is>
@@ -23769,12 +24830,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A79:N79"/>
     <mergeCell ref="D3:G3"/>
-    <mergeCell ref="A88:N88"/>
     <mergeCell ref="H3:K3"/>
+    <mergeCell ref="A84:N84"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A93:N93"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -23934,25 +24995,25 @@
         </is>
       </c>
       <c r="B5" s="65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" s="65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="65" t="n">
         <v>6</v>
       </c>
       <c r="E5" s="66" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="F5" s="67" t="n">
-        <v>-475</v>
+        <v>5425</v>
       </c>
       <c r="G5" s="66" t="n">
-        <v>-0.038</v>
+        <v>0.3616666666666667</v>
       </c>
       <c r="H5" s="67" t="n">
-        <v>12500</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="6">
@@ -23990,31 +25051,31 @@
         </is>
       </c>
       <c r="B7" s="68" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C7" s="68" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="68" t="n">
         <v>24</v>
       </c>
       <c r="E7" s="69" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="F7" s="70" t="n">
-        <v>90015.92999999999</v>
+        <v>95915.92999999999</v>
       </c>
       <c r="G7" s="69" t="n">
-        <v>1.117647558316291</v>
+        <v>1.155049548696281</v>
       </c>
       <c r="H7" s="70" t="n">
-        <v>80540.53</v>
+        <v>83040.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="71" t="inlineStr">
         <is>
-          <t>Generado: 06/04/2026 23:37</t>
+          <t>Generado: 08/04/2026 13:30</t>
         </is>
       </c>
     </row>

--- a/Backtest_Modelo.xlsx
+++ b/Backtest_Modelo.xlsx
@@ -235,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -390,10 +390,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -423,13 +423,10 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -908,7 +905,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado: 10/04/2026 12:31   |   Bankroll: $100,000.00</t>
+          <t>Generado: 10/04/2026 12:43   |   Bankroll: $100,000.00</t>
         </is>
       </c>
     </row>
@@ -948,13 +945,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>72022.7663</v>
+        <v>91774.9134</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>81812.7885</v>
+        <v>98604.0658</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-9790.022199999999</v>
+        <v>-6829.152399999999</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -964,13 +961,13 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>0.6443325098623282</v>
+        <v>0.8210398368636365</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>1.694284681483887</v>
+        <v>1.42828764642966</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>-0.1541945338397958</v>
+        <v>-0.1597749584018836</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -983,10 +980,10 @@
         <v>111778.88</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>48287.51</v>
+        <v>69036.56</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>63491.37</v>
+        <v>42742.32</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -999,10 +996,10 @@
         <v>74</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
@@ -1037,13 +1034,13 @@
         </is>
       </c>
       <c r="B11" s="14" t="n">
-        <v>0.5</v>
+        <v>0.527027027027027</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6170212765957447</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.3703703703703703</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -1053,13 +1050,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>0.6369047619047619</v>
+        <v>0.6504182754182755</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.7317323481116584</v>
+        <v>0.6954154002026343</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.3703703703703703</v>
       </c>
     </row>
     <row r="13" ht="14" customHeight="1">
@@ -1076,13 +1073,13 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>2.8718</v>
+        <v>3.6866</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>4.5307</v>
+        <v>4.5103</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.9881</v>
+        <v>-0.4857</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -1092,13 +1089,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>0.0041</v>
+        <v>0.0002</v>
       </c>
       <c r="C15" s="17" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>0.3231</v>
+        <v>0.6272</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -4026,20 +4023,20 @@
       <c r="R25" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T25" s="31">
-        <f>IF(OR(Q25="",R25=""),"[APOSTAR] OVER 2.5",IF((Q25+R25)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S25" s="31">
+        <f>IF(OR(Q25="",R25=""),"[APOSTAR] VISITA",IF(Q25&lt;R25,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T25" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U25" s="35" t="n">
-        <v>0</v>
+        <v>1020.62</v>
       </c>
       <c r="V25" s="35" t="n">
-        <v>1020.62</v>
+        <v>0</v>
       </c>
       <c r="W25" s="31">
         <f>IF(L25="","",IF((MAX(L25,M25,N25)-MEDIAN(L25,M25,N25))&gt;0.05,IF(OR(Q25="",R25=""),"[PREDICCION] "&amp;IF(L25=MAX(L25,M25,N25),"LOCAL",IF(M25=MAX(L25,M25,N25),"EMPATE","VISITA")),IF(L25=MAX(L25,M25,N25),IF(Q25&gt;R25,"[ACIERTO]","[FALLO]"),IF(M25=MAX(L25,M25,N25),IF(Q25=R25,"[ACIERTO]","[FALLO]"),IF(Q25&lt;R25,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -4244,20 +4241,20 @@
       <c r="R27" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="S27" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T27" s="31">
-        <f>IF(OR(Q27="",R27=""),"[APOSTAR] OVER 2.5",IF((Q27+R27)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S27" s="31">
+        <f>IF(OR(Q27="",R27=""),"[APOSTAR] LOCAL",IF(Q27&gt;R27,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T27" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U27" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V27" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W27" s="31">
         <f>IF(L27="","",IF((MAX(L27,M27,N27)-MEDIAN(L27,M27,N27))&gt;0.05,IF(OR(Q27="",R27=""),"[PREDICCION] "&amp;IF(L27=MAX(L27,M27,N27),"LOCAL",IF(M27=MAX(L27,M27,N27),"EMPATE","VISITA")),IF(L27=MAX(L27,M27,N27),IF(Q27&gt;R27,"[ACIERTO]","[FALLO]"),IF(M27=MAX(L27,M27,N27),IF(Q27=R27,"[ACIERTO]","[FALLO]"),IF(Q27&lt;R27,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -4353,20 +4350,20 @@
       <c r="R28" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T28" s="31">
-        <f>IF(OR(Q28="",R28=""),"[APOSTAR] OVER 2.5",IF((Q28+R28)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S28" s="31">
+        <f>IF(OR(Q28="",R28=""),"[APOSTAR] LOCAL",IF(Q28&gt;R28,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T28" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U28" s="35" t="n">
-        <v>0</v>
+        <v>1020.62</v>
       </c>
       <c r="V28" s="35" t="n">
-        <v>1020.62</v>
+        <v>0</v>
       </c>
       <c r="W28" s="31">
         <f>IF(L28="","",IF((MAX(L28,M28,N28)-MEDIAN(L28,M28,N28))&gt;0.05,IF(OR(Q28="",R28=""),"[PREDICCION] "&amp;IF(L28=MAX(L28,M28,N28),"LOCAL",IF(M28=MAX(L28,M28,N28),"EMPATE","VISITA")),IF(L28=MAX(L28,M28,N28),IF(Q28&gt;R28,"[ACIERTO]","[FALLO]"),IF(M28=MAX(L28,M28,N28),IF(Q28=R28,"[ACIERTO]","[FALLO]"),IF(Q28&lt;R28,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -4462,20 +4459,20 @@
       <c r="R29" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T29" s="31">
-        <f>IF(OR(Q29="",R29=""),"[APOSTAR] OVER 2.5",IF((Q29+R29)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S29" s="31">
+        <f>IF(OR(Q29="",R29=""),"[APOSTAR] LOCAL",IF(Q29&gt;R29,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T29" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U29" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V29" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W29" s="31">
         <f>IF(L29="","",IF((MAX(L29,M29,N29)-MEDIAN(L29,M29,N29))&gt;0.05,IF(OR(Q29="",R29=""),"[PREDICCION] "&amp;IF(L29=MAX(L29,M29,N29),"LOCAL",IF(M29=MAX(L29,M29,N29),"EMPATE","VISITA")),IF(L29=MAX(L29,M29,N29),IF(Q29&gt;R29,"[ACIERTO]","[FALLO]"),IF(M29=MAX(L29,M29,N29),IF(Q29=R29,"[ACIERTO]","[FALLO]"),IF(Q29&lt;R29,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -5225,20 +5222,20 @@
       <c r="R36" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="S36" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T36" s="31">
-        <f>IF(OR(Q36="",R36=""),"[APOSTAR] OVER 2.5",IF((Q36+R36)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S36" s="31">
+        <f>IF(OR(Q36="",R36=""),"[APOSTAR] VISITA",IF(Q36&lt;R36,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T36" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U36" s="35" t="n">
-        <v>0</v>
+        <v>1767.77</v>
       </c>
       <c r="V36" s="35" t="n">
-        <v>1767.77</v>
+        <v>0</v>
       </c>
       <c r="W36" s="31">
         <f>IF(L36="","",IF((MAX(L36,M36,N36)-MEDIAN(L36,M36,N36))&gt;0.05,IF(OR(Q36="",R36=""),"[PREDICCION] "&amp;IF(L36=MAX(L36,M36,N36),"LOCAL",IF(M36=MAX(L36,M36,N36),"EMPATE","VISITA")),IF(L36=MAX(L36,M36,N36),IF(Q36&gt;R36,"[ACIERTO]","[FALLO]"),IF(M36=MAX(L36,M36,N36),IF(Q36=R36,"[ACIERTO]","[FALLO]"),IF(Q36&lt;R36,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -5449,7 +5446,7 @@
       </c>
       <c r="T38" s="31" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (1X2 Priorizado)</t>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
         </is>
       </c>
       <c r="U38" s="35" t="n">
@@ -5661,20 +5658,20 @@
       <c r="R40" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T40" s="31">
-        <f>IF(OR(Q40="",R40=""),"[APOSTAR] OVER 2.5",IF((Q40+R40)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S40" s="31">
+        <f>IF(OR(Q40="",R40=""),"[APOSTAR] VISITA",IF(Q40&lt;R40,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T40" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U40" s="35" t="n">
-        <v>0</v>
+        <v>883.88</v>
       </c>
       <c r="V40" s="35" t="n">
-        <v>883.88</v>
+        <v>0</v>
       </c>
       <c r="W40" s="31">
         <f>IF(L40="","",IF((MAX(L40,M40,N40)-MEDIAN(L40,M40,N40))&gt;0.05,IF(OR(Q40="",R40=""),"[PREDICCION] "&amp;IF(L40=MAX(L40,M40,N40),"LOCAL",IF(M40=MAX(L40,M40,N40),"EMPATE","VISITA")),IF(L40=MAX(L40,M40,N40),IF(Q40&gt;R40,"[ACIERTO]","[FALLO]"),IF(M40=MAX(L40,M40,N40),IF(Q40=R40,"[ACIERTO]","[FALLO]"),IF(Q40&lt;R40,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -5988,20 +5985,20 @@
       <c r="R43" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="S43" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T43" s="31">
-        <f>IF(OR(Q43="",R43=""),"[APOSTAR] OVER 2.5",IF((Q43+R43)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S43" s="31">
+        <f>IF(OR(Q43="",R43=""),"[APOSTAR] LOCAL",IF(Q43&gt;R43,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T43" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U43" s="35" t="n">
-        <v>0</v>
+        <v>883.88</v>
       </c>
       <c r="V43" s="35" t="n">
-        <v>883.88</v>
+        <v>0</v>
       </c>
       <c r="W43" s="31">
         <f>IF(L43="","",IF((MAX(L43,M43,N43)-MEDIAN(L43,M43,N43))&gt;0.05,IF(OR(Q43="",R43=""),"[PREDICCION] "&amp;IF(L43=MAX(L43,M43,N43),"LOCAL",IF(M43=MAX(L43,M43,N43),"EMPATE","VISITA")),IF(L43=MAX(L43,M43,N43),IF(Q43&gt;R43,"[ACIERTO]","[FALLO]"),IF(M43=MAX(L43,M43,N43),IF(Q43=R43,"[ACIERTO]","[FALLO]"),IF(Q43&lt;R43,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -6097,20 +6094,20 @@
       <c r="R44" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T44" s="31">
-        <f>IF(OR(Q44="",R44=""),"[APOSTAR] OVER 2.5",IF((Q44+R44)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S44" s="31">
+        <f>IF(OR(Q44="",R44=""),"[APOSTAR] VISITA",IF(Q44&lt;R44,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T44" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U44" s="35" t="n">
-        <v>0</v>
+        <v>883.88</v>
       </c>
       <c r="V44" s="35" t="n">
-        <v>883.88</v>
+        <v>0</v>
       </c>
       <c r="W44" s="31">
         <f>IF(L44="","",IF((MAX(L44,M44,N44)-MEDIAN(L44,M44,N44))&gt;0.05,IF(OR(Q44="",R44=""),"[PREDICCION] "&amp;IF(L44=MAX(L44,M44,N44),"LOCAL",IF(M44=MAX(L44,M44,N44),"EMPATE","VISITA")),IF(L44=MAX(L44,M44,N44),IF(Q44&gt;R44,"[ACIERTO]","[FALLO]"),IF(M44=MAX(L44,M44,N44),IF(Q44=R44,"[ACIERTO]","[FALLO]"),IF(Q44&lt;R44,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -6315,20 +6312,20 @@
       <c r="R46" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="S46" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T46" s="31">
-        <f>IF(OR(Q46="",R46=""),"[APOSTAR] OVER 2.5",IF((Q46+R46)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S46" s="31">
+        <f>IF(OR(Q46="",R46=""),"[APOSTAR] VISITA",IF(Q46&lt;R46,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T46" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U46" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V46" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W46" s="31">
         <f>IF(L46="","",IF((MAX(L46,M46,N46)-MEDIAN(L46,M46,N46))&gt;0.05,IF(OR(Q46="",R46=""),"[PREDICCION] "&amp;IF(L46=MAX(L46,M46,N46),"LOCAL",IF(M46=MAX(L46,M46,N46),"EMPATE","VISITA")),IF(L46=MAX(L46,M46,N46),IF(Q46&gt;R46,"[ACIERTO]","[FALLO]"),IF(M46=MAX(L46,M46,N46),IF(Q46=R46,"[ACIERTO]","[FALLO]"),IF(Q46&lt;R46,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -6539,7 +6536,7 @@
       </c>
       <c r="T48" s="31" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (1X2 Priorizado)</t>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
         </is>
       </c>
       <c r="U48" s="35" t="n">
@@ -6648,7 +6645,7 @@
       </c>
       <c r="T49" s="31" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (1X2 Priorizado)</t>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
         </is>
       </c>
       <c r="U49" s="35" t="n">
@@ -6751,20 +6748,20 @@
       <c r="R50" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="S50" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T50" s="31">
-        <f>IF(OR(Q50="",R50=""),"[APOSTAR] OVER 2.5",IF((Q50+R50)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S50" s="31">
+        <f>IF(OR(Q50="",R50=""),"[APOSTAR] LOCAL",IF(Q50&gt;R50,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T50" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U50" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V50" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W50" s="31">
         <f>IF(L50="","",IF((MAX(L50,M50,N50)-MEDIAN(L50,M50,N50))&gt;0.05,IF(OR(Q50="",R50=""),"[PREDICCION] "&amp;IF(L50=MAX(L50,M50,N50),"LOCAL",IF(M50=MAX(L50,M50,N50),"EMPATE","VISITA")),IF(L50=MAX(L50,M50,N50),IF(Q50&gt;R50,"[ACIERTO]","[FALLO]"),IF(M50=MAX(L50,M50,N50),IF(Q50=R50,"[ACIERTO]","[FALLO]"),IF(Q50&lt;R50,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -6860,20 +6857,20 @@
       <c r="R51" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="S51" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T51" s="31">
-        <f>IF(OR(Q51="",R51=""),"[APOSTAR] OVER 2.5",IF((Q51+R51)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S51" s="31">
+        <f>IF(OR(Q51="",R51=""),"[APOSTAR] VISITA",IF(Q51&lt;R51,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T51" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U51" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V51" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W51" s="31">
         <f>IF(L51="","",IF((MAX(L51,M51,N51)-MEDIAN(L51,M51,N51))&gt;0.05,IF(OR(Q51="",R51=""),"[PREDICCION] "&amp;IF(L51=MAX(L51,M51,N51),"LOCAL",IF(M51=MAX(L51,M51,N51),"EMPATE","VISITA")),IF(L51=MAX(L51,M51,N51),IF(Q51&gt;R51,"[ACIERTO]","[FALLO]"),IF(M51=MAX(L51,M51,N51),IF(Q51=R51,"[ACIERTO]","[FALLO]"),IF(Q51&lt;R51,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -6969,20 +6966,20 @@
       <c r="R52" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="S52" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T52" s="31">
-        <f>IF(OR(Q52="",R52=""),"[APOSTAR] OVER 2.5",IF((Q52+R52)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S52" s="31">
+        <f>IF(OR(Q52="",R52=""),"[APOSTAR] LOCAL",IF(Q52&gt;R52,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T52" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U52" s="35" t="n">
-        <v>0</v>
+        <v>883.88</v>
       </c>
       <c r="V52" s="35" t="n">
-        <v>883.88</v>
+        <v>0</v>
       </c>
       <c r="W52" s="31">
         <f>IF(L52="","",IF((MAX(L52,M52,N52)-MEDIAN(L52,M52,N52))&gt;0.05,IF(OR(Q52="",R52=""),"[PREDICCION] "&amp;IF(L52=MAX(L52,M52,N52),"LOCAL",IF(M52=MAX(L52,M52,N52),"EMPATE","VISITA")),IF(L52=MAX(L52,M52,N52),IF(Q52&gt;R52,"[ACIERTO]","[FALLO]"),IF(M52=MAX(L52,M52,N52),IF(Q52=R52,"[ACIERTO]","[FALLO]"),IF(Q52&lt;R52,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -7078,20 +7075,20 @@
       <c r="R53" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T53" s="31">
-        <f>IF(OR(Q53="",R53=""),"[APOSTAR] OVER 2.5",IF((Q53+R53)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S53" s="31">
+        <f>IF(OR(Q53="",R53=""),"[APOSTAR] VISITA",IF(Q53&lt;R53,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T53" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U53" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V53" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W53" s="31">
         <f>IF(L53="","",IF((MAX(L53,M53,N53)-MEDIAN(L53,M53,N53))&gt;0.05,IF(OR(Q53="",R53=""),"[PREDICCION] "&amp;IF(L53=MAX(L53,M53,N53),"LOCAL",IF(M53=MAX(L53,M53,N53),"EMPATE","VISITA")),IF(L53=MAX(L53,M53,N53),IF(Q53&gt;R53,"[ACIERTO]","[FALLO]"),IF(M53=MAX(L53,M53,N53),IF(Q53=R53,"[ACIERTO]","[FALLO]"),IF(Q53&lt;R53,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -7187,20 +7184,20 @@
       <c r="R54" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="S54" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T54" s="31">
-        <f>IF(OR(Q54="",R54=""),"[APOSTAR] OVER 2.5",IF((Q54+R54)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S54" s="31">
+        <f>IF(OR(Q54="",R54=""),"[APOSTAR] VISITA",IF(Q54&lt;R54,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T54" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U54" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V54" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W54" s="31">
         <f>IF(L54="","",IF((MAX(L54,M54,N54)-MEDIAN(L54,M54,N54))&gt;0.05,IF(OR(Q54="",R54=""),"[PREDICCION] "&amp;IF(L54=MAX(L54,M54,N54),"LOCAL",IF(M54=MAX(L54,M54,N54),"EMPATE","VISITA")),IF(L54=MAX(L54,M54,N54),IF(Q54&gt;R54,"[ACIERTO]","[FALLO]"),IF(M54=MAX(L54,M54,N54),IF(Q54=R54,"[ACIERTO]","[FALLO]"),IF(Q54&lt;R54,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -7296,20 +7293,20 @@
       <c r="R55" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="S55" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T55" s="31">
-        <f>IF(OR(Q55="",R55=""),"[APOSTAR] OVER 2.5",IF((Q55+R55)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S55" s="31">
+        <f>IF(OR(Q55="",R55=""),"[APOSTAR] VISITA",IF(Q55&lt;R55,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T55" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U55" s="35" t="n">
-        <v>0</v>
+        <v>1443.38</v>
       </c>
       <c r="V55" s="35" t="n">
-        <v>1443.38</v>
+        <v>0</v>
       </c>
       <c r="W55" s="31">
         <f>IF(L55="","",IF((MAX(L55,M55,N55)-MEDIAN(L55,M55,N55))&gt;0.05,IF(OR(Q55="",R55=""),"[PREDICCION] "&amp;IF(L55=MAX(L55,M55,N55),"LOCAL",IF(M55=MAX(L55,M55,N55),"EMPATE","VISITA")),IF(L55=MAX(L55,M55,N55),IF(Q55&gt;R55,"[ACIERTO]","[FALLO]"),IF(M55=MAX(L55,M55,N55),IF(Q55=R55,"[ACIERTO]","[FALLO]"),IF(Q55&lt;R55,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -7405,20 +7402,20 @@
       <c r="R56" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="S56" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T56" s="31">
-        <f>IF(OR(Q56="",R56=""),"[APOSTAR] OVER 2.5",IF((Q56+R56)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S56" s="31">
+        <f>IF(OR(Q56="",R56=""),"[APOSTAR] VISITA",IF(Q56&lt;R56,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T56" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U56" s="35" t="n">
-        <v>0</v>
+        <v>883.88</v>
       </c>
       <c r="V56" s="35" t="n">
-        <v>883.88</v>
+        <v>0</v>
       </c>
       <c r="W56" s="31">
         <f>IF(L56="","",IF((MAX(L56,M56,N56)-MEDIAN(L56,M56,N56))&gt;0.05,IF(OR(Q56="",R56=""),"[PREDICCION] "&amp;IF(L56=MAX(L56,M56,N56),"LOCAL",IF(M56=MAX(L56,M56,N56),"EMPATE","VISITA")),IF(L56=MAX(L56,M56,N56),IF(Q56&gt;R56,"[ACIERTO]","[FALLO]"),IF(M56=MAX(L56,M56,N56),IF(Q56=R56,"[ACIERTO]","[FALLO]"),IF(Q56&lt;R56,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -7514,20 +7511,20 @@
       <c r="R57" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T57" s="31">
-        <f>IF(OR(Q57="",R57=""),"[APOSTAR] OVER 2.5",IF((Q57+R57)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S57" s="31">
+        <f>IF(OR(Q57="",R57=""),"[APOSTAR] LOCAL",IF(Q57&gt;R57,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T57" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U57" s="35" t="n">
-        <v>0</v>
+        <v>883.88</v>
       </c>
       <c r="V57" s="35" t="n">
-        <v>883.88</v>
+        <v>0</v>
       </c>
       <c r="W57" s="31">
         <f>IF(L57="","",IF((MAX(L57,M57,N57)-MEDIAN(L57,M57,N57))&gt;0.05,IF(OR(Q57="",R57=""),"[PREDICCION] "&amp;IF(L57=MAX(L57,M57,N57),"LOCAL",IF(M57=MAX(L57,M57,N57),"EMPATE","VISITA")),IF(L57=MAX(L57,M57,N57),IF(Q57&gt;R57,"[ACIERTO]","[FALLO]"),IF(M57=MAX(L57,M57,N57),IF(Q57=R57,"[ACIERTO]","[FALLO]"),IF(Q57&lt;R57,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -7841,20 +7838,20 @@
       <c r="R60" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T60" s="31">
-        <f>IF(OR(Q60="",R60=""),"[APOSTAR] OVER 2.5",IF((Q60+R60)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S60" s="31">
+        <f>IF(OR(Q60="",R60=""),"[APOSTAR] LOCAL",IF(Q60&gt;R60,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T60" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U60" s="35" t="n">
-        <v>0</v>
+        <v>1443.38</v>
       </c>
       <c r="V60" s="35" t="n">
-        <v>1443.38</v>
+        <v>0</v>
       </c>
       <c r="W60" s="31">
         <f>IF(L60="","",IF((MAX(L60,M60,N60)-MEDIAN(L60,M60,N60))&gt;0.05,IF(OR(Q60="",R60=""),"[PREDICCION] "&amp;IF(L60=MAX(L60,M60,N60),"LOCAL",IF(M60=MAX(L60,M60,N60),"EMPATE","VISITA")),IF(L60=MAX(L60,M60,N60),IF(Q60&gt;R60,"[ACIERTO]","[FALLO]"),IF(M60=MAX(L60,M60,N60),IF(Q60=R60,"[ACIERTO]","[FALLO]"),IF(Q60&lt;R60,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -14651,7 +14648,7 @@
         <v>3.87</v>
       </c>
       <c r="H124" s="32" t="n">
-        <v>4.53</v>
+        <v>4.52</v>
       </c>
       <c r="I124" s="32" t="n">
         <v>1.85</v>
@@ -14687,7 +14684,7 @@
       </c>
       <c r="T124" s="31" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (1X2 Priorizado)</t>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
         </is>
       </c>
       <c r="U124" s="35" t="n">
@@ -14786,20 +14783,20 @@
       </c>
       <c r="Q125" s="38" t="n"/>
       <c r="R125" s="38" t="n"/>
-      <c r="S125" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T125" s="31">
-        <f>IF(OR(Q125="",R125=""),"[APOSTAR] OVER 2.5",IF((Q125+R125)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S125" s="31">
+        <f>IF(OR(Q125="",R125=""),"[APOSTAR] LOCAL",IF(Q125&gt;R125,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T125" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U125" s="35" t="n">
-        <v>0</v>
+        <v>1443.38</v>
       </c>
       <c r="V125" s="35" t="n">
-        <v>1443.38</v>
+        <v>0</v>
       </c>
       <c r="W125" s="31">
         <f>IF(L125="","",IF((MAX(L125,M125,N125)-MEDIAN(L125,M125,N125))&gt;0.05,IF(OR(Q125="",R125=""),"[PREDICCION] "&amp;IF(L125=MAX(L125,M125,N125),"LOCAL",IF(M125=MAX(L125,M125,N125),"EMPATE","VISITA")),IF(L125=MAX(L125,M125,N125),IF(Q125&gt;R125,"[ACIERTO]","[FALLO]"),IF(M125=MAX(L125,M125,N125),IF(Q125=R125,"[ACIERTO]","[FALLO]"),IF(Q125&lt;R125,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -14957,13 +14954,13 @@
         </is>
       </c>
       <c r="F127" s="32" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G127" s="32" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="H127" s="32" t="n">
-        <v>7.13</v>
+        <v>7.37</v>
       </c>
       <c r="I127" s="32" t="n"/>
       <c r="J127" s="32" t="n"/>
@@ -15808,20 +15805,20 @@
       </c>
       <c r="Q135" s="38" t="n"/>
       <c r="R135" s="38" t="n"/>
-      <c r="S135" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T135" s="31">
-        <f>IF(OR(Q135="",R135=""),"[APOSTAR] OVER 2.5",IF((Q135+R135)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S135" s="31">
+        <f>IF(OR(Q135="",R135=""),"[APOSTAR] VISITA",IF(Q135&lt;R135,"[GANADA] VISITA","[PERDIDA] VISITA"))</f>
+        <v/>
+      </c>
+      <c r="T135" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U135" s="35" t="n">
-        <v>0</v>
+        <v>1020.62</v>
       </c>
       <c r="V135" s="35" t="n">
-        <v>1020.62</v>
+        <v>0</v>
       </c>
       <c r="W135" s="31">
         <f>IF(L135="","",IF((MAX(L135,M135,N135)-MEDIAN(L135,M135,N135))&gt;0.05,IF(OR(Q135="",R135=""),"[PREDICCION] "&amp;IF(L135=MAX(L135,M135,N135),"LOCAL",IF(M135=MAX(L135,M135,N135),"EMPATE","VISITA")),IF(L135=MAX(L135,M135,N135),IF(Q135&gt;R135,"[ACIERTO]","[FALLO]"),IF(M135=MAX(L135,M135,N135),IF(Q135=R135,"[ACIERTO]","[FALLO]"),IF(Q135&lt;R135,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -16428,20 +16425,20 @@
       </c>
       <c r="Q141" s="38" t="n"/>
       <c r="R141" s="38" t="n"/>
-      <c r="S141" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T141" s="31">
-        <f>IF(OR(Q141="",R141=""),"[APOSTAR] OVER 2.5",IF((Q141+R141)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S141" s="31">
+        <f>IF(OR(Q141="",R141=""),"[APOSTAR] LOCAL",IF(Q141&gt;R141,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T141" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U141" s="35" t="n">
-        <v>0</v>
+        <v>1020.62</v>
       </c>
       <c r="V141" s="35" t="n">
-        <v>1020.62</v>
+        <v>0</v>
       </c>
       <c r="W141" s="31">
         <f>IF(L141="","",IF((MAX(L141,M141,N141)-MEDIAN(L141,M141,N141))&gt;0.05,IF(OR(Q141="",R141=""),"[PREDICCION] "&amp;IF(L141=MAX(L141,M141,N141),"LOCAL",IF(M141=MAX(L141,M141,N141),"EMPATE","VISITA")),IF(L141=MAX(L141,M141,N141),IF(Q141&gt;R141,"[ACIERTO]","[FALLO]"),IF(M141=MAX(L141,M141,N141),IF(Q141=R141,"[ACIERTO]","[FALLO]"),IF(Q141&lt;R141,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -17615,13 +17612,13 @@
         </is>
       </c>
       <c r="F153" s="32" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="G153" s="32" t="n">
         <v>3.63</v>
       </c>
       <c r="H153" s="32" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="I153" s="32" t="n"/>
       <c r="J153" s="32" t="n"/>
@@ -18563,20 +18560,20 @@
       </c>
       <c r="Q162" s="38" t="n"/>
       <c r="R162" s="38" t="n"/>
-      <c r="S162" s="31" t="inlineStr">
-        <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="T162" s="31">
-        <f>IF(OR(Q162="",R162=""),"[APOSTAR] OVER 2.5",IF((Q162+R162)&gt;2.5,"[GANADA] OVER 2.5","[PERDIDA] OVER 2.5"))</f>
-        <v/>
+      <c r="S162" s="31">
+        <f>IF(OR(Q162="",R162=""),"[APOSTAR] LOCAL",IF(Q162&gt;R162,"[GANADA] LOCAL","[PERDIDA] LOCAL"))</f>
+        <v/>
+      </c>
+      <c r="T162" s="31" t="inlineStr">
+        <is>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
+        </is>
       </c>
       <c r="U162" s="35" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="V162" s="35" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="W162" s="31">
         <f>IF(L162="","",IF((MAX(L162,M162,N162)-MEDIAN(L162,M162,N162))&gt;0.05,IF(OR(Q162="",R162=""),"[PREDICCION] "&amp;IF(L162=MAX(L162,M162,N162),"LOCAL",IF(M162=MAX(L162,M162,N162),"EMPATE","VISITA")),IF(L162=MAX(L162,M162,N162),IF(Q162&gt;R162,"[ACIERTO]","[FALLO]"),IF(M162=MAX(L162,M162,N162),IF(Q162=R162,"[ACIERTO]","[FALLO]"),IF(Q162&lt;R162,"[ACIERTO]","[FALLO]")))),"[PASAR] Margen Insuf"))</f>
@@ -19389,7 +19386,7 @@
       </c>
       <c r="T170" s="31" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (1X2 Priorizado)</t>
+          <t>[PASAR] Overlap 1X2 Prioritario</t>
         </is>
       </c>
       <c r="U170" s="35" t="n">
@@ -20105,7 +20102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -20310,20 +20307,20 @@
       </c>
       <c r="D6" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E6" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E6" s="48" t="n">
+        <v>1020.62</v>
+      </c>
+      <c r="F6" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G6" s="50" t="n">
+        <v>-1020.62</v>
+      </c>
       <c r="H6" s="51" t="inlineStr">
         <is>
           <t>[APOSTAR] VISITA</t>
@@ -20340,10 +20337,12 @@
       <c r="K6" s="50" t="n">
         <v>-2500</v>
       </c>
-      <c r="L6" s="48" t="n"/>
-      <c r="M6" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="L6" s="52" t="n">
+        <v>1479.38</v>
+      </c>
+      <c r="M6" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N6" s="49" t="inlineStr">
@@ -20360,55 +20359,55 @@
       </c>
       <c r="B7" s="45" t="inlineStr">
         <is>
-          <t>Defensa y Justicia vs Unión (santa Fe)</t>
+          <t>Brighton &amp; Hove Albion vs Liverpool</t>
         </is>
       </c>
       <c r="C7" s="44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D7" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E7" s="46" t="inlineStr">
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F7" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G7" s="52" t="n">
+        <v>2812.5</v>
+      </c>
+      <c r="H7" s="45" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I7" s="46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="47" t="inlineStr">
+      <c r="J7" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="48" t="n"/>
-      <c r="H7" s="45" t="inlineStr">
-        <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I7" s="46" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J7" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K7" s="53" t="n">
-        <v>4750</v>
-      </c>
+      <c r="K7" s="48" t="n"/>
       <c r="L7" s="48" t="n"/>
-      <c r="M7" s="44" t="inlineStr">
+      <c r="M7" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N7" s="44" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
@@ -20420,30 +20419,30 @@
       </c>
       <c r="B8" s="51" t="inlineStr">
         <is>
-          <t>Everton vs Chelsea</t>
+          <t>Defensa y Justicia vs Unión (santa Fe)</t>
         </is>
       </c>
       <c r="C8" s="47" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D8" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E8" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="48" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="n">
+        <v>1020.62</v>
+      </c>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G8" s="52" t="n">
+        <v>1939.18</v>
+      </c>
       <c r="H8" s="51" t="inlineStr">
         <is>
           <t>[APOSTAR] LOCAL</t>
@@ -20452,21 +20451,23 @@
       <c r="I8" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J8" s="52" t="inlineStr">
+      <c r="J8" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K8" s="53" t="n">
-        <v>6500</v>
-      </c>
-      <c r="L8" s="48" t="n"/>
-      <c r="M8" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="52" t="inlineStr">
+      <c r="K8" s="52" t="n">
+        <v>4750</v>
+      </c>
+      <c r="L8" s="50" t="n">
+        <v>-2810.82</v>
+      </c>
+      <c r="M8" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N8" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -20480,53 +20481,55 @@
       </c>
       <c r="B9" s="45" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino vs Botafogo</t>
+          <t>Everton vs Chelsea</t>
         </is>
       </c>
       <c r="C9" s="44" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D9" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E9" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="48" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E9" s="46" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F9" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G9" s="52" t="n">
+        <v>3250</v>
+      </c>
       <c r="H9" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I9" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J9" s="52" t="inlineStr">
+      <c r="J9" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K9" s="53" t="n">
-        <v>6975</v>
-      </c>
-      <c r="L9" s="48" t="n"/>
-      <c r="M9" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="52" t="inlineStr">
+      <c r="K9" s="52" t="n">
+        <v>6500</v>
+      </c>
+      <c r="L9" s="50" t="n">
+        <v>-3250</v>
+      </c>
+      <c r="M9" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N9" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -20540,12 +20543,12 @@
       </c>
       <c r="B10" s="51" t="inlineStr">
         <is>
-          <t>Viking fk vs Molde</t>
+          <t>Red Bull Bragantino vs Botafogo</t>
         </is>
       </c>
       <c r="C10" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D10" s="51" t="inlineStr">
@@ -20556,13 +20559,13 @@
       <c r="E10" s="48" t="n">
         <v>1767.77</v>
       </c>
-      <c r="F10" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="G10" s="50" t="n">
-        <v>-1767.77</v>
+      <c r="F10" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G10" s="52" t="n">
+        <v>4932.08</v>
       </c>
       <c r="H10" s="51" t="inlineStr">
         <is>
@@ -20572,60 +20575,60 @@
       <c r="I10" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J10" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K10" s="50" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L10" s="53" t="n">
-        <v>732.23</v>
-      </c>
-      <c r="M10" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="N10" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J10" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K10" s="52" t="n">
+        <v>6975</v>
+      </c>
+      <c r="L10" s="50" t="n">
+        <v>-2042.92</v>
+      </c>
+      <c r="M10" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N10" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="44" t="inlineStr">
         <is>
-          <t>22/03/2026</t>
+          <t>21/03/2026</t>
         </is>
       </c>
       <c r="B11" s="45" t="inlineStr">
         <is>
-          <t>Athletico Paranaense vs Coritiba</t>
+          <t>Viking fk vs Molde</t>
         </is>
       </c>
       <c r="C11" s="44" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D11" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E11" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E11" s="46" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F11" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G11" s="50" t="n">
+        <v>-1767.77</v>
+      </c>
       <c r="H11" s="45" t="inlineStr">
         <is>
           <t>[APOSTAR] VISITA</t>
@@ -20642,10 +20645,12 @@
       <c r="K11" s="50" t="n">
         <v>-2500</v>
       </c>
-      <c r="L11" s="48" t="n"/>
-      <c r="M11" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="L11" s="52" t="n">
+        <v>732.23</v>
+      </c>
+      <c r="M11" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N11" s="49" t="inlineStr">
@@ -20662,7 +20667,7 @@
       </c>
       <c r="B12" s="51" t="inlineStr">
         <is>
-          <t>Cruzeiro vs Santos</t>
+          <t>Athletico Paranaense vs Coritiba</t>
         </is>
       </c>
       <c r="C12" s="47" t="inlineStr">
@@ -20672,20 +20677,20 @@
       </c>
       <c r="D12" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E12" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="n">
+        <v>883.88</v>
+      </c>
+      <c r="F12" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G12" s="50" t="n">
+        <v>-883.88</v>
+      </c>
       <c r="H12" s="51" t="inlineStr">
         <is>
           <t>[APOSTAR] VISITA</t>
@@ -20702,10 +20707,12 @@
       <c r="K12" s="50" t="n">
         <v>-2500</v>
       </c>
-      <c r="L12" s="48" t="n"/>
-      <c r="M12" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="L12" s="52" t="n">
+        <v>1616.12</v>
+      </c>
+      <c r="M12" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N12" s="49" t="inlineStr">
@@ -20722,29 +20729,29 @@
       </c>
       <c r="B13" s="45" t="inlineStr">
         <is>
-          <t>Newcastle United vs Sunderland</t>
+          <t>Corinthians vs Flamengo</t>
         </is>
       </c>
       <c r="C13" s="44" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D13" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E13" s="46" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F13" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G13" s="53" t="n">
-        <v>6639.55</v>
+        <v>883.88</v>
+      </c>
+      <c r="F13" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G13" s="50" t="n">
+        <v>-883.88</v>
       </c>
       <c r="H13" s="45" t="inlineStr">
         <is>
@@ -20763,9 +20770,9 @@
       </c>
       <c r="K13" s="48" t="n"/>
       <c r="L13" s="48" t="n"/>
-      <c r="M13" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="M13" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="N13" s="44" t="inlineStr">
@@ -20782,7 +20789,7 @@
       </c>
       <c r="B14" s="51" t="inlineStr">
         <is>
-          <t>Remo vs Bahia</t>
+          <t>Cruzeiro vs Santos</t>
         </is>
       </c>
       <c r="C14" s="47" t="inlineStr">
@@ -20792,47 +20799,47 @@
       </c>
       <c r="D14" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E14" s="48" t="n">
         <v>883.88</v>
       </c>
-      <c r="F14" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="G14" s="53" t="n">
-        <v>2377.64</v>
+      <c r="F14" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G14" s="50" t="n">
+        <v>-883.88</v>
       </c>
       <c r="H14" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I14" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J14" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K14" s="53" t="n">
-        <v>6725</v>
-      </c>
-      <c r="L14" s="50" t="n">
-        <v>-4347.36</v>
-      </c>
-      <c r="M14" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
-      <c r="N14" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="J14" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K14" s="50" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L14" s="52" t="n">
+        <v>1616.12</v>
+      </c>
+      <c r="M14" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N14" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -20844,55 +20851,55 @@
       </c>
       <c r="B15" s="45" t="inlineStr">
         <is>
-          <t>Sarmiento (junín) vs Aldosivi</t>
+          <t>Fredrikstad vs Kfum Oslo</t>
         </is>
       </c>
       <c r="C15" s="44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D15" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E15" s="46" t="inlineStr">
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E15" s="46" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F15" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G15" s="50" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="H15" s="45" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I15" s="46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="47" t="inlineStr">
+      <c r="J15" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="48" t="n"/>
-      <c r="H15" s="45" t="inlineStr">
-        <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I15" s="46" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J15" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K15" s="50" t="n">
-        <v>-2500</v>
-      </c>
+      <c r="K15" s="48" t="n"/>
       <c r="L15" s="48" t="n"/>
-      <c r="M15" s="44" t="inlineStr">
+      <c r="M15" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N15" s="44" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
@@ -20904,55 +20911,55 @@
       </c>
       <c r="B16" s="51" t="inlineStr">
         <is>
-          <t>Sk Brann vs Tromso</t>
+          <t>Newcastle United vs Sunderland</t>
         </is>
       </c>
       <c r="C16" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D16" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E16" s="48" t="inlineStr">
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F16" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G16" s="52" t="n">
+        <v>6639.55</v>
+      </c>
+      <c r="H16" s="51" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I16" s="48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F16" s="47" t="inlineStr">
+      <c r="J16" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="51" t="inlineStr">
-        <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I16" s="48" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J16" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K16" s="53" t="n">
-        <v>6000</v>
-      </c>
+      <c r="K16" s="48" t="n"/>
       <c r="L16" s="48" t="n"/>
-      <c r="M16" s="47" t="inlineStr">
+      <c r="M16" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N16" s="47" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
@@ -20964,53 +20971,55 @@
       </c>
       <c r="B17" s="45" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur vs Nottingham Forest</t>
+          <t>Remo vs Bahia</t>
         </is>
       </c>
       <c r="C17" s="44" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E17" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="48" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E17" s="46" t="n">
+        <v>883.88</v>
+      </c>
+      <c r="F17" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G17" s="52" t="n">
+        <v>2377.64</v>
+      </c>
       <c r="H17" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I17" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J17" s="52" t="inlineStr">
+      <c r="J17" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K17" s="53" t="n">
-        <v>6000</v>
-      </c>
-      <c r="L17" s="48" t="n"/>
-      <c r="M17" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N17" s="52" t="inlineStr">
+      <c r="K17" s="52" t="n">
+        <v>6725</v>
+      </c>
+      <c r="L17" s="50" t="n">
+        <v>-4347.36</v>
+      </c>
+      <c r="M17" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N17" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -21024,127 +21033,127 @@
       </c>
       <c r="B18" s="51" t="inlineStr">
         <is>
-          <t>Vitória vs Mirassol</t>
+          <t>Rosenborg vs Valerenga</t>
         </is>
       </c>
       <c r="C18" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D18" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E18" s="48" t="inlineStr">
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E18" s="48" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F18" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G18" s="50" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="H18" s="51" t="inlineStr">
+        <is>
+          <t>[PASAR] Shadow-EV (0.056&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="I18" s="48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F18" s="47" t="inlineStr">
+      <c r="J18" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="48" t="n"/>
-      <c r="H18" s="51" t="inlineStr">
-        <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I18" s="48" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J18" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K18" s="53" t="n">
-        <v>3875</v>
-      </c>
+      <c r="K18" s="48" t="n"/>
       <c r="L18" s="48" t="n"/>
-      <c r="M18" s="47" t="inlineStr">
+      <c r="M18" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N18" s="47" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="N18" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="44" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B19" s="45" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia vs Rosario Central</t>
+          <t>Sandefjord vs Sarpsborg fk</t>
         </is>
       </c>
       <c r="C19" s="44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D19" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E19" s="46" t="inlineStr">
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E19" s="46" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F19" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G19" s="52" t="n">
+        <v>2687.5</v>
+      </c>
+      <c r="H19" s="45" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I19" s="46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" s="47" t="inlineStr">
+      <c r="J19" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="48" t="n"/>
-      <c r="H19" s="45" t="inlineStr">
-        <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I19" s="46" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J19" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K19" s="53" t="n">
-        <v>4375</v>
-      </c>
+      <c r="K19" s="48" t="n"/>
       <c r="L19" s="48" t="n"/>
-      <c r="M19" s="44" t="inlineStr">
+      <c r="M19" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N19" s="44" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="N19" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="47" t="inlineStr">
         <is>
-          <t>29/03/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B20" s="51" t="inlineStr">
         <is>
-          <t>Athletico Paranaense vs Botafogo</t>
+          <t>São Paulo vs Palmeiras</t>
         </is>
       </c>
       <c r="C20" s="47" t="inlineStr">
@@ -21154,11 +21163,11 @@
       </c>
       <c r="D20" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E20" s="48" t="n">
-        <v>2500</v>
+        <v>883.88</v>
       </c>
       <c r="F20" s="49" t="inlineStr">
         <is>
@@ -21166,153 +21175,155 @@
         </is>
       </c>
       <c r="G20" s="50" t="n">
-        <v>-2500</v>
+        <v>-883.88</v>
       </c>
       <c r="H20" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I20" s="48" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J20" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K20" s="50" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L20" s="54" t="n">
-        <v>0</v>
-      </c>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I20" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="48" t="n"/>
+      <c r="L20" s="48" t="n"/>
       <c r="M20" s="49" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="N20" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N20" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="44" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B21" s="45" t="inlineStr">
         <is>
-          <t>Bahia vs Athletico Paranaense</t>
+          <t>Sarmiento (junín) vs Aldosivi</t>
         </is>
       </c>
       <c r="C21" s="44" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D21" s="45" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E21" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E21" s="46" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F21" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G21" s="50" t="n">
+        <v>-1250</v>
+      </c>
       <c r="H21" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I21" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J21" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K21" s="53" t="n">
-        <v>8900</v>
-      </c>
-      <c r="L21" s="48" t="n"/>
-      <c r="M21" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N21" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="J21" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K21" s="50" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L21" s="52" t="n">
+        <v>1250</v>
+      </c>
+      <c r="M21" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N21" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="47" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B22" s="51" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Sk Brann vs Tromso</t>
         </is>
       </c>
       <c r="C22" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D22" s="51" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E22" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E22" s="48" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F22" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G22" s="52" t="n">
+        <v>3000</v>
+      </c>
       <c r="H22" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I22" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J22" s="52" t="inlineStr">
+      <c r="J22" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K22" s="53" t="n">
-        <v>12075</v>
-      </c>
-      <c r="L22" s="48" t="n"/>
-      <c r="M22" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N22" s="52" t="inlineStr">
+      <c r="K22" s="52" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L22" s="50" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="M22" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N22" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -21321,35 +21332,35 @@
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="44" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B23" s="45" t="inlineStr">
         <is>
-          <t>Internacional vs São Paulo</t>
+          <t>Tottenham Hotspur vs Nottingham Forest</t>
         </is>
       </c>
       <c r="C23" s="44" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D23" s="45" t="inlineStr">
         <is>
-          <t>[PERDIDA] VISITA</t>
-        </is>
-      </c>
-      <c r="E23" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E23" s="46" t="n">
+        <v>1443.38</v>
+      </c>
+      <c r="F23" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G23" s="52" t="n">
+        <v>3464.11</v>
+      </c>
       <c r="H23" s="45" t="inlineStr">
         <is>
           <t>[APOSTAR] VISITA</t>
@@ -21358,95 +21369,97 @@
       <c r="I23" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J23" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K23" s="50" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L23" s="48" t="n"/>
-      <c r="M23" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N23" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J23" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K23" s="52" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L23" s="50" t="n">
+        <v>-2535.89</v>
+      </c>
+      <c r="M23" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N23" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="47" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B24" s="51" t="inlineStr">
         <is>
-          <t>Lanús vs Platense</t>
+          <t>Vasco da Gama vs Grêmio</t>
         </is>
       </c>
       <c r="C24" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D24" s="51" t="inlineStr">
         <is>
-          <t>[PERDIDA] VISITA</t>
-        </is>
-      </c>
-      <c r="E24" s="48" t="inlineStr">
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E24" s="48" t="n">
+        <v>883.88</v>
+      </c>
+      <c r="F24" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G24" s="50" t="n">
+        <v>-883.88</v>
+      </c>
+      <c r="H24" s="51" t="inlineStr">
+        <is>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I24" s="48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F24" s="47" t="inlineStr">
+      <c r="J24" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="48" t="n"/>
-      <c r="H24" s="51" t="inlineStr">
-        <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I24" s="48" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J24" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K24" s="50" t="n">
-        <v>-2500</v>
-      </c>
+      <c r="K24" s="48" t="n"/>
       <c r="L24" s="48" t="n"/>
-      <c r="M24" s="47" t="inlineStr">
+      <c r="M24" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N24" s="47" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="N24" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="44" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>22/03/2026</t>
         </is>
       </c>
       <c r="B25" s="45" t="inlineStr">
         <is>
-          <t>Chapecoense vs Atlético-mg</t>
+          <t>Vitória vs Mirassol</t>
         </is>
       </c>
       <c r="C25" s="44" t="inlineStr">
@@ -21456,43 +21469,45 @@
       </c>
       <c r="D25" s="45" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
-        </is>
-      </c>
-      <c r="E25" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="48" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E25" s="46" t="n">
+        <v>883.88</v>
+      </c>
+      <c r="F25" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G25" s="52" t="n">
+        <v>1370.01</v>
+      </c>
       <c r="H25" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I25" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J25" s="52" t="inlineStr">
+      <c r="J25" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K25" s="53" t="n">
-        <v>4675</v>
-      </c>
-      <c r="L25" s="48" t="n"/>
-      <c r="M25" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N25" s="52" t="inlineStr">
+      <c r="K25" s="52" t="n">
+        <v>3875</v>
+      </c>
+      <c r="L25" s="50" t="n">
+        <v>-2504.99</v>
+      </c>
+      <c r="M25" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N25" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -21501,17 +21516,17 @@
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="47" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="B26" s="51" t="inlineStr">
         <is>
-          <t>Fluminense vs Corinthians</t>
+          <t>Independiente Rivadavia vs Rosario Central</t>
         </is>
       </c>
       <c r="C26" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D26" s="51" t="inlineStr">
@@ -21520,15 +21535,15 @@
         </is>
       </c>
       <c r="E26" s="48" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F26" s="52" t="inlineStr">
+        <v>1443.38</v>
+      </c>
+      <c r="F26" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="G26" s="53" t="n">
-        <v>12075</v>
+      <c r="G26" s="52" t="n">
+        <v>2525.91</v>
       </c>
       <c r="H26" s="51" t="inlineStr">
         <is>
@@ -21538,23 +21553,23 @@
       <c r="I26" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J26" s="52" t="inlineStr">
+      <c r="J26" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K26" s="53" t="n">
-        <v>12075</v>
-      </c>
-      <c r="L26" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="52" t="inlineStr">
+      <c r="K26" s="52" t="n">
+        <v>4375</v>
+      </c>
+      <c r="L26" s="50" t="n">
+        <v>-1849.09</v>
+      </c>
+      <c r="M26" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="N26" s="52" t="inlineStr">
+      <c r="N26" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -21563,12 +21578,12 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>29/03/2026</t>
         </is>
       </c>
       <c r="B27" s="45" t="inlineStr">
         <is>
-          <t>Palmeiras vs Grêmio</t>
+          <t>Athletico Paranaense vs Botafogo</t>
         </is>
       </c>
       <c r="C27" s="44" t="inlineStr">
@@ -21578,57 +21593,59 @@
       </c>
       <c r="D27" s="45" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
-        </is>
-      </c>
-      <c r="E27" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E27" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="G27" s="50" t="n">
+        <v>-2500</v>
+      </c>
       <c r="H27" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I27" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J27" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K27" s="53" t="n">
-        <v>12575</v>
-      </c>
-      <c r="L27" s="48" t="n"/>
-      <c r="M27" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N27" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="J27" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K27" s="50" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="L27" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N27" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="47" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B28" s="51" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino vs Flamengo</t>
+          <t>Bahia vs Athletico Paranaense</t>
         </is>
       </c>
       <c r="C28" s="47" t="inlineStr">
@@ -21660,13 +21677,13 @@
       <c r="I28" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J28" s="52" t="inlineStr">
+      <c r="J28" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K28" s="53" t="n">
-        <v>8550</v>
+      <c r="K28" s="52" t="n">
+        <v>8900</v>
       </c>
       <c r="L28" s="48" t="n"/>
       <c r="M28" s="47" t="inlineStr">
@@ -21674,7 +21691,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N28" s="52" t="inlineStr">
+      <c r="N28" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -21683,17 +21700,17 @@
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B29" s="45" t="inlineStr">
         <is>
-          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C29" s="44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D29" s="45" t="inlineStr">
@@ -21720,13 +21737,13 @@
       <c r="I29" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J29" s="52" t="inlineStr">
+      <c r="J29" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K29" s="53" t="n">
-        <v>7750</v>
+      <c r="K29" s="52" t="n">
+        <v>12075</v>
       </c>
       <c r="L29" s="48" t="n"/>
       <c r="M29" s="44" t="inlineStr">
@@ -21734,7 +21751,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N29" s="52" t="inlineStr">
+      <c r="N29" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -21743,12 +21760,12 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="47" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B30" s="51" t="inlineStr">
         <is>
-          <t>Palmeiras vs Gremio</t>
+          <t>Internacional vs São Paulo</t>
         </is>
       </c>
       <c r="C30" s="47" t="inlineStr">
@@ -21758,7 +21775,7 @@
       </c>
       <c r="D30" s="51" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PERDIDA] VISITA</t>
         </is>
       </c>
       <c r="E30" s="48" t="inlineStr">
@@ -21774,19 +21791,19 @@
       <c r="G30" s="48" t="n"/>
       <c r="H30" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I30" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J30" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K30" s="53" t="n">
-        <v>13800</v>
+      <c r="J30" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K30" s="50" t="n">
+        <v>-2500</v>
       </c>
       <c r="L30" s="48" t="n"/>
       <c r="M30" s="47" t="inlineStr">
@@ -21794,31 +21811,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N30" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N30" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>Genclerbirligi vs Goztepe</t>
+          <t>Lanús vs Platense</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D31" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.062&lt;0.080)</t>
+          <t>[PERDIDA] VISITA</t>
         </is>
       </c>
       <c r="E31" s="46" t="inlineStr">
@@ -21834,7 +21851,7 @@
       <c r="G31" s="48" t="n"/>
       <c r="H31" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I31" s="46" t="n">
@@ -21863,22 +21880,22 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="47" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B32" s="51" t="inlineStr">
         <is>
-          <t>Kasimpasa vs Kayserispor</t>
+          <t>Chapecoense vs Atlético-mg</t>
         </is>
       </c>
       <c r="C32" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D32" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.053&lt;0.080)</t>
+          <t>[GANADA] VISITA</t>
         </is>
       </c>
       <c r="E32" s="48" t="inlineStr">
@@ -21900,13 +21917,13 @@
       <c r="I32" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J32" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K32" s="50" t="n">
-        <v>-2500</v>
+      <c r="J32" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K32" s="52" t="n">
+        <v>4675</v>
       </c>
       <c r="L32" s="48" t="n"/>
       <c r="M32" s="47" t="inlineStr">
@@ -21914,81 +21931,83 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N32" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N32" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="B33" s="45" t="inlineStr">
         <is>
-          <t>Antalyaspor vs Eyupspor</t>
+          <t>Fluminense vs Corinthians</t>
         </is>
       </c>
       <c r="C33" s="44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D33" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.056&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="E33" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F33" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" s="48" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E33" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F33" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="G33" s="52" t="n">
+        <v>12075</v>
+      </c>
       <c r="H33" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I33" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J33" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K33" s="50" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="L33" s="48" t="n"/>
-      <c r="M33" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N33" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="J33" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K33" s="52" t="n">
+        <v>12075</v>
+      </c>
+      <c r="L33" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N33" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="47" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B34" s="51" t="inlineStr">
         <is>
-          <t>Corinthians vs Internacional</t>
+          <t>Palmeiras vs Grêmio</t>
         </is>
       </c>
       <c r="C34" s="47" t="inlineStr">
@@ -21998,7 +22017,7 @@
       </c>
       <c r="D34" s="51" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E34" s="48" t="inlineStr">
@@ -22014,19 +22033,19 @@
       <c r="G34" s="48" t="n"/>
       <c r="H34" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I34" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J34" s="52" t="inlineStr">
+      <c r="J34" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K34" s="53" t="n">
-        <v>6700</v>
+      <c r="K34" s="52" t="n">
+        <v>12575</v>
       </c>
       <c r="L34" s="48" t="n"/>
       <c r="M34" s="47" t="inlineStr">
@@ -22034,7 +22053,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N34" s="52" t="inlineStr">
+      <c r="N34" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -22043,17 +22062,17 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B35" s="45" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük vs Caykur Rizespor</t>
+          <t>Red Bull Bragantino vs Flamengo</t>
         </is>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D35" s="45" t="inlineStr">
@@ -22080,13 +22099,13 @@
       <c r="I35" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J35" s="52" t="inlineStr">
+      <c r="J35" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K35" s="53" t="n">
-        <v>5675</v>
+      <c r="K35" s="52" t="n">
+        <v>8550</v>
       </c>
       <c r="L35" s="48" t="n"/>
       <c r="M35" s="44" t="inlineStr">
@@ -22094,7 +22113,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N35" s="52" t="inlineStr">
+      <c r="N35" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -22103,17 +22122,17 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="47" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B36" s="51" t="inlineStr">
         <is>
-          <t>Fenerbahce vs Besiktas</t>
+          <t>Gimnasia Mendoza vs Velez Sarsfield</t>
         </is>
       </c>
       <c r="C36" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D36" s="51" t="inlineStr">
@@ -22140,13 +22159,13 @@
       <c r="I36" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J36" s="52" t="inlineStr">
+      <c r="J36" s="53" t="inlineStr">
         <is>
           <t>GANADA</t>
         </is>
       </c>
-      <c r="K36" s="53" t="n">
-        <v>4225</v>
+      <c r="K36" s="52" t="n">
+        <v>7750</v>
       </c>
       <c r="L36" s="48" t="n"/>
       <c r="M36" s="47" t="inlineStr">
@@ -22154,7 +22173,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N36" s="52" t="inlineStr">
+      <c r="N36" s="53" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -22163,22 +22182,22 @@
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="44" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="B37" s="45" t="inlineStr">
         <is>
-          <t>Hamkam vs Sk Brann</t>
+          <t>Palmeiras vs Gremio</t>
         </is>
       </c>
       <c r="C37" s="44" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D37" s="45" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E37" s="46" t="inlineStr">
@@ -22200,13 +22219,13 @@
       <c r="I37" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J37" s="49" t="inlineStr">
-        <is>
-          <t>PERDIDA</t>
-        </is>
-      </c>
-      <c r="K37" s="50" t="n">
-        <v>-2500</v>
+      <c r="J37" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K37" s="52" t="n">
+        <v>13800</v>
       </c>
       <c r="L37" s="48" t="n"/>
       <c r="M37" s="44" t="inlineStr">
@@ -22214,31 +22233,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N37" s="49" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="N37" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="47" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B38" s="51" t="inlineStr">
         <is>
-          <t>Valerenga vs Viking fk</t>
+          <t>Genclerbirligi vs Goztepe</t>
         </is>
       </c>
       <c r="C38" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D38" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.109&lt;0.120)</t>
+          <t>[PASAR] EV Insuf (0.062&lt;0.080)</t>
         </is>
       </c>
       <c r="E38" s="48" t="inlineStr">
@@ -22283,22 +22302,22 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="44" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B39" s="45" t="inlineStr">
         <is>
-          <t>Kfum Oslo vs Sandefjord</t>
+          <t>Kasimpasa vs Kayserispor</t>
         </is>
       </c>
       <c r="C39" s="44" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D39" s="45" t="inlineStr">
         <is>
-          <t>[GANADA] VISITA</t>
+          <t>[PASAR] EV Insuf (0.053&lt;0.080)</t>
         </is>
       </c>
       <c r="E39" s="46" t="inlineStr">
@@ -22320,13 +22339,13 @@
       <c r="I39" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J39" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K39" s="53" t="n">
-        <v>5900</v>
+      <c r="J39" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K39" s="50" t="n">
+        <v>-2500</v>
       </c>
       <c r="L39" s="48" t="n"/>
       <c r="M39" s="44" t="inlineStr">
@@ -22334,21 +22353,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N39" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N39" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="47" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B40" s="51" t="inlineStr">
         <is>
-          <t>Caykur Rizespor vs Samsunspor</t>
+          <t>Antalyaspor vs Eyupspor</t>
         </is>
       </c>
       <c r="C40" s="47" t="inlineStr">
@@ -22358,7 +22377,7 @@
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>[GANADA] LOCAL</t>
+          <t>[PASAR] EV Insuf (0.056&lt;0.080)</t>
         </is>
       </c>
       <c r="E40" s="48" t="inlineStr">
@@ -22374,19 +22393,19 @@
       <c r="G40" s="48" t="n"/>
       <c r="H40" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I40" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J40" s="52" t="inlineStr">
-        <is>
-          <t>GANADA</t>
-        </is>
-      </c>
-      <c r="K40" s="53" t="n">
-        <v>8325</v>
+      <c r="J40" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K40" s="50" t="n">
+        <v>-2500</v>
       </c>
       <c r="L40" s="48" t="n"/>
       <c r="M40" s="47" t="inlineStr">
@@ -22394,79 +22413,81 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N40" s="52" t="inlineStr">
-        <is>
-          <t>SI</t>
+      <c r="N40" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="44" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B41" s="45" t="inlineStr">
         <is>
-          <t>West Ham United vs Wolverhampton Wanderers</t>
+          <t>Corinthians vs Internacional</t>
         </is>
       </c>
       <c r="C41" s="44" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D41" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E41" s="46" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F41" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] VISITA</t>
+        </is>
+      </c>
+      <c r="E41" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="48" t="n"/>
       <c r="H41" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I41" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K41" s="48" t="n"/>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I41" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J41" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K41" s="52" t="n">
+        <v>6700</v>
+      </c>
       <c r="L41" s="48" t="n"/>
       <c r="M41" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N41" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N41" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="47" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B42" s="51" t="inlineStr">
         <is>
-          <t>Alanyaspor vs Trabzonspor</t>
+          <t>Fatih Karagümrük vs Caykur Rizespor</t>
         </is>
       </c>
       <c r="C42" s="47" t="inlineStr">
@@ -22476,7 +22497,7 @@
       </c>
       <c r="D42" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E42" s="48" t="inlineStr">
@@ -22484,9 +22505,9 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="F42" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G42" s="48" t="n"/>
@@ -22498,107 +22519,115 @@
       <c r="I42" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J42" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K42" s="48" t="n"/>
+      <c r="J42" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K42" s="52" t="n">
+        <v>5675</v>
+      </c>
       <c r="L42" s="48" t="n"/>
       <c r="M42" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N42" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N42" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="44" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B43" s="45" t="inlineStr">
         <is>
-          <t>Boca Juniors vs Independiente</t>
+          <t>Fenerbahce vs Besiktas</t>
         </is>
       </c>
       <c r="C43" s="44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D43" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E43" s="46" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F43" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] LOCAL</t>
+        </is>
+      </c>
+      <c r="E43" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G43" s="48" t="n"/>
       <c r="H43" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I43" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J43" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K43" s="48" t="n"/>
+      <c r="J43" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K43" s="52" t="n">
+        <v>4225</v>
+      </c>
       <c r="L43" s="48" t="n"/>
       <c r="M43" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N43" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N43" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="47" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B44" s="51" t="inlineStr">
         <is>
-          <t>Deportivo Riestra vs Instituto (córdoba)</t>
+          <t>Hamkam vs Sk Brann</t>
         </is>
       </c>
       <c r="C44" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D44" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E44" s="48" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F44" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] VISITA</t>
+        </is>
+      </c>
+      <c r="E44" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G44" s="48" t="n"/>
@@ -22610,157 +22639,165 @@
       <c r="I44" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J44" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K44" s="48" t="n"/>
+      <c r="J44" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K44" s="50" t="n">
+        <v>-2500</v>
+      </c>
       <c r="L44" s="48" t="n"/>
       <c r="M44" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N44" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N44" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B45" s="45" t="inlineStr">
         <is>
-          <t>Estudiantes de la Plata vs Union (santa Fe)</t>
+          <t>Valerenga vs Viking fk</t>
         </is>
       </c>
       <c r="C45" s="44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D45" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E45" s="46" t="n">
-        <v>1443.38</v>
-      </c>
-      <c r="F45" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[PASAR] EV Insuf (0.109&lt;0.120)</t>
+        </is>
+      </c>
+      <c r="E45" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G45" s="48" t="n"/>
       <c r="H45" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Shadow-EV (0.046&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="I45" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K45" s="48" t="n"/>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I45" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J45" s="49" t="inlineStr">
+        <is>
+          <t>PERDIDA</t>
+        </is>
+      </c>
+      <c r="K45" s="50" t="n">
+        <v>-2500</v>
+      </c>
       <c r="L45" s="48" t="n"/>
       <c r="M45" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N45" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N45" s="49" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="47" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B46" s="51" t="inlineStr">
         <is>
-          <t>Fluminense vs Flamengo</t>
+          <t>Kfum Oslo vs Sandefjord</t>
         </is>
       </c>
       <c r="C46" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D46" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="E46" s="48" t="n">
-        <v>1020.62</v>
-      </c>
-      <c r="F46" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+          <t>[GANADA] VISITA</t>
+        </is>
+      </c>
+      <c r="E46" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G46" s="48" t="n"/>
       <c r="H46" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I46" s="48" t="n">
         <v>2500</v>
       </c>
-      <c r="J46" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K46" s="48" t="n"/>
+      <c r="J46" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K46" s="52" t="n">
+        <v>5900</v>
+      </c>
       <c r="L46" s="48" t="n"/>
       <c r="M46" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N46" s="47" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N46" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B47" s="45" t="inlineStr">
         <is>
-          <t>Internacional vs Gremio</t>
+          <t>Caykur Rizespor vs Samsunspor</t>
         </is>
       </c>
       <c r="C47" s="44" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D47" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
+          <t>[GANADA] LOCAL</t>
         </is>
       </c>
       <c r="E47" s="46" t="inlineStr">
@@ -22768,61 +22805,63 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F47" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
+      <c r="F47" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="G47" s="48" t="n"/>
       <c r="H47" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I47" s="46" t="n">
         <v>2500</v>
       </c>
-      <c r="J47" s="55" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="K47" s="48" t="n"/>
+      <c r="J47" s="53" t="inlineStr">
+        <is>
+          <t>GANADA</t>
+        </is>
+      </c>
+      <c r="K47" s="52" t="n">
+        <v>8325</v>
+      </c>
       <c r="L47" s="48" t="n"/>
       <c r="M47" s="44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N47" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="N47" s="53" t="inlineStr">
+        <is>
+          <t>SI</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="47" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B48" s="51" t="inlineStr">
         <is>
-          <t>Kayserispor vs Fenerbahce</t>
+          <t>West Ham United vs Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="C48" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D48" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E48" s="48" t="n">
-        <v>1443.38</v>
+        <v>2500</v>
       </c>
       <c r="F48" s="55" t="inlineStr">
         <is>
@@ -22832,11 +22871,13 @@
       <c r="G48" s="48" t="n"/>
       <c r="H48" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I48" s="48" t="n">
-        <v>2500</v>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I48" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="55" t="inlineStr">
         <is>
@@ -22864,23 +22905,21 @@
       </c>
       <c r="B49" s="45" t="inlineStr">
         <is>
-          <t>Mirassol vs Bahia</t>
+          <t>Alanyaspor vs Trabzonspor</t>
         </is>
       </c>
       <c r="C49" s="44" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] EV Insuf (0.044&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="E49" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E49" s="46" t="n">
+        <v>1443.38</v>
       </c>
       <c r="F49" s="55" t="inlineStr">
         <is>
@@ -22890,7 +22929,7 @@
       <c r="G49" s="48" t="n"/>
       <c r="H49" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I49" s="46" t="n">
@@ -22922,23 +22961,21 @@
       </c>
       <c r="B50" s="51" t="inlineStr">
         <is>
-          <t>Remo vs Vasco da Gama</t>
+          <t>Boca Juniors vs Independiente</t>
         </is>
       </c>
       <c r="C50" s="47" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D50" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E50" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E50" s="48" t="n">
+        <v>1443.38</v>
       </c>
       <c r="F50" s="55" t="inlineStr">
         <is>
@@ -22948,7 +22985,7 @@
       <c r="G50" s="48" t="n"/>
       <c r="H50" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I50" s="48" t="n">
@@ -22980,21 +23017,21 @@
       </c>
       <c r="B51" s="45" t="inlineStr">
         <is>
-          <t>Santos vs Atlético-mg</t>
+          <t>Deportivo Riestra vs Instituto (córdoba)</t>
         </is>
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D51" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E51" s="46" t="n">
-        <v>1020.62</v>
+        <v>1443.38</v>
       </c>
       <c r="F51" s="55" t="inlineStr">
         <is>
@@ -23004,7 +23041,7 @@
       <c r="G51" s="48" t="n"/>
       <c r="H51" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I51" s="46" t="n">
@@ -23036,12 +23073,12 @@
       </c>
       <c r="B52" s="51" t="inlineStr">
         <is>
-          <t>Viking fk vs Bodo/glimt</t>
+          <t>Estudiantes de la Plata vs Union (santa Fe)</t>
         </is>
       </c>
       <c r="C52" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D52" s="51" t="inlineStr">
@@ -23050,7 +23087,7 @@
         </is>
       </c>
       <c r="E52" s="48" t="n">
-        <v>2500</v>
+        <v>1443.38</v>
       </c>
       <c r="F52" s="55" t="inlineStr">
         <is>
@@ -23060,11 +23097,13 @@
       <c r="G52" s="48" t="n"/>
       <c r="H52" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I52" s="48" t="n">
-        <v>2500</v>
+          <t>[PASAR] Shadow-EV (0.046&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="I52" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="55" t="inlineStr">
         <is>
@@ -23092,7 +23131,7 @@
       </c>
       <c r="B53" s="45" t="inlineStr">
         <is>
-          <t>Vitoria vs Sao Paulo</t>
+          <t>Fluminense vs Flamengo</t>
         </is>
       </c>
       <c r="C53" s="44" t="inlineStr">
@@ -23143,12 +23182,12 @@
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="47" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B54" s="51" t="inlineStr">
         <is>
-          <t>Botafogo vs Coritiba</t>
+          <t>Internacional vs Gremio</t>
         </is>
       </c>
       <c r="C54" s="47" t="inlineStr">
@@ -23162,7 +23201,7 @@
         </is>
       </c>
       <c r="E54" s="48" t="n">
-        <v>1250</v>
+        <v>1020.62</v>
       </c>
       <c r="F54" s="55" t="inlineStr">
         <is>
@@ -23172,13 +23211,11 @@
       <c r="G54" s="48" t="n"/>
       <c r="H54" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I54" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I54" s="48" t="n">
+        <v>2500</v>
       </c>
       <c r="J54" s="55" t="inlineStr">
         <is>
@@ -23201,17 +23238,17 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="44" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B55" s="45" t="inlineStr">
         <is>
-          <t>Chelsea vs Manchester City</t>
+          <t>Kayserispor vs Fenerbahce</t>
         </is>
       </c>
       <c r="C55" s="44" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Turquia</t>
         </is>
       </c>
       <c r="D55" s="45" t="inlineStr">
@@ -23220,7 +23257,7 @@
         </is>
       </c>
       <c r="E55" s="46" t="n">
-        <v>1250</v>
+        <v>1443.38</v>
       </c>
       <c r="F55" s="55" t="inlineStr">
         <is>
@@ -23257,12 +23294,12 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="47" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B56" s="51" t="inlineStr">
         <is>
-          <t>Corinthians vs Palmeiras</t>
+          <t>Mirassol vs Bahia</t>
         </is>
       </c>
       <c r="C56" s="47" t="inlineStr">
@@ -23272,11 +23309,13 @@
       </c>
       <c r="D56" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="E56" s="48" t="n">
-        <v>1250</v>
+          <t>[PASAR] EV Insuf (0.044&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="E56" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="55" t="inlineStr">
         <is>
@@ -23286,13 +23325,11 @@
       <c r="G56" s="48" t="n"/>
       <c r="H56" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Shadow-EV (0.042&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="I56" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I56" s="48" t="n">
+        <v>2500</v>
       </c>
       <c r="J56" s="55" t="inlineStr">
         <is>
@@ -23315,12 +23352,12 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="44" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B57" s="45" t="inlineStr">
         <is>
-          <t>Cruzeiro vs Red Bull Bragantino</t>
+          <t>Remo vs Vasco da Gama</t>
         </is>
       </c>
       <c r="C57" s="44" t="inlineStr">
@@ -23330,11 +23367,11 @@
       </c>
       <c r="D57" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E57" s="46" t="n">
-        <v>1250</v>
+        <v>1020.62</v>
       </c>
       <c r="F57" s="55" t="inlineStr">
         <is>
@@ -23344,7 +23381,7 @@
       <c r="G57" s="48" t="n"/>
       <c r="H57" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I57" s="46" t="n">
@@ -23371,26 +23408,26 @@
     <row r="58" ht="16" customHeight="1">
       <c r="A58" s="47" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B58" s="51" t="inlineStr">
         <is>
-          <t>Crystal Palace vs Newcastle United</t>
+          <t>Santos vs Atlético-mg</t>
         </is>
       </c>
       <c r="C58" s="47" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D58" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E58" s="48" t="n">
-        <v>1250</v>
+        <v>1020.62</v>
       </c>
       <c r="F58" s="55" t="inlineStr">
         <is>
@@ -23400,13 +23437,11 @@
       <c r="G58" s="48" t="n"/>
       <c r="H58" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
-        </is>
-      </c>
-      <c r="I58" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I58" s="48" t="n">
+        <v>2500</v>
       </c>
       <c r="J58" s="55" t="inlineStr">
         <is>
@@ -23429,12 +23464,12 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="44" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B59" s="45" t="inlineStr">
         <is>
-          <t>Fredrikstad vs Valerenga</t>
+          <t>Viking fk vs Bodo/glimt</t>
         </is>
       </c>
       <c r="C59" s="44" t="inlineStr">
@@ -23448,7 +23483,7 @@
         </is>
       </c>
       <c r="E59" s="46" t="n">
-        <v>1767.77</v>
+        <v>2500</v>
       </c>
       <c r="F59" s="55" t="inlineStr">
         <is>
@@ -23458,13 +23493,11 @@
       <c r="G59" s="48" t="n"/>
       <c r="H59" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Shadow-EV (0.052&lt;0.080)</t>
-        </is>
-      </c>
-      <c r="I59" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I59" s="46" t="n">
+        <v>2500</v>
       </c>
       <c r="J59" s="55" t="inlineStr">
         <is>
@@ -23487,26 +23520,26 @@
     <row r="60" ht="16" customHeight="1">
       <c r="A60" s="47" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B60" s="51" t="inlineStr">
         <is>
-          <t>Goztepe vs Kasimpasa</t>
+          <t>Vitoria vs Sao Paulo</t>
         </is>
       </c>
       <c r="C60" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D60" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E60" s="48" t="n">
-        <v>1767.77</v>
+        <v>1020.62</v>
       </c>
       <c r="F60" s="55" t="inlineStr">
         <is>
@@ -23516,7 +23549,7 @@
       <c r="G60" s="48" t="n"/>
       <c r="H60" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="I60" s="48" t="n">
@@ -23548,23 +23581,21 @@
       </c>
       <c r="B61" s="45" t="inlineStr">
         <is>
-          <t>Nottingham Forest vs Aston Villa</t>
+          <t>Botafogo vs Coritiba</t>
         </is>
       </c>
       <c r="C61" s="44" t="inlineStr">
         <is>
-          <t>Inglaterra</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D61" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Overlap Riesgo (O/U Priorizado)</t>
-        </is>
-      </c>
-      <c r="E61" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E61" s="46" t="n">
+        <v>1250</v>
       </c>
       <c r="F61" s="55" t="inlineStr">
         <is>
@@ -23574,11 +23605,13 @@
       <c r="G61" s="48" t="n"/>
       <c r="H61" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
-        </is>
-      </c>
-      <c r="I61" s="46" t="n">
-        <v>2500</v>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I61" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="55" t="inlineStr">
         <is>
@@ -23606,12 +23639,12 @@
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
-          <t>Rosenborg vs Sarpsborg fk</t>
+          <t>Chelsea vs Manchester City</t>
         </is>
       </c>
       <c r="C62" s="47" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D62" s="51" t="inlineStr">
@@ -23620,7 +23653,7 @@
         </is>
       </c>
       <c r="E62" s="48" t="n">
-        <v>1767.77</v>
+        <v>1250</v>
       </c>
       <c r="F62" s="55" t="inlineStr">
         <is>
@@ -23630,13 +23663,11 @@
       <c r="G62" s="48" t="n"/>
       <c r="H62" s="51" t="inlineStr">
         <is>
-          <t>[PASAR] Shadow-EV (0.082&lt;0.120)</t>
-        </is>
-      </c>
-      <c r="I62" s="48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I62" s="48" t="n">
+        <v>2500</v>
       </c>
       <c r="J62" s="55" t="inlineStr">
         <is>
@@ -23659,17 +23690,17 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="44" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B63" s="45" t="inlineStr">
         <is>
-          <t>Caykur Rizespor vs Gaziantep FK</t>
+          <t>Corinthians vs Palmeiras</t>
         </is>
       </c>
       <c r="C63" s="44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D63" s="45" t="inlineStr">
@@ -23678,7 +23709,7 @@
         </is>
       </c>
       <c r="E63" s="46" t="n">
-        <v>1767.77</v>
+        <v>1250</v>
       </c>
       <c r="F63" s="55" t="inlineStr">
         <is>
@@ -23688,11 +23719,13 @@
       <c r="G63" s="48" t="n"/>
       <c r="H63" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I63" s="46" t="n">
-        <v>2500</v>
+          <t>[PASAR] Shadow-EV (0.042&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="I63" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="55" t="inlineStr">
         <is>
@@ -23715,26 +23748,26 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="47" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B64" s="51" t="inlineStr">
         <is>
-          <t>Eyupspor vs Samsunspor</t>
+          <t>Cruzeiro vs Red Bull Bragantino</t>
         </is>
       </c>
       <c r="C64" s="47" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>Brasil</t>
         </is>
       </c>
       <c r="D64" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="E64" s="48" t="n">
-        <v>1767.77</v>
+        <v>1250</v>
       </c>
       <c r="F64" s="55" t="inlineStr">
         <is>
@@ -23744,7 +23777,7 @@
       <c r="G64" s="48" t="n"/>
       <c r="H64" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] LOCAL</t>
+          <t>[APOSTAR] VISITA</t>
         </is>
       </c>
       <c r="I64" s="48" t="n">
@@ -23771,28 +23804,26 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="44" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B65" s="45" t="inlineStr">
         <is>
-          <t>Lanus vs Banfield</t>
+          <t>Crystal Palace vs Newcastle United</t>
         </is>
       </c>
       <c r="C65" s="44" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="D65" s="45" t="inlineStr">
         <is>
-          <t>[PASAR] Floor Prob (33%&lt;33%)</t>
-        </is>
-      </c>
-      <c r="E65" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E65" s="46" t="n">
+        <v>1250</v>
       </c>
       <c r="F65" s="55" t="inlineStr">
         <is>
@@ -23802,11 +23833,13 @@
       <c r="G65" s="48" t="n"/>
       <c r="H65" s="45" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I65" s="46" t="n">
-        <v>2500</v>
+          <t>[PASAR] Margen Predictivo Insuficiente (&lt;5%)</t>
+        </is>
+      </c>
+      <c r="I65" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="55" t="inlineStr">
         <is>
@@ -23829,26 +23862,26 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="47" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B66" s="51" t="inlineStr">
         <is>
-          <t>Sarmiento (junin) vs Gimnasia la Plata</t>
+          <t>Fredrikstad vs Valerenga</t>
         </is>
       </c>
       <c r="C66" s="47" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="D66" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
+          <t>[APOSTAR] LOCAL</t>
         </is>
       </c>
       <c r="E66" s="48" t="n">
-        <v>2500</v>
+        <v>1767.77</v>
       </c>
       <c r="F66" s="55" t="inlineStr">
         <is>
@@ -23858,11 +23891,13 @@
       <c r="G66" s="48" t="n"/>
       <c r="H66" s="51" t="inlineStr">
         <is>
-          <t>[APOSTAR] VISITA</t>
-        </is>
-      </c>
-      <c r="I66" s="48" t="n">
-        <v>2500</v>
+          <t>[PASAR] Shadow-EV (0.052&lt;0.080)</t>
+        </is>
+      </c>
+      <c r="I66" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="55" t="inlineStr">
         <is>
@@ -23882,181 +23917,577 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="18" customHeight="1">
-      <c r="A68" s="56" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="44" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="45" t="inlineStr">
+        <is>
+          <t>Goztepe vs Kasimpasa</t>
+        </is>
+      </c>
+      <c r="C67" s="44" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="D67" s="45" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E67" s="46" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F67" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G67" s="48" t="n"/>
+      <c r="H67" s="45" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I67" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J67" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K67" s="48" t="n"/>
+      <c r="L67" s="48" t="n"/>
+      <c r="M67" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="47" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="51" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C68" s="47" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="D68" s="51" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E68" s="48" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F68" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G68" s="48" t="n"/>
+      <c r="H68" s="51" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I68" s="48" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J68" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K68" s="48" t="n"/>
+      <c r="L68" s="48" t="n"/>
+      <c r="M68" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="44" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="45" t="inlineStr">
+        <is>
+          <t>Rosenborg vs Sarpsborg fk</t>
+        </is>
+      </c>
+      <c r="C69" s="44" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="D69" s="45" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E69" s="46" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F69" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G69" s="48" t="n"/>
+      <c r="H69" s="45" t="inlineStr">
+        <is>
+          <t>[PASAR] Shadow-EV (0.082&lt;0.120)</t>
+        </is>
+      </c>
+      <c r="I69" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K69" s="48" t="n"/>
+      <c r="L69" s="48" t="n"/>
+      <c r="M69" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="47" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="51" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor vs Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="C70" s="47" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="D70" s="51" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E70" s="48" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F70" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G70" s="48" t="n"/>
+      <c r="H70" s="51" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I70" s="48" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J70" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K70" s="48" t="n"/>
+      <c r="L70" s="48" t="n"/>
+      <c r="M70" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="44" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="45" t="inlineStr">
+        <is>
+          <t>Eyupspor vs Samsunspor</t>
+        </is>
+      </c>
+      <c r="C71" s="44" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="D71" s="45" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="E71" s="46" t="n">
+        <v>1767.77</v>
+      </c>
+      <c r="F71" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G71" s="48" t="n"/>
+      <c r="H71" s="45" t="inlineStr">
+        <is>
+          <t>[APOSTAR] LOCAL</t>
+        </is>
+      </c>
+      <c r="I71" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J71" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K71" s="48" t="n"/>
+      <c r="L71" s="48" t="n"/>
+      <c r="M71" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="47" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="51" t="inlineStr">
+        <is>
+          <t>Lanus vs Banfield</t>
+        </is>
+      </c>
+      <c r="C72" s="47" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D72" s="51" t="inlineStr">
+        <is>
+          <t>[PASAR] Floor Prob (33%&lt;33%)</t>
+        </is>
+      </c>
+      <c r="E72" s="48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G72" s="48" t="n"/>
+      <c r="H72" s="51" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I72" s="48" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J72" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K72" s="48" t="n"/>
+      <c r="L72" s="48" t="n"/>
+      <c r="M72" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="45" t="inlineStr">
+        <is>
+          <t>Sarmiento (junin) vs Gimnasia la Plata</t>
+        </is>
+      </c>
+      <c r="C73" s="44" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D73" s="45" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="E73" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F73" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="G73" s="48" t="n"/>
+      <c r="H73" s="45" t="inlineStr">
+        <is>
+          <t>[APOSTAR] VISITA</t>
+        </is>
+      </c>
+      <c r="I73" s="46" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J73" s="55" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="K73" s="48" t="n"/>
+      <c r="L73" s="48" t="n"/>
+      <c r="M73" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="56" t="inlineStr">
         <is>
           <t>RESUMEN COMPARATIVO DE RENDIMIENTO</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="40" t="inlineStr">
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="40" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B69" s="41" t="inlineStr">
+      <c r="B76" s="41" t="inlineStr">
         <is>
           <t>Opcion 1 (Activa)</t>
         </is>
       </c>
-      <c r="D69" s="42" t="inlineStr">
+      <c r="D76" s="42" t="inlineStr">
         <is>
           <t>Opcion 4 (Shadow)</t>
         </is>
       </c>
-      <c r="F69" s="43" t="inlineStr">
+      <c r="F76" s="43" t="inlineStr">
         <is>
           <t>Mejor</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="57" t="inlineStr">
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" s="57" t="inlineStr">
         <is>
           <t>N apuestas liquidadas</t>
         </is>
       </c>
-      <c r="B70" s="58" t="n">
-        <v>5</v>
-      </c>
-      <c r="C70" s="58" t="n">
-        <v>5</v>
-      </c>
-      <c r="D70" s="58" t="n">
+      <c r="B77" s="58" t="n">
+        <v>23</v>
+      </c>
+      <c r="C77" s="58" t="n">
+        <v>23</v>
+      </c>
+      <c r="D77" s="58" t="n">
         <v>35</v>
       </c>
-      <c r="E70" s="58" t="n">
+      <c r="E77" s="58" t="n">
         <v>35</v>
       </c>
-      <c r="F70" s="59" t="inlineStr">
+      <c r="F77" s="59" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="57" t="inlineStr">
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="57" t="inlineStr">
         <is>
           <t>Ganadas</t>
         </is>
       </c>
-      <c r="B71" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="C71" s="60" t="n">
-        <v>3</v>
-      </c>
-      <c r="D71" s="61" t="n">
+      <c r="B78" s="60" t="n">
+        <v>12</v>
+      </c>
+      <c r="C78" s="60" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="E71" s="61" t="n">
+      <c r="E78" s="61" t="n">
         <v>21</v>
       </c>
-      <c r="F71" s="62" t="inlineStr">
+      <c r="F78" s="62" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="57" t="inlineStr">
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="57" t="inlineStr">
         <is>
           <t>Hit rate</t>
         </is>
       </c>
-      <c r="B72" s="63" t="n">
+      <c r="B79" s="63" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="C79" s="63" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="D79" s="64" t="n">
         <v>0.6</v>
       </c>
-      <c r="C72" s="63" t="n">
+      <c r="E79" s="64" t="n">
         <v>0.6</v>
       </c>
-      <c r="D72" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E72" s="63" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F72" s="59" t="inlineStr">
+      <c r="F79" s="62" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="57" t="inlineStr">
+        <is>
+          <t>Volumen apostado</t>
+        </is>
+      </c>
+      <c r="B80" s="54" t="n">
+        <v>29844.08000000001</v>
+      </c>
+      <c r="C80" s="54" t="n">
+        <v>29844.08000000001</v>
+      </c>
+      <c r="D80" s="54" t="n">
+        <v>87500</v>
+      </c>
+      <c r="E80" s="54" t="n">
+        <v>87500</v>
+      </c>
+      <c r="F80" s="59" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="57" t="inlineStr">
-        <is>
-          <t>Volumen apostado</t>
-        </is>
-      </c>
-      <c r="B73" s="54" t="n">
-        <v>9095.030000000001</v>
-      </c>
-      <c r="C73" s="54" t="n">
-        <v>9095.030000000001</v>
-      </c>
-      <c r="D73" s="54" t="n">
-        <v>87500</v>
-      </c>
-      <c r="E73" s="54" t="n">
-        <v>87500</v>
-      </c>
-      <c r="F73" s="59" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="17" customHeight="1">
-      <c r="A74" s="57" t="inlineStr">
+    <row r="81" ht="17" customHeight="1">
+      <c r="A81" s="57" t="inlineStr">
         <is>
           <t>P/L neto</t>
         </is>
       </c>
-      <c r="B74" s="50" t="n">
-        <v>16824.42</v>
-      </c>
-      <c r="C74" s="50" t="n">
-        <v>16824.42</v>
-      </c>
-      <c r="D74" s="53" t="n">
+      <c r="B81" s="50" t="n">
+        <v>33615.69</v>
+      </c>
+      <c r="C81" s="50" t="n">
+        <v>33615.69</v>
+      </c>
+      <c r="D81" s="52" t="n">
         <v>121425</v>
       </c>
-      <c r="E74" s="53" t="n">
+      <c r="E81" s="52" t="n">
         <v>121425</v>
       </c>
-      <c r="F74" s="62" t="inlineStr">
+      <c r="F81" s="62" t="inlineStr">
         <is>
           <t>Op4</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="17" customHeight="1">
-      <c r="A75" s="57" t="inlineStr">
+    <row r="82" ht="17" customHeight="1">
+      <c r="A82" s="57" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="B75" s="64" t="n">
-        <v>1.849847664053884</v>
-      </c>
-      <c r="C75" s="64" t="n">
-        <v>1.849847664053884</v>
-      </c>
-      <c r="D75" s="65" t="n">
+      <c r="B82" s="63" t="n">
+        <v>1.126377157546823</v>
+      </c>
+      <c r="C82" s="63" t="n">
+        <v>1.126377157546823</v>
+      </c>
+      <c r="D82" s="64" t="n">
         <v>1.387714285714286</v>
       </c>
-      <c r="E75" s="65" t="n">
+      <c r="E82" s="64" t="n">
         <v>1.387714285714286</v>
       </c>
-      <c r="F75" s="62" t="inlineStr">
-        <is>
-          <t>Op1</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="66" t="inlineStr">
+      <c r="F82" s="62" t="inlineStr">
+        <is>
+          <t>Op4</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="65" t="inlineStr">
         <is>
           <t>Verde = celda ganadora en ese KPI / partido   |   Rojo = celda perdedora   |   Amarillo en Resultado = pendiente de liquidar   |   Op1 activa desde V4.3: empates bloqueados + xG Margen O/U + Camino 2B (desacuerdo) + Camino 3 (alta conv.)</t>
         </is>
@@ -24065,11 +24496,11 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="D3:G3"/>
-    <mergeCell ref="A77:N77"/>
     <mergeCell ref="H3:K3"/>
+    <mergeCell ref="A84:N84"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A68:N68"/>
+    <mergeCell ref="A75:N75"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
@@ -24139,182 +24570,182 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t>Argentina</t>
         </is>
       </c>
-      <c r="B2" s="67" t="n">
+      <c r="B2" s="66" t="n">
         <v>25</v>
       </c>
-      <c r="C2" s="67" t="n">
+      <c r="C2" s="66" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="66" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" s="67" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F2" s="68" t="n">
+        <v>3703.12</v>
+      </c>
+      <c r="G2" s="67" t="n">
+        <v>0.09467472888321204</v>
+      </c>
+      <c r="H2" s="68" t="n">
+        <v>39114.14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="66" t="inlineStr">
+        <is>
+          <t>Brasil</t>
+        </is>
+      </c>
+      <c r="B3" s="66" t="n">
+        <v>26</v>
+      </c>
+      <c r="C3" s="66" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" s="66" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" s="67" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="F3" s="68" t="n">
+        <v>46395.36</v>
+      </c>
+      <c r="G3" s="67" t="n">
+        <v>1.400404558168933</v>
+      </c>
+      <c r="H3" s="68" t="n">
+        <v>33129.97</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="66" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="B4" s="66" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="66" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="66" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="67" t="n">
+        <v>0.7777777777777779</v>
+      </c>
+      <c r="F4" s="68" t="n">
+        <v>17497.78</v>
+      </c>
+      <c r="G4" s="67" t="n">
+        <v>1.221047386836416</v>
+      </c>
+      <c r="H4" s="68" t="n">
+        <v>14330.14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="B5" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="D2" s="67" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" s="68" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="F2" s="69" t="n">
-        <v>-3225.97</v>
-      </c>
-      <c r="G2" s="68" t="n">
-        <v>-0.08247586167048537</v>
-      </c>
-      <c r="H2" s="69" t="n">
-        <v>39114.14</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="67" t="inlineStr">
-        <is>
-          <t>Brasil</t>
-        </is>
-      </c>
-      <c r="B3" s="67" t="n">
-        <v>26</v>
-      </c>
-      <c r="C3" s="67" t="n">
-        <v>14</v>
-      </c>
-      <c r="D3" s="67" t="n">
-        <v>12</v>
-      </c>
-      <c r="E3" s="68" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="F3" s="69" t="n">
-        <v>42886.34</v>
-      </c>
-      <c r="G3" s="68" t="n">
-        <v>1.294487749309765</v>
-      </c>
-      <c r="H3" s="69" t="n">
-        <v>33129.97</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="67" t="inlineStr">
-        <is>
-          <t>Inglaterra</t>
-        </is>
-      </c>
-      <c r="B4" s="67" t="n">
-        <v>9</v>
-      </c>
-      <c r="C4" s="67" t="n">
-        <v>7</v>
-      </c>
-      <c r="D4" s="67" t="n">
+      <c r="C5" s="66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="66" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="67" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="68" t="n">
+        <v>8031.25</v>
+      </c>
+      <c r="G5" s="67" t="n">
+        <v>0.6004899626079199</v>
+      </c>
+      <c r="H5" s="68" t="n">
+        <v>13374.49</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
+        <is>
+          <t>Turquia</t>
+        </is>
+      </c>
+      <c r="B6" s="66" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="68" t="n">
-        <v>0.7777777777777779</v>
-      </c>
-      <c r="F4" s="69" t="n">
-        <v>11471.25</v>
-      </c>
-      <c r="G4" s="68" t="n">
-        <v>0.8004978737123293</v>
-      </c>
-      <c r="H4" s="69" t="n">
-        <v>14330.14</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="67" t="inlineStr">
-        <is>
-          <t>Noruega</t>
-        </is>
-      </c>
-      <c r="B5" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" s="68" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="69" t="n">
-        <v>4743.75</v>
-      </c>
-      <c r="G5" s="68" t="n">
-        <v>0.3546861973802365</v>
-      </c>
-      <c r="H5" s="69" t="n">
-        <v>13374.49</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="67" t="inlineStr">
-        <is>
-          <t>Turquia</t>
-        </is>
-      </c>
-      <c r="B6" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="C6" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="68" t="n">
+      <c r="E6" s="67" t="n">
         <v>0.6666666666666665</v>
       </c>
-      <c r="F6" s="69" t="n">
+      <c r="F6" s="68" t="n">
         <v>16147.4</v>
       </c>
-      <c r="G6" s="68" t="n">
+      <c r="G6" s="67" t="n">
         <v>1.364937760668936</v>
       </c>
-      <c r="H6" s="69" t="n">
+      <c r="H6" s="68" t="n">
         <v>11830.14</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="70" t="n">
+      <c r="B7" s="69" t="n">
         <v>74</v>
       </c>
-      <c r="C7" s="70" t="n">
-        <v>37</v>
-      </c>
-      <c r="D7" s="70" t="n">
-        <v>37</v>
-      </c>
-      <c r="E7" s="71" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="72" t="n">
-        <v>72022.77</v>
-      </c>
-      <c r="G7" s="71" t="n">
-        <v>0.6443325098623282</v>
-      </c>
-      <c r="H7" s="72" t="n">
+      <c r="C7" s="69" t="n">
+        <v>39</v>
+      </c>
+      <c r="D7" s="69" t="n">
+        <v>35</v>
+      </c>
+      <c r="E7" s="70" t="n">
+        <v>0.527027027027027</v>
+      </c>
+      <c r="F7" s="71" t="n">
+        <v>91774.91</v>
+      </c>
+      <c r="G7" s="70" t="n">
+        <v>0.8210398368636365</v>
+      </c>
+      <c r="H7" s="71" t="n">
         <v>111778.88</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="73" t="inlineStr">
-        <is>
-          <t>Generado: 10/04/2026 12:31</t>
+      <c r="A9" s="72" t="inlineStr">
+        <is>
+          <t>Generado: 10/04/2026 12:43</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="73" t="inlineStr">
+      <c r="A10" s="72" t="inlineStr">
         <is>
           <t>Bankroll base: $100,000.00</t>
         </is>
